--- a/JavaPrograms/Work Done.xlsx
+++ b/JavaPrograms/Work Done.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13284" windowHeight="5700" firstSheet="4" activeTab="11"/>
+    <workbookView windowWidth="23040" windowHeight="8280" firstSheet="4" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="DSA plan" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="457">
   <si>
     <r>
       <rPr>
@@ -3405,6 +3405,104 @@
 Once valid, we shrink the window greedily while maintaining validity, tracking the minimum length.”</t>
   </si>
   <si>
+    <t>String Recap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+# 🧵 QUICK STRING RECAP — 15-MIN MENTAL MODEL
+Use this like a **checklist in your head**.
+If you can explain each section calmly, strings are locked.
+## 1️⃣ STRING FUNDAMENTALS (BASE LAYER)
+If this layer is weak, everything above collapses.
+You must instantly recall:
+* Strings are **immutable**
+* `charAt(i)` → O(1)
+* `toCharArray()` → creates new array
+* `StringBuilder` → mutable, preferred for construction
+* ASCII math:
+  * `'a' → 97`
+  * `'A' → 65`
+  * `c - 'a'` maps to `0–25`
+Mental rule:
+&gt; “If order doesn’t matter → frequency
+&gt; If order matters → pointers/window”
+## 2️⃣ TWO POINTERS (STRUCTURE CHECK)
+Used when:
+* You compare from **both ends**
+* Or compress / reverse
+Examples you’ve done:
+* Reverse String
+* Valid Palindrome
+Mental model:
+&gt; Move pointers inward while maintaining a condition.
+If you see:
+* symmetry
+* reverse
+* mirror
+👉 Two pointers is your first instinct.
+## 3️⃣ SLIDING WINDOW (CORE POWER)
+This is your strongest string area now.
+### Ask ONE question:
+&gt; “Am I looking for a **contiguous substring** with a condition?”
+If yes → sliding window.
+### Invariant mindset (THIS MATTERS)
+Every window problem has:
+* what makes window **valid**
+* what makes it **invalid**
+* when to **expand**
+* when to **shrink**
+### Problems you mastered
+* **LC 3**
+  Invariant: all characters unique
+* **LC 567**
+  Invariant: frequency match of target string
+* **LC 424**
+  Invariant: window size − maxCharFreq ≤ k
+* **LC 76**
+  Invariant: all required chars satisfied
+Mental trigger:
+&gt; Right pointer grows the window
+&gt; Left pointer restores validity
+## 4️⃣ FREQUENCY + HASHING (COUNTING LOGIC)
+Used when:
+* order doesn’t matter
+* grouping / matching needed
+Problems:
+* LC 242 (Valid Anagram)
+* LC 49 (Group Anagrams)
+Mental rule:
+&gt; Same frequency pattern = same group
+Key idea:
+* frequency array → key
+* HashMap → grouping
+## 5️⃣   PALINDROMES (CENTER EXPANSION)
+Used when:
+* symmetry around center
+* substrings that read same backward
+Pattern:
+* expand around center
+* `(i, i)` odd
+* `(i, i+1)` even
+Problems:
+* LC 647 → count
+* LC 5 → longest
+Mental model:
+&gt; Every palindrome grows from a center.
+## 6️⃣ WHAT YOU **DO NOT** MIX UP
+* ❌ Sliding window ≠ two pointers (they look similar, but invariant differs)
+* ❌ Prefix sum ≠ strings (mostly arrays)
+* ❌ DP strings ≠ current phase (later)
+You’re disciplined here. Keep it that way.
+## 7️⃣ INTERVIEW SAFETY SENTENCES (MEMORIZE)
+These alone save you:
+* “I maintain a sliding window with a frequency array.”
+* “I expand around the center to handle palindromes.”
+* “I use a hashmap to group strings by frequency pattern.”
+* “The window is adjusted until the invariant holds.”
+Say less. Mean more.
+Say one line.</t>
+  </si>
+  <si>
     <t>Space Complexity</t>
   </si>
   <si>
@@ -5045,15 +5143,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <i/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -7296,10 +7394,10 @@
   <sheetData>
     <row r="1" ht="409" customHeight="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -7445,18 +7543,18 @@
     </row>
     <row r="2" ht="409.5" spans="1:3">
       <c r="A2" s="6" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" ht="409.5" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C3"/>
     </row>
@@ -7505,32 +7603,32 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="10" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="36" ht="23.4" spans="1:1">
@@ -7538,177 +7636,177 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="10" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="60" ht="23.4" spans="1:1">
       <c r="A60" s="9" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="10" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="86" ht="23.4" spans="1:1">
       <c r="A86" s="9" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="103" spans="1:1">
@@ -7718,12 +7816,12 @@
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="108" spans="1:1">
@@ -7731,12 +7829,12 @@
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="112" ht="23.4" spans="1:1">
@@ -7744,42 +7842,42 @@
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="128" spans="1:1">
@@ -7787,12 +7885,12 @@
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="132" ht="23.4" spans="1:1">
@@ -7800,62 +7898,62 @@
     </row>
     <row r="133" spans="1:1">
       <c r="A133" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" s="10" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" ht="23.4" spans="1:1">
@@ -7863,62 +7961,62 @@
     </row>
     <row r="156" spans="1:1">
       <c r="A156" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174" s="10" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="176" spans="1:1">
       <c r="A176" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="180" spans="1:1">
@@ -7928,7 +8026,7 @@
     </row>
     <row r="182" spans="1:1">
       <c r="A182" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="184" spans="1:1">
@@ -7938,87 +8036,87 @@
     </row>
     <row r="186" spans="1:1">
       <c r="A186" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="188" spans="1:1">
       <c r="A188" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="189" spans="1:1">
       <c r="A189" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="192" spans="1:1">
       <c r="A192" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="193" spans="1:1">
       <c r="A193" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="195" spans="1:1">
       <c r="A195" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="196" spans="1:1">
       <c r="A196" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="198" spans="1:1">
       <c r="A198" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="199" spans="1:1">
       <c r="A199" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="201" spans="1:1">
       <c r="A201" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="203" spans="1:1">
       <c r="A203" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="205" spans="1:1">
       <c r="A205" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="209" spans="1:1">
       <c r="A209" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="211" spans="1:1">
@@ -8028,32 +8126,32 @@
     </row>
     <row r="213" spans="1:1">
       <c r="A213" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="217" spans="1:1">
       <c r="A217" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="219" spans="1:1">
       <c r="A219" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="221" spans="1:1">
       <c r="A221" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
   </sheetData>
@@ -8074,7 +8172,7 @@
   <sheetData>
     <row r="2" spans="3:3">
       <c r="C2" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="3" spans="3:3">
@@ -10650,9 +10748,13 @@
         <v>261</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
-      <c r="A78" s="23"/>
-      <c r="B78" s="23"/>
+    <row r="78" ht="409.5" spans="1:2">
+      <c r="A78" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="B78" s="25" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="23"/>
@@ -10757,7 +10859,7 @@
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="23" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -10795,7 +10897,7 @@
         <v>38</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -10805,76 +10907,76 @@
     </row>
     <row r="19" ht="72" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" ht="100.8" spans="1:2">
       <c r="A21" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="26" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B22" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="23" ht="57.6" spans="1:2">
       <c r="A23" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="24" ht="72" spans="1:2">
       <c r="A24" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="25" ht="86.4" spans="1:2">
       <c r="A25" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="26" ht="43.2" spans="1:2">
       <c r="A26" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="27" ht="28.8" spans="1:2">
       <c r="A27" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="28" ht="43.2" spans="1:2">
       <c r="A28" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -10891,17 +10993,17 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="22" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -10925,201 +11027,201 @@
   <sheetData>
     <row r="1" spans="2:3">
       <c r="B1" s="16" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="2" spans="2:3">
       <c r="B2" s="17" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3" spans="2:3">
       <c r="B3" s="17" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>290</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="B5" s="17" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" spans="2:3">
       <c r="B6" s="17" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="B7" s="17" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8" ht="43.2" spans="2:3">
       <c r="B8" s="17" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" s="18" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10" spans="2:2">
       <c r="B10" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11" ht="23.4" spans="2:2">
       <c r="B11" s="19" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" s="20" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15" spans="2:2">
       <c r="B15" s="20" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16" spans="2:2">
       <c r="B16" s="20" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" s="20" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" s="20" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" s="20" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" s="20" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" s="20" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" s="20" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" s="20" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="26" ht="23.4" spans="2:2">
       <c r="B26" s="19" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" s="20" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="29" spans="2:2">
       <c r="B29" s="20" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" s="20" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="31" spans="2:2">
       <c r="B31" s="20" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" s="20" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" s="20" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" s="20" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="36" spans="2:2">
@@ -11144,83 +11246,83 @@
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="41" ht="23.4" spans="2:2">
       <c r="B41" s="19" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="43" spans="2:2">
       <c r="B43" s="20" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" s="20" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="45" spans="2:2">
       <c r="B45" s="20" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" s="20" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" s="21" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" s="21" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" s="21" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" s="21" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="54" ht="13" customHeight="1"/>
     <row r="55" ht="22" customHeight="1" spans="2:2">
       <c r="B55" s="19" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="57" spans="2:2">
       <c r="B57" s="20" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="58" spans="2:2">
@@ -11235,17 +11337,17 @@
     </row>
     <row r="60" spans="2:2">
       <c r="B60" s="20" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61" s="20" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -11262,7 +11364,7 @@
   <sheetData>
     <row r="1" spans="1:21">
       <c r="A1" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -11277,7 +11379,7 @@
       <c r="L1" s="12"/>
       <c r="M1" s="12"/>
       <c r="N1" s="14" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O1" s="15"/>
       <c r="P1" s="15"/>
@@ -11519,7 +11621,7 @@
     </row>
     <row r="12" spans="1:21">
       <c r="A12" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
@@ -11705,7 +11807,7 @@
     </row>
     <row r="22" spans="1:21">
       <c r="A22" s="13" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B22" s="13"/>
       <c r="C22" s="13"/>

--- a/JavaPrograms/Work Done.xlsx
+++ b/JavaPrograms/Work Done.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="470">
   <si>
     <r>
       <rPr>
@@ -3503,6 +3503,92 @@
 Say one line.</t>
   </si>
   <si>
+    <t>this keyword</t>
+  </si>
+  <si>
+    <t>Think of this as “me, the current object”.
+When you write:
+class ListNode {
+    int val;
+    ListNode next;
+    ListNode(int val) {
+        this.val = val;
+        this.next = null;
+    }
+}
+Here’s what’s happening in plain English:
+val (without this) is the parameter coming into the constructor
+this.val is the variable that belongs to the object
+So this line:
+this.val = val;
+means:
+“Take the value I received and store it inside this specific node.”
+Without this, Java would get confused about which val you mean.
+👉 Rule to remember
+this = the current object you are creating or working on.</t>
+  </si>
+  <si>
+    <t>Linkedlist</t>
+  </si>
+  <si>
+    <t>A Linked List is just a chain of boxes.
+Each box (node) has:
+A value
+A pointer to the next box
+That’s it.
+Example:
+[1 | next] → [2 | next] → [3 | next] → null
+Important:
+Nodes are not stored together in memory
+Each node only knows where the next node is
+Unlike arrays:
+Arrays → continuous memory
+Linked lists → scattered memory, connected by pointers</t>
+  </si>
+  <si>
+    <t>“A linked list is a sequence of nodes where each node stores a value and a reference to the next node. Reversing it means rewiring the next pointers one by one.”</t>
+  </si>
+  <si>
+    <t>ListNode</t>
+  </si>
+  <si>
+    <t>When you write:
+ListNode head = new ListNode(1);
+You are:
+Creating a node somewhere in memory
+head does NOT store the value 1
+head stores the address (reference) of that node
+So:
+head.val
+means:
+“Go to the memory location head is pointing to, and read val.”
+This is the most important mental shift.</t>
+  </si>
+  <si>
+    <t>next</t>
+  </si>
+  <si>
+    <t>When you write:
+head.next = new ListNode(2);
+You are saying:
+“Inside the first node, store the address of the second node.”
+So visually:
+head ──► [1 | next ──► [2 | next ──► null]]
+next is NOT the value.
+next is a reference to another node.</t>
+  </si>
+  <si>
+    <t>Why Linked List feels confusing (and arrays didn’t)</t>
+  </si>
+  <si>
+    <t>Arrays: arr[i] = 10;
+You directly access memory by index.
+Linked Lists:
+node.next.next.next
+You walk step by step, following pointers.
+That’s why linked lists feel “slow” mentally at first.</t>
+  </si>
+  <si>
     <t>Space Complexity</t>
   </si>
   <si>
@@ -3624,6 +3710,16 @@
   </si>
   <si>
     <t>https://docs.google.com/document/d/1hYEHHG7wFNZBR7gGSbEmxl3pQdKUVl1JyW77fyIhAP4/edit?tab=t.0</t>
+  </si>
+  <si>
+    <t>It’s important to show how you arrive at a solution, so think out loud, give context on your answers, add data points where you can, and please don’t be afraid to ask questions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpful questions to think about as you prepare:
+How do you work best, both as an individual and as part of a team?
+What challenges have you faced at school or at work and how did you overcome them?
+What was the impact of your accomplishments, projects, or leadership experiences? What changed? What has been improved? Was a goal achieved? How did you measure success?
+Which of your skills or experiences would be assets in the role and why? </t>
   </si>
   <si>
     <t>Problem</t>
@@ -4933,7 +5029,7 @@
     <numFmt numFmtId="181" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="182" formatCode="dd/mmm/yy"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4986,6 +5082,12 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF202124"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -5143,15 +5245,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <i/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -5628,7 +5730,7 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5637,128 +5739,128 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5828,6 +5930,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5870,16 +5978,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="181" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5891,10 +6005,10 @@
     <xf numFmtId="181" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
@@ -6580,780 +6694,780 @@
   </cols>
   <sheetData>
     <row r="1" ht="90" customHeight="1" spans="1:6">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64" t="s">
+      <c r="B1" s="67"/>
+      <c r="C1" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="65"/>
-      <c r="E1" s="66" t="s">
+      <c r="D1" s="69"/>
+      <c r="E1" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="66"/>
+      <c r="F1" s="70"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="68" t="s">
+      <c r="B2" s="25"/>
+      <c r="C2" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="69"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="23"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="66"/>
+      <c r="A3" s="25"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="23"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="70"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="66"/>
+      <c r="A4" s="25"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="23"/>
-      <c r="B5" s="23"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="71"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
+      <c r="A5" s="25"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="75"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="70"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
+      <c r="A6" s="25"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="74"/>
+      <c r="D6" s="75"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="23"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="71"/>
-      <c r="E7" s="66"/>
-      <c r="F7" s="66"/>
+      <c r="A7" s="25"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="74"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="70"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="23"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="72"/>
-      <c r="D8" s="73"/>
-      <c r="E8" s="66"/>
-      <c r="F8" s="66"/>
+      <c r="A8" s="25"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="70"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="67" t="s">
+      <c r="A9" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="25"/>
-      <c r="C9" s="74" t="s">
+      <c r="B9" s="27"/>
+      <c r="C9" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="75"/>
-      <c r="E9" s="66"/>
-      <c r="F9" s="66"/>
+      <c r="D9" s="79"/>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="76"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="66"/>
-      <c r="F10" s="66"/>
+      <c r="A10" s="27"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="80"/>
+      <c r="D10" s="81"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="25"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="76"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="80"/>
+      <c r="D11" s="81"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="25"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="76"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="66"/>
-      <c r="F12" s="66"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="80"/>
+      <c r="D12" s="81"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="25"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="76"/>
-      <c r="D13" s="77"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="66"/>
+      <c r="A13" s="27"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="80"/>
+      <c r="D13" s="81"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="25"/>
-      <c r="B14" s="25"/>
-      <c r="C14" s="76"/>
-      <c r="D14" s="77"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="66"/>
+      <c r="A14" s="27"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="80"/>
+      <c r="D14" s="81"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="70"/>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:6">
-      <c r="A15" s="25"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="78"/>
-      <c r="D15" s="79"/>
-      <c r="E15" s="66"/>
-      <c r="F15" s="66"/>
+      <c r="A15" s="27"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="82"/>
+      <c r="D15" s="83"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="25"/>
-      <c r="B16" s="25"/>
-      <c r="C16" s="80" t="s">
+      <c r="A16" s="27"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="81"/>
-      <c r="E16" s="66"/>
-      <c r="F16" s="66"/>
+      <c r="D16" s="85"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="25"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="82"/>
-      <c r="D17" s="83"/>
-      <c r="E17" s="66"/>
-      <c r="F17" s="66"/>
+      <c r="A17" s="27"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="86"/>
+      <c r="D17" s="87"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="25"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="82"/>
-      <c r="D18" s="83"/>
-      <c r="E18" s="66"/>
-      <c r="F18" s="66"/>
+      <c r="A18" s="27"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="86"/>
+      <c r="D18" s="87"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="67" t="s">
+      <c r="A19" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="82"/>
-      <c r="D19" s="83"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="66"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="86"/>
+      <c r="D19" s="87"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="23"/>
-      <c r="B20" s="23"/>
-      <c r="C20" s="82"/>
-      <c r="D20" s="83"/>
-      <c r="E20" s="66"/>
-      <c r="F20" s="66"/>
+      <c r="A20" s="25"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="86"/>
+      <c r="D20" s="87"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="23"/>
-      <c r="B21" s="23"/>
-      <c r="C21" s="82"/>
-      <c r="D21" s="83"/>
-      <c r="E21" s="66"/>
-      <c r="F21" s="66"/>
+      <c r="A21" s="25"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="86"/>
+      <c r="D21" s="87"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="23"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="82"/>
-      <c r="D22" s="83"/>
+      <c r="A22" s="25"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="86"/>
+      <c r="D22" s="87"/>
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="23"/>
-      <c r="B23" s="23"/>
-      <c r="C23" s="84"/>
-      <c r="D23" s="85"/>
+      <c r="A23" s="25"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="88"/>
+      <c r="D23" s="89"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="23"/>
-      <c r="B24" s="23"/>
-      <c r="C24" s="86" t="s">
+      <c r="A24" s="25"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="87"/>
+      <c r="D24" s="91"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="23"/>
-      <c r="B25" s="23"/>
-      <c r="C25" s="88"/>
-      <c r="D25" s="89"/>
+      <c r="A25" s="25"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="92"/>
+      <c r="D25" s="93"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="23"/>
-      <c r="B26" s="23"/>
-      <c r="C26" s="88"/>
-      <c r="D26" s="89"/>
+      <c r="A26" s="25"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="92"/>
+      <c r="D26" s="93"/>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="23"/>
-      <c r="B27" s="23"/>
-      <c r="C27" s="88"/>
-      <c r="D27" s="89"/>
+      <c r="A27" s="25"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="92"/>
+      <c r="D27" s="93"/>
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="23"/>
-      <c r="B28" s="23"/>
-      <c r="C28" s="90"/>
-      <c r="D28" s="91"/>
+      <c r="A28" s="25"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="94"/>
+      <c r="D28" s="95"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="23"/>
-      <c r="B29" s="23"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
+      <c r="A29" s="25"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="23"/>
-      <c r="B30" s="23"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
+      <c r="A30" s="25"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="67" t="s">
+      <c r="A31" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="B31" s="25"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
+      <c r="B31" s="27"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="25"/>
-      <c r="B32" s="25"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
+      <c r="A32" s="27"/>
+      <c r="B32" s="27"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="25"/>
-      <c r="B33" s="25"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="27"/>
+      <c r="A33" s="27"/>
+      <c r="B33" s="27"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="25"/>
-      <c r="B34" s="25"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="27"/>
+      <c r="A34" s="27"/>
+      <c r="B34" s="27"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="25"/>
-      <c r="B35" s="25"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="27"/>
+      <c r="A35" s="27"/>
+      <c r="B35" s="27"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="25"/>
-      <c r="B36" s="25"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="27"/>
+      <c r="A36" s="27"/>
+      <c r="B36" s="27"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="29"/>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="25"/>
-      <c r="B37" s="25"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="27"/>
+      <c r="A37" s="27"/>
+      <c r="B37" s="27"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="25"/>
-      <c r="B38" s="25"/>
-      <c r="C38" s="27"/>
-      <c r="D38" s="27"/>
+      <c r="A38" s="27"/>
+      <c r="B38" s="27"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="25"/>
-      <c r="B39" s="25"/>
-      <c r="C39" s="27"/>
-      <c r="D39" s="27"/>
+      <c r="A39" s="27"/>
+      <c r="B39" s="27"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="29"/>
     </row>
     <row r="40" ht="18" customHeight="1" spans="1:4">
-      <c r="A40" s="67" t="s">
+      <c r="A40" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="B40" s="25"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
+      <c r="B40" s="27"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="29"/>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="25"/>
-      <c r="B41" s="25"/>
-      <c r="C41" s="27"/>
-      <c r="D41" s="27"/>
+      <c r="A41" s="27"/>
+      <c r="B41" s="27"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="29"/>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="25"/>
-      <c r="B42" s="25"/>
-      <c r="C42" s="27"/>
-      <c r="D42" s="27"/>
+      <c r="A42" s="27"/>
+      <c r="B42" s="27"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="29"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="25"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
+      <c r="A43" s="27"/>
+      <c r="B43" s="27"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="29"/>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="25"/>
-      <c r="B44" s="25"/>
-      <c r="C44" s="27"/>
-      <c r="D44" s="27"/>
+      <c r="A44" s="27"/>
+      <c r="B44" s="27"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="29"/>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="25"/>
-      <c r="B45" s="25"/>
-      <c r="C45" s="27"/>
-      <c r="D45" s="27"/>
+      <c r="A45" s="27"/>
+      <c r="B45" s="27"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="29"/>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="25"/>
-      <c r="B46" s="25"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="27"/>
+      <c r="A46" s="27"/>
+      <c r="B46" s="27"/>
+      <c r="C46" s="29"/>
+      <c r="D46" s="29"/>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="25"/>
-      <c r="B47" s="25"/>
-      <c r="C47" s="27"/>
-      <c r="D47" s="27"/>
+      <c r="A47" s="27"/>
+      <c r="B47" s="27"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="29"/>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="25"/>
-      <c r="B48" s="25"/>
-      <c r="C48" s="27"/>
-      <c r="D48" s="27"/>
+      <c r="A48" s="27"/>
+      <c r="B48" s="27"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="29"/>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="25"/>
-      <c r="B49" s="25"/>
-      <c r="C49" s="27"/>
-      <c r="D49" s="27"/>
+      <c r="A49" s="27"/>
+      <c r="B49" s="27"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="29"/>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="67" t="s">
+      <c r="A50" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="B50" s="25"/>
-      <c r="C50" s="27"/>
-      <c r="D50" s="27"/>
+      <c r="B50" s="27"/>
+      <c r="C50" s="29"/>
+      <c r="D50" s="29"/>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="25"/>
-      <c r="B51" s="25"/>
-      <c r="C51" s="27"/>
-      <c r="D51" s="27"/>
+      <c r="A51" s="27"/>
+      <c r="B51" s="27"/>
+      <c r="C51" s="29"/>
+      <c r="D51" s="29"/>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="25"/>
-      <c r="B52" s="25"/>
-      <c r="C52" s="27"/>
-      <c r="D52" s="27"/>
+      <c r="A52" s="27"/>
+      <c r="B52" s="27"/>
+      <c r="C52" s="29"/>
+      <c r="D52" s="29"/>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="25"/>
-      <c r="B53" s="25"/>
-      <c r="C53" s="27"/>
-      <c r="D53" s="27"/>
+      <c r="A53" s="27"/>
+      <c r="B53" s="27"/>
+      <c r="C53" s="29"/>
+      <c r="D53" s="29"/>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="25"/>
-      <c r="B54" s="25"/>
-      <c r="C54" s="27"/>
-      <c r="D54" s="27"/>
+      <c r="A54" s="27"/>
+      <c r="B54" s="27"/>
+      <c r="C54" s="29"/>
+      <c r="D54" s="29"/>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="25"/>
-      <c r="B55" s="25"/>
-      <c r="C55" s="27"/>
-      <c r="D55" s="27"/>
+      <c r="A55" s="27"/>
+      <c r="B55" s="27"/>
+      <c r="C55" s="29"/>
+      <c r="D55" s="29"/>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="25"/>
-      <c r="B56" s="25"/>
-      <c r="C56" s="27"/>
-      <c r="D56" s="27"/>
+      <c r="A56" s="27"/>
+      <c r="B56" s="27"/>
+      <c r="C56" s="29"/>
+      <c r="D56" s="29"/>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="25"/>
-      <c r="B57" s="25"/>
-      <c r="C57" s="27"/>
-      <c r="D57" s="27"/>
+      <c r="A57" s="27"/>
+      <c r="B57" s="27"/>
+      <c r="C57" s="29"/>
+      <c r="D57" s="29"/>
     </row>
     <row r="58" spans="1:4">
-      <c r="A58" s="25"/>
-      <c r="B58" s="25"/>
-      <c r="C58" s="27"/>
-      <c r="D58" s="27"/>
+      <c r="A58" s="27"/>
+      <c r="B58" s="27"/>
+      <c r="C58" s="29"/>
+      <c r="D58" s="29"/>
     </row>
     <row r="59" spans="1:4">
-      <c r="A59" s="67" t="s">
+      <c r="A59" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="B59" s="23"/>
-      <c r="C59" s="27"/>
-      <c r="D59" s="27"/>
+      <c r="B59" s="25"/>
+      <c r="C59" s="29"/>
+      <c r="D59" s="29"/>
     </row>
     <row r="60" spans="1:4">
-      <c r="A60" s="23"/>
-      <c r="B60" s="23"/>
-      <c r="C60" s="27"/>
-      <c r="D60" s="27"/>
+      <c r="A60" s="25"/>
+      <c r="B60" s="25"/>
+      <c r="C60" s="29"/>
+      <c r="D60" s="29"/>
     </row>
     <row r="61" spans="1:4">
-      <c r="A61" s="23"/>
-      <c r="B61" s="23"/>
-      <c r="C61" s="27"/>
-      <c r="D61" s="27"/>
+      <c r="A61" s="25"/>
+      <c r="B61" s="25"/>
+      <c r="C61" s="29"/>
+      <c r="D61" s="29"/>
     </row>
     <row r="62" spans="1:4">
-      <c r="A62" s="23"/>
-      <c r="B62" s="23"/>
-      <c r="C62" s="27"/>
-      <c r="D62" s="27"/>
+      <c r="A62" s="25"/>
+      <c r="B62" s="25"/>
+      <c r="C62" s="29"/>
+      <c r="D62" s="29"/>
     </row>
     <row r="63" spans="1:4">
-      <c r="A63" s="23"/>
-      <c r="B63" s="23"/>
-      <c r="C63" s="27"/>
-      <c r="D63" s="27"/>
+      <c r="A63" s="25"/>
+      <c r="B63" s="25"/>
+      <c r="C63" s="29"/>
+      <c r="D63" s="29"/>
     </row>
     <row r="64" spans="1:4">
-      <c r="A64" s="23"/>
-      <c r="B64" s="23"/>
-      <c r="C64" s="27"/>
-      <c r="D64" s="27"/>
+      <c r="A64" s="25"/>
+      <c r="B64" s="25"/>
+      <c r="C64" s="29"/>
+      <c r="D64" s="29"/>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65" s="23"/>
-      <c r="B65" s="23"/>
-      <c r="C65" s="27"/>
-      <c r="D65" s="27"/>
+      <c r="A65" s="25"/>
+      <c r="B65" s="25"/>
+      <c r="C65" s="29"/>
+      <c r="D65" s="29"/>
     </row>
     <row r="66" spans="1:4">
-      <c r="A66" s="23"/>
-      <c r="B66" s="23"/>
-      <c r="C66" s="27"/>
-      <c r="D66" s="27"/>
+      <c r="A66" s="25"/>
+      <c r="B66" s="25"/>
+      <c r="C66" s="29"/>
+      <c r="D66" s="29"/>
     </row>
     <row r="67" spans="1:4">
-      <c r="A67" s="23"/>
-      <c r="B67" s="23"/>
-      <c r="C67" s="27"/>
-      <c r="D67" s="27"/>
+      <c r="A67" s="25"/>
+      <c r="B67" s="25"/>
+      <c r="C67" s="29"/>
+      <c r="D67" s="29"/>
     </row>
     <row r="68" spans="1:4">
-      <c r="A68" s="67" t="s">
+      <c r="A68" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="B68" s="23"/>
-      <c r="C68" s="27"/>
-      <c r="D68" s="27"/>
+      <c r="B68" s="25"/>
+      <c r="C68" s="29"/>
+      <c r="D68" s="29"/>
     </row>
     <row r="69" spans="1:4">
-      <c r="A69" s="23"/>
-      <c r="B69" s="23"/>
-      <c r="C69" s="27"/>
-      <c r="D69" s="27"/>
+      <c r="A69" s="25"/>
+      <c r="B69" s="25"/>
+      <c r="C69" s="29"/>
+      <c r="D69" s="29"/>
     </row>
     <row r="70" spans="1:4">
-      <c r="A70" s="23"/>
-      <c r="B70" s="23"/>
-      <c r="C70" s="27"/>
-      <c r="D70" s="27"/>
+      <c r="A70" s="25"/>
+      <c r="B70" s="25"/>
+      <c r="C70" s="29"/>
+      <c r="D70" s="29"/>
     </row>
     <row r="71" spans="1:4">
-      <c r="A71" s="23"/>
-      <c r="B71" s="23"/>
-      <c r="C71" s="27"/>
-      <c r="D71" s="27"/>
+      <c r="A71" s="25"/>
+      <c r="B71" s="25"/>
+      <c r="C71" s="29"/>
+      <c r="D71" s="29"/>
     </row>
     <row r="72" spans="1:4">
-      <c r="A72" s="23"/>
-      <c r="B72" s="23"/>
-      <c r="C72" s="27"/>
-      <c r="D72" s="27"/>
+      <c r="A72" s="25"/>
+      <c r="B72" s="25"/>
+      <c r="C72" s="29"/>
+      <c r="D72" s="29"/>
     </row>
     <row r="73" spans="1:4">
-      <c r="A73" s="23"/>
-      <c r="B73" s="23"/>
-      <c r="C73" s="27"/>
-      <c r="D73" s="27"/>
+      <c r="A73" s="25"/>
+      <c r="B73" s="25"/>
+      <c r="C73" s="29"/>
+      <c r="D73" s="29"/>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74" s="23"/>
-      <c r="B74" s="23"/>
-      <c r="C74" s="27"/>
-      <c r="D74" s="27"/>
+      <c r="A74" s="25"/>
+      <c r="B74" s="25"/>
+      <c r="C74" s="29"/>
+      <c r="D74" s="29"/>
     </row>
     <row r="75" spans="1:4">
-      <c r="A75" s="23"/>
-      <c r="B75" s="23"/>
-      <c r="C75" s="27"/>
-      <c r="D75" s="27"/>
+      <c r="A75" s="25"/>
+      <c r="B75" s="25"/>
+      <c r="C75" s="29"/>
+      <c r="D75" s="29"/>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76" s="23"/>
-      <c r="B76" s="23"/>
-      <c r="C76" s="27"/>
-      <c r="D76" s="27"/>
+      <c r="A76" s="25"/>
+      <c r="B76" s="25"/>
+      <c r="C76" s="29"/>
+      <c r="D76" s="29"/>
     </row>
     <row r="77" spans="1:4">
-      <c r="A77" s="23"/>
-      <c r="B77" s="23"/>
-      <c r="C77" s="27"/>
-      <c r="D77" s="27"/>
+      <c r="A77" s="25"/>
+      <c r="B77" s="25"/>
+      <c r="C77" s="29"/>
+      <c r="D77" s="29"/>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="67" t="s">
+      <c r="A78" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="B78" s="23"/>
-      <c r="C78" s="27"/>
-      <c r="D78" s="27"/>
+      <c r="B78" s="25"/>
+      <c r="C78" s="29"/>
+      <c r="D78" s="29"/>
     </row>
     <row r="79" spans="1:4">
-      <c r="A79" s="23"/>
-      <c r="B79" s="23"/>
-      <c r="C79" s="27"/>
-      <c r="D79" s="27"/>
+      <c r="A79" s="25"/>
+      <c r="B79" s="25"/>
+      <c r="C79" s="29"/>
+      <c r="D79" s="29"/>
     </row>
     <row r="80" spans="1:4">
-      <c r="A80" s="23"/>
-      <c r="B80" s="23"/>
-      <c r="C80" s="27"/>
-      <c r="D80" s="27"/>
+      <c r="A80" s="25"/>
+      <c r="B80" s="25"/>
+      <c r="C80" s="29"/>
+      <c r="D80" s="29"/>
     </row>
     <row r="81" spans="1:4">
-      <c r="A81" s="23"/>
-      <c r="B81" s="23"/>
-      <c r="C81" s="27"/>
-      <c r="D81" s="27"/>
+      <c r="A81" s="25"/>
+      <c r="B81" s="25"/>
+      <c r="C81" s="29"/>
+      <c r="D81" s="29"/>
     </row>
     <row r="82" spans="1:4">
-      <c r="A82" s="23"/>
-      <c r="B82" s="23"/>
-      <c r="C82" s="27"/>
-      <c r="D82" s="27"/>
+      <c r="A82" s="25"/>
+      <c r="B82" s="25"/>
+      <c r="C82" s="29"/>
+      <c r="D82" s="29"/>
     </row>
     <row r="83" spans="1:4">
-      <c r="A83" s="23"/>
-      <c r="B83" s="23"/>
-      <c r="C83" s="27"/>
-      <c r="D83" s="27"/>
+      <c r="A83" s="25"/>
+      <c r="B83" s="25"/>
+      <c r="C83" s="29"/>
+      <c r="D83" s="29"/>
     </row>
     <row r="84" spans="1:4">
-      <c r="A84" s="23"/>
-      <c r="B84" s="23"/>
-      <c r="C84" s="27"/>
-      <c r="D84" s="27"/>
+      <c r="A84" s="25"/>
+      <c r="B84" s="25"/>
+      <c r="C84" s="29"/>
+      <c r="D84" s="29"/>
     </row>
     <row r="85" spans="1:4">
-      <c r="A85" s="23"/>
-      <c r="B85" s="23"/>
-      <c r="C85" s="27"/>
-      <c r="D85" s="27"/>
+      <c r="A85" s="25"/>
+      <c r="B85" s="25"/>
+      <c r="C85" s="29"/>
+      <c r="D85" s="29"/>
     </row>
     <row r="86" spans="1:4">
-      <c r="A86" s="23"/>
-      <c r="B86" s="23"/>
-      <c r="C86" s="27"/>
-      <c r="D86" s="27"/>
+      <c r="A86" s="25"/>
+      <c r="B86" s="25"/>
+      <c r="C86" s="29"/>
+      <c r="D86" s="29"/>
     </row>
     <row r="87" spans="1:4">
-      <c r="A87" s="23"/>
-      <c r="B87" s="23"/>
-      <c r="C87" s="27"/>
-      <c r="D87" s="27"/>
+      <c r="A87" s="25"/>
+      <c r="B87" s="25"/>
+      <c r="C87" s="29"/>
+      <c r="D87" s="29"/>
     </row>
     <row r="88" spans="1:4">
-      <c r="A88" s="67" t="s">
+      <c r="A88" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="B88" s="23"/>
-      <c r="C88" s="27"/>
-      <c r="D88" s="27"/>
+      <c r="B88" s="25"/>
+      <c r="C88" s="29"/>
+      <c r="D88" s="29"/>
     </row>
     <row r="89" spans="1:4">
-      <c r="A89" s="23"/>
-      <c r="B89" s="23"/>
-      <c r="C89" s="27"/>
-      <c r="D89" s="27"/>
+      <c r="A89" s="25"/>
+      <c r="B89" s="25"/>
+      <c r="C89" s="29"/>
+      <c r="D89" s="29"/>
     </row>
     <row r="90" spans="1:4">
-      <c r="A90" s="23"/>
-      <c r="B90" s="23"/>
-      <c r="C90" s="27"/>
-      <c r="D90" s="27"/>
+      <c r="A90" s="25"/>
+      <c r="B90" s="25"/>
+      <c r="C90" s="29"/>
+      <c r="D90" s="29"/>
     </row>
     <row r="91" spans="1:4">
-      <c r="A91" s="23"/>
-      <c r="B91" s="23"/>
-      <c r="C91" s="27"/>
-      <c r="D91" s="27"/>
+      <c r="A91" s="25"/>
+      <c r="B91" s="25"/>
+      <c r="C91" s="29"/>
+      <c r="D91" s="29"/>
     </row>
     <row r="92" spans="1:4">
-      <c r="A92" s="23"/>
-      <c r="B92" s="23"/>
-      <c r="C92" s="27"/>
-      <c r="D92" s="27"/>
+      <c r="A92" s="25"/>
+      <c r="B92" s="25"/>
+      <c r="C92" s="29"/>
+      <c r="D92" s="29"/>
     </row>
     <row r="93" spans="1:4">
-      <c r="A93" s="23"/>
-      <c r="B93" s="23"/>
-      <c r="C93" s="27"/>
-      <c r="D93" s="27"/>
+      <c r="A93" s="25"/>
+      <c r="B93" s="25"/>
+      <c r="C93" s="29"/>
+      <c r="D93" s="29"/>
     </row>
     <row r="94" spans="1:4">
-      <c r="A94" s="23"/>
-      <c r="B94" s="23"/>
-      <c r="C94" s="27"/>
-      <c r="D94" s="27"/>
+      <c r="A94" s="25"/>
+      <c r="B94" s="25"/>
+      <c r="C94" s="29"/>
+      <c r="D94" s="29"/>
     </row>
     <row r="95" spans="1:4">
-      <c r="A95" s="23"/>
-      <c r="B95" s="23"/>
-      <c r="C95" s="27"/>
-      <c r="D95" s="27"/>
+      <c r="A95" s="25"/>
+      <c r="B95" s="25"/>
+      <c r="C95" s="29"/>
+      <c r="D95" s="29"/>
     </row>
     <row r="96" spans="1:4">
-      <c r="A96" s="23"/>
-      <c r="B96" s="23"/>
-      <c r="C96" s="27"/>
-      <c r="D96" s="27"/>
+      <c r="A96" s="25"/>
+      <c r="B96" s="25"/>
+      <c r="C96" s="29"/>
+      <c r="D96" s="29"/>
     </row>
     <row r="97" spans="1:4">
-      <c r="A97" s="67" t="s">
+      <c r="A97" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="B97" s="25"/>
-      <c r="C97" s="27"/>
-      <c r="D97" s="27"/>
+      <c r="B97" s="27"/>
+      <c r="C97" s="29"/>
+      <c r="D97" s="29"/>
     </row>
     <row r="98" spans="1:4">
-      <c r="A98" s="25"/>
-      <c r="B98" s="25"/>
-      <c r="C98" s="27"/>
-      <c r="D98" s="27"/>
+      <c r="A98" s="27"/>
+      <c r="B98" s="27"/>
+      <c r="C98" s="29"/>
+      <c r="D98" s="29"/>
     </row>
     <row r="99" spans="1:4">
-      <c r="A99" s="25"/>
-      <c r="B99" s="25"/>
-      <c r="C99" s="27"/>
-      <c r="D99" s="27"/>
+      <c r="A99" s="27"/>
+      <c r="B99" s="27"/>
+      <c r="C99" s="29"/>
+      <c r="D99" s="29"/>
     </row>
     <row r="100" spans="1:4">
-      <c r="A100" s="25"/>
-      <c r="B100" s="25"/>
-      <c r="C100" s="27"/>
-      <c r="D100" s="27"/>
+      <c r="A100" s="27"/>
+      <c r="B100" s="27"/>
+      <c r="C100" s="29"/>
+      <c r="D100" s="29"/>
     </row>
     <row r="101" spans="1:4">
-      <c r="A101" s="25"/>
-      <c r="B101" s="25"/>
-      <c r="C101" s="27"/>
-      <c r="D101" s="27"/>
+      <c r="A101" s="27"/>
+      <c r="B101" s="27"/>
+      <c r="C101" s="29"/>
+      <c r="D101" s="29"/>
     </row>
     <row r="102" spans="1:4">
-      <c r="A102" s="25"/>
-      <c r="B102" s="25"/>
-      <c r="C102" s="27"/>
-      <c r="D102" s="27"/>
+      <c r="A102" s="27"/>
+      <c r="B102" s="27"/>
+      <c r="C102" s="29"/>
+      <c r="D102" s="29"/>
     </row>
     <row r="103" spans="1:4">
-      <c r="A103" s="25"/>
-      <c r="B103" s="25"/>
-      <c r="C103" s="27"/>
-      <c r="D103" s="27"/>
+      <c r="A103" s="27"/>
+      <c r="B103" s="27"/>
+      <c r="C103" s="29"/>
+      <c r="D103" s="29"/>
     </row>
     <row r="104" spans="1:4">
-      <c r="A104" s="25"/>
-      <c r="B104" s="25"/>
-      <c r="C104" s="27"/>
-      <c r="D104" s="27"/>
+      <c r="A104" s="27"/>
+      <c r="B104" s="27"/>
+      <c r="C104" s="29"/>
+      <c r="D104" s="29"/>
     </row>
     <row r="105" spans="1:4">
-      <c r="A105" s="25"/>
-      <c r="B105" s="25"/>
-      <c r="C105" s="27"/>
-      <c r="D105" s="27"/>
+      <c r="A105" s="27"/>
+      <c r="B105" s="27"/>
+      <c r="C105" s="29"/>
+      <c r="D105" s="29"/>
     </row>
     <row r="106" spans="1:4">
-      <c r="A106" s="67" t="s">
+      <c r="A106" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="B106" s="23"/>
-      <c r="C106" s="27"/>
-      <c r="D106" s="27"/>
+      <c r="B106" s="25"/>
+      <c r="C106" s="29"/>
+      <c r="D106" s="29"/>
     </row>
     <row r="107" spans="1:4">
-      <c r="A107" s="23"/>
-      <c r="B107" s="23"/>
-      <c r="C107" s="27"/>
-      <c r="D107" s="27"/>
+      <c r="A107" s="25"/>
+      <c r="B107" s="25"/>
+      <c r="C107" s="29"/>
+      <c r="D107" s="29"/>
     </row>
     <row r="108" spans="1:4">
-      <c r="A108" s="23"/>
-      <c r="B108" s="23"/>
-      <c r="C108" s="27"/>
-      <c r="D108" s="27"/>
+      <c r="A108" s="25"/>
+      <c r="B108" s="25"/>
+      <c r="C108" s="29"/>
+      <c r="D108" s="29"/>
     </row>
     <row r="109" spans="1:4">
-      <c r="A109" s="23"/>
-      <c r="B109" s="23"/>
-      <c r="C109" s="27"/>
-      <c r="D109" s="27"/>
+      <c r="A109" s="25"/>
+      <c r="B109" s="25"/>
+      <c r="C109" s="29"/>
+      <c r="D109" s="29"/>
     </row>
     <row r="110" spans="1:4">
-      <c r="A110" s="23"/>
-      <c r="B110" s="23"/>
-      <c r="C110" s="27"/>
-      <c r="D110" s="27"/>
+      <c r="A110" s="25"/>
+      <c r="B110" s="25"/>
+      <c r="C110" s="29"/>
+      <c r="D110" s="29"/>
     </row>
     <row r="111" spans="1:4">
-      <c r="A111" s="23"/>
-      <c r="B111" s="23"/>
-      <c r="C111" s="27"/>
-      <c r="D111" s="27"/>
+      <c r="A111" s="25"/>
+      <c r="B111" s="25"/>
+      <c r="C111" s="29"/>
+      <c r="D111" s="29"/>
     </row>
     <row r="112" spans="1:4">
-      <c r="A112" s="23"/>
-      <c r="B112" s="23"/>
-      <c r="C112" s="27"/>
-      <c r="D112" s="27"/>
+      <c r="A112" s="25"/>
+      <c r="B112" s="25"/>
+      <c r="C112" s="29"/>
+      <c r="D112" s="29"/>
     </row>
     <row r="113" spans="1:4">
-      <c r="A113" s="23"/>
-      <c r="B113" s="23"/>
-      <c r="C113" s="27"/>
-      <c r="D113" s="27"/>
+      <c r="A113" s="25"/>
+      <c r="B113" s="25"/>
+      <c r="C113" s="29"/>
+      <c r="D113" s="29"/>
     </row>
     <row r="114" spans="1:4">
-      <c r="A114" s="23"/>
-      <c r="B114" s="23"/>
-      <c r="C114" s="27"/>
-      <c r="D114" s="27"/>
+      <c r="A114" s="25"/>
+      <c r="B114" s="25"/>
+      <c r="C114" s="29"/>
+      <c r="D114" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -7394,10 +7508,10 @@
   <sheetData>
     <row r="1" ht="409" customHeight="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -7543,18 +7657,18 @@
     </row>
     <row r="2" ht="409.5" spans="1:3">
       <c r="A2" s="6" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
     </row>
     <row r="3" ht="409.5" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="C3"/>
     </row>
@@ -7603,32 +7717,32 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="2" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="2" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="2" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="10" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="2" t="s">
-        <v>358</v>
+        <v>371</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="2" t="s">
-        <v>359</v>
+        <v>372</v>
       </c>
     </row>
     <row r="36" ht="23.4" spans="1:1">
@@ -7636,177 +7750,177 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="2" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="2" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="2" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="2" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="2" t="s">
-        <v>364</v>
+        <v>377</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="2" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="2" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="2" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="2" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="2" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="10" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="2" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
     </row>
     <row r="60" ht="23.4" spans="1:1">
       <c r="A60" s="9" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="2" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="2" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="2" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="2" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="2" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="2" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="2" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="2" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="2" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="2" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="10" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="2" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
     </row>
     <row r="86" ht="23.4" spans="1:1">
       <c r="A86" s="9" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="2" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="2" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="2" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="2" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="2" t="s">
-        <v>390</v>
+        <v>403</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="2" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="2" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="2" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="2" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
     </row>
     <row r="103" spans="1:1">
@@ -7816,12 +7930,12 @@
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="2" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="2" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
     </row>
     <row r="108" spans="1:1">
@@ -7829,12 +7943,12 @@
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="2" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" s="2" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
     </row>
     <row r="112" ht="23.4" spans="1:1">
@@ -7842,42 +7956,42 @@
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="2" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="2" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="2" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="2" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="2" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="2" t="s">
-        <v>403</v>
+        <v>416</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="2" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="2" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
     </row>
     <row r="128" spans="1:1">
@@ -7885,12 +7999,12 @@
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="2" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" s="2" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
     </row>
     <row r="132" ht="23.4" spans="1:1">
@@ -7898,62 +8012,62 @@
     </row>
     <row r="133" spans="1:1">
       <c r="A133" s="2" t="s">
-        <v>408</v>
+        <v>421</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="2" t="s">
-        <v>409</v>
+        <v>422</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="2" t="s">
-        <v>410</v>
+        <v>423</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" s="2" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="2" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" s="2" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="2" t="s">
-        <v>414</v>
+        <v>427</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="2" t="s">
-        <v>415</v>
+        <v>428</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" s="2" t="s">
-        <v>416</v>
+        <v>429</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" s="10" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" s="2" t="s">
-        <v>418</v>
+        <v>431</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" s="2" t="s">
-        <v>419</v>
+        <v>432</v>
       </c>
     </row>
     <row r="154" ht="23.4" spans="1:1">
@@ -7961,62 +8075,62 @@
     </row>
     <row r="156" spans="1:1">
       <c r="A156" s="2" t="s">
-        <v>420</v>
+        <v>433</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" s="2" t="s">
-        <v>421</v>
+        <v>434</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" s="2" t="s">
-        <v>422</v>
+        <v>435</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" s="2" t="s">
-        <v>423</v>
+        <v>436</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164" s="2" t="s">
-        <v>424</v>
+        <v>437</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" s="2" t="s">
-        <v>425</v>
+        <v>438</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" s="2" t="s">
-        <v>426</v>
+        <v>439</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170" s="2" t="s">
-        <v>427</v>
+        <v>440</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" s="2" t="s">
-        <v>428</v>
+        <v>441</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174" s="10" t="s">
-        <v>429</v>
+        <v>442</v>
       </c>
     </row>
     <row r="176" spans="1:1">
       <c r="A176" s="2" t="s">
-        <v>430</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" s="2" t="s">
-        <v>431</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:1">
@@ -8026,7 +8140,7 @@
     </row>
     <row r="182" spans="1:1">
       <c r="A182" s="2" t="s">
-        <v>432</v>
+        <v>445</v>
       </c>
     </row>
     <row r="184" spans="1:1">
@@ -8036,87 +8150,87 @@
     </row>
     <row r="186" spans="1:1">
       <c r="A186" s="2" t="s">
-        <v>433</v>
+        <v>446</v>
       </c>
     </row>
     <row r="188" spans="1:1">
       <c r="A188" s="2" t="s">
-        <v>434</v>
+        <v>447</v>
       </c>
     </row>
     <row r="189" spans="1:1">
       <c r="A189" s="2" t="s">
-        <v>435</v>
+        <v>448</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190" s="2" t="s">
-        <v>436</v>
+        <v>449</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191" s="2" t="s">
-        <v>437</v>
+        <v>450</v>
       </c>
     </row>
     <row r="192" spans="1:1">
       <c r="A192" s="2" t="s">
-        <v>438</v>
+        <v>451</v>
       </c>
     </row>
     <row r="193" spans="1:1">
       <c r="A193" s="2" t="s">
-        <v>439</v>
+        <v>452</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194" s="2" t="s">
-        <v>440</v>
+        <v>453</v>
       </c>
     </row>
     <row r="195" spans="1:1">
       <c r="A195" s="2" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
     </row>
     <row r="196" spans="1:1">
       <c r="A196" s="2" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
     </row>
     <row r="198" spans="1:1">
       <c r="A198" s="2" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
     </row>
     <row r="199" spans="1:1">
       <c r="A199" s="2" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
     </row>
     <row r="201" spans="1:1">
       <c r="A201" s="2" t="s">
-        <v>445</v>
+        <v>458</v>
       </c>
     </row>
     <row r="203" spans="1:1">
       <c r="A203" s="2" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
     </row>
     <row r="205" spans="1:1">
       <c r="A205" s="2" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207" s="2" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
     </row>
     <row r="209" spans="1:1">
       <c r="A209" s="2" t="s">
-        <v>449</v>
+        <v>462</v>
       </c>
     </row>
     <row r="211" spans="1:1">
@@ -8126,32 +8240,32 @@
     </row>
     <row r="213" spans="1:1">
       <c r="A213" s="2" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215" s="2" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
     </row>
     <row r="217" spans="1:1">
       <c r="A217" s="2" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
     </row>
     <row r="219" spans="1:1">
       <c r="A219" s="2" t="s">
-        <v>453</v>
+        <v>466</v>
       </c>
     </row>
     <row r="221" spans="1:1">
       <c r="A221" s="2" t="s">
-        <v>454</v>
+        <v>467</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223" s="2" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>
@@ -8172,7 +8286,7 @@
   <sheetData>
     <row r="2" spans="3:3">
       <c r="C2" s="1" t="s">
-        <v>456</v>
+        <v>469</v>
       </c>
     </row>
     <row r="3" spans="3:3">
@@ -8480,19 +8594,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="E1" s="54" t="s">
         <v>23</v>
       </c>
     </row>
@@ -8500,191 +8614,191 @@
       <c r="A2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="51">
+      <c r="B2" s="55">
         <v>45976</v>
       </c>
-      <c r="C2" s="52">
+      <c r="C2" s="56">
         <v>45983</v>
       </c>
-      <c r="D2" s="23">
+      <c r="D2" s="25">
         <v>4</v>
       </c>
-      <c r="E2" s="53"/>
+      <c r="E2" s="57"/>
     </row>
     <row r="3" ht="115.2" spans="1:5">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="51">
+      <c r="B3" s="55">
         <v>45976</v>
       </c>
-      <c r="C3" s="52">
+      <c r="C3" s="56">
         <v>45983</v>
       </c>
-      <c r="D3" s="23">
+      <c r="D3" s="25">
         <v>4</v>
       </c>
-      <c r="E3" s="54" t="s">
+      <c r="E3" s="58" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" ht="129.6" spans="1:5">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="51">
+      <c r="B4" s="55">
         <v>45976</v>
       </c>
-      <c r="C4" s="52">
+      <c r="C4" s="56">
         <v>45983</v>
       </c>
-      <c r="D4" s="23">
+      <c r="D4" s="25">
         <v>3</v>
       </c>
-      <c r="E4" s="55" t="s">
+      <c r="E4" s="59" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" ht="144" spans="1:5">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="51">
+      <c r="B5" s="55">
         <v>45976</v>
       </c>
-      <c r="C5" s="52">
+      <c r="C5" s="56">
         <v>45983</v>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="25">
         <v>2</v>
       </c>
-      <c r="E5" s="56"/>
+      <c r="E5" s="60"/>
     </row>
     <row r="6" ht="115.2" spans="1:5">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="51">
+      <c r="B6" s="55">
         <v>45976</v>
       </c>
-      <c r="C6" s="52">
+      <c r="C6" s="56">
         <v>45983</v>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="25">
         <v>2</v>
       </c>
-      <c r="E6" s="56"/>
+      <c r="E6" s="60"/>
     </row>
     <row r="7" ht="129.6" spans="1:5">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="51">
+      <c r="B7" s="55">
         <v>45976</v>
       </c>
-      <c r="C7" s="52">
+      <c r="C7" s="56">
         <v>45983</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="25">
         <v>2</v>
       </c>
-      <c r="E7" s="56"/>
-    </row>
-    <row r="8" s="49" customFormat="1" ht="144" spans="1:5">
-      <c r="A8" s="57" t="s">
+      <c r="E7" s="60"/>
+    </row>
+    <row r="8" s="53" customFormat="1" ht="144" spans="1:5">
+      <c r="A8" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="52">
+      <c r="B8" s="56">
         <v>45976</v>
       </c>
-      <c r="C8" s="52">
+      <c r="C8" s="56">
         <v>45983</v>
       </c>
-      <c r="D8" s="58">
+      <c r="D8" s="62">
         <v>2</v>
       </c>
-      <c r="E8" s="59"/>
-    </row>
-    <row r="9" s="49" customFormat="1" ht="158.4" spans="1:5">
-      <c r="A9" s="57" t="s">
+      <c r="E8" s="63"/>
+    </row>
+    <row r="9" s="53" customFormat="1" ht="158.4" spans="1:5">
+      <c r="A9" s="61" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="52">
+      <c r="B9" s="56">
         <v>45976</v>
       </c>
-      <c r="C9" s="52">
+      <c r="C9" s="56">
         <v>45983</v>
       </c>
-      <c r="D9" s="58">
+      <c r="D9" s="62">
         <v>1</v>
       </c>
-      <c r="E9" s="60"/>
-    </row>
-    <row r="10" s="49" customFormat="1" spans="1:5">
-      <c r="A10" s="58" t="s">
+      <c r="E9" s="64"/>
+    </row>
+    <row r="10" s="53" customFormat="1" spans="1:5">
+      <c r="A10" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="52">
+      <c r="B10" s="56">
         <v>45976</v>
       </c>
-      <c r="C10" s="52">
+      <c r="C10" s="56">
         <v>45983</v>
       </c>
-      <c r="D10" s="58">
+      <c r="D10" s="62">
         <v>1</v>
       </c>
-      <c r="E10" s="61" t="s">
+      <c r="E10" s="65" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" s="49" customFormat="1" spans="1:5">
-      <c r="A11" s="58" t="s">
+    <row r="11" s="53" customFormat="1" spans="1:5">
+      <c r="A11" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="52">
+      <c r="B11" s="56">
         <v>45976</v>
       </c>
-      <c r="C11" s="52">
+      <c r="C11" s="56">
         <v>45983</v>
       </c>
-      <c r="D11" s="58">
+      <c r="D11" s="62">
         <v>1</v>
       </c>
-      <c r="E11" s="61" t="s">
+      <c r="E11" s="65" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" s="49" customFormat="1" spans="1:5">
-      <c r="A12" s="58" t="s">
+    <row r="12" s="53" customFormat="1" spans="1:5">
+      <c r="A12" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="52">
+      <c r="B12" s="56">
         <v>45976</v>
       </c>
-      <c r="C12" s="52">
+      <c r="C12" s="56">
         <v>45983</v>
       </c>
-      <c r="D12" s="58">
+      <c r="D12" s="62">
         <v>1</v>
       </c>
-      <c r="E12" s="61" t="s">
+      <c r="E12" s="65" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="13" ht="14" customHeight="1" spans="1:5">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="52">
+      <c r="B13" s="56">
         <v>45977</v>
       </c>
-      <c r="C13" s="52">
+      <c r="C13" s="56">
         <v>45982</v>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="25">
         <v>1</v>
       </c>
-      <c r="E13" s="61" t="s">
+      <c r="E13" s="65" t="s">
         <v>35</v>
       </c>
     </row>
@@ -8692,339 +8806,339 @@
       <c r="A14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="52">
+      <c r="B14" s="56">
         <v>45980</v>
       </c>
-      <c r="C14" s="52">
+      <c r="C14" s="56">
         <v>45982</v>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="25">
         <v>1</v>
       </c>
-      <c r="E14" s="61" t="s">
+      <c r="E14" s="65" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="52">
+      <c r="B15" s="56">
         <v>45980</v>
       </c>
-      <c r="C15" s="52">
+      <c r="C15" s="56">
         <v>45982</v>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="25">
         <v>1</v>
       </c>
-      <c r="E15" s="61" t="s">
+      <c r="E15" s="65" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="52">
+      <c r="B16" s="56">
         <v>45980</v>
       </c>
-      <c r="C16" s="52">
+      <c r="C16" s="56">
         <v>45982</v>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="25">
         <v>1</v>
       </c>
-      <c r="E16" s="61" t="s">
+      <c r="E16" s="65" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="52">
+      <c r="B17" s="56">
         <v>45980</v>
       </c>
-      <c r="C17" s="52">
+      <c r="C17" s="56">
         <v>45982</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="25">
         <v>1</v>
       </c>
-      <c r="E17" s="61" t="s">
+      <c r="E17" s="65" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="52">
+      <c r="B18" s="56">
         <v>45981</v>
       </c>
-      <c r="C18" s="52">
+      <c r="C18" s="56">
         <v>45983</v>
       </c>
-      <c r="D18" s="23">
+      <c r="D18" s="25">
         <v>1</v>
       </c>
-      <c r="E18" s="61" t="s">
+      <c r="E18" s="65" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="52">
+      <c r="B19" s="56">
         <v>45982</v>
       </c>
-      <c r="C19" s="52">
+      <c r="C19" s="56">
         <v>45984</v>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="25">
         <v>1</v>
       </c>
-      <c r="E19" s="61" t="s">
+      <c r="E19" s="65" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="52">
+      <c r="B20" s="56">
         <v>45983</v>
       </c>
-      <c r="C20" s="52">
+      <c r="C20" s="56">
         <v>45985</v>
       </c>
-      <c r="D20" s="23">
+      <c r="D20" s="25">
         <v>1</v>
       </c>
-      <c r="E20" s="61" t="s">
+      <c r="E20" s="65" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="52">
+      <c r="B21" s="56">
         <v>45986</v>
       </c>
-      <c r="C21" s="52">
+      <c r="C21" s="56">
         <v>45987</v>
       </c>
-      <c r="D21" s="23">
+      <c r="D21" s="25">
         <v>1</v>
       </c>
-      <c r="E21" s="61" t="s">
+      <c r="E21" s="65" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="52">
+      <c r="B22" s="56">
         <v>45986</v>
       </c>
-      <c r="C22" s="52">
+      <c r="C22" s="56">
         <v>45987</v>
       </c>
-      <c r="D22" s="23">
+      <c r="D22" s="25">
         <v>1</v>
       </c>
-      <c r="E22" s="61" t="s">
+      <c r="E22" s="65" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="23" ht="14" customHeight="1" spans="1:5">
-      <c r="A23" s="23" t="s">
+      <c r="A23" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="52">
+      <c r="B23" s="56">
         <v>45986</v>
       </c>
-      <c r="C23" s="52">
+      <c r="C23" s="56">
         <v>45987</v>
       </c>
-      <c r="D23" s="23">
+      <c r="D23" s="25">
         <v>1</v>
       </c>
-      <c r="E23" s="61" t="s">
+      <c r="E23" s="65" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="23" t="s">
+      <c r="A24" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="52">
+      <c r="B24" s="56">
         <v>45986</v>
       </c>
-      <c r="C24" s="52">
+      <c r="C24" s="56">
         <v>45987</v>
       </c>
-      <c r="D24" s="23">
+      <c r="D24" s="25">
         <v>1</v>
       </c>
-      <c r="E24" s="61" t="s">
+      <c r="E24" s="65" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="52">
+      <c r="B25" s="56">
         <v>45986</v>
       </c>
-      <c r="C25" s="52">
+      <c r="C25" s="56">
         <v>45987</v>
       </c>
-      <c r="D25" s="23">
+      <c r="D25" s="25">
         <v>1</v>
       </c>
-      <c r="E25" s="61" t="s">
+      <c r="E25" s="65" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="23" t="s">
+      <c r="A26" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="52">
+      <c r="B26" s="56">
         <v>45986</v>
       </c>
-      <c r="C26" s="52">
+      <c r="C26" s="56">
         <v>45987</v>
       </c>
-      <c r="D26" s="23">
+      <c r="D26" s="25">
         <v>1</v>
       </c>
-      <c r="E26" s="61" t="s">
+      <c r="E26" s="65" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="52">
+      <c r="B27" s="56">
         <v>45986</v>
       </c>
-      <c r="C27" s="52">
+      <c r="C27" s="56">
         <v>45987</v>
       </c>
-      <c r="D27" s="23">
+      <c r="D27" s="25">
         <v>1</v>
       </c>
-      <c r="E27" s="61" t="s">
+      <c r="E27" s="65" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="23" t="s">
+      <c r="A28" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="52">
+      <c r="B28" s="56">
         <v>45986</v>
       </c>
-      <c r="C28" s="52">
+      <c r="C28" s="56">
         <v>45987</v>
       </c>
-      <c r="D28" s="23">
+      <c r="D28" s="25">
         <v>1</v>
       </c>
-      <c r="E28" s="61" t="s">
+      <c r="E28" s="65" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="23" t="s">
+      <c r="A29" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="52">
+      <c r="B29" s="56">
         <v>45986</v>
       </c>
-      <c r="C29" s="52">
+      <c r="C29" s="56">
         <v>45987</v>
       </c>
-      <c r="D29" s="23">
+      <c r="D29" s="25">
         <v>1</v>
       </c>
-      <c r="E29" s="61" t="s">
+      <c r="E29" s="65" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="23" t="s">
+      <c r="A30" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="52">
+      <c r="B30" s="56">
         <v>45986</v>
       </c>
-      <c r="C30" s="52">
+      <c r="C30" s="56">
         <v>45987</v>
       </c>
-      <c r="D30" s="23">
+      <c r="D30" s="25">
         <v>1</v>
       </c>
-      <c r="E30" s="61" t="s">
+      <c r="E30" s="65" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="23" t="s">
+      <c r="A31" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="52">
+      <c r="B31" s="56">
         <v>45992</v>
       </c>
-      <c r="C31" s="52">
+      <c r="C31" s="56">
         <v>45993</v>
       </c>
-      <c r="D31" s="23">
+      <c r="D31" s="25">
         <v>1</v>
       </c>
-      <c r="E31" s="61" t="s">
+      <c r="E31" s="65" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="23" t="s">
+      <c r="A32" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="52">
+      <c r="B32" s="56">
         <v>45992</v>
       </c>
-      <c r="C32" s="52">
+      <c r="C32" s="56">
         <v>45993</v>
       </c>
-      <c r="D32" s="23">
+      <c r="D32" s="25">
         <v>1</v>
       </c>
-      <c r="E32" s="61" t="s">
+      <c r="E32" s="65" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="23" t="s">
+      <c r="A33" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="52">
+      <c r="B33" s="56">
         <v>45992</v>
       </c>
-      <c r="C33" s="52">
+      <c r="C33" s="56">
         <v>45993</v>
       </c>
-      <c r="D33" s="23">
+      <c r="D33" s="25">
         <v>1</v>
       </c>
-      <c r="E33" s="61" t="s">
+      <c r="E33" s="65" t="s">
         <v>35</v>
       </c>
     </row>
@@ -9032,606 +9146,606 @@
       <c r="A34" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="52">
+      <c r="B34" s="56">
         <v>45993</v>
       </c>
-      <c r="C34" s="52">
+      <c r="C34" s="56">
         <v>45993</v>
       </c>
-      <c r="D34" s="23">
+      <c r="D34" s="25">
         <v>1</v>
       </c>
-      <c r="E34" s="61" t="s">
+      <c r="E34" s="65" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="27"/>
-      <c r="B35" s="23"/>
-      <c r="C35" s="23"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="23"/>
+      <c r="A35" s="29"/>
+      <c r="B35" s="25"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="23"/>
-      <c r="B36" s="23"/>
-      <c r="C36" s="23"/>
-      <c r="D36" s="23"/>
-      <c r="E36" s="23"/>
+      <c r="A36" s="25"/>
+      <c r="B36" s="25"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="25"/>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="23"/>
-      <c r="B37" s="23"/>
-      <c r="C37" s="23"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
+      <c r="A37" s="25"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="23"/>
-      <c r="B38" s="23"/>
-      <c r="C38" s="23"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="23"/>
+      <c r="A38" s="25"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="23"/>
-      <c r="B39" s="23"/>
-      <c r="C39" s="23"/>
-      <c r="D39" s="23"/>
-      <c r="E39" s="23"/>
+      <c r="A39" s="25"/>
+      <c r="B39" s="25"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="23"/>
-      <c r="B40" s="23"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="23"/>
-      <c r="E40" s="23"/>
+      <c r="A40" s="25"/>
+      <c r="B40" s="25"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="25"/>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="23"/>
-      <c r="B41" s="23"/>
-      <c r="C41" s="23"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
+      <c r="A41" s="25"/>
+      <c r="B41" s="25"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="25"/>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="23"/>
-      <c r="B42" s="23"/>
-      <c r="C42" s="23"/>
-      <c r="D42" s="23"/>
-      <c r="E42" s="23"/>
+      <c r="A42" s="25"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="23"/>
-      <c r="B43" s="23"/>
-      <c r="C43" s="23"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23"/>
+      <c r="A43" s="25"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="25"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="23"/>
-      <c r="B44" s="23"/>
-      <c r="C44" s="23"/>
-      <c r="D44" s="23"/>
-      <c r="E44" s="23"/>
+      <c r="A44" s="25"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="25"/>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="23"/>
-      <c r="B45" s="23"/>
-      <c r="C45" s="23"/>
-      <c r="D45" s="23"/>
-      <c r="E45" s="23"/>
+      <c r="A45" s="25"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="25"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="25"/>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="23"/>
-      <c r="B46" s="23"/>
-      <c r="C46" s="23"/>
-      <c r="D46" s="23"/>
-      <c r="E46" s="23"/>
+      <c r="A46" s="25"/>
+      <c r="B46" s="25"/>
+      <c r="C46" s="25"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="25"/>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="23"/>
-      <c r="B47" s="23"/>
-      <c r="C47" s="23"/>
-      <c r="D47" s="23"/>
-      <c r="E47" s="23"/>
+      <c r="A47" s="25"/>
+      <c r="B47" s="25"/>
+      <c r="C47" s="25"/>
+      <c r="D47" s="25"/>
+      <c r="E47" s="25"/>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="23"/>
-      <c r="B48" s="23"/>
-      <c r="C48" s="23"/>
-      <c r="D48" s="23"/>
-      <c r="E48" s="23"/>
+      <c r="A48" s="25"/>
+      <c r="B48" s="25"/>
+      <c r="C48" s="25"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="25"/>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="23"/>
-      <c r="B49" s="23"/>
-      <c r="C49" s="23"/>
-      <c r="D49" s="23"/>
-      <c r="E49" s="23"/>
+      <c r="A49" s="25"/>
+      <c r="B49" s="25"/>
+      <c r="C49" s="25"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="25"/>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="23"/>
-      <c r="B50" s="23"/>
-      <c r="C50" s="23"/>
-      <c r="D50" s="23"/>
-      <c r="E50" s="23"/>
+      <c r="A50" s="25"/>
+      <c r="B50" s="25"/>
+      <c r="C50" s="25"/>
+      <c r="D50" s="25"/>
+      <c r="E50" s="25"/>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="23"/>
-      <c r="B51" s="23"/>
-      <c r="C51" s="23"/>
-      <c r="D51" s="23"/>
-      <c r="E51" s="23"/>
+      <c r="A51" s="25"/>
+      <c r="B51" s="25"/>
+      <c r="C51" s="25"/>
+      <c r="D51" s="25"/>
+      <c r="E51" s="25"/>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="23"/>
-      <c r="B52" s="23"/>
-      <c r="C52" s="23"/>
-      <c r="D52" s="23"/>
-      <c r="E52" s="23"/>
+      <c r="A52" s="25"/>
+      <c r="B52" s="25"/>
+      <c r="C52" s="25"/>
+      <c r="D52" s="25"/>
+      <c r="E52" s="25"/>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="23"/>
-      <c r="B53" s="23"/>
-      <c r="C53" s="23"/>
-      <c r="D53" s="23"/>
-      <c r="E53" s="23"/>
+      <c r="A53" s="25"/>
+      <c r="B53" s="25"/>
+      <c r="C53" s="25"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="25"/>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="23"/>
-      <c r="B54" s="23"/>
-      <c r="C54" s="23"/>
-      <c r="D54" s="23"/>
-      <c r="E54" s="23"/>
+      <c r="A54" s="25"/>
+      <c r="B54" s="25"/>
+      <c r="C54" s="25"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="25"/>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="23"/>
-      <c r="B55" s="23"/>
-      <c r="C55" s="23"/>
-      <c r="D55" s="23"/>
-      <c r="E55" s="23"/>
+      <c r="A55" s="25"/>
+      <c r="B55" s="25"/>
+      <c r="C55" s="25"/>
+      <c r="D55" s="25"/>
+      <c r="E55" s="25"/>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="23"/>
-      <c r="B56" s="23"/>
-      <c r="C56" s="23"/>
-      <c r="D56" s="23"/>
-      <c r="E56" s="23"/>
+      <c r="A56" s="25"/>
+      <c r="B56" s="25"/>
+      <c r="C56" s="25"/>
+      <c r="D56" s="25"/>
+      <c r="E56" s="25"/>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="23"/>
-      <c r="B57" s="23"/>
-      <c r="C57" s="23"/>
-      <c r="D57" s="23"/>
-      <c r="E57" s="23"/>
+      <c r="A57" s="25"/>
+      <c r="B57" s="25"/>
+      <c r="C57" s="25"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="25"/>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="23"/>
-      <c r="B58" s="23"/>
-      <c r="C58" s="23"/>
-      <c r="D58" s="23"/>
-      <c r="E58" s="23"/>
+      <c r="A58" s="25"/>
+      <c r="B58" s="25"/>
+      <c r="C58" s="25"/>
+      <c r="D58" s="25"/>
+      <c r="E58" s="25"/>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="23"/>
-      <c r="B59" s="23"/>
-      <c r="C59" s="23"/>
-      <c r="D59" s="23"/>
-      <c r="E59" s="23"/>
+      <c r="A59" s="25"/>
+      <c r="B59" s="25"/>
+      <c r="C59" s="25"/>
+      <c r="D59" s="25"/>
+      <c r="E59" s="25"/>
     </row>
     <row r="60" spans="1:5">
-      <c r="A60" s="23"/>
-      <c r="B60" s="23"/>
-      <c r="C60" s="23"/>
-      <c r="D60" s="23"/>
-      <c r="E60" s="23"/>
+      <c r="A60" s="25"/>
+      <c r="B60" s="25"/>
+      <c r="C60" s="25"/>
+      <c r="D60" s="25"/>
+      <c r="E60" s="25"/>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="23"/>
-      <c r="B61" s="23"/>
-      <c r="C61" s="23"/>
-      <c r="D61" s="23"/>
-      <c r="E61" s="23"/>
+      <c r="A61" s="25"/>
+      <c r="B61" s="25"/>
+      <c r="C61" s="25"/>
+      <c r="D61" s="25"/>
+      <c r="E61" s="25"/>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="23"/>
-      <c r="B62" s="23"/>
-      <c r="C62" s="23"/>
-      <c r="D62" s="23"/>
-      <c r="E62" s="23"/>
+      <c r="A62" s="25"/>
+      <c r="B62" s="25"/>
+      <c r="C62" s="25"/>
+      <c r="D62" s="25"/>
+      <c r="E62" s="25"/>
     </row>
     <row r="63" spans="1:5">
-      <c r="A63" s="23"/>
-      <c r="B63" s="23"/>
-      <c r="C63" s="23"/>
-      <c r="D63" s="23"/>
-      <c r="E63" s="23"/>
+      <c r="A63" s="25"/>
+      <c r="B63" s="25"/>
+      <c r="C63" s="25"/>
+      <c r="D63" s="25"/>
+      <c r="E63" s="25"/>
     </row>
     <row r="64" spans="1:5">
-      <c r="A64" s="23"/>
-      <c r="B64" s="23"/>
-      <c r="C64" s="23"/>
-      <c r="D64" s="23"/>
-      <c r="E64" s="23"/>
+      <c r="A64" s="25"/>
+      <c r="B64" s="25"/>
+      <c r="C64" s="25"/>
+      <c r="D64" s="25"/>
+      <c r="E64" s="25"/>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="23"/>
-      <c r="B65" s="23"/>
-      <c r="C65" s="23"/>
-      <c r="D65" s="23"/>
-      <c r="E65" s="23"/>
+      <c r="A65" s="25"/>
+      <c r="B65" s="25"/>
+      <c r="C65" s="25"/>
+      <c r="D65" s="25"/>
+      <c r="E65" s="25"/>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="23"/>
-      <c r="B66" s="23"/>
-      <c r="C66" s="23"/>
-      <c r="D66" s="23"/>
-      <c r="E66" s="23"/>
+      <c r="A66" s="25"/>
+      <c r="B66" s="25"/>
+      <c r="C66" s="25"/>
+      <c r="D66" s="25"/>
+      <c r="E66" s="25"/>
     </row>
     <row r="67" spans="1:5">
-      <c r="A67" s="23"/>
-      <c r="B67" s="23"/>
-      <c r="C67" s="23"/>
-      <c r="D67" s="23"/>
-      <c r="E67" s="23"/>
+      <c r="A67" s="25"/>
+      <c r="B67" s="25"/>
+      <c r="C67" s="25"/>
+      <c r="D67" s="25"/>
+      <c r="E67" s="25"/>
     </row>
     <row r="68" spans="1:5">
-      <c r="A68" s="23"/>
-      <c r="B68" s="23"/>
-      <c r="C68" s="23"/>
-      <c r="D68" s="23"/>
-      <c r="E68" s="23"/>
+      <c r="A68" s="25"/>
+      <c r="B68" s="25"/>
+      <c r="C68" s="25"/>
+      <c r="D68" s="25"/>
+      <c r="E68" s="25"/>
     </row>
     <row r="69" spans="1:5">
-      <c r="A69" s="23"/>
-      <c r="B69" s="23"/>
-      <c r="C69" s="23"/>
-      <c r="D69" s="23"/>
-      <c r="E69" s="23"/>
+      <c r="A69" s="25"/>
+      <c r="B69" s="25"/>
+      <c r="C69" s="25"/>
+      <c r="D69" s="25"/>
+      <c r="E69" s="25"/>
     </row>
     <row r="70" spans="1:5">
-      <c r="A70" s="23"/>
-      <c r="B70" s="23"/>
-      <c r="C70" s="23"/>
-      <c r="D70" s="23"/>
-      <c r="E70" s="23"/>
+      <c r="A70" s="25"/>
+      <c r="B70" s="25"/>
+      <c r="C70" s="25"/>
+      <c r="D70" s="25"/>
+      <c r="E70" s="25"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="A71" s="23"/>
-      <c r="B71" s="23"/>
-      <c r="C71" s="23"/>
-      <c r="D71" s="23"/>
-      <c r="E71" s="23"/>
+      <c r="A71" s="25"/>
+      <c r="B71" s="25"/>
+      <c r="C71" s="25"/>
+      <c r="D71" s="25"/>
+      <c r="E71" s="25"/>
     </row>
     <row r="72" spans="1:5">
-      <c r="A72" s="23"/>
-      <c r="B72" s="23"/>
-      <c r="C72" s="23"/>
-      <c r="D72" s="23"/>
-      <c r="E72" s="23"/>
+      <c r="A72" s="25"/>
+      <c r="B72" s="25"/>
+      <c r="C72" s="25"/>
+      <c r="D72" s="25"/>
+      <c r="E72" s="25"/>
     </row>
     <row r="73" spans="1:5">
-      <c r="A73" s="23"/>
-      <c r="B73" s="23"/>
-      <c r="C73" s="23"/>
-      <c r="D73" s="23"/>
-      <c r="E73" s="23"/>
+      <c r="A73" s="25"/>
+      <c r="B73" s="25"/>
+      <c r="C73" s="25"/>
+      <c r="D73" s="25"/>
+      <c r="E73" s="25"/>
     </row>
     <row r="74" spans="1:5">
-      <c r="A74" s="23"/>
-      <c r="B74" s="23"/>
-      <c r="C74" s="23"/>
-      <c r="D74" s="23"/>
-      <c r="E74" s="23"/>
+      <c r="A74" s="25"/>
+      <c r="B74" s="25"/>
+      <c r="C74" s="25"/>
+      <c r="D74" s="25"/>
+      <c r="E74" s="25"/>
     </row>
     <row r="75" spans="1:5">
-      <c r="A75" s="23"/>
-      <c r="B75" s="23"/>
-      <c r="C75" s="23"/>
-      <c r="D75" s="23"/>
-      <c r="E75" s="23"/>
+      <c r="A75" s="25"/>
+      <c r="B75" s="25"/>
+      <c r="C75" s="25"/>
+      <c r="D75" s="25"/>
+      <c r="E75" s="25"/>
     </row>
     <row r="76" spans="1:5">
-      <c r="A76" s="23"/>
-      <c r="B76" s="23"/>
-      <c r="C76" s="23"/>
-      <c r="D76" s="23"/>
-      <c r="E76" s="23"/>
+      <c r="A76" s="25"/>
+      <c r="B76" s="25"/>
+      <c r="C76" s="25"/>
+      <c r="D76" s="25"/>
+      <c r="E76" s="25"/>
     </row>
     <row r="77" spans="1:5">
-      <c r="A77" s="23"/>
-      <c r="B77" s="23"/>
-      <c r="C77" s="23"/>
-      <c r="D77" s="23"/>
-      <c r="E77" s="23"/>
+      <c r="A77" s="25"/>
+      <c r="B77" s="25"/>
+      <c r="C77" s="25"/>
+      <c r="D77" s="25"/>
+      <c r="E77" s="25"/>
     </row>
     <row r="78" spans="1:5">
-      <c r="A78" s="23"/>
-      <c r="B78" s="23"/>
-      <c r="C78" s="23"/>
-      <c r="D78" s="23"/>
-      <c r="E78" s="23"/>
+      <c r="A78" s="25"/>
+      <c r="B78" s="25"/>
+      <c r="C78" s="25"/>
+      <c r="D78" s="25"/>
+      <c r="E78" s="25"/>
     </row>
     <row r="79" spans="1:5">
-      <c r="A79" s="23"/>
-      <c r="B79" s="23"/>
-      <c r="C79" s="23"/>
-      <c r="D79" s="23"/>
-      <c r="E79" s="23"/>
+      <c r="A79" s="25"/>
+      <c r="B79" s="25"/>
+      <c r="C79" s="25"/>
+      <c r="D79" s="25"/>
+      <c r="E79" s="25"/>
     </row>
     <row r="80" spans="1:5">
-      <c r="A80" s="23"/>
-      <c r="B80" s="23"/>
-      <c r="C80" s="23"/>
-      <c r="D80" s="23"/>
-      <c r="E80" s="23"/>
+      <c r="A80" s="25"/>
+      <c r="B80" s="25"/>
+      <c r="C80" s="25"/>
+      <c r="D80" s="25"/>
+      <c r="E80" s="25"/>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="23"/>
-      <c r="B81" s="23"/>
-      <c r="C81" s="23"/>
-      <c r="D81" s="23"/>
-      <c r="E81" s="23"/>
+      <c r="A81" s="25"/>
+      <c r="B81" s="25"/>
+      <c r="C81" s="25"/>
+      <c r="D81" s="25"/>
+      <c r="E81" s="25"/>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="23"/>
-      <c r="B82" s="23"/>
-      <c r="C82" s="23"/>
-      <c r="D82" s="23"/>
-      <c r="E82" s="23"/>
+      <c r="A82" s="25"/>
+      <c r="B82" s="25"/>
+      <c r="C82" s="25"/>
+      <c r="D82" s="25"/>
+      <c r="E82" s="25"/>
     </row>
     <row r="83" spans="1:5">
-      <c r="A83" s="23"/>
-      <c r="B83" s="23"/>
-      <c r="C83" s="23"/>
-      <c r="D83" s="23"/>
-      <c r="E83" s="23"/>
+      <c r="A83" s="25"/>
+      <c r="B83" s="25"/>
+      <c r="C83" s="25"/>
+      <c r="D83" s="25"/>
+      <c r="E83" s="25"/>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="23"/>
-      <c r="B84" s="23"/>
-      <c r="C84" s="23"/>
-      <c r="D84" s="23"/>
-      <c r="E84" s="23"/>
+      <c r="A84" s="25"/>
+      <c r="B84" s="25"/>
+      <c r="C84" s="25"/>
+      <c r="D84" s="25"/>
+      <c r="E84" s="25"/>
     </row>
     <row r="85" spans="1:5">
-      <c r="A85" s="23"/>
-      <c r="B85" s="23"/>
-      <c r="C85" s="23"/>
-      <c r="D85" s="23"/>
-      <c r="E85" s="23"/>
+      <c r="A85" s="25"/>
+      <c r="B85" s="25"/>
+      <c r="C85" s="25"/>
+      <c r="D85" s="25"/>
+      <c r="E85" s="25"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="A86" s="23"/>
-      <c r="B86" s="23"/>
-      <c r="C86" s="23"/>
-      <c r="D86" s="23"/>
-      <c r="E86" s="23"/>
+      <c r="A86" s="25"/>
+      <c r="B86" s="25"/>
+      <c r="C86" s="25"/>
+      <c r="D86" s="25"/>
+      <c r="E86" s="25"/>
     </row>
     <row r="87" spans="1:5">
-      <c r="A87" s="23"/>
-      <c r="B87" s="23"/>
-      <c r="C87" s="23"/>
-      <c r="D87" s="23"/>
-      <c r="E87" s="23"/>
+      <c r="A87" s="25"/>
+      <c r="B87" s="25"/>
+      <c r="C87" s="25"/>
+      <c r="D87" s="25"/>
+      <c r="E87" s="25"/>
     </row>
     <row r="88" spans="1:5">
-      <c r="A88" s="23"/>
-      <c r="B88" s="23"/>
-      <c r="C88" s="23"/>
-      <c r="D88" s="23"/>
-      <c r="E88" s="23"/>
+      <c r="A88" s="25"/>
+      <c r="B88" s="25"/>
+      <c r="C88" s="25"/>
+      <c r="D88" s="25"/>
+      <c r="E88" s="25"/>
     </row>
     <row r="89" spans="1:5">
-      <c r="A89" s="23"/>
-      <c r="B89" s="23"/>
-      <c r="C89" s="23"/>
-      <c r="D89" s="23"/>
-      <c r="E89" s="23"/>
+      <c r="A89" s="25"/>
+      <c r="B89" s="25"/>
+      <c r="C89" s="25"/>
+      <c r="D89" s="25"/>
+      <c r="E89" s="25"/>
     </row>
     <row r="90" spans="1:5">
-      <c r="A90" s="23"/>
-      <c r="B90" s="23"/>
-      <c r="C90" s="23"/>
-      <c r="D90" s="23"/>
-      <c r="E90" s="23"/>
+      <c r="A90" s="25"/>
+      <c r="B90" s="25"/>
+      <c r="C90" s="25"/>
+      <c r="D90" s="25"/>
+      <c r="E90" s="25"/>
     </row>
     <row r="91" spans="1:5">
-      <c r="A91" s="23"/>
-      <c r="B91" s="23"/>
-      <c r="C91" s="23"/>
-      <c r="D91" s="23"/>
-      <c r="E91" s="23"/>
+      <c r="A91" s="25"/>
+      <c r="B91" s="25"/>
+      <c r="C91" s="25"/>
+      <c r="D91" s="25"/>
+      <c r="E91" s="25"/>
     </row>
     <row r="92" spans="1:5">
-      <c r="A92" s="23"/>
-      <c r="B92" s="23"/>
-      <c r="C92" s="23"/>
-      <c r="D92" s="23"/>
-      <c r="E92" s="23"/>
+      <c r="A92" s="25"/>
+      <c r="B92" s="25"/>
+      <c r="C92" s="25"/>
+      <c r="D92" s="25"/>
+      <c r="E92" s="25"/>
     </row>
     <row r="93" spans="1:5">
-      <c r="A93" s="23"/>
-      <c r="B93" s="23"/>
-      <c r="C93" s="23"/>
-      <c r="D93" s="23"/>
-      <c r="E93" s="23"/>
+      <c r="A93" s="25"/>
+      <c r="B93" s="25"/>
+      <c r="C93" s="25"/>
+      <c r="D93" s="25"/>
+      <c r="E93" s="25"/>
     </row>
     <row r="94" spans="1:5">
-      <c r="A94" s="23"/>
-      <c r="B94" s="23"/>
-      <c r="C94" s="23"/>
-      <c r="D94" s="23"/>
-      <c r="E94" s="23"/>
+      <c r="A94" s="25"/>
+      <c r="B94" s="25"/>
+      <c r="C94" s="25"/>
+      <c r="D94" s="25"/>
+      <c r="E94" s="25"/>
     </row>
     <row r="95" spans="1:5">
-      <c r="A95" s="23"/>
-      <c r="B95" s="23"/>
-      <c r="C95" s="23"/>
-      <c r="D95" s="23"/>
-      <c r="E95" s="23"/>
+      <c r="A95" s="25"/>
+      <c r="B95" s="25"/>
+      <c r="C95" s="25"/>
+      <c r="D95" s="25"/>
+      <c r="E95" s="25"/>
     </row>
     <row r="96" spans="1:5">
-      <c r="A96" s="23"/>
-      <c r="B96" s="23"/>
-      <c r="C96" s="23"/>
-      <c r="D96" s="23"/>
-      <c r="E96" s="23"/>
+      <c r="A96" s="25"/>
+      <c r="B96" s="25"/>
+      <c r="C96" s="25"/>
+      <c r="D96" s="25"/>
+      <c r="E96" s="25"/>
     </row>
     <row r="97" spans="1:5">
-      <c r="A97" s="23"/>
-      <c r="B97" s="23"/>
-      <c r="C97" s="23"/>
-      <c r="D97" s="23"/>
-      <c r="E97" s="23"/>
+      <c r="A97" s="25"/>
+      <c r="B97" s="25"/>
+      <c r="C97" s="25"/>
+      <c r="D97" s="25"/>
+      <c r="E97" s="25"/>
     </row>
     <row r="98" spans="1:5">
-      <c r="A98" s="23"/>
-      <c r="B98" s="23"/>
-      <c r="C98" s="23"/>
-      <c r="D98" s="23"/>
-      <c r="E98" s="23"/>
+      <c r="A98" s="25"/>
+      <c r="B98" s="25"/>
+      <c r="C98" s="25"/>
+      <c r="D98" s="25"/>
+      <c r="E98" s="25"/>
     </row>
     <row r="99" spans="1:5">
-      <c r="A99" s="23"/>
-      <c r="B99" s="23"/>
-      <c r="C99" s="23"/>
-      <c r="D99" s="23"/>
-      <c r="E99" s="23"/>
+      <c r="A99" s="25"/>
+      <c r="B99" s="25"/>
+      <c r="C99" s="25"/>
+      <c r="D99" s="25"/>
+      <c r="E99" s="25"/>
     </row>
     <row r="100" spans="1:5">
-      <c r="A100" s="23"/>
-      <c r="B100" s="23"/>
-      <c r="C100" s="23"/>
-      <c r="D100" s="23"/>
-      <c r="E100" s="23"/>
+      <c r="A100" s="25"/>
+      <c r="B100" s="25"/>
+      <c r="C100" s="25"/>
+      <c r="D100" s="25"/>
+      <c r="E100" s="25"/>
     </row>
     <row r="101" spans="1:5">
-      <c r="A101" s="23"/>
-      <c r="B101" s="23"/>
-      <c r="C101" s="23"/>
-      <c r="D101" s="23"/>
-      <c r="E101" s="23"/>
+      <c r="A101" s="25"/>
+      <c r="B101" s="25"/>
+      <c r="C101" s="25"/>
+      <c r="D101" s="25"/>
+      <c r="E101" s="25"/>
     </row>
     <row r="102" spans="1:5">
-      <c r="A102" s="23"/>
-      <c r="B102" s="23"/>
-      <c r="C102" s="23"/>
-      <c r="D102" s="23"/>
-      <c r="E102" s="23"/>
+      <c r="A102" s="25"/>
+      <c r="B102" s="25"/>
+      <c r="C102" s="25"/>
+      <c r="D102" s="25"/>
+      <c r="E102" s="25"/>
     </row>
     <row r="103" spans="1:5">
-      <c r="A103" s="23"/>
-      <c r="B103" s="23"/>
-      <c r="C103" s="23"/>
-      <c r="D103" s="23"/>
-      <c r="E103" s="23"/>
+      <c r="A103" s="25"/>
+      <c r="B103" s="25"/>
+      <c r="C103" s="25"/>
+      <c r="D103" s="25"/>
+      <c r="E103" s="25"/>
     </row>
     <row r="104" spans="1:5">
-      <c r="A104" s="23"/>
-      <c r="B104" s="23"/>
-      <c r="C104" s="23"/>
-      <c r="D104" s="23"/>
-      <c r="E104" s="23"/>
+      <c r="A104" s="25"/>
+      <c r="B104" s="25"/>
+      <c r="C104" s="25"/>
+      <c r="D104" s="25"/>
+      <c r="E104" s="25"/>
     </row>
     <row r="105" spans="1:5">
-      <c r="A105" s="23"/>
-      <c r="B105" s="23"/>
-      <c r="C105" s="23"/>
-      <c r="D105" s="23"/>
-      <c r="E105" s="23"/>
+      <c r="A105" s="25"/>
+      <c r="B105" s="25"/>
+      <c r="C105" s="25"/>
+      <c r="D105" s="25"/>
+      <c r="E105" s="25"/>
     </row>
     <row r="106" spans="1:5">
-      <c r="A106" s="23"/>
-      <c r="B106" s="23"/>
-      <c r="C106" s="23"/>
-      <c r="D106" s="23"/>
-      <c r="E106" s="23"/>
+      <c r="A106" s="25"/>
+      <c r="B106" s="25"/>
+      <c r="C106" s="25"/>
+      <c r="D106" s="25"/>
+      <c r="E106" s="25"/>
     </row>
     <row r="107" spans="1:5">
-      <c r="A107" s="23"/>
-      <c r="B107" s="23"/>
-      <c r="C107" s="23"/>
-      <c r="D107" s="23"/>
-      <c r="E107" s="23"/>
+      <c r="A107" s="25"/>
+      <c r="B107" s="25"/>
+      <c r="C107" s="25"/>
+      <c r="D107" s="25"/>
+      <c r="E107" s="25"/>
     </row>
     <row r="108" spans="1:5">
-      <c r="A108" s="23"/>
-      <c r="B108" s="23"/>
-      <c r="C108" s="23"/>
-      <c r="D108" s="23"/>
-      <c r="E108" s="23"/>
+      <c r="A108" s="25"/>
+      <c r="B108" s="25"/>
+      <c r="C108" s="25"/>
+      <c r="D108" s="25"/>
+      <c r="E108" s="25"/>
     </row>
     <row r="109" spans="1:5">
-      <c r="A109" s="23"/>
-      <c r="B109" s="23"/>
-      <c r="C109" s="23"/>
-      <c r="D109" s="23"/>
-      <c r="E109" s="23"/>
+      <c r="A109" s="25"/>
+      <c r="B109" s="25"/>
+      <c r="C109" s="25"/>
+      <c r="D109" s="25"/>
+      <c r="E109" s="25"/>
     </row>
     <row r="110" spans="1:5">
-      <c r="A110" s="23"/>
-      <c r="B110" s="23"/>
-      <c r="C110" s="23"/>
-      <c r="D110" s="23"/>
-      <c r="E110" s="23"/>
+      <c r="A110" s="25"/>
+      <c r="B110" s="25"/>
+      <c r="C110" s="25"/>
+      <c r="D110" s="25"/>
+      <c r="E110" s="25"/>
     </row>
     <row r="111" spans="1:5">
-      <c r="A111" s="23"/>
-      <c r="B111" s="23"/>
-      <c r="C111" s="23"/>
-      <c r="D111" s="23"/>
-      <c r="E111" s="23"/>
+      <c r="A111" s="25"/>
+      <c r="B111" s="25"/>
+      <c r="C111" s="25"/>
+      <c r="D111" s="25"/>
+      <c r="E111" s="25"/>
     </row>
     <row r="112" spans="1:5">
-      <c r="A112" s="23"/>
-      <c r="B112" s="23"/>
-      <c r="C112" s="23"/>
-      <c r="D112" s="23"/>
-      <c r="E112" s="23"/>
+      <c r="A112" s="25"/>
+      <c r="B112" s="25"/>
+      <c r="C112" s="25"/>
+      <c r="D112" s="25"/>
+      <c r="E112" s="25"/>
     </row>
     <row r="113" spans="1:5">
-      <c r="A113" s="23"/>
-      <c r="B113" s="23"/>
-      <c r="C113" s="23"/>
-      <c r="D113" s="23"/>
-      <c r="E113" s="23"/>
+      <c r="A113" s="25"/>
+      <c r="B113" s="25"/>
+      <c r="C113" s="25"/>
+      <c r="D113" s="25"/>
+      <c r="E113" s="25"/>
     </row>
     <row r="114" spans="1:5">
-      <c r="A114" s="23"/>
-      <c r="B114" s="23"/>
-      <c r="C114" s="23"/>
-      <c r="D114" s="23"/>
-      <c r="E114" s="23"/>
+      <c r="A114" s="25"/>
+      <c r="B114" s="25"/>
+      <c r="C114" s="25"/>
+      <c r="D114" s="25"/>
+      <c r="E114" s="25"/>
     </row>
     <row r="115" spans="1:5">
-      <c r="A115" s="23"/>
-      <c r="B115" s="23"/>
-      <c r="C115" s="23"/>
-      <c r="D115" s="23"/>
-      <c r="E115" s="23"/>
+      <c r="A115" s="25"/>
+      <c r="B115" s="25"/>
+      <c r="C115" s="25"/>
+      <c r="D115" s="25"/>
+      <c r="E115" s="25"/>
     </row>
     <row r="116" spans="1:5">
-      <c r="A116" s="23"/>
-      <c r="B116" s="23"/>
-      <c r="C116" s="23"/>
-      <c r="D116" s="23"/>
-      <c r="E116" s="23"/>
+      <c r="A116" s="25"/>
+      <c r="B116" s="25"/>
+      <c r="C116" s="25"/>
+      <c r="D116" s="25"/>
+      <c r="E116" s="25"/>
     </row>
     <row r="117" spans="1:5">
-      <c r="A117" s="23"/>
-      <c r="B117" s="23"/>
-      <c r="C117" s="23"/>
-      <c r="D117" s="23"/>
-      <c r="E117" s="23"/>
+      <c r="A117" s="25"/>
+      <c r="B117" s="25"/>
+      <c r="C117" s="25"/>
+      <c r="D117" s="25"/>
+      <c r="E117" s="25"/>
     </row>
     <row r="118" spans="1:5">
-      <c r="A118" s="23"/>
-      <c r="B118" s="23"/>
-      <c r="C118" s="23"/>
-      <c r="D118" s="23"/>
-      <c r="E118" s="23"/>
+      <c r="A118" s="25"/>
+      <c r="B118" s="25"/>
+      <c r="C118" s="25"/>
+      <c r="D118" s="25"/>
+      <c r="E118" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -9655,312 +9769,312 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="50" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="2" ht="409.5" spans="1:3">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="32" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="3" ht="86.4" spans="1:3">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="27"/>
+      <c r="C3" s="29"/>
     </row>
     <row r="4" ht="57.6" spans="1:3">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="27"/>
+      <c r="C4" s="29"/>
     </row>
     <row r="5" ht="72" spans="1:3">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="27"/>
+      <c r="C5" s="29"/>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="27"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
+      <c r="A6" s="29"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
     </row>
     <row r="7" ht="144" spans="1:3">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="27"/>
+      <c r="C7" s="29"/>
     </row>
     <row r="8" ht="158.4" spans="1:3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="27"/>
+      <c r="C8" s="29"/>
     </row>
     <row r="9" ht="345.6" spans="1:3">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="C9" s="27"/>
+      <c r="C9" s="29"/>
     </row>
     <row r="10" ht="403.2" spans="1:3">
-      <c r="A10" s="27"/>
-      <c r="B10" s="30" t="s">
+      <c r="A10" s="29"/>
+      <c r="B10" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="C10" s="27"/>
+      <c r="C10" s="29"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="27"/>
-      <c r="C11" s="27"/>
+      <c r="A11" s="29"/>
+      <c r="C11" s="29"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="27"/>
-      <c r="C12" s="27"/>
+      <c r="A12" s="29"/>
+      <c r="C12" s="29"/>
     </row>
     <row r="13" ht="409.5" spans="1:3">
-      <c r="A13" s="27"/>
-      <c r="B13" s="30" t="s">
+      <c r="A13" s="29"/>
+      <c r="B13" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="27"/>
+      <c r="C13" s="29"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="27"/>
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
+      <c r="A14" s="29"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="27"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
+      <c r="A15" s="29"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="27"/>
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
+      <c r="A16" s="29"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="27"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
+      <c r="A17" s="29"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="27"/>
-      <c r="B18" s="27"/>
-      <c r="C18" s="27"/>
+      <c r="A18" s="29"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="27"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
+      <c r="A19" s="29"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="27"/>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
+      <c r="A20" s="29"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="27"/>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
+      <c r="A21" s="29"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="27"/>
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
+      <c r="A22" s="29"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="27"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
+      <c r="A23" s="29"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="27"/>
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
+      <c r="A24" s="29"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="27"/>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
+      <c r="A25" s="29"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="27"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
+      <c r="A26" s="29"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="27"/>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
+      <c r="A27" s="29"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="27"/>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
+      <c r="A28" s="29"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="27"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
+      <c r="A29" s="29"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="27"/>
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
+      <c r="A30" s="29"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="27"/>
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
+      <c r="A31" s="29"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="27"/>
-      <c r="B32" s="27"/>
-      <c r="C32" s="27"/>
+      <c r="A32" s="29"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="27"/>
-      <c r="B33" s="27"/>
-      <c r="C33" s="27"/>
+      <c r="A33" s="29"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="27"/>
-      <c r="B34" s="27"/>
-      <c r="C34" s="27"/>
+      <c r="A34" s="29"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="27"/>
-      <c r="B35" s="27"/>
-      <c r="C35" s="27"/>
+      <c r="A35" s="29"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="27"/>
-      <c r="B36" s="27"/>
-      <c r="C36" s="27"/>
+      <c r="A36" s="29"/>
+      <c r="B36" s="29"/>
+      <c r="C36" s="29"/>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="27"/>
-      <c r="B37" s="27"/>
-      <c r="C37" s="27"/>
+      <c r="A37" s="29"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="27"/>
-      <c r="B38" s="27"/>
-      <c r="C38" s="27"/>
+      <c r="A38" s="29"/>
+      <c r="B38" s="29"/>
+      <c r="C38" s="29"/>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="27"/>
-      <c r="B39" s="27"/>
-      <c r="C39" s="27"/>
+      <c r="A39" s="29"/>
+      <c r="B39" s="29"/>
+      <c r="C39" s="29"/>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="27"/>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
+      <c r="A40" s="29"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="27"/>
-      <c r="B41" s="27"/>
-      <c r="C41" s="27"/>
+      <c r="A41" s="29"/>
+      <c r="B41" s="29"/>
+      <c r="C41" s="29"/>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="27"/>
-      <c r="B42" s="27"/>
-      <c r="C42" s="27"/>
+      <c r="A42" s="29"/>
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="27"/>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
+      <c r="A43" s="29"/>
+      <c r="B43" s="29"/>
+      <c r="C43" s="29"/>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="27"/>
-      <c r="B44" s="27"/>
-      <c r="C44" s="27"/>
+      <c r="A44" s="29"/>
+      <c r="B44" s="29"/>
+      <c r="C44" s="29"/>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="27"/>
-      <c r="B45" s="27"/>
-      <c r="C45" s="27"/>
+      <c r="A45" s="29"/>
+      <c r="B45" s="29"/>
+      <c r="C45" s="29"/>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="27"/>
-      <c r="B46" s="27"/>
-      <c r="C46" s="27"/>
+      <c r="A46" s="29"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="27"/>
-      <c r="B47" s="27"/>
-      <c r="C47" s="27"/>
+      <c r="A47" s="29"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="29"/>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="27"/>
-      <c r="B48" s="27"/>
-      <c r="C48" s="27"/>
+      <c r="A48" s="29"/>
+      <c r="B48" s="29"/>
+      <c r="C48" s="29"/>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="27"/>
-      <c r="B49" s="27"/>
-      <c r="C49" s="27"/>
+      <c r="A49" s="29"/>
+      <c r="B49" s="29"/>
+      <c r="C49" s="29"/>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="27"/>
-      <c r="B50" s="27"/>
-      <c r="C50" s="27"/>
+      <c r="A50" s="29"/>
+      <c r="B50" s="29"/>
+      <c r="C50" s="29"/>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="27"/>
-      <c r="B51" s="27"/>
-      <c r="C51" s="27"/>
+      <c r="A51" s="29"/>
+      <c r="B51" s="29"/>
+      <c r="C51" s="29"/>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="27"/>
-      <c r="B52" s="27"/>
-      <c r="C52" s="27"/>
+      <c r="A52" s="29"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="27"/>
-      <c r="B53" s="27"/>
-      <c r="C53" s="27"/>
+      <c r="A53" s="29"/>
+      <c r="B53" s="29"/>
+      <c r="C53" s="29"/>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="27"/>
-      <c r="B54" s="27"/>
-      <c r="C54" s="27"/>
+      <c r="A54" s="29"/>
+      <c r="B54" s="29"/>
+      <c r="C54" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9979,52 +10093,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="27"/>
+      <c r="B1" s="29"/>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="41">
+      <c r="A2" s="45">
         <v>45962</v>
       </c>
-      <c r="B2" s="27"/>
+      <c r="B2" s="29"/>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="46" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="46" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="46" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="43">
+      <c r="A6" s="47">
         <v>45969</v>
       </c>
-      <c r="B6" s="27"/>
-    </row>
-    <row r="7" s="40" customFormat="1" ht="57.6" spans="1:2">
-      <c r="A7" s="44" t="s">
+      <c r="B6" s="29"/>
+    </row>
+    <row r="7" s="44" customFormat="1" ht="57.6" spans="1:2">
+      <c r="A7" s="48" t="s">
         <v>87</v>
       </c>
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="49" t="s">
         <v>88</v>
       </c>
     </row>
@@ -10045,752 +10159,775 @@
   <dimension ref="A1:D87"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="38.4444444444444" style="27" customWidth="1"/>
-    <col min="2" max="2" width="88.4444444444444" style="27" customWidth="1"/>
-    <col min="3" max="3" width="45.2222222222222" style="27" customWidth="1"/>
-    <col min="4" max="4" width="9.55555555555556" style="27" customWidth="1"/>
-    <col min="5" max="16384" width="8.88888888888889" style="27"/>
+    <col min="1" max="1" width="38.4444444444444" style="29" customWidth="1"/>
+    <col min="2" max="2" width="88.4444444444444" style="29" customWidth="1"/>
+    <col min="3" max="3" width="45.2222222222222" style="29" customWidth="1"/>
+    <col min="4" max="4" width="9.55555555555556" style="29" customWidth="1"/>
+    <col min="5" max="16384" width="8.88888888888889" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="31" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="2" ht="201.6" spans="1:3">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="32" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="3" ht="100.8" spans="1:3">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="32" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="4" ht="72" spans="1:2">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="27" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="5" ht="129.6" spans="1:3">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="32" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="6" ht="129.6" spans="1:4">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="32" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="7" ht="158.4" spans="1:3">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="C7" s="32" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="8" ht="86.4" spans="1:2">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="27" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="9" ht="129.6" spans="1:2">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="27" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="10" ht="129.6" spans="1:2">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="27" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="11" ht="158.4" spans="1:2">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="27" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="12" ht="115.2" spans="1:3">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C12" s="32" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="13" ht="158.4" spans="1:3">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="32" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="14" ht="158.4" spans="1:3">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="C14" s="30"/>
+      <c r="C14" s="32"/>
     </row>
     <row r="15" ht="43.2" spans="1:3">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="C15" s="30"/>
+      <c r="C15" s="32"/>
     </row>
     <row r="16" ht="129.6" spans="1:3">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="27" t="s">
         <v>128</v>
       </c>
-      <c r="C16" s="30" t="s">
+      <c r="C16" s="32" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="17" ht="172.8" spans="1:3">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="27" t="s">
         <v>130</v>
       </c>
-      <c r="C17" s="30" t="s">
+      <c r="C17" s="32" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="18" ht="409.5" spans="1:4">
-      <c r="A18" s="32" t="s">
+      <c r="A18" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="33" t="s">
+      <c r="B18" s="35" t="s">
         <v>132</v>
       </c>
-      <c r="C18" s="34" t="s">
+      <c r="C18" s="36" t="s">
         <v>133</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="D18" s="32" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="19" ht="409.5" spans="1:4">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="27" t="s">
         <v>135</v>
       </c>
-      <c r="C19" s="30" t="s">
+      <c r="C19" s="32" t="s">
         <v>136</v>
       </c>
-      <c r="D19" s="30" t="s">
+      <c r="D19" s="32" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="20" ht="409.5" spans="1:4">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="25" t="s">
         <v>138</v>
       </c>
-      <c r="B20" s="25" t="s">
+      <c r="B20" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="C20" s="32" t="s">
         <v>140</v>
       </c>
-      <c r="D20" s="30" t="s">
+      <c r="D20" s="32" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="21" ht="174" customHeight="1" spans="1:2">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="B21" s="25" t="s">
+      <c r="B21" s="27" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="22" ht="187.2" spans="1:2">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="B22" s="25" t="s">
+      <c r="B22" s="27" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="23" ht="244.8" spans="1:2">
-      <c r="A23" s="23" t="s">
+      <c r="A23" s="25" t="s">
         <v>146</v>
       </c>
-      <c r="B23" s="25" t="s">
+      <c r="B23" s="27" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="24" ht="158.4" spans="1:2">
-      <c r="A24" s="23" t="s">
+      <c r="A24" s="25" t="s">
         <v>148</v>
       </c>
-      <c r="B24" s="25" t="s">
+      <c r="B24" s="27" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="25" ht="100.8" spans="1:2">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="25" t="s">
         <v>150</v>
       </c>
-      <c r="B25" s="25" t="s">
+      <c r="B25" s="27" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="26" ht="409" customHeight="1" spans="1:3">
-      <c r="A26" s="23" t="s">
+      <c r="A26" s="25" t="s">
         <v>152</v>
       </c>
-      <c r="B26" s="25" t="s">
+      <c r="B26" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="C26" s="30" t="s">
+      <c r="C26" s="32" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="27" ht="57.6" spans="1:2">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="B27" s="25" t="s">
+      <c r="B27" s="27" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="28" ht="409.5" spans="1:4">
-      <c r="A28" s="23" t="s">
+      <c r="A28" s="25" t="s">
         <v>157</v>
       </c>
-      <c r="B28" s="25" t="s">
+      <c r="B28" s="27" t="s">
         <v>158</v>
       </c>
-      <c r="C28" s="30" t="s">
+      <c r="C28" s="32" t="s">
         <v>159</v>
       </c>
-      <c r="D28" s="30" t="s">
+      <c r="D28" s="32" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="29" ht="244.8" spans="1:3">
-      <c r="A29" s="23" t="s">
+      <c r="A29" s="25" t="s">
         <v>161</v>
       </c>
-      <c r="B29" s="25" t="s">
+      <c r="B29" s="27" t="s">
         <v>162</v>
       </c>
-      <c r="C29" s="30" t="s">
+      <c r="C29" s="32" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="30" ht="244.8" spans="1:2">
-      <c r="A30" s="23" t="s">
+      <c r="A30" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="B30" s="25" t="s">
+      <c r="B30" s="27" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="31" ht="187.2" spans="1:2">
-      <c r="A31" s="35" t="s">
+      <c r="A31" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="B31" s="25" t="s">
+      <c r="B31" s="27" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="32" ht="345.6" spans="1:2">
-      <c r="A32" s="36"/>
-      <c r="B32" s="37" t="s">
+      <c r="A32" s="38"/>
+      <c r="B32" s="39" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="33" ht="259.2" spans="1:2">
-      <c r="A33" s="38" t="s">
+      <c r="A33" s="40" t="s">
         <v>169</v>
       </c>
-      <c r="B33" s="37" t="s">
+      <c r="B33" s="39" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="34" ht="100.8" spans="1:2">
-      <c r="A34" s="23" t="s">
+      <c r="A34" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B34" s="27" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="35" ht="72" spans="1:2">
-      <c r="A35" s="23" t="s">
+      <c r="A35" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="B35" s="25" t="s">
+      <c r="B35" s="27" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="36" ht="409" customHeight="1" spans="1:3">
-      <c r="A36" s="23" t="s">
+      <c r="A36" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="B36" s="25" t="s">
+      <c r="B36" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="C36" s="39" t="s">
+      <c r="C36" s="41" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="37" ht="187.2" spans="1:3">
-      <c r="A37" s="23" t="s">
+      <c r="A37" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="B37" s="25" t="s">
+      <c r="B37" s="27" t="s">
         <v>179</v>
       </c>
-      <c r="C37" s="39"/>
+      <c r="C37" s="41"/>
     </row>
     <row r="38" ht="288" spans="1:3">
-      <c r="A38" s="23" t="s">
+      <c r="A38" s="25" t="s">
         <v>180</v>
       </c>
-      <c r="B38" s="25" t="s">
+      <c r="B38" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="C38" s="39"/>
+      <c r="C38" s="41"/>
     </row>
     <row r="39" ht="216" spans="1:2">
-      <c r="A39" s="23" t="s">
+      <c r="A39" s="25" t="s">
         <v>182</v>
       </c>
-      <c r="B39" s="25" t="s">
+      <c r="B39" s="27" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="40" ht="100.8" spans="1:2">
-      <c r="A40" s="25" t="s">
+      <c r="A40" s="27" t="s">
         <v>184</v>
       </c>
-      <c r="B40" s="25" t="s">
+      <c r="B40" s="27" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="23" t="s">
+      <c r="A41" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="B41" s="23"/>
+      <c r="B41" s="25"/>
     </row>
     <row r="42" ht="144" spans="1:3">
-      <c r="A42" s="25" t="s">
+      <c r="A42" s="27" t="s">
         <v>186</v>
       </c>
-      <c r="B42" s="25" t="s">
+      <c r="B42" s="27" t="s">
         <v>187</v>
       </c>
-      <c r="C42" s="30" t="s">
+      <c r="C42" s="32" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="43" ht="57.6" spans="1:2">
-      <c r="A43" s="25" t="s">
+      <c r="A43" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="B43" s="25" t="s">
+      <c r="B43" s="27" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="44" ht="273.6" spans="1:2">
-      <c r="A44" s="25" t="s">
+      <c r="A44" s="27" t="s">
         <v>191</v>
       </c>
-      <c r="B44" s="25" t="s">
+      <c r="B44" s="27" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="45" ht="172.8" spans="1:3">
-      <c r="A45" s="23" t="s">
+      <c r="A45" s="25" t="s">
         <v>193</v>
       </c>
-      <c r="B45" s="25" t="s">
+      <c r="B45" s="27" t="s">
         <v>194</v>
       </c>
-      <c r="C45" s="30" t="s">
+      <c r="C45" s="32" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="46" ht="43.2" spans="1:2">
-      <c r="A46" s="23" t="s">
+      <c r="A46" s="25" t="s">
         <v>196</v>
       </c>
-      <c r="B46" s="25" t="s">
+      <c r="B46" s="27" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="47" ht="144" spans="1:2">
-      <c r="A47" s="23" t="s">
+      <c r="A47" s="25" t="s">
         <v>198</v>
       </c>
-      <c r="B47" s="25" t="s">
+      <c r="B47" s="27" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="48" ht="72" spans="1:2">
-      <c r="A48" s="23" t="s">
+      <c r="A48" s="25" t="s">
         <v>200</v>
       </c>
-      <c r="B48" s="25" t="s">
+      <c r="B48" s="27" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="49" ht="57.6" spans="1:2">
-      <c r="A49" s="23" t="s">
+      <c r="A49" s="25" t="s">
         <v>202</v>
       </c>
-      <c r="B49" s="25" t="s">
+      <c r="B49" s="27" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="50" ht="28.8" spans="1:2">
-      <c r="A50" s="23" t="s">
+      <c r="A50" s="25" t="s">
         <v>204</v>
       </c>
-      <c r="B50" s="25" t="s">
+      <c r="B50" s="27" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="51" ht="230.4" spans="1:2">
-      <c r="A51" s="23" t="s">
+      <c r="A51" s="25" t="s">
         <v>206</v>
       </c>
-      <c r="B51" s="25" t="s">
+      <c r="B51" s="27" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="52" ht="158.4" spans="1:2">
-      <c r="A52" s="23" t="s">
+      <c r="A52" s="25" t="s">
         <v>208</v>
       </c>
-      <c r="B52" s="25" t="s">
+      <c r="B52" s="27" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="53" ht="129.6" spans="1:2">
-      <c r="A53" s="23" t="s">
+      <c r="A53" s="25" t="s">
         <v>210</v>
       </c>
-      <c r="B53" s="25" t="s">
+      <c r="B53" s="27" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="54" ht="409.5" spans="1:2">
-      <c r="A54" s="23" t="s">
+      <c r="A54" s="25" t="s">
         <v>212</v>
       </c>
-      <c r="B54" s="25" t="s">
+      <c r="B54" s="27" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="55" ht="201.6" spans="1:3">
-      <c r="A55" s="23" t="s">
+      <c r="A55" s="25" t="s">
         <v>214</v>
       </c>
-      <c r="B55" s="25" t="s">
+      <c r="B55" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="C55" s="30" t="s">
+      <c r="C55" s="32" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="56" ht="409.5" spans="1:2">
-      <c r="A56" s="23"/>
-      <c r="B56" s="30" t="s">
+      <c r="A56" s="25"/>
+      <c r="B56" s="32" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="57" ht="409.5" spans="1:2">
-      <c r="A57" s="23"/>
-      <c r="B57" s="30" t="s">
+      <c r="A57" s="25"/>
+      <c r="B57" s="32" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="58" ht="115.2" spans="1:2">
-      <c r="A58" s="27" t="s">
+      <c r="A58" s="29" t="s">
         <v>219</v>
       </c>
-      <c r="B58" s="25" t="s">
+      <c r="B58" s="27" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="59" ht="100.8" spans="1:2">
-      <c r="A59" s="23" t="s">
+      <c r="A59" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="B59" s="25" t="s">
+      <c r="B59" s="27" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="23" t="s">
+      <c r="A60" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="B60" s="23" t="s">
+      <c r="B60" s="25" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="61" ht="86.4" spans="1:2">
-      <c r="A61" s="23" t="s">
+      <c r="A61" s="25" t="s">
         <v>225</v>
       </c>
-      <c r="B61" s="25" t="s">
+      <c r="B61" s="27" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="62" ht="144" spans="1:2">
-      <c r="A62" s="23" t="s">
+      <c r="A62" s="25" t="s">
         <v>227</v>
       </c>
-      <c r="B62" s="25" t="s">
+      <c r="B62" s="27" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="63" ht="43.2" spans="1:2">
-      <c r="A63" s="23" t="s">
+      <c r="A63" s="25" t="s">
         <v>229</v>
       </c>
-      <c r="B63" s="25" t="s">
+      <c r="B63" s="27" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="64" ht="28.8" spans="1:2">
-      <c r="A64" s="23" t="s">
+      <c r="A64" s="25" t="s">
         <v>231</v>
       </c>
-      <c r="B64" s="25" t="s">
+      <c r="B64" s="27" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="65" ht="86.4" spans="1:2">
-      <c r="A65" s="27" t="s">
+      <c r="A65" s="29" t="s">
         <v>233</v>
       </c>
-      <c r="B65" s="25" t="s">
+      <c r="B65" s="27" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="66" ht="86.4" spans="1:2">
-      <c r="A66" s="23" t="s">
+      <c r="A66" s="25" t="s">
         <v>235</v>
       </c>
-      <c r="B66" s="25" t="s">
+      <c r="B66" s="27" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="67" ht="28.8" spans="1:2">
-      <c r="A67" s="27" t="s">
+      <c r="A67" s="29" t="s">
         <v>237</v>
       </c>
-      <c r="B67" s="30" t="s">
+      <c r="B67" s="32" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="68" ht="43.2" spans="1:2">
-      <c r="A68" s="23" t="s">
+      <c r="A68" s="25" t="s">
         <v>239</v>
       </c>
-      <c r="B68" s="25" t="s">
+      <c r="B68" s="27" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="69" ht="28.8" spans="1:2">
-      <c r="A69" s="27" t="s">
+      <c r="A69" s="29" t="s">
         <v>241</v>
       </c>
-      <c r="B69" s="25" t="s">
+      <c r="B69" s="27" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="70" ht="28.8" spans="1:2">
-      <c r="A70" s="23" t="s">
+      <c r="A70" s="25" t="s">
         <v>243</v>
       </c>
-      <c r="B70" s="25" t="s">
+      <c r="B70" s="27" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="71" ht="100.8" spans="1:2">
-      <c r="A71" s="25" t="s">
+      <c r="A71" s="27" t="s">
         <v>245</v>
       </c>
-      <c r="B71" s="25" t="s">
+      <c r="B71" s="27" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="72" ht="158.4" spans="1:2">
-      <c r="A72" s="23" t="s">
+      <c r="A72" s="25" t="s">
         <v>247</v>
       </c>
-      <c r="B72" s="25" t="s">
+      <c r="B72" s="27" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="73" ht="86.4" spans="1:2">
-      <c r="A73" s="23" t="s">
+      <c r="A73" s="25" t="s">
         <v>249</v>
       </c>
-      <c r="B73" s="25" t="s">
+      <c r="B73" s="27" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="74" ht="409.5" spans="1:2">
-      <c r="A74" s="23" t="s">
+      <c r="A74" s="25" t="s">
         <v>251</v>
       </c>
-      <c r="B74" s="25" t="s">
+      <c r="B74" s="27" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="75" ht="360" spans="1:3">
-      <c r="A75" s="23" t="s">
+      <c r="A75" s="25" t="s">
         <v>253</v>
       </c>
-      <c r="B75" s="25" t="s">
+      <c r="B75" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="C75" s="30" t="s">
+      <c r="C75" s="32" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="76" ht="172.8" spans="1:3">
-      <c r="A76" s="23" t="s">
+      <c r="A76" s="25" t="s">
         <v>256</v>
       </c>
-      <c r="B76" s="25" t="s">
+      <c r="B76" s="27" t="s">
         <v>257</v>
       </c>
-      <c r="C76" s="30" t="s">
+      <c r="C76" s="32" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="77" ht="409.5" spans="1:3">
-      <c r="A77" s="23" t="s">
+      <c r="A77" s="25" t="s">
         <v>259</v>
       </c>
-      <c r="B77" s="25" t="s">
+      <c r="B77" s="27" t="s">
         <v>260</v>
       </c>
-      <c r="C77" s="30" t="s">
+      <c r="C77" s="32" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="78" ht="409.5" spans="1:2">
-      <c r="A78" s="23" t="s">
+      <c r="A78" s="25" t="s">
         <v>262</v>
       </c>
-      <c r="B78" s="25" t="s">
+      <c r="B78" s="27" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
-      <c r="A79" s="23"/>
-      <c r="B79" s="23"/>
-    </row>
-    <row r="80" spans="1:2">
-      <c r="A80" s="23"/>
-      <c r="B80" s="23"/>
-    </row>
-    <row r="81" spans="1:2">
-      <c r="A81" s="23"/>
-      <c r="B81" s="23"/>
-    </row>
-    <row r="82" spans="1:2">
-      <c r="A82" s="23"/>
-      <c r="B82" s="23"/>
-    </row>
-    <row r="83" spans="1:2">
-      <c r="A83" s="23"/>
-      <c r="B83" s="23"/>
+    <row r="79" ht="302.4" spans="1:2">
+      <c r="A79" s="25" t="s">
+        <v>264</v>
+      </c>
+      <c r="B79" s="27" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="80" ht="187.2" spans="1:3">
+      <c r="A80" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="B80" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="C80" s="42" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="81" ht="158.4" spans="1:2">
+      <c r="A81" s="43" t="s">
+        <v>269</v>
+      </c>
+      <c r="B81" s="27" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="82" ht="115.2" spans="1:2">
+      <c r="A82" s="43" t="s">
+        <v>271</v>
+      </c>
+      <c r="B82" s="27" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="83" ht="86.4" spans="1:2">
+      <c r="A83" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="B83" s="27" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="23"/>
-      <c r="B84" s="23"/>
+      <c r="A84" s="25"/>
+      <c r="B84" s="25"/>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="23"/>
-      <c r="B85" s="23"/>
+      <c r="A85" s="25"/>
+      <c r="B85" s="25"/>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="23"/>
-      <c r="B86" s="23"/>
+      <c r="A86" s="25"/>
+      <c r="B86" s="25"/>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="23"/>
-      <c r="B87" s="23"/>
+      <c r="A87" s="25"/>
+      <c r="B87" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -10813,82 +10950,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="25" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="25" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="26" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="27" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="27" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="25" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="27" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="27" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="25" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="23" t="s">
-        <v>264</v>
+      <c r="A10" s="25" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="27" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="25" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="25" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="25" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="25" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="25" t="s">
         <v>36</v>
       </c>
     </row>
@@ -10897,7 +11034,7 @@
         <v>38</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -10907,76 +11044,76 @@
     </row>
     <row r="19" ht="72" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
     </row>
     <row r="21" ht="100.8" spans="1:2">
       <c r="A21" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="26" t="s">
-        <v>270</v>
+      <c r="A22" s="28" t="s">
+        <v>281</v>
       </c>
       <c r="B22" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
     </row>
     <row r="23" ht="57.6" spans="1:2">
       <c r="A23" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" ht="72" spans="1:2">
       <c r="A24" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" ht="86.4" spans="1:2">
       <c r="A25" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" ht="43.2" spans="1:2">
       <c r="A26" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" ht="28.8" spans="1:2">
       <c r="A27" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" ht="43.2" spans="1:2">
       <c r="A28" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -10988,22 +11125,35 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:A5"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="4"/>
+  <dimension ref="A2:A9"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="88.2222222222222" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="22" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>286</v>
+        <v>297</v>
+      </c>
+    </row>
+    <row r="8" ht="15" spans="1:1">
+      <c r="A8" s="23" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="9" ht="120" customHeight="1" spans="1:1">
+      <c r="A9" s="24" t="s">
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -11027,201 +11177,201 @@
   <sheetData>
     <row r="1" spans="2:3">
       <c r="B1" s="16" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
     </row>
     <row r="2" spans="2:3">
       <c r="B2" s="17" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" spans="2:3">
       <c r="B3" s="17" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" s="17" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="B5" s="17" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6" spans="2:3">
       <c r="B6" s="17" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="B7" s="17" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8" ht="43.2" spans="2:3">
       <c r="B8" s="17" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" s="18" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10" spans="2:2">
       <c r="B10" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11" ht="23.4" spans="2:2">
       <c r="B11" s="19" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" s="20" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
     </row>
     <row r="15" spans="2:2">
       <c r="B15" s="20" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
     </row>
     <row r="16" spans="2:2">
       <c r="B16" s="20" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" s="20" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" s="20" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" s="20" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" s="20" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" s="20" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" s="20" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" s="20" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
     </row>
     <row r="26" ht="23.4" spans="2:2">
       <c r="B26" s="19" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" s="20" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
     </row>
     <row r="29" spans="2:2">
       <c r="B29" s="20" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" s="20" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
     </row>
     <row r="31" spans="2:2">
       <c r="B31" s="20" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" s="20" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" s="20" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" s="20" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
     </row>
     <row r="36" spans="2:2">
@@ -11246,83 +11396,83 @@
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
     </row>
     <row r="41" ht="23.4" spans="2:2">
       <c r="B41" s="19" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
     </row>
     <row r="43" spans="2:2">
       <c r="B43" s="20" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" s="20" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
     </row>
     <row r="45" spans="2:2">
       <c r="B45" s="20" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" s="20" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" s="21" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" s="21" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" s="21" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" s="21" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
     </row>
     <row r="54" ht="13" customHeight="1"/>
     <row r="55" ht="22" customHeight="1" spans="2:2">
       <c r="B55" s="19" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
     </row>
     <row r="57" spans="2:2">
       <c r="B57" s="20" t="s">
-        <v>340</v>
+        <v>353</v>
       </c>
     </row>
     <row r="58" spans="2:2">
@@ -11337,17 +11487,17 @@
     </row>
     <row r="60" spans="2:2">
       <c r="B60" s="20" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61" s="20" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -11364,7 +11514,7 @@
   <sheetData>
     <row r="1" spans="1:21">
       <c r="A1" s="12" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -11379,7 +11529,7 @@
       <c r="L1" s="12"/>
       <c r="M1" s="12"/>
       <c r="N1" s="14" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="O1" s="15"/>
       <c r="P1" s="15"/>
@@ -11621,7 +11771,7 @@
     </row>
     <row r="12" spans="1:21">
       <c r="A12" s="12" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
@@ -11807,7 +11957,7 @@
     </row>
     <row r="22" spans="1:21">
       <c r="A22" s="13" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="B22" s="13"/>
       <c r="C22" s="13"/>

--- a/JavaPrograms/Work Done.xlsx
+++ b/JavaPrograms/Work Done.xlsx
@@ -5860,7 +5860,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5991,6 +5991,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -6694,246 +6697,246 @@
   </cols>
   <sheetData>
     <row r="1" ht="90" customHeight="1" spans="1:6">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="68" t="s">
+      <c r="B1" s="68"/>
+      <c r="C1" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="69"/>
-      <c r="E1" s="70" t="s">
+      <c r="D1" s="70"/>
+      <c r="E1" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="70"/>
+      <c r="F1" s="71"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="72" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="25"/>
-      <c r="C2" s="72" t="s">
+      <c r="C2" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="73"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="25"/>
       <c r="B3" s="25"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="25"/>
       <c r="B4" s="25"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="25"/>
       <c r="B5" s="25"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="75"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="25"/>
       <c r="B6" s="25"/>
-      <c r="C6" s="74"/>
-      <c r="D6" s="75"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
+      <c r="C6" s="75"/>
+      <c r="D6" s="76"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="25"/>
       <c r="B7" s="25"/>
-      <c r="C7" s="74"/>
-      <c r="D7" s="75"/>
-      <c r="E7" s="70"/>
-      <c r="F7" s="70"/>
+      <c r="C7" s="75"/>
+      <c r="D7" s="76"/>
+      <c r="E7" s="71"/>
+      <c r="F7" s="71"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="25"/>
       <c r="B8" s="25"/>
-      <c r="C8" s="76"/>
-      <c r="D8" s="77"/>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="78"/>
+      <c r="E8" s="71"/>
+      <c r="F8" s="71"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="71" t="s">
+      <c r="A9" s="72" t="s">
         <v>5</v>
       </c>
       <c r="B9" s="27"/>
-      <c r="C9" s="78" t="s">
+      <c r="C9" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="79"/>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
+      <c r="D9" s="80"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="27"/>
       <c r="B10" s="27"/>
-      <c r="C10" s="80"/>
-      <c r="D10" s="81"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
+      <c r="C10" s="81"/>
+      <c r="D10" s="82"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="27"/>
       <c r="B11" s="27"/>
-      <c r="C11" s="80"/>
-      <c r="D11" s="81"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
+      <c r="C11" s="81"/>
+      <c r="D11" s="82"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="27"/>
       <c r="B12" s="27"/>
-      <c r="C12" s="80"/>
-      <c r="D12" s="81"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
+      <c r="C12" s="81"/>
+      <c r="D12" s="82"/>
+      <c r="E12" s="71"/>
+      <c r="F12" s="71"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="27"/>
       <c r="B13" s="27"/>
-      <c r="C13" s="80"/>
-      <c r="D13" s="81"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
+      <c r="C13" s="81"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="27"/>
       <c r="B14" s="27"/>
-      <c r="C14" s="80"/>
-      <c r="D14" s="81"/>
-      <c r="E14" s="70"/>
-      <c r="F14" s="70"/>
+      <c r="C14" s="81"/>
+      <c r="D14" s="82"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:6">
       <c r="A15" s="27"/>
       <c r="B15" s="27"/>
-      <c r="C15" s="82"/>
-      <c r="D15" s="83"/>
-      <c r="E15" s="70"/>
-      <c r="F15" s="70"/>
+      <c r="C15" s="83"/>
+      <c r="D15" s="84"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="27"/>
       <c r="B16" s="27"/>
-      <c r="C16" s="84" t="s">
+      <c r="C16" s="85" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="85"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="70"/>
+      <c r="D16" s="86"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="71"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="27"/>
       <c r="B17" s="27"/>
-      <c r="C17" s="86"/>
-      <c r="D17" s="87"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="70"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="88"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="27"/>
       <c r="B18" s="27"/>
-      <c r="C18" s="86"/>
-      <c r="D18" s="87"/>
-      <c r="E18" s="70"/>
-      <c r="F18" s="70"/>
+      <c r="C18" s="87"/>
+      <c r="D18" s="88"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="71" t="s">
+      <c r="A19" s="72" t="s">
         <v>8</v>
       </c>
       <c r="B19" s="25"/>
-      <c r="C19" s="86"/>
-      <c r="D19" s="87"/>
-      <c r="E19" s="70"/>
-      <c r="F19" s="70"/>
+      <c r="C19" s="87"/>
+      <c r="D19" s="88"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="25"/>
       <c r="B20" s="25"/>
-      <c r="C20" s="86"/>
-      <c r="D20" s="87"/>
-      <c r="E20" s="70"/>
-      <c r="F20" s="70"/>
+      <c r="C20" s="87"/>
+      <c r="D20" s="88"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="25"/>
       <c r="B21" s="25"/>
-      <c r="C21" s="86"/>
-      <c r="D21" s="87"/>
-      <c r="E21" s="70"/>
-      <c r="F21" s="70"/>
+      <c r="C21" s="87"/>
+      <c r="D21" s="88"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="25"/>
       <c r="B22" s="25"/>
-      <c r="C22" s="86"/>
-      <c r="D22" s="87"/>
+      <c r="C22" s="87"/>
+      <c r="D22" s="88"/>
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="25"/>
       <c r="B23" s="25"/>
-      <c r="C23" s="88"/>
-      <c r="D23" s="89"/>
+      <c r="C23" s="89"/>
+      <c r="D23" s="90"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="25"/>
       <c r="B24" s="25"/>
-      <c r="C24" s="90" t="s">
+      <c r="C24" s="91" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="91"/>
+      <c r="D24" s="92"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="25"/>
       <c r="B25" s="25"/>
-      <c r="C25" s="92"/>
-      <c r="D25" s="93"/>
+      <c r="C25" s="93"/>
+      <c r="D25" s="94"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="25"/>
       <c r="B26" s="25"/>
-      <c r="C26" s="92"/>
-      <c r="D26" s="93"/>
+      <c r="C26" s="93"/>
+      <c r="D26" s="94"/>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="25"/>
       <c r="B27" s="25"/>
-      <c r="C27" s="92"/>
-      <c r="D27" s="93"/>
+      <c r="C27" s="93"/>
+      <c r="D27" s="94"/>
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="25"/>
       <c r="B28" s="25"/>
-      <c r="C28" s="94"/>
-      <c r="D28" s="95"/>
+      <c r="C28" s="95"/>
+      <c r="D28" s="96"/>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="25"/>
@@ -6948,7 +6951,7 @@
       <c r="D30" s="29"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="71" t="s">
+      <c r="A31" s="72" t="s">
         <v>10</v>
       </c>
       <c r="B31" s="27"/>
@@ -7004,7 +7007,7 @@
       <c r="D39" s="29"/>
     </row>
     <row r="40" ht="18" customHeight="1" spans="1:4">
-      <c r="A40" s="71" t="s">
+      <c r="A40" s="72" t="s">
         <v>11</v>
       </c>
       <c r="B40" s="27"/>
@@ -7066,7 +7069,7 @@
       <c r="D49" s="29"/>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="71" t="s">
+      <c r="A50" s="72" t="s">
         <v>12</v>
       </c>
       <c r="B50" s="27"/>
@@ -7122,7 +7125,7 @@
       <c r="D58" s="29"/>
     </row>
     <row r="59" spans="1:4">
-      <c r="A59" s="71" t="s">
+      <c r="A59" s="72" t="s">
         <v>13</v>
       </c>
       <c r="B59" s="25"/>
@@ -7178,7 +7181,7 @@
       <c r="D67" s="29"/>
     </row>
     <row r="68" spans="1:4">
-      <c r="A68" s="71" t="s">
+      <c r="A68" s="72" t="s">
         <v>14</v>
       </c>
       <c r="B68" s="25"/>
@@ -7240,7 +7243,7 @@
       <c r="D77" s="29"/>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="71" t="s">
+      <c r="A78" s="72" t="s">
         <v>15</v>
       </c>
       <c r="B78" s="25"/>
@@ -7302,7 +7305,7 @@
       <c r="D87" s="29"/>
     </row>
     <row r="88" spans="1:4">
-      <c r="A88" s="71" t="s">
+      <c r="A88" s="72" t="s">
         <v>16</v>
       </c>
       <c r="B88" s="25"/>
@@ -7358,7 +7361,7 @@
       <c r="D96" s="29"/>
     </row>
     <row r="97" spans="1:4">
-      <c r="A97" s="71" t="s">
+      <c r="A97" s="72" t="s">
         <v>17</v>
       </c>
       <c r="B97" s="27"/>
@@ -7414,7 +7417,7 @@
       <c r="D105" s="29"/>
     </row>
     <row r="106" spans="1:4">
-      <c r="A106" s="71" t="s">
+      <c r="A106" s="72" t="s">
         <v>18</v>
       </c>
       <c r="B106" s="25"/>
@@ -8606,7 +8609,7 @@
       <c r="D1" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="E1" s="55" t="s">
         <v>23</v>
       </c>
     </row>
@@ -8614,31 +8617,31 @@
       <c r="A2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="55">
+      <c r="B2" s="56">
         <v>45976</v>
       </c>
-      <c r="C2" s="56">
+      <c r="C2" s="57">
         <v>45983</v>
       </c>
       <c r="D2" s="25">
         <v>4</v>
       </c>
-      <c r="E2" s="57"/>
+      <c r="E2" s="58"/>
     </row>
     <row r="3" ht="115.2" spans="1:5">
       <c r="A3" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="55">
+      <c r="B3" s="56">
         <v>45976</v>
       </c>
-      <c r="C3" s="56">
+      <c r="C3" s="57">
         <v>45983</v>
       </c>
       <c r="D3" s="25">
         <v>4</v>
       </c>
-      <c r="E3" s="58" t="s">
+      <c r="E3" s="59" t="s">
         <v>26</v>
       </c>
     </row>
@@ -8646,16 +8649,16 @@
       <c r="A4" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="55">
+      <c r="B4" s="56">
         <v>45976</v>
       </c>
-      <c r="C4" s="56">
+      <c r="C4" s="57">
         <v>45983</v>
       </c>
       <c r="D4" s="25">
         <v>3</v>
       </c>
-      <c r="E4" s="59" t="s">
+      <c r="E4" s="60" t="s">
         <v>28</v>
       </c>
     </row>
@@ -8663,125 +8666,125 @@
       <c r="A5" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="55">
+      <c r="B5" s="56">
         <v>45976</v>
       </c>
-      <c r="C5" s="56">
+      <c r="C5" s="57">
         <v>45983</v>
       </c>
       <c r="D5" s="25">
         <v>2</v>
       </c>
-      <c r="E5" s="60"/>
+      <c r="E5" s="61"/>
     </row>
     <row r="6" ht="115.2" spans="1:5">
       <c r="A6" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="55">
+      <c r="B6" s="56">
         <v>45976</v>
       </c>
-      <c r="C6" s="56">
+      <c r="C6" s="57">
         <v>45983</v>
       </c>
       <c r="D6" s="25">
         <v>2</v>
       </c>
-      <c r="E6" s="60"/>
+      <c r="E6" s="61"/>
     </row>
     <row r="7" ht="129.6" spans="1:5">
       <c r="A7" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="55">
+      <c r="B7" s="56">
         <v>45976</v>
       </c>
-      <c r="C7" s="56">
+      <c r="C7" s="57">
         <v>45983</v>
       </c>
       <c r="D7" s="25">
         <v>2</v>
       </c>
-      <c r="E7" s="60"/>
-    </row>
-    <row r="8" s="53" customFormat="1" ht="144" spans="1:5">
-      <c r="A8" s="61" t="s">
+      <c r="E7" s="61"/>
+    </row>
+    <row r="8" s="54" customFormat="1" ht="144" spans="1:5">
+      <c r="A8" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="56">
+      <c r="B8" s="57">
         <v>45976</v>
       </c>
-      <c r="C8" s="56">
+      <c r="C8" s="57">
         <v>45983</v>
       </c>
-      <c r="D8" s="62">
+      <c r="D8" s="63">
         <v>2</v>
       </c>
-      <c r="E8" s="63"/>
-    </row>
-    <row r="9" s="53" customFormat="1" ht="158.4" spans="1:5">
-      <c r="A9" s="61" t="s">
+      <c r="E8" s="64"/>
+    </row>
+    <row r="9" s="54" customFormat="1" ht="158.4" spans="1:5">
+      <c r="A9" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="56">
+      <c r="B9" s="57">
         <v>45976</v>
       </c>
-      <c r="C9" s="56">
+      <c r="C9" s="57">
         <v>45983</v>
       </c>
-      <c r="D9" s="62">
+      <c r="D9" s="63">
         <v>1</v>
       </c>
-      <c r="E9" s="64"/>
-    </row>
-    <row r="10" s="53" customFormat="1" spans="1:5">
-      <c r="A10" s="62" t="s">
+      <c r="E9" s="65"/>
+    </row>
+    <row r="10" s="54" customFormat="1" spans="1:5">
+      <c r="A10" s="63" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="56">
+      <c r="B10" s="57">
         <v>45976</v>
       </c>
-      <c r="C10" s="56">
+      <c r="C10" s="57">
         <v>45983</v>
       </c>
-      <c r="D10" s="62">
+      <c r="D10" s="63">
         <v>1</v>
       </c>
-      <c r="E10" s="65" t="s">
+      <c r="E10" s="66" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" s="53" customFormat="1" spans="1:5">
-      <c r="A11" s="62" t="s">
+    <row r="11" s="54" customFormat="1" spans="1:5">
+      <c r="A11" s="63" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="56">
+      <c r="B11" s="57">
         <v>45976</v>
       </c>
-      <c r="C11" s="56">
+      <c r="C11" s="57">
         <v>45983</v>
       </c>
-      <c r="D11" s="62">
+      <c r="D11" s="63">
         <v>1</v>
       </c>
-      <c r="E11" s="65" t="s">
+      <c r="E11" s="66" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" s="53" customFormat="1" spans="1:5">
-      <c r="A12" s="62" t="s">
+    <row r="12" s="54" customFormat="1" spans="1:5">
+      <c r="A12" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="56">
+      <c r="B12" s="57">
         <v>45976</v>
       </c>
-      <c r="C12" s="56">
+      <c r="C12" s="57">
         <v>45983</v>
       </c>
-      <c r="D12" s="62">
+      <c r="D12" s="63">
         <v>1</v>
       </c>
-      <c r="E12" s="65" t="s">
+      <c r="E12" s="66" t="s">
         <v>35</v>
       </c>
     </row>
@@ -8789,16 +8792,16 @@
       <c r="A13" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="56">
+      <c r="B13" s="57">
         <v>45977</v>
       </c>
-      <c r="C13" s="56">
+      <c r="C13" s="57">
         <v>45982</v>
       </c>
       <c r="D13" s="25">
         <v>1</v>
       </c>
-      <c r="E13" s="65" t="s">
+      <c r="E13" s="66" t="s">
         <v>35</v>
       </c>
     </row>
@@ -8806,16 +8809,16 @@
       <c r="A14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="56">
+      <c r="B14" s="57">
         <v>45980</v>
       </c>
-      <c r="C14" s="56">
+      <c r="C14" s="57">
         <v>45982</v>
       </c>
       <c r="D14" s="25">
         <v>1</v>
       </c>
-      <c r="E14" s="65" t="s">
+      <c r="E14" s="66" t="s">
         <v>35</v>
       </c>
     </row>
@@ -8823,16 +8826,16 @@
       <c r="A15" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="56">
+      <c r="B15" s="57">
         <v>45980</v>
       </c>
-      <c r="C15" s="56">
+      <c r="C15" s="57">
         <v>45982</v>
       </c>
       <c r="D15" s="25">
         <v>1</v>
       </c>
-      <c r="E15" s="65" t="s">
+      <c r="E15" s="66" t="s">
         <v>35</v>
       </c>
     </row>
@@ -8840,16 +8843,16 @@
       <c r="A16" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="56">
+      <c r="B16" s="57">
         <v>45980</v>
       </c>
-      <c r="C16" s="56">
+      <c r="C16" s="57">
         <v>45982</v>
       </c>
       <c r="D16" s="25">
         <v>1</v>
       </c>
-      <c r="E16" s="65" t="s">
+      <c r="E16" s="66" t="s">
         <v>35</v>
       </c>
     </row>
@@ -8857,16 +8860,16 @@
       <c r="A17" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="56">
+      <c r="B17" s="57">
         <v>45980</v>
       </c>
-      <c r="C17" s="56">
+      <c r="C17" s="57">
         <v>45982</v>
       </c>
       <c r="D17" s="25">
         <v>1</v>
       </c>
-      <c r="E17" s="65" t="s">
+      <c r="E17" s="66" t="s">
         <v>35</v>
       </c>
     </row>
@@ -8874,16 +8877,16 @@
       <c r="A18" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="56">
+      <c r="B18" s="57">
         <v>45981</v>
       </c>
-      <c r="C18" s="56">
+      <c r="C18" s="57">
         <v>45983</v>
       </c>
       <c r="D18" s="25">
         <v>1</v>
       </c>
-      <c r="E18" s="65" t="s">
+      <c r="E18" s="66" t="s">
         <v>35</v>
       </c>
     </row>
@@ -8891,16 +8894,16 @@
       <c r="A19" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="56">
+      <c r="B19" s="57">
         <v>45982</v>
       </c>
-      <c r="C19" s="56">
+      <c r="C19" s="57">
         <v>45984</v>
       </c>
       <c r="D19" s="25">
         <v>1</v>
       </c>
-      <c r="E19" s="65" t="s">
+      <c r="E19" s="66" t="s">
         <v>35</v>
       </c>
     </row>
@@ -8908,16 +8911,16 @@
       <c r="A20" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="56">
+      <c r="B20" s="57">
         <v>45983</v>
       </c>
-      <c r="C20" s="56">
+      <c r="C20" s="57">
         <v>45985</v>
       </c>
       <c r="D20" s="25">
         <v>1</v>
       </c>
-      <c r="E20" s="65" t="s">
+      <c r="E20" s="66" t="s">
         <v>35</v>
       </c>
     </row>
@@ -8925,16 +8928,16 @@
       <c r="A21" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="56">
+      <c r="B21" s="57">
         <v>45986</v>
       </c>
-      <c r="C21" s="56">
+      <c r="C21" s="57">
         <v>45987</v>
       </c>
       <c r="D21" s="25">
         <v>1</v>
       </c>
-      <c r="E21" s="65" t="s">
+      <c r="E21" s="66" t="s">
         <v>35</v>
       </c>
     </row>
@@ -8942,16 +8945,16 @@
       <c r="A22" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="56">
+      <c r="B22" s="57">
         <v>45986</v>
       </c>
-      <c r="C22" s="56">
+      <c r="C22" s="57">
         <v>45987</v>
       </c>
       <c r="D22" s="25">
         <v>1</v>
       </c>
-      <c r="E22" s="65" t="s">
+      <c r="E22" s="66" t="s">
         <v>35</v>
       </c>
     </row>
@@ -8959,16 +8962,16 @@
       <c r="A23" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="56">
+      <c r="B23" s="57">
         <v>45986</v>
       </c>
-      <c r="C23" s="56">
+      <c r="C23" s="57">
         <v>45987</v>
       </c>
       <c r="D23" s="25">
         <v>1</v>
       </c>
-      <c r="E23" s="65" t="s">
+      <c r="E23" s="66" t="s">
         <v>35</v>
       </c>
     </row>
@@ -8976,16 +8979,16 @@
       <c r="A24" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="56">
+      <c r="B24" s="57">
         <v>45986</v>
       </c>
-      <c r="C24" s="56">
+      <c r="C24" s="57">
         <v>45987</v>
       </c>
       <c r="D24" s="25">
         <v>1</v>
       </c>
-      <c r="E24" s="65" t="s">
+      <c r="E24" s="66" t="s">
         <v>35</v>
       </c>
     </row>
@@ -8993,16 +8996,16 @@
       <c r="A25" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="56">
+      <c r="B25" s="57">
         <v>45986</v>
       </c>
-      <c r="C25" s="56">
+      <c r="C25" s="57">
         <v>45987</v>
       </c>
       <c r="D25" s="25">
         <v>1</v>
       </c>
-      <c r="E25" s="65" t="s">
+      <c r="E25" s="66" t="s">
         <v>35</v>
       </c>
     </row>
@@ -9010,16 +9013,16 @@
       <c r="A26" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="56">
+      <c r="B26" s="57">
         <v>45986</v>
       </c>
-      <c r="C26" s="56">
+      <c r="C26" s="57">
         <v>45987</v>
       </c>
       <c r="D26" s="25">
         <v>1</v>
       </c>
-      <c r="E26" s="65" t="s">
+      <c r="E26" s="66" t="s">
         <v>35</v>
       </c>
     </row>
@@ -9027,16 +9030,16 @@
       <c r="A27" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="56">
+      <c r="B27" s="57">
         <v>45986</v>
       </c>
-      <c r="C27" s="56">
+      <c r="C27" s="57">
         <v>45987</v>
       </c>
       <c r="D27" s="25">
         <v>1</v>
       </c>
-      <c r="E27" s="65" t="s">
+      <c r="E27" s="66" t="s">
         <v>35</v>
       </c>
     </row>
@@ -9044,16 +9047,16 @@
       <c r="A28" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="56">
+      <c r="B28" s="57">
         <v>45986</v>
       </c>
-      <c r="C28" s="56">
+      <c r="C28" s="57">
         <v>45987</v>
       </c>
       <c r="D28" s="25">
         <v>1</v>
       </c>
-      <c r="E28" s="65" t="s">
+      <c r="E28" s="66" t="s">
         <v>35</v>
       </c>
     </row>
@@ -9061,16 +9064,16 @@
       <c r="A29" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="56">
+      <c r="B29" s="57">
         <v>45986</v>
       </c>
-      <c r="C29" s="56">
+      <c r="C29" s="57">
         <v>45987</v>
       </c>
       <c r="D29" s="25">
         <v>1</v>
       </c>
-      <c r="E29" s="65" t="s">
+      <c r="E29" s="66" t="s">
         <v>35</v>
       </c>
     </row>
@@ -9078,16 +9081,16 @@
       <c r="A30" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="56">
+      <c r="B30" s="57">
         <v>45986</v>
       </c>
-      <c r="C30" s="56">
+      <c r="C30" s="57">
         <v>45987</v>
       </c>
       <c r="D30" s="25">
         <v>1</v>
       </c>
-      <c r="E30" s="65" t="s">
+      <c r="E30" s="66" t="s">
         <v>35</v>
       </c>
     </row>
@@ -9095,16 +9098,16 @@
       <c r="A31" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="56">
+      <c r="B31" s="57">
         <v>45992</v>
       </c>
-      <c r="C31" s="56">
+      <c r="C31" s="57">
         <v>45993</v>
       </c>
       <c r="D31" s="25">
         <v>1</v>
       </c>
-      <c r="E31" s="65" t="s">
+      <c r="E31" s="66" t="s">
         <v>35</v>
       </c>
     </row>
@@ -9112,16 +9115,16 @@
       <c r="A32" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="56">
+      <c r="B32" s="57">
         <v>45992</v>
       </c>
-      <c r="C32" s="56">
+      <c r="C32" s="57">
         <v>45993</v>
       </c>
       <c r="D32" s="25">
         <v>1</v>
       </c>
-      <c r="E32" s="65" t="s">
+      <c r="E32" s="66" t="s">
         <v>35</v>
       </c>
     </row>
@@ -9129,16 +9132,16 @@
       <c r="A33" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="56">
+      <c r="B33" s="57">
         <v>45992</v>
       </c>
-      <c r="C33" s="56">
+      <c r="C33" s="57">
         <v>45993</v>
       </c>
       <c r="D33" s="25">
         <v>1</v>
       </c>
-      <c r="E33" s="65" t="s">
+      <c r="E33" s="66" t="s">
         <v>35</v>
       </c>
     </row>
@@ -9146,16 +9149,16 @@
       <c r="A34" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="56">
+      <c r="B34" s="57">
         <v>45993</v>
       </c>
-      <c r="C34" s="56">
+      <c r="C34" s="57">
         <v>45993</v>
       </c>
       <c r="D34" s="25">
         <v>1</v>
       </c>
-      <c r="E34" s="65" t="s">
+      <c r="E34" s="66" t="s">
         <v>35</v>
       </c>
     </row>
@@ -9769,21 +9772,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="50" t="s">
+      <c r="C1" s="51" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="2" ht="409.5" spans="1:3">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="53" t="s">
         <v>64</v>
       </c>
       <c r="C2" s="32" t="s">
@@ -10099,7 +10102,7 @@
       <c r="B1" s="29"/>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="45">
+      <c r="A2" s="46">
         <v>45962</v>
       </c>
       <c r="B2" s="29"/>
@@ -10108,7 +10111,7 @@
       <c r="A3" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="47" t="s">
         <v>82</v>
       </c>
     </row>
@@ -10116,7 +10119,7 @@
       <c r="A4" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="B4" s="46" t="s">
+      <c r="B4" s="47" t="s">
         <v>84</v>
       </c>
     </row>
@@ -10124,21 +10127,21 @@
       <c r="A5" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="47" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="47">
+      <c r="A6" s="48">
         <v>45969</v>
       </c>
       <c r="B6" s="29"/>
     </row>
-    <row r="7" s="44" customFormat="1" ht="57.6" spans="1:2">
-      <c r="A7" s="48" t="s">
+    <row r="7" s="45" customFormat="1" ht="57.6" spans="1:2">
+      <c r="A7" s="49" t="s">
         <v>87</v>
       </c>
-      <c r="B7" s="49" t="s">
+      <c r="B7" s="50" t="s">
         <v>88</v>
       </c>
     </row>
@@ -10898,7 +10901,7 @@
       </c>
     </row>
     <row r="82" ht="115.2" spans="1:2">
-      <c r="A82" s="43" t="s">
+      <c r="A82" s="44" t="s">
         <v>271</v>
       </c>
       <c r="B82" s="27" t="s">

--- a/JavaPrograms/Work Done.xlsx
+++ b/JavaPrograms/Work Done.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8280" firstSheet="4" activeTab="4"/>
+    <workbookView windowWidth="23040" windowHeight="8280" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="DSA plan" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="479">
   <si>
     <r>
       <rPr>
@@ -813,49 +813,144 @@
     <t>The Mental Model: The "Digital Restaurant" 🍔You know Java, so you know "Functions." But an API is different.Think of your computer as a Restaurant.1. The Server (uvicorn) = The Kitchen Staff 👨‍🍳Your Python script is just a recipe book. It does nothing by itself.Uvicorn is the team of chefs. They show up, turn on the lights, and wait for orders.That is why the terminal hangs. They are standing there, waiting.2. The App (app = FastAPI()) = The Front Counter 🏪This is where customers (users) walk up to talk to you.If you didn't have this, the chefs (Uvicorn) wouldn't know who to talk to.3. The Decorator (@app.post("/review")) = The Menu Board 📜This is the most confusing part for new Python devs.The Symbol: @ means "Decorate this function."The Concept: Imagine you have a function make_burger().In a normal script, you call it.In an API, you stick a sign on it: "Order Here for Burgers."@app.post("/review") tells the server: "If a customer comes to the /review window, run THIS specific function."4. JSON ({"code": "..."}) = The Order Ticket 📝Computers don't speak English. They speak JSON (JavaScript Object Notation).It is just a fancy text format that looks like a Dictionary.Key: What is it? ("code")Value: The actual data. ("print hello")The "Why" Behind The ToolsYou asked for the deeper reasoning. Here is the engineering reality.ToolWhy do we use it?The "Java Way" (Comparison)FastAPIIt is the fastest Python framework today. It writes the documentation for you automatically.Like Spring Boot, but 10x less code.UvicornPython is slow. Uvicorn is a "wrapper" written in C++ that makes Python run fast on the web.Like Tomcat in Java.Decorators (@)To attach "metadata" to a function without changing the code inside it.Like Annotations (@Override, @GetMapping) in Java.</t>
   </si>
   <si>
-    <t>Why does QuickSelect run faster than QuickSort?
-ans: QuickSort sorts both sides of the pivot
-QuickSelect only cares about one index
-So after partition:
-If pivot is at target index → DONE
-Else → recurse into only one side
-Complexity difference
-QuickSort → T(n) = T(left) + T(right)
-QuickSelect → T(n) = T(one side only)
-👉 That’s why average O(n) instead of O(n log n) 
-“QuickSelect is faster because it avoids unnecessary recursion and only explores the partition that contains the target element.”
-When would you prefer Merge Sort over QuickSort?
-ans. I prefer Merge Sort when I need guaranteed O(n log n) performance or stability, especially for linked lists or external sorting.  
-You prefer Merge Sort when:
-1️⃣ Guaranteed performance matters
-Merge Sort is always O(n log n)
-QuickSort can degrade to O(n²)
-2️⃣ Stability is required
-Merge Sort is stable
-QuickSort is not stable
-3️⃣ External sorting / large data
-Works well when data doesn’t fit in memory
-4️⃣ Linked Lists
-Merge Sort works beautifully on linked lists
-QuickSort doesn’t
-Why does Binary Search on Answer work?
-Your answer: Binary Search on Answer works because:
-The answer space is monotonic
-Meaning:
-If a value works, all bigger (or smaller) values also work
-OR
-If a value fails, all smaller (or bigger) values fail
-Example: Koko Eating Bananas
-Eating speed = x
-If Koko can eat at speed x
-→ she can eat at any speed &gt; x
-That’s a monotonic yes/no function.
-Pattern
-Define search space (low → high)
-Define can(mid)
-Use binary search on that space
-Interview-ready line
-“Binary Search on Answer works because the feasibility function is monotonic, allowing us to binary search the solution space.”</t>
+    <t>Pydantic</t>
+  </si>
+  <si>
+    <t>The Pydantic Explanation (The "Club Bouncer") 🛡️
+Your Answer: "I forgot the use case." The Upgrade:
+Think of your Server Function (review_code) as a VIP Club. The code inside (the logic) is delicate. If you let just anyone in, they break things.
+Without Pydantic:
+A user sends {"username": "admin"} instead of code.
+Your function tries to do request.code.
+CRASH. The server explodes with a AttributeError. Your logs are full of garbage.
+With Pydantic (CodeRequest):
+Pydantic is the Bouncer at the door.
+It checks the ID. "Do you have a field called code? Is it a String?"
+If NO: Pydantic kicks them out immediately with a 422 Error.
+Benefit: Your function never runs. Your server is safe. You save processing power.
+Interview Answer: "I use Pydantic for Data Validation. It acts as a contract that ensures my function only receives clean, correct data types, preventing runtime crashes."</t>
+  </si>
+  <si>
+    <t>what’s this project about?</t>
+  </si>
+  <si>
+    <t>"I built an automated code-review tool. You send it broken Python code, and it uses Google's AI to send back a fixed version instantly. It’s like having a senior developer review your code 24/7."</t>
+  </si>
+  <si>
+    <t>Tell me about a time you built something interesting.</t>
+  </si>
+  <si>
+    <t>I wanted to see if I could automate debugging. I built a server that takes a piece of buggy code and asks an AI model to fix it.
+The hardest part wasn't the AI—it was making the server reliable.
+I added a 'Guard Dog' feature so if a user sends empty or bad data, the system blocks it before it crashes the server.
+I also made it 'Smart Retry', meaning if the AI is busy or the connection drops, the system tries again automatically so the user doesn't just see a 'Failed' message.</t>
+  </si>
+  <si>
+    <t>Use this in technical rounds when you want to show competence without showing off.</t>
+  </si>
+  <si>
+    <t>I built a Python backend using FastAPI that connects to the Gemini API to fix code.
+I focused on making it production-ready in three ways:
+Validation: I used Pydantic to make sure the input is always a valid string, so the server never crashes on bad input.
+Reliability: I wrote a loop that retries the request if the AI fails the first time, which handles network blips smoothly.
+Debugging: I set up a log file that saves a history of every request, so if something goes wrong, I can see exactly what happened and when.</t>
+  </si>
+  <si>
+    <t>Tell me about a challenging project</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I architected a Resilient AI Microservice using FastAPI to automate code debugging.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Security:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> I implemented a strict schema using Pydantic to reject malformed payloads (422 Unprocessable Entity) before they reached the core logic, saving compute resources.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Resilience</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: I built a custom Retry Mechanism with exponential backoff to handle transient 5xx errors from the LLM provider, ensuring high availability.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Observability</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: I integrated structured Logging to track request latency and error rates for debugging production issues.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Integration</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: The backend connects to Google's Gemini 2.5 via a secure API gateway."
+That is how a Senior Engineer speaks. You have earned the right to say that now.</t>
+    </r>
   </si>
   <si>
     <t>Recall</t>
@@ -5860,7 +5955,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5933,9 +6028,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5987,15 +6079,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -6022,6 +6105,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
@@ -6697,780 +6795,780 @@
   </cols>
   <sheetData>
     <row r="1" ht="90" customHeight="1" spans="1:6">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="69" t="s">
+      <c r="B1" s="69"/>
+      <c r="C1" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="70"/>
-      <c r="E1" s="71" t="s">
+      <c r="D1" s="71"/>
+      <c r="E1" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="71"/>
+      <c r="F1" s="72"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="73" t="s">
+      <c r="B2" s="24"/>
+      <c r="C2" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="74"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="25"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
+      <c r="A3" s="24"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="25"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
+      <c r="A4" s="24"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="25"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="75"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
+      <c r="A5" s="24"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="25"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="75"/>
-      <c r="D6" s="76"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
+      <c r="A6" s="24"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="25"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="75"/>
-      <c r="D7" s="76"/>
-      <c r="E7" s="71"/>
-      <c r="F7" s="71"/>
+      <c r="A7" s="24"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="76"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="72"/>
+      <c r="F7" s="72"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="25"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="78"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
+      <c r="A8" s="24"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="78"/>
+      <c r="D8" s="79"/>
+      <c r="E8" s="72"/>
+      <c r="F8" s="72"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="72" t="s">
+      <c r="A9" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="27"/>
-      <c r="C9" s="79" t="s">
+      <c r="B9" s="26"/>
+      <c r="C9" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="80"/>
-      <c r="E9" s="71"/>
-      <c r="F9" s="71"/>
+      <c r="D9" s="81"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="72"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="27"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="81"/>
-      <c r="D10" s="82"/>
-      <c r="E10" s="71"/>
-      <c r="F10" s="71"/>
+      <c r="A10" s="26"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="82"/>
+      <c r="D10" s="83"/>
+      <c r="E10" s="72"/>
+      <c r="F10" s="72"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="27"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="81"/>
-      <c r="D11" s="82"/>
-      <c r="E11" s="71"/>
-      <c r="F11" s="71"/>
+      <c r="A11" s="26"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="82"/>
+      <c r="D11" s="83"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="72"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="27"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="81"/>
-      <c r="D12" s="82"/>
-      <c r="E12" s="71"/>
-      <c r="F12" s="71"/>
+      <c r="A12" s="26"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="82"/>
+      <c r="D12" s="83"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="27"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="81"/>
-      <c r="D13" s="82"/>
-      <c r="E13" s="71"/>
-      <c r="F13" s="71"/>
+      <c r="A13" s="26"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="82"/>
+      <c r="D13" s="83"/>
+      <c r="E13" s="72"/>
+      <c r="F13" s="72"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="27"/>
-      <c r="B14" s="27"/>
-      <c r="C14" s="81"/>
-      <c r="D14" s="82"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="71"/>
+      <c r="A14" s="26"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="82"/>
+      <c r="D14" s="83"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="72"/>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:6">
-      <c r="A15" s="27"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="83"/>
-      <c r="D15" s="84"/>
-      <c r="E15" s="71"/>
-      <c r="F15" s="71"/>
+      <c r="A15" s="26"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="84"/>
+      <c r="D15" s="85"/>
+      <c r="E15" s="72"/>
+      <c r="F15" s="72"/>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="27"/>
-      <c r="B16" s="27"/>
-      <c r="C16" s="85" t="s">
+      <c r="A16" s="26"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="86"/>
-      <c r="E16" s="71"/>
-      <c r="F16" s="71"/>
+      <c r="D16" s="87"/>
+      <c r="E16" s="72"/>
+      <c r="F16" s="72"/>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="27"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="87"/>
-      <c r="D17" s="88"/>
-      <c r="E17" s="71"/>
-      <c r="F17" s="71"/>
+      <c r="A17" s="26"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="88"/>
+      <c r="D17" s="89"/>
+      <c r="E17" s="72"/>
+      <c r="F17" s="72"/>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="27"/>
-      <c r="B18" s="27"/>
-      <c r="C18" s="87"/>
-      <c r="D18" s="88"/>
-      <c r="E18" s="71"/>
-      <c r="F18" s="71"/>
+      <c r="A18" s="26"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="88"/>
+      <c r="D18" s="89"/>
+      <c r="E18" s="72"/>
+      <c r="F18" s="72"/>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="72" t="s">
+      <c r="A19" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="25"/>
-      <c r="C19" s="87"/>
-      <c r="D19" s="88"/>
-      <c r="E19" s="71"/>
-      <c r="F19" s="71"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="88"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="72"/>
+      <c r="F19" s="72"/>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="25"/>
-      <c r="B20" s="25"/>
-      <c r="C20" s="87"/>
-      <c r="D20" s="88"/>
-      <c r="E20" s="71"/>
-      <c r="F20" s="71"/>
+      <c r="A20" s="24"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="88"/>
+      <c r="D20" s="89"/>
+      <c r="E20" s="72"/>
+      <c r="F20" s="72"/>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="25"/>
-      <c r="B21" s="25"/>
-      <c r="C21" s="87"/>
-      <c r="D21" s="88"/>
-      <c r="E21" s="71"/>
-      <c r="F21" s="71"/>
+      <c r="A21" s="24"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="88"/>
+      <c r="D21" s="89"/>
+      <c r="E21" s="72"/>
+      <c r="F21" s="72"/>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="25"/>
-      <c r="B22" s="25"/>
-      <c r="C22" s="87"/>
-      <c r="D22" s="88"/>
+      <c r="A22" s="24"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="88"/>
+      <c r="D22" s="89"/>
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="25"/>
-      <c r="B23" s="25"/>
-      <c r="C23" s="89"/>
-      <c r="D23" s="90"/>
+      <c r="A23" s="24"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="90"/>
+      <c r="D23" s="91"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="25"/>
-      <c r="B24" s="25"/>
-      <c r="C24" s="91" t="s">
+      <c r="A24" s="24"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="92"/>
+      <c r="D24" s="93"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="25"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="93"/>
-      <c r="D25" s="94"/>
+      <c r="A25" s="24"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="94"/>
+      <c r="D25" s="95"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="25"/>
-      <c r="B26" s="25"/>
-      <c r="C26" s="93"/>
-      <c r="D26" s="94"/>
+      <c r="A26" s="24"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="94"/>
+      <c r="D26" s="95"/>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="25"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="93"/>
-      <c r="D27" s="94"/>
+      <c r="A27" s="24"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="94"/>
+      <c r="D27" s="95"/>
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="25"/>
-      <c r="B28" s="25"/>
-      <c r="C28" s="95"/>
-      <c r="D28" s="96"/>
+      <c r="A28" s="24"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="96"/>
+      <c r="D28" s="97"/>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="25"/>
-      <c r="B29" s="25"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
+      <c r="A29" s="24"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="25"/>
-      <c r="B30" s="25"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
+      <c r="A30" s="24"/>
+      <c r="B30" s="24"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="72" t="s">
+      <c r="A31" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="B31" s="27"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
+      <c r="B31" s="26"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="27"/>
-      <c r="B32" s="27"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
+      <c r="A32" s="26"/>
+      <c r="B32" s="26"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="27"/>
-      <c r="B33" s="27"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
+      <c r="A33" s="26"/>
+      <c r="B33" s="26"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="27"/>
-      <c r="B34" s="27"/>
-      <c r="C34" s="29"/>
-      <c r="D34" s="29"/>
+      <c r="A34" s="26"/>
+      <c r="B34" s="26"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="27"/>
-      <c r="B35" s="27"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
+      <c r="A35" s="26"/>
+      <c r="B35" s="26"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="27"/>
-      <c r="B36" s="27"/>
-      <c r="C36" s="29"/>
-      <c r="D36" s="29"/>
+      <c r="A36" s="26"/>
+      <c r="B36" s="26"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="27"/>
-      <c r="B37" s="27"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
+      <c r="A37" s="26"/>
+      <c r="B37" s="26"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="27"/>
-      <c r="B38" s="27"/>
-      <c r="C38" s="29"/>
-      <c r="D38" s="29"/>
+      <c r="A38" s="26"/>
+      <c r="B38" s="26"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="28"/>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="27"/>
-      <c r="B39" s="27"/>
-      <c r="C39" s="29"/>
-      <c r="D39" s="29"/>
+      <c r="A39" s="26"/>
+      <c r="B39" s="26"/>
+      <c r="C39" s="28"/>
+      <c r="D39" s="28"/>
     </row>
     <row r="40" ht="18" customHeight="1" spans="1:4">
-      <c r="A40" s="72" t="s">
+      <c r="A40" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="B40" s="27"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
+      <c r="B40" s="26"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="28"/>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="27"/>
-      <c r="B41" s="27"/>
-      <c r="C41" s="29"/>
-      <c r="D41" s="29"/>
+      <c r="A41" s="26"/>
+      <c r="B41" s="26"/>
+      <c r="C41" s="28"/>
+      <c r="D41" s="28"/>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="27"/>
-      <c r="B42" s="27"/>
-      <c r="C42" s="29"/>
-      <c r="D42" s="29"/>
+      <c r="A42" s="26"/>
+      <c r="B42" s="26"/>
+      <c r="C42" s="28"/>
+      <c r="D42" s="28"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="27"/>
-      <c r="B43" s="27"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
+      <c r="A43" s="26"/>
+      <c r="B43" s="26"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="27"/>
-      <c r="B44" s="27"/>
-      <c r="C44" s="29"/>
-      <c r="D44" s="29"/>
+      <c r="A44" s="26"/>
+      <c r="B44" s="26"/>
+      <c r="C44" s="28"/>
+      <c r="D44" s="28"/>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="27"/>
-      <c r="B45" s="27"/>
-      <c r="C45" s="29"/>
-      <c r="D45" s="29"/>
+      <c r="A45" s="26"/>
+      <c r="B45" s="26"/>
+      <c r="C45" s="28"/>
+      <c r="D45" s="28"/>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="27"/>
-      <c r="B46" s="27"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
+      <c r="A46" s="26"/>
+      <c r="B46" s="26"/>
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="27"/>
-      <c r="B47" s="27"/>
-      <c r="C47" s="29"/>
-      <c r="D47" s="29"/>
+      <c r="A47" s="26"/>
+      <c r="B47" s="26"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="28"/>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="27"/>
-      <c r="B48" s="27"/>
-      <c r="C48" s="29"/>
-      <c r="D48" s="29"/>
+      <c r="A48" s="26"/>
+      <c r="B48" s="26"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28"/>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="27"/>
-      <c r="B49" s="27"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
+      <c r="A49" s="26"/>
+      <c r="B49" s="26"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="72" t="s">
+      <c r="A50" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="B50" s="27"/>
-      <c r="C50" s="29"/>
-      <c r="D50" s="29"/>
+      <c r="B50" s="26"/>
+      <c r="C50" s="28"/>
+      <c r="D50" s="28"/>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="27"/>
-      <c r="B51" s="27"/>
-      <c r="C51" s="29"/>
-      <c r="D51" s="29"/>
+      <c r="A51" s="26"/>
+      <c r="B51" s="26"/>
+      <c r="C51" s="28"/>
+      <c r="D51" s="28"/>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="27"/>
-      <c r="B52" s="27"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="29"/>
+      <c r="A52" s="26"/>
+      <c r="B52" s="26"/>
+      <c r="C52" s="28"/>
+      <c r="D52" s="28"/>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="27"/>
-      <c r="B53" s="27"/>
-      <c r="C53" s="29"/>
-      <c r="D53" s="29"/>
+      <c r="A53" s="26"/>
+      <c r="B53" s="26"/>
+      <c r="C53" s="28"/>
+      <c r="D53" s="28"/>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="27"/>
-      <c r="B54" s="27"/>
-      <c r="C54" s="29"/>
-      <c r="D54" s="29"/>
+      <c r="A54" s="26"/>
+      <c r="B54" s="26"/>
+      <c r="C54" s="28"/>
+      <c r="D54" s="28"/>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="27"/>
-      <c r="B55" s="27"/>
-      <c r="C55" s="29"/>
-      <c r="D55" s="29"/>
+      <c r="A55" s="26"/>
+      <c r="B55" s="26"/>
+      <c r="C55" s="28"/>
+      <c r="D55" s="28"/>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="27"/>
-      <c r="B56" s="27"/>
-      <c r="C56" s="29"/>
-      <c r="D56" s="29"/>
+      <c r="A56" s="26"/>
+      <c r="B56" s="26"/>
+      <c r="C56" s="28"/>
+      <c r="D56" s="28"/>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="27"/>
-      <c r="B57" s="27"/>
-      <c r="C57" s="29"/>
-      <c r="D57" s="29"/>
+      <c r="A57" s="26"/>
+      <c r="B57" s="26"/>
+      <c r="C57" s="28"/>
+      <c r="D57" s="28"/>
     </row>
     <row r="58" spans="1:4">
-      <c r="A58" s="27"/>
-      <c r="B58" s="27"/>
-      <c r="C58" s="29"/>
-      <c r="D58" s="29"/>
+      <c r="A58" s="26"/>
+      <c r="B58" s="26"/>
+      <c r="C58" s="28"/>
+      <c r="D58" s="28"/>
     </row>
     <row r="59" spans="1:4">
-      <c r="A59" s="72" t="s">
+      <c r="A59" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="B59" s="25"/>
-      <c r="C59" s="29"/>
-      <c r="D59" s="29"/>
+      <c r="B59" s="24"/>
+      <c r="C59" s="28"/>
+      <c r="D59" s="28"/>
     </row>
     <row r="60" spans="1:4">
-      <c r="A60" s="25"/>
-      <c r="B60" s="25"/>
-      <c r="C60" s="29"/>
-      <c r="D60" s="29"/>
+      <c r="A60" s="24"/>
+      <c r="B60" s="24"/>
+      <c r="C60" s="28"/>
+      <c r="D60" s="28"/>
     </row>
     <row r="61" spans="1:4">
-      <c r="A61" s="25"/>
-      <c r="B61" s="25"/>
-      <c r="C61" s="29"/>
-      <c r="D61" s="29"/>
+      <c r="A61" s="24"/>
+      <c r="B61" s="24"/>
+      <c r="C61" s="28"/>
+      <c r="D61" s="28"/>
     </row>
     <row r="62" spans="1:4">
-      <c r="A62" s="25"/>
-      <c r="B62" s="25"/>
-      <c r="C62" s="29"/>
-      <c r="D62" s="29"/>
+      <c r="A62" s="24"/>
+      <c r="B62" s="24"/>
+      <c r="C62" s="28"/>
+      <c r="D62" s="28"/>
     </row>
     <row r="63" spans="1:4">
-      <c r="A63" s="25"/>
-      <c r="B63" s="25"/>
-      <c r="C63" s="29"/>
-      <c r="D63" s="29"/>
+      <c r="A63" s="24"/>
+      <c r="B63" s="24"/>
+      <c r="C63" s="28"/>
+      <c r="D63" s="28"/>
     </row>
     <row r="64" spans="1:4">
-      <c r="A64" s="25"/>
-      <c r="B64" s="25"/>
-      <c r="C64" s="29"/>
-      <c r="D64" s="29"/>
+      <c r="A64" s="24"/>
+      <c r="B64" s="24"/>
+      <c r="C64" s="28"/>
+      <c r="D64" s="28"/>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65" s="25"/>
-      <c r="B65" s="25"/>
-      <c r="C65" s="29"/>
-      <c r="D65" s="29"/>
+      <c r="A65" s="24"/>
+      <c r="B65" s="24"/>
+      <c r="C65" s="28"/>
+      <c r="D65" s="28"/>
     </row>
     <row r="66" spans="1:4">
-      <c r="A66" s="25"/>
-      <c r="B66" s="25"/>
-      <c r="C66" s="29"/>
-      <c r="D66" s="29"/>
+      <c r="A66" s="24"/>
+      <c r="B66" s="24"/>
+      <c r="C66" s="28"/>
+      <c r="D66" s="28"/>
     </row>
     <row r="67" spans="1:4">
-      <c r="A67" s="25"/>
-      <c r="B67" s="25"/>
-      <c r="C67" s="29"/>
-      <c r="D67" s="29"/>
+      <c r="A67" s="24"/>
+      <c r="B67" s="24"/>
+      <c r="C67" s="28"/>
+      <c r="D67" s="28"/>
     </row>
     <row r="68" spans="1:4">
-      <c r="A68" s="72" t="s">
+      <c r="A68" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="B68" s="25"/>
-      <c r="C68" s="29"/>
-      <c r="D68" s="29"/>
+      <c r="B68" s="24"/>
+      <c r="C68" s="28"/>
+      <c r="D68" s="28"/>
     </row>
     <row r="69" spans="1:4">
-      <c r="A69" s="25"/>
-      <c r="B69" s="25"/>
-      <c r="C69" s="29"/>
-      <c r="D69" s="29"/>
+      <c r="A69" s="24"/>
+      <c r="B69" s="24"/>
+      <c r="C69" s="28"/>
+      <c r="D69" s="28"/>
     </row>
     <row r="70" spans="1:4">
-      <c r="A70" s="25"/>
-      <c r="B70" s="25"/>
-      <c r="C70" s="29"/>
-      <c r="D70" s="29"/>
+      <c r="A70" s="24"/>
+      <c r="B70" s="24"/>
+      <c r="C70" s="28"/>
+      <c r="D70" s="28"/>
     </row>
     <row r="71" spans="1:4">
-      <c r="A71" s="25"/>
-      <c r="B71" s="25"/>
-      <c r="C71" s="29"/>
-      <c r="D71" s="29"/>
+      <c r="A71" s="24"/>
+      <c r="B71" s="24"/>
+      <c r="C71" s="28"/>
+      <c r="D71" s="28"/>
     </row>
     <row r="72" spans="1:4">
-      <c r="A72" s="25"/>
-      <c r="B72" s="25"/>
-      <c r="C72" s="29"/>
-      <c r="D72" s="29"/>
+      <c r="A72" s="24"/>
+      <c r="B72" s="24"/>
+      <c r="C72" s="28"/>
+      <c r="D72" s="28"/>
     </row>
     <row r="73" spans="1:4">
-      <c r="A73" s="25"/>
-      <c r="B73" s="25"/>
-      <c r="C73" s="29"/>
-      <c r="D73" s="29"/>
+      <c r="A73" s="24"/>
+      <c r="B73" s="24"/>
+      <c r="C73" s="28"/>
+      <c r="D73" s="28"/>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74" s="25"/>
-      <c r="B74" s="25"/>
-      <c r="C74" s="29"/>
-      <c r="D74" s="29"/>
+      <c r="A74" s="24"/>
+      <c r="B74" s="24"/>
+      <c r="C74" s="28"/>
+      <c r="D74" s="28"/>
     </row>
     <row r="75" spans="1:4">
-      <c r="A75" s="25"/>
-      <c r="B75" s="25"/>
-      <c r="C75" s="29"/>
-      <c r="D75" s="29"/>
+      <c r="A75" s="24"/>
+      <c r="B75" s="24"/>
+      <c r="C75" s="28"/>
+      <c r="D75" s="28"/>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76" s="25"/>
-      <c r="B76" s="25"/>
-      <c r="C76" s="29"/>
-      <c r="D76" s="29"/>
+      <c r="A76" s="24"/>
+      <c r="B76" s="24"/>
+      <c r="C76" s="28"/>
+      <c r="D76" s="28"/>
     </row>
     <row r="77" spans="1:4">
-      <c r="A77" s="25"/>
-      <c r="B77" s="25"/>
-      <c r="C77" s="29"/>
-      <c r="D77" s="29"/>
+      <c r="A77" s="24"/>
+      <c r="B77" s="24"/>
+      <c r="C77" s="28"/>
+      <c r="D77" s="28"/>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="72" t="s">
+      <c r="A78" s="73" t="s">
         <v>15</v>
       </c>
-      <c r="B78" s="25"/>
-      <c r="C78" s="29"/>
-      <c r="D78" s="29"/>
+      <c r="B78" s="24"/>
+      <c r="C78" s="28"/>
+      <c r="D78" s="28"/>
     </row>
     <row r="79" spans="1:4">
-      <c r="A79" s="25"/>
-      <c r="B79" s="25"/>
-      <c r="C79" s="29"/>
-      <c r="D79" s="29"/>
+      <c r="A79" s="24"/>
+      <c r="B79" s="24"/>
+      <c r="C79" s="28"/>
+      <c r="D79" s="28"/>
     </row>
     <row r="80" spans="1:4">
-      <c r="A80" s="25"/>
-      <c r="B80" s="25"/>
-      <c r="C80" s="29"/>
-      <c r="D80" s="29"/>
+      <c r="A80" s="24"/>
+      <c r="B80" s="24"/>
+      <c r="C80" s="28"/>
+      <c r="D80" s="28"/>
     </row>
     <row r="81" spans="1:4">
-      <c r="A81" s="25"/>
-      <c r="B81" s="25"/>
-      <c r="C81" s="29"/>
-      <c r="D81" s="29"/>
+      <c r="A81" s="24"/>
+      <c r="B81" s="24"/>
+      <c r="C81" s="28"/>
+      <c r="D81" s="28"/>
     </row>
     <row r="82" spans="1:4">
-      <c r="A82" s="25"/>
-      <c r="B82" s="25"/>
-      <c r="C82" s="29"/>
-      <c r="D82" s="29"/>
+      <c r="A82" s="24"/>
+      <c r="B82" s="24"/>
+      <c r="C82" s="28"/>
+      <c r="D82" s="28"/>
     </row>
     <row r="83" spans="1:4">
-      <c r="A83" s="25"/>
-      <c r="B83" s="25"/>
-      <c r="C83" s="29"/>
-      <c r="D83" s="29"/>
+      <c r="A83" s="24"/>
+      <c r="B83" s="24"/>
+      <c r="C83" s="28"/>
+      <c r="D83" s="28"/>
     </row>
     <row r="84" spans="1:4">
-      <c r="A84" s="25"/>
-      <c r="B84" s="25"/>
-      <c r="C84" s="29"/>
-      <c r="D84" s="29"/>
+      <c r="A84" s="24"/>
+      <c r="B84" s="24"/>
+      <c r="C84" s="28"/>
+      <c r="D84" s="28"/>
     </row>
     <row r="85" spans="1:4">
-      <c r="A85" s="25"/>
-      <c r="B85" s="25"/>
-      <c r="C85" s="29"/>
-      <c r="D85" s="29"/>
+      <c r="A85" s="24"/>
+      <c r="B85" s="24"/>
+      <c r="C85" s="28"/>
+      <c r="D85" s="28"/>
     </row>
     <row r="86" spans="1:4">
-      <c r="A86" s="25"/>
-      <c r="B86" s="25"/>
-      <c r="C86" s="29"/>
-      <c r="D86" s="29"/>
+      <c r="A86" s="24"/>
+      <c r="B86" s="24"/>
+      <c r="C86" s="28"/>
+      <c r="D86" s="28"/>
     </row>
     <row r="87" spans="1:4">
-      <c r="A87" s="25"/>
-      <c r="B87" s="25"/>
-      <c r="C87" s="29"/>
-      <c r="D87" s="29"/>
+      <c r="A87" s="24"/>
+      <c r="B87" s="24"/>
+      <c r="C87" s="28"/>
+      <c r="D87" s="28"/>
     </row>
     <row r="88" spans="1:4">
-      <c r="A88" s="72" t="s">
+      <c r="A88" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="B88" s="25"/>
-      <c r="C88" s="29"/>
-      <c r="D88" s="29"/>
+      <c r="B88" s="24"/>
+      <c r="C88" s="28"/>
+      <c r="D88" s="28"/>
     </row>
     <row r="89" spans="1:4">
-      <c r="A89" s="25"/>
-      <c r="B89" s="25"/>
-      <c r="C89" s="29"/>
-      <c r="D89" s="29"/>
+      <c r="A89" s="24"/>
+      <c r="B89" s="24"/>
+      <c r="C89" s="28"/>
+      <c r="D89" s="28"/>
     </row>
     <row r="90" spans="1:4">
-      <c r="A90" s="25"/>
-      <c r="B90" s="25"/>
-      <c r="C90" s="29"/>
-      <c r="D90" s="29"/>
+      <c r="A90" s="24"/>
+      <c r="B90" s="24"/>
+      <c r="C90" s="28"/>
+      <c r="D90" s="28"/>
     </row>
     <row r="91" spans="1:4">
-      <c r="A91" s="25"/>
-      <c r="B91" s="25"/>
-      <c r="C91" s="29"/>
-      <c r="D91" s="29"/>
+      <c r="A91" s="24"/>
+      <c r="B91" s="24"/>
+      <c r="C91" s="28"/>
+      <c r="D91" s="28"/>
     </row>
     <row r="92" spans="1:4">
-      <c r="A92" s="25"/>
-      <c r="B92" s="25"/>
-      <c r="C92" s="29"/>
-      <c r="D92" s="29"/>
+      <c r="A92" s="24"/>
+      <c r="B92" s="24"/>
+      <c r="C92" s="28"/>
+      <c r="D92" s="28"/>
     </row>
     <row r="93" spans="1:4">
-      <c r="A93" s="25"/>
-      <c r="B93" s="25"/>
-      <c r="C93" s="29"/>
-      <c r="D93" s="29"/>
+      <c r="A93" s="24"/>
+      <c r="B93" s="24"/>
+      <c r="C93" s="28"/>
+      <c r="D93" s="28"/>
     </row>
     <row r="94" spans="1:4">
-      <c r="A94" s="25"/>
-      <c r="B94" s="25"/>
-      <c r="C94" s="29"/>
-      <c r="D94" s="29"/>
+      <c r="A94" s="24"/>
+      <c r="B94" s="24"/>
+      <c r="C94" s="28"/>
+      <c r="D94" s="28"/>
     </row>
     <row r="95" spans="1:4">
-      <c r="A95" s="25"/>
-      <c r="B95" s="25"/>
-      <c r="C95" s="29"/>
-      <c r="D95" s="29"/>
+      <c r="A95" s="24"/>
+      <c r="B95" s="24"/>
+      <c r="C95" s="28"/>
+      <c r="D95" s="28"/>
     </row>
     <row r="96" spans="1:4">
-      <c r="A96" s="25"/>
-      <c r="B96" s="25"/>
-      <c r="C96" s="29"/>
-      <c r="D96" s="29"/>
+      <c r="A96" s="24"/>
+      <c r="B96" s="24"/>
+      <c r="C96" s="28"/>
+      <c r="D96" s="28"/>
     </row>
     <row r="97" spans="1:4">
-      <c r="A97" s="72" t="s">
+      <c r="A97" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="B97" s="27"/>
-      <c r="C97" s="29"/>
-      <c r="D97" s="29"/>
+      <c r="B97" s="26"/>
+      <c r="C97" s="28"/>
+      <c r="D97" s="28"/>
     </row>
     <row r="98" spans="1:4">
-      <c r="A98" s="27"/>
-      <c r="B98" s="27"/>
-      <c r="C98" s="29"/>
-      <c r="D98" s="29"/>
+      <c r="A98" s="26"/>
+      <c r="B98" s="26"/>
+      <c r="C98" s="28"/>
+      <c r="D98" s="28"/>
     </row>
     <row r="99" spans="1:4">
-      <c r="A99" s="27"/>
-      <c r="B99" s="27"/>
-      <c r="C99" s="29"/>
-      <c r="D99" s="29"/>
+      <c r="A99" s="26"/>
+      <c r="B99" s="26"/>
+      <c r="C99" s="28"/>
+      <c r="D99" s="28"/>
     </row>
     <row r="100" spans="1:4">
-      <c r="A100" s="27"/>
-      <c r="B100" s="27"/>
-      <c r="C100" s="29"/>
-      <c r="D100" s="29"/>
+      <c r="A100" s="26"/>
+      <c r="B100" s="26"/>
+      <c r="C100" s="28"/>
+      <c r="D100" s="28"/>
     </row>
     <row r="101" spans="1:4">
-      <c r="A101" s="27"/>
-      <c r="B101" s="27"/>
-      <c r="C101" s="29"/>
-      <c r="D101" s="29"/>
+      <c r="A101" s="26"/>
+      <c r="B101" s="26"/>
+      <c r="C101" s="28"/>
+      <c r="D101" s="28"/>
     </row>
     <row r="102" spans="1:4">
-      <c r="A102" s="27"/>
-      <c r="B102" s="27"/>
-      <c r="C102" s="29"/>
-      <c r="D102" s="29"/>
+      <c r="A102" s="26"/>
+      <c r="B102" s="26"/>
+      <c r="C102" s="28"/>
+      <c r="D102" s="28"/>
     </row>
     <row r="103" spans="1:4">
-      <c r="A103" s="27"/>
-      <c r="B103" s="27"/>
-      <c r="C103" s="29"/>
-      <c r="D103" s="29"/>
+      <c r="A103" s="26"/>
+      <c r="B103" s="26"/>
+      <c r="C103" s="28"/>
+      <c r="D103" s="28"/>
     </row>
     <row r="104" spans="1:4">
-      <c r="A104" s="27"/>
-      <c r="B104" s="27"/>
-      <c r="C104" s="29"/>
-      <c r="D104" s="29"/>
+      <c r="A104" s="26"/>
+      <c r="B104" s="26"/>
+      <c r="C104" s="28"/>
+      <c r="D104" s="28"/>
     </row>
     <row r="105" spans="1:4">
-      <c r="A105" s="27"/>
-      <c r="B105" s="27"/>
-      <c r="C105" s="29"/>
-      <c r="D105" s="29"/>
+      <c r="A105" s="26"/>
+      <c r="B105" s="26"/>
+      <c r="C105" s="28"/>
+      <c r="D105" s="28"/>
     </row>
     <row r="106" spans="1:4">
-      <c r="A106" s="72" t="s">
+      <c r="A106" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="B106" s="25"/>
-      <c r="C106" s="29"/>
-      <c r="D106" s="29"/>
+      <c r="B106" s="24"/>
+      <c r="C106" s="28"/>
+      <c r="D106" s="28"/>
     </row>
     <row r="107" spans="1:4">
-      <c r="A107" s="25"/>
-      <c r="B107" s="25"/>
-      <c r="C107" s="29"/>
-      <c r="D107" s="29"/>
+      <c r="A107" s="24"/>
+      <c r="B107" s="24"/>
+      <c r="C107" s="28"/>
+      <c r="D107" s="28"/>
     </row>
     <row r="108" spans="1:4">
-      <c r="A108" s="25"/>
-      <c r="B108" s="25"/>
-      <c r="C108" s="29"/>
-      <c r="D108" s="29"/>
+      <c r="A108" s="24"/>
+      <c r="B108" s="24"/>
+      <c r="C108" s="28"/>
+      <c r="D108" s="28"/>
     </row>
     <row r="109" spans="1:4">
-      <c r="A109" s="25"/>
-      <c r="B109" s="25"/>
-      <c r="C109" s="29"/>
-      <c r="D109" s="29"/>
+      <c r="A109" s="24"/>
+      <c r="B109" s="24"/>
+      <c r="C109" s="28"/>
+      <c r="D109" s="28"/>
     </row>
     <row r="110" spans="1:4">
-      <c r="A110" s="25"/>
-      <c r="B110" s="25"/>
-      <c r="C110" s="29"/>
-      <c r="D110" s="29"/>
+      <c r="A110" s="24"/>
+      <c r="B110" s="24"/>
+      <c r="C110" s="28"/>
+      <c r="D110" s="28"/>
     </row>
     <row r="111" spans="1:4">
-      <c r="A111" s="25"/>
-      <c r="B111" s="25"/>
-      <c r="C111" s="29"/>
-      <c r="D111" s="29"/>
+      <c r="A111" s="24"/>
+      <c r="B111" s="24"/>
+      <c r="C111" s="28"/>
+      <c r="D111" s="28"/>
     </row>
     <row r="112" spans="1:4">
-      <c r="A112" s="25"/>
-      <c r="B112" s="25"/>
-      <c r="C112" s="29"/>
-      <c r="D112" s="29"/>
+      <c r="A112" s="24"/>
+      <c r="B112" s="24"/>
+      <c r="C112" s="28"/>
+      <c r="D112" s="28"/>
     </row>
     <row r="113" spans="1:4">
-      <c r="A113" s="25"/>
-      <c r="B113" s="25"/>
-      <c r="C113" s="29"/>
-      <c r="D113" s="29"/>
+      <c r="A113" s="24"/>
+      <c r="B113" s="24"/>
+      <c r="C113" s="28"/>
+      <c r="D113" s="28"/>
     </row>
     <row r="114" spans="1:4">
-      <c r="A114" s="25"/>
-      <c r="B114" s="25"/>
-      <c r="C114" s="29"/>
-      <c r="D114" s="29"/>
+      <c r="A114" s="24"/>
+      <c r="B114" s="24"/>
+      <c r="C114" s="28"/>
+      <c r="D114" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -7511,10 +7609,10 @@
   <sheetData>
     <row r="1" ht="409" customHeight="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -7660,18 +7758,18 @@
     </row>
     <row r="2" ht="409.5" spans="1:3">
       <c r="A2" s="6" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
     </row>
     <row r="3" ht="409.5" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="C3"/>
     </row>
@@ -7720,32 +7818,32 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="2" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="2" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="2" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="10" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="2" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="2" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
     </row>
     <row r="36" ht="23.4" spans="1:1">
@@ -7753,177 +7851,177 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="2" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="2" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="2" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="2" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="2" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="2" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="2" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="2" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="2" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="2" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="10" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="2" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
     </row>
     <row r="60" ht="23.4" spans="1:1">
       <c r="A60" s="9" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="2" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="2" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="2" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="2" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="2" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="2" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="2" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="2" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="2" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="2" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="10" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="2" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
     </row>
     <row r="86" ht="23.4" spans="1:1">
       <c r="A86" s="9" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="2" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="2" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="2" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="2" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="2" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="2" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="2" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="2" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="2" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
     </row>
     <row r="103" spans="1:1">
@@ -7933,12 +8031,12 @@
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="2" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="2" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
     </row>
     <row r="108" spans="1:1">
@@ -7946,12 +8044,12 @@
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="2" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" s="2" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
     </row>
     <row r="112" ht="23.4" spans="1:1">
@@ -7959,42 +8057,42 @@
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="2" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" s="2" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="2" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="2" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="2" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="2" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="2" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="2" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
     </row>
     <row r="128" spans="1:1">
@@ -8002,12 +8100,12 @@
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="2" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" s="2" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
     </row>
     <row r="132" ht="23.4" spans="1:1">
@@ -8015,62 +8113,62 @@
     </row>
     <row r="133" spans="1:1">
       <c r="A133" s="2" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" s="2" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="2" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" s="2" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" s="2" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" s="2" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" s="2" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="2" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" s="2" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" s="10" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" s="2" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" s="2" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
     </row>
     <row r="154" ht="23.4" spans="1:1">
@@ -8078,62 +8176,62 @@
     </row>
     <row r="156" spans="1:1">
       <c r="A156" s="2" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" s="2" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" s="2" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" s="2" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164" s="2" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" s="2" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" s="2" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170" s="2" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" s="2" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174" s="10" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
     </row>
     <row r="176" spans="1:1">
       <c r="A176" s="2" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" s="2" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
     </row>
     <row r="180" spans="1:1">
@@ -8143,7 +8241,7 @@
     </row>
     <row r="182" spans="1:1">
       <c r="A182" s="2" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
     </row>
     <row r="184" spans="1:1">
@@ -8153,122 +8251,122 @@
     </row>
     <row r="186" spans="1:1">
       <c r="A186" s="2" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
     </row>
     <row r="188" spans="1:1">
       <c r="A188" s="2" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
     </row>
     <row r="189" spans="1:1">
       <c r="A189" s="2" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190" s="2" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191" s="2" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
     </row>
     <row r="192" spans="1:1">
       <c r="A192" s="2" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
     </row>
     <row r="193" spans="1:1">
       <c r="A193" s="2" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194" s="2" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
     </row>
     <row r="195" spans="1:1">
       <c r="A195" s="2" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
     </row>
     <row r="196" spans="1:1">
       <c r="A196" s="2" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
     </row>
     <row r="198" spans="1:1">
       <c r="A198" s="2" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
     </row>
     <row r="199" spans="1:1">
       <c r="A199" s="2" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:1">
       <c r="A201" s="2" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:1">
       <c r="A203" s="2" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
     </row>
     <row r="205" spans="1:1">
       <c r="A205" s="2" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207" s="2" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
     </row>
     <row r="209" spans="1:1">
       <c r="A209" s="2" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
     </row>
     <row r="211" spans="1:1">
       <c r="A211" s="2" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
     </row>
     <row r="213" spans="1:1">
       <c r="A213" s="2" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215" s="2" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
     </row>
     <row r="217" spans="1:1">
       <c r="A217" s="2" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
     </row>
     <row r="219" spans="1:1">
       <c r="A219" s="2" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
     </row>
     <row r="221" spans="1:1">
       <c r="A221" s="2" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223" s="2" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
     </row>
   </sheetData>
@@ -8289,7 +8387,7 @@
   <sheetData>
     <row r="2" spans="3:3">
       <c r="C2" s="1" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
     </row>
     <row r="3" spans="3:3">
@@ -8597,19 +8695,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="55" t="s">
+      <c r="E1" s="56" t="s">
         <v>23</v>
       </c>
     </row>
@@ -8617,191 +8715,191 @@
       <c r="A2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="56">
+      <c r="B2" s="57">
         <v>45976</v>
       </c>
-      <c r="C2" s="57">
+      <c r="C2" s="58">
         <v>45983</v>
       </c>
-      <c r="D2" s="25">
+      <c r="D2" s="24">
         <v>4</v>
       </c>
-      <c r="E2" s="58"/>
+      <c r="E2" s="59"/>
     </row>
     <row r="3" ht="115.2" spans="1:5">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="56">
+      <c r="B3" s="57">
         <v>45976</v>
       </c>
-      <c r="C3" s="57">
+      <c r="C3" s="58">
         <v>45983</v>
       </c>
-      <c r="D3" s="25">
+      <c r="D3" s="24">
         <v>4</v>
       </c>
-      <c r="E3" s="59" t="s">
+      <c r="E3" s="60" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" ht="129.6" spans="1:5">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="56">
+      <c r="B4" s="57">
         <v>45976</v>
       </c>
-      <c r="C4" s="57">
+      <c r="C4" s="58">
         <v>45983</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="24">
         <v>3</v>
       </c>
-      <c r="E4" s="60" t="s">
+      <c r="E4" s="61" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" ht="144" spans="1:5">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="56">
+      <c r="B5" s="57">
         <v>45976</v>
       </c>
-      <c r="C5" s="57">
+      <c r="C5" s="58">
         <v>45983</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="24">
         <v>2</v>
       </c>
-      <c r="E5" s="61"/>
+      <c r="E5" s="62"/>
     </row>
     <row r="6" ht="115.2" spans="1:5">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="56">
+      <c r="B6" s="57">
         <v>45976</v>
       </c>
-      <c r="C6" s="57">
+      <c r="C6" s="58">
         <v>45983</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="24">
         <v>2</v>
       </c>
-      <c r="E6" s="61"/>
+      <c r="E6" s="62"/>
     </row>
     <row r="7" ht="129.6" spans="1:5">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="56">
+      <c r="B7" s="57">
         <v>45976</v>
       </c>
-      <c r="C7" s="57">
+      <c r="C7" s="58">
         <v>45983</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="24">
         <v>2</v>
       </c>
-      <c r="E7" s="61"/>
-    </row>
-    <row r="8" s="54" customFormat="1" ht="144" spans="1:5">
-      <c r="A8" s="62" t="s">
+      <c r="E7" s="62"/>
+    </row>
+    <row r="8" s="55" customFormat="1" ht="144" spans="1:5">
+      <c r="A8" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="57">
+      <c r="B8" s="58">
         <v>45976</v>
       </c>
-      <c r="C8" s="57">
+      <c r="C8" s="58">
         <v>45983</v>
       </c>
-      <c r="D8" s="63">
+      <c r="D8" s="64">
         <v>2</v>
       </c>
-      <c r="E8" s="64"/>
-    </row>
-    <row r="9" s="54" customFormat="1" ht="158.4" spans="1:5">
-      <c r="A9" s="62" t="s">
+      <c r="E8" s="65"/>
+    </row>
+    <row r="9" s="55" customFormat="1" ht="158.4" spans="1:5">
+      <c r="A9" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="57">
+      <c r="B9" s="58">
         <v>45976</v>
       </c>
-      <c r="C9" s="57">
+      <c r="C9" s="58">
         <v>45983</v>
       </c>
-      <c r="D9" s="63">
+      <c r="D9" s="64">
         <v>1</v>
       </c>
-      <c r="E9" s="65"/>
-    </row>
-    <row r="10" s="54" customFormat="1" spans="1:5">
-      <c r="A10" s="63" t="s">
+      <c r="E9" s="66"/>
+    </row>
+    <row r="10" s="55" customFormat="1" spans="1:5">
+      <c r="A10" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="57">
+      <c r="B10" s="58">
         <v>45976</v>
       </c>
-      <c r="C10" s="57">
+      <c r="C10" s="58">
         <v>45983</v>
       </c>
-      <c r="D10" s="63">
+      <c r="D10" s="64">
         <v>1</v>
       </c>
-      <c r="E10" s="66" t="s">
+      <c r="E10" s="67" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" s="54" customFormat="1" spans="1:5">
-      <c r="A11" s="63" t="s">
+    <row r="11" s="55" customFormat="1" spans="1:5">
+      <c r="A11" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="57">
+      <c r="B11" s="58">
         <v>45976</v>
       </c>
-      <c r="C11" s="57">
+      <c r="C11" s="58">
         <v>45983</v>
       </c>
-      <c r="D11" s="63">
+      <c r="D11" s="64">
         <v>1</v>
       </c>
-      <c r="E11" s="66" t="s">
+      <c r="E11" s="67" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" s="54" customFormat="1" spans="1:5">
-      <c r="A12" s="63" t="s">
+    <row r="12" s="55" customFormat="1" spans="1:5">
+      <c r="A12" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="57">
+      <c r="B12" s="58">
         <v>45976</v>
       </c>
-      <c r="C12" s="57">
+      <c r="C12" s="58">
         <v>45983</v>
       </c>
-      <c r="D12" s="63">
+      <c r="D12" s="64">
         <v>1</v>
       </c>
-      <c r="E12" s="66" t="s">
+      <c r="E12" s="67" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="13" ht="14" customHeight="1" spans="1:5">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="57">
+      <c r="B13" s="58">
         <v>45977</v>
       </c>
-      <c r="C13" s="57">
+      <c r="C13" s="58">
         <v>45982</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="24">
         <v>1</v>
       </c>
-      <c r="E13" s="66" t="s">
+      <c r="E13" s="67" t="s">
         <v>35</v>
       </c>
     </row>
@@ -8809,339 +8907,339 @@
       <c r="A14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="57">
+      <c r="B14" s="58">
         <v>45980</v>
       </c>
-      <c r="C14" s="57">
+      <c r="C14" s="58">
         <v>45982</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="24">
         <v>1</v>
       </c>
-      <c r="E14" s="66" t="s">
+      <c r="E14" s="67" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="57">
+      <c r="B15" s="58">
         <v>45980</v>
       </c>
-      <c r="C15" s="57">
+      <c r="C15" s="58">
         <v>45982</v>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="24">
         <v>1</v>
       </c>
-      <c r="E15" s="66" t="s">
+      <c r="E15" s="67" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="57">
+      <c r="B16" s="58">
         <v>45980</v>
       </c>
-      <c r="C16" s="57">
+      <c r="C16" s="58">
         <v>45982</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="24">
         <v>1</v>
       </c>
-      <c r="E16" s="66" t="s">
+      <c r="E16" s="67" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="57">
+      <c r="B17" s="58">
         <v>45980</v>
       </c>
-      <c r="C17" s="57">
+      <c r="C17" s="58">
         <v>45982</v>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="24">
         <v>1</v>
       </c>
-      <c r="E17" s="66" t="s">
+      <c r="E17" s="67" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="25" t="s">
+      <c r="A18" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="57">
+      <c r="B18" s="58">
         <v>45981</v>
       </c>
-      <c r="C18" s="57">
+      <c r="C18" s="58">
         <v>45983</v>
       </c>
-      <c r="D18" s="25">
+      <c r="D18" s="24">
         <v>1</v>
       </c>
-      <c r="E18" s="66" t="s">
+      <c r="E18" s="67" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="25" t="s">
+      <c r="A19" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="57">
+      <c r="B19" s="58">
         <v>45982</v>
       </c>
-      <c r="C19" s="57">
+      <c r="C19" s="58">
         <v>45984</v>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="24">
         <v>1</v>
       </c>
-      <c r="E19" s="66" t="s">
+      <c r="E19" s="67" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="25" t="s">
+      <c r="A20" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="57">
+      <c r="B20" s="58">
         <v>45983</v>
       </c>
-      <c r="C20" s="57">
+      <c r="C20" s="58">
         <v>45985</v>
       </c>
-      <c r="D20" s="25">
+      <c r="D20" s="24">
         <v>1</v>
       </c>
-      <c r="E20" s="66" t="s">
+      <c r="E20" s="67" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="57">
+      <c r="B21" s="58">
         <v>45986</v>
       </c>
-      <c r="C21" s="57">
+      <c r="C21" s="58">
         <v>45987</v>
       </c>
-      <c r="D21" s="25">
+      <c r="D21" s="24">
         <v>1</v>
       </c>
-      <c r="E21" s="66" t="s">
+      <c r="E21" s="67" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="25" t="s">
+      <c r="A22" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="57">
+      <c r="B22" s="58">
         <v>45986</v>
       </c>
-      <c r="C22" s="57">
+      <c r="C22" s="58">
         <v>45987</v>
       </c>
-      <c r="D22" s="25">
+      <c r="D22" s="24">
         <v>1</v>
       </c>
-      <c r="E22" s="66" t="s">
+      <c r="E22" s="67" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="23" ht="14" customHeight="1" spans="1:5">
-      <c r="A23" s="25" t="s">
+      <c r="A23" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="57">
+      <c r="B23" s="58">
         <v>45986</v>
       </c>
-      <c r="C23" s="57">
+      <c r="C23" s="58">
         <v>45987</v>
       </c>
-      <c r="D23" s="25">
+      <c r="D23" s="24">
         <v>1</v>
       </c>
-      <c r="E23" s="66" t="s">
+      <c r="E23" s="67" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="25" t="s">
+      <c r="A24" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="57">
+      <c r="B24" s="58">
         <v>45986</v>
       </c>
-      <c r="C24" s="57">
+      <c r="C24" s="58">
         <v>45987</v>
       </c>
-      <c r="D24" s="25">
+      <c r="D24" s="24">
         <v>1</v>
       </c>
-      <c r="E24" s="66" t="s">
+      <c r="E24" s="67" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="25" t="s">
+      <c r="A25" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="57">
+      <c r="B25" s="58">
         <v>45986</v>
       </c>
-      <c r="C25" s="57">
+      <c r="C25" s="58">
         <v>45987</v>
       </c>
-      <c r="D25" s="25">
+      <c r="D25" s="24">
         <v>1</v>
       </c>
-      <c r="E25" s="66" t="s">
+      <c r="E25" s="67" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="25" t="s">
+      <c r="A26" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="57">
+      <c r="B26" s="58">
         <v>45986</v>
       </c>
-      <c r="C26" s="57">
+      <c r="C26" s="58">
         <v>45987</v>
       </c>
-      <c r="D26" s="25">
+      <c r="D26" s="24">
         <v>1</v>
       </c>
-      <c r="E26" s="66" t="s">
+      <c r="E26" s="67" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="25" t="s">
+      <c r="A27" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="57">
+      <c r="B27" s="58">
         <v>45986</v>
       </c>
-      <c r="C27" s="57">
+      <c r="C27" s="58">
         <v>45987</v>
       </c>
-      <c r="D27" s="25">
+      <c r="D27" s="24">
         <v>1</v>
       </c>
-      <c r="E27" s="66" t="s">
+      <c r="E27" s="67" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="25" t="s">
+      <c r="A28" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="57">
+      <c r="B28" s="58">
         <v>45986</v>
       </c>
-      <c r="C28" s="57">
+      <c r="C28" s="58">
         <v>45987</v>
       </c>
-      <c r="D28" s="25">
+      <c r="D28" s="24">
         <v>1</v>
       </c>
-      <c r="E28" s="66" t="s">
+      <c r="E28" s="67" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="25" t="s">
+      <c r="A29" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="57">
+      <c r="B29" s="58">
         <v>45986</v>
       </c>
-      <c r="C29" s="57">
+      <c r="C29" s="58">
         <v>45987</v>
       </c>
-      <c r="D29" s="25">
+      <c r="D29" s="24">
         <v>1</v>
       </c>
-      <c r="E29" s="66" t="s">
+      <c r="E29" s="67" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="25" t="s">
+      <c r="A30" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="57">
+      <c r="B30" s="58">
         <v>45986</v>
       </c>
-      <c r="C30" s="57">
+      <c r="C30" s="58">
         <v>45987</v>
       </c>
-      <c r="D30" s="25">
+      <c r="D30" s="24">
         <v>1</v>
       </c>
-      <c r="E30" s="66" t="s">
+      <c r="E30" s="67" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="25" t="s">
+      <c r="A31" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="57">
+      <c r="B31" s="58">
         <v>45992</v>
       </c>
-      <c r="C31" s="57">
+      <c r="C31" s="58">
         <v>45993</v>
       </c>
-      <c r="D31" s="25">
+      <c r="D31" s="24">
         <v>1</v>
       </c>
-      <c r="E31" s="66" t="s">
+      <c r="E31" s="67" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="25" t="s">
+      <c r="A32" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="57">
+      <c r="B32" s="58">
         <v>45992</v>
       </c>
-      <c r="C32" s="57">
+      <c r="C32" s="58">
         <v>45993</v>
       </c>
-      <c r="D32" s="25">
+      <c r="D32" s="24">
         <v>1</v>
       </c>
-      <c r="E32" s="66" t="s">
+      <c r="E32" s="67" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="25" t="s">
+      <c r="A33" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="57">
+      <c r="B33" s="58">
         <v>45992</v>
       </c>
-      <c r="C33" s="57">
+      <c r="C33" s="58">
         <v>45993</v>
       </c>
-      <c r="D33" s="25">
+      <c r="D33" s="24">
         <v>1</v>
       </c>
-      <c r="E33" s="66" t="s">
+      <c r="E33" s="67" t="s">
         <v>35</v>
       </c>
     </row>
@@ -9149,606 +9247,606 @@
       <c r="A34" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="57">
+      <c r="B34" s="58">
         <v>45993</v>
       </c>
-      <c r="C34" s="57">
+      <c r="C34" s="58">
         <v>45993</v>
       </c>
-      <c r="D34" s="25">
+      <c r="D34" s="24">
         <v>1</v>
       </c>
-      <c r="E34" s="66" t="s">
+      <c r="E34" s="67" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="29"/>
-      <c r="B35" s="25"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
+      <c r="A35" s="28"/>
+      <c r="B35" s="24"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="25"/>
-      <c r="B36" s="25"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="25"/>
+      <c r="A36" s="24"/>
+      <c r="B36" s="24"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="25"/>
-      <c r="B37" s="25"/>
-      <c r="C37" s="25"/>
-      <c r="D37" s="25"/>
-      <c r="E37" s="25"/>
+      <c r="A37" s="24"/>
+      <c r="B37" s="24"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="25"/>
-      <c r="B38" s="25"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="25"/>
-      <c r="E38" s="25"/>
+      <c r="A38" s="24"/>
+      <c r="B38" s="24"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="24"/>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="25"/>
-      <c r="B39" s="25"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="25"/>
+      <c r="A39" s="24"/>
+      <c r="B39" s="24"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="25"/>
-      <c r="B40" s="25"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="25"/>
+      <c r="A40" s="24"/>
+      <c r="B40" s="24"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="25"/>
-      <c r="B41" s="25"/>
-      <c r="C41" s="25"/>
-      <c r="D41" s="25"/>
-      <c r="E41" s="25"/>
+      <c r="A41" s="24"/>
+      <c r="B41" s="24"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="25"/>
-      <c r="B42" s="25"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="25"/>
-      <c r="E42" s="25"/>
+      <c r="A42" s="24"/>
+      <c r="B42" s="24"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="25"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="25"/>
-      <c r="D43" s="25"/>
-      <c r="E43" s="25"/>
+      <c r="A43" s="24"/>
+      <c r="B43" s="24"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="24"/>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="25"/>
-      <c r="B44" s="25"/>
-      <c r="C44" s="25"/>
-      <c r="D44" s="25"/>
-      <c r="E44" s="25"/>
+      <c r="A44" s="24"/>
+      <c r="B44" s="24"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="24"/>
+      <c r="E44" s="24"/>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="25"/>
-      <c r="B45" s="25"/>
-      <c r="C45" s="25"/>
-      <c r="D45" s="25"/>
-      <c r="E45" s="25"/>
+      <c r="A45" s="24"/>
+      <c r="B45" s="24"/>
+      <c r="C45" s="24"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="24"/>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="25"/>
-      <c r="B46" s="25"/>
-      <c r="C46" s="25"/>
-      <c r="D46" s="25"/>
-      <c r="E46" s="25"/>
+      <c r="A46" s="24"/>
+      <c r="B46" s="24"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="24"/>
+      <c r="E46" s="24"/>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="25"/>
-      <c r="B47" s="25"/>
-      <c r="C47" s="25"/>
-      <c r="D47" s="25"/>
-      <c r="E47" s="25"/>
+      <c r="A47" s="24"/>
+      <c r="B47" s="24"/>
+      <c r="C47" s="24"/>
+      <c r="D47" s="24"/>
+      <c r="E47" s="24"/>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="25"/>
-      <c r="B48" s="25"/>
-      <c r="C48" s="25"/>
-      <c r="D48" s="25"/>
-      <c r="E48" s="25"/>
+      <c r="A48" s="24"/>
+      <c r="B48" s="24"/>
+      <c r="C48" s="24"/>
+      <c r="D48" s="24"/>
+      <c r="E48" s="24"/>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="25"/>
-      <c r="B49" s="25"/>
-      <c r="C49" s="25"/>
-      <c r="D49" s="25"/>
-      <c r="E49" s="25"/>
+      <c r="A49" s="24"/>
+      <c r="B49" s="24"/>
+      <c r="C49" s="24"/>
+      <c r="D49" s="24"/>
+      <c r="E49" s="24"/>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="25"/>
-      <c r="B50" s="25"/>
-      <c r="C50" s="25"/>
-      <c r="D50" s="25"/>
-      <c r="E50" s="25"/>
+      <c r="A50" s="24"/>
+      <c r="B50" s="24"/>
+      <c r="C50" s="24"/>
+      <c r="D50" s="24"/>
+      <c r="E50" s="24"/>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="25"/>
-      <c r="B51" s="25"/>
-      <c r="C51" s="25"/>
-      <c r="D51" s="25"/>
-      <c r="E51" s="25"/>
+      <c r="A51" s="24"/>
+      <c r="B51" s="24"/>
+      <c r="C51" s="24"/>
+      <c r="D51" s="24"/>
+      <c r="E51" s="24"/>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="25"/>
-      <c r="B52" s="25"/>
-      <c r="C52" s="25"/>
-      <c r="D52" s="25"/>
-      <c r="E52" s="25"/>
+      <c r="A52" s="24"/>
+      <c r="B52" s="24"/>
+      <c r="C52" s="24"/>
+      <c r="D52" s="24"/>
+      <c r="E52" s="24"/>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="25"/>
-      <c r="B53" s="25"/>
-      <c r="C53" s="25"/>
-      <c r="D53" s="25"/>
-      <c r="E53" s="25"/>
+      <c r="A53" s="24"/>
+      <c r="B53" s="24"/>
+      <c r="C53" s="24"/>
+      <c r="D53" s="24"/>
+      <c r="E53" s="24"/>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="25"/>
-      <c r="B54" s="25"/>
-      <c r="C54" s="25"/>
-      <c r="D54" s="25"/>
-      <c r="E54" s="25"/>
+      <c r="A54" s="24"/>
+      <c r="B54" s="24"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="24"/>
+      <c r="E54" s="24"/>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="25"/>
-      <c r="B55" s="25"/>
-      <c r="C55" s="25"/>
-      <c r="D55" s="25"/>
-      <c r="E55" s="25"/>
+      <c r="A55" s="24"/>
+      <c r="B55" s="24"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="24"/>
+      <c r="E55" s="24"/>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="25"/>
-      <c r="B56" s="25"/>
-      <c r="C56" s="25"/>
-      <c r="D56" s="25"/>
-      <c r="E56" s="25"/>
+      <c r="A56" s="24"/>
+      <c r="B56" s="24"/>
+      <c r="C56" s="24"/>
+      <c r="D56" s="24"/>
+      <c r="E56" s="24"/>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="25"/>
-      <c r="B57" s="25"/>
-      <c r="C57" s="25"/>
-      <c r="D57" s="25"/>
-      <c r="E57" s="25"/>
+      <c r="A57" s="24"/>
+      <c r="B57" s="24"/>
+      <c r="C57" s="24"/>
+      <c r="D57" s="24"/>
+      <c r="E57" s="24"/>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="25"/>
-      <c r="B58" s="25"/>
-      <c r="C58" s="25"/>
-      <c r="D58" s="25"/>
-      <c r="E58" s="25"/>
+      <c r="A58" s="24"/>
+      <c r="B58" s="24"/>
+      <c r="C58" s="24"/>
+      <c r="D58" s="24"/>
+      <c r="E58" s="24"/>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="25"/>
-      <c r="B59" s="25"/>
-      <c r="C59" s="25"/>
-      <c r="D59" s="25"/>
-      <c r="E59" s="25"/>
+      <c r="A59" s="24"/>
+      <c r="B59" s="24"/>
+      <c r="C59" s="24"/>
+      <c r="D59" s="24"/>
+      <c r="E59" s="24"/>
     </row>
     <row r="60" spans="1:5">
-      <c r="A60" s="25"/>
-      <c r="B60" s="25"/>
-      <c r="C60" s="25"/>
-      <c r="D60" s="25"/>
-      <c r="E60" s="25"/>
+      <c r="A60" s="24"/>
+      <c r="B60" s="24"/>
+      <c r="C60" s="24"/>
+      <c r="D60" s="24"/>
+      <c r="E60" s="24"/>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="25"/>
-      <c r="B61" s="25"/>
-      <c r="C61" s="25"/>
-      <c r="D61" s="25"/>
-      <c r="E61" s="25"/>
+      <c r="A61" s="24"/>
+      <c r="B61" s="24"/>
+      <c r="C61" s="24"/>
+      <c r="D61" s="24"/>
+      <c r="E61" s="24"/>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="25"/>
-      <c r="B62" s="25"/>
-      <c r="C62" s="25"/>
-      <c r="D62" s="25"/>
-      <c r="E62" s="25"/>
+      <c r="A62" s="24"/>
+      <c r="B62" s="24"/>
+      <c r="C62" s="24"/>
+      <c r="D62" s="24"/>
+      <c r="E62" s="24"/>
     </row>
     <row r="63" spans="1:5">
-      <c r="A63" s="25"/>
-      <c r="B63" s="25"/>
-      <c r="C63" s="25"/>
-      <c r="D63" s="25"/>
-      <c r="E63" s="25"/>
+      <c r="A63" s="24"/>
+      <c r="B63" s="24"/>
+      <c r="C63" s="24"/>
+      <c r="D63" s="24"/>
+      <c r="E63" s="24"/>
     </row>
     <row r="64" spans="1:5">
-      <c r="A64" s="25"/>
-      <c r="B64" s="25"/>
-      <c r="C64" s="25"/>
-      <c r="D64" s="25"/>
-      <c r="E64" s="25"/>
+      <c r="A64" s="24"/>
+      <c r="B64" s="24"/>
+      <c r="C64" s="24"/>
+      <c r="D64" s="24"/>
+      <c r="E64" s="24"/>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="25"/>
-      <c r="B65" s="25"/>
-      <c r="C65" s="25"/>
-      <c r="D65" s="25"/>
-      <c r="E65" s="25"/>
+      <c r="A65" s="24"/>
+      <c r="B65" s="24"/>
+      <c r="C65" s="24"/>
+      <c r="D65" s="24"/>
+      <c r="E65" s="24"/>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="25"/>
-      <c r="B66" s="25"/>
-      <c r="C66" s="25"/>
-      <c r="D66" s="25"/>
-      <c r="E66" s="25"/>
+      <c r="A66" s="24"/>
+      <c r="B66" s="24"/>
+      <c r="C66" s="24"/>
+      <c r="D66" s="24"/>
+      <c r="E66" s="24"/>
     </row>
     <row r="67" spans="1:5">
-      <c r="A67" s="25"/>
-      <c r="B67" s="25"/>
-      <c r="C67" s="25"/>
-      <c r="D67" s="25"/>
-      <c r="E67" s="25"/>
+      <c r="A67" s="24"/>
+      <c r="B67" s="24"/>
+      <c r="C67" s="24"/>
+      <c r="D67" s="24"/>
+      <c r="E67" s="24"/>
     </row>
     <row r="68" spans="1:5">
-      <c r="A68" s="25"/>
-      <c r="B68" s="25"/>
-      <c r="C68" s="25"/>
-      <c r="D68" s="25"/>
-      <c r="E68" s="25"/>
+      <c r="A68" s="24"/>
+      <c r="B68" s="24"/>
+      <c r="C68" s="24"/>
+      <c r="D68" s="24"/>
+      <c r="E68" s="24"/>
     </row>
     <row r="69" spans="1:5">
-      <c r="A69" s="25"/>
-      <c r="B69" s="25"/>
-      <c r="C69" s="25"/>
-      <c r="D69" s="25"/>
-      <c r="E69" s="25"/>
+      <c r="A69" s="24"/>
+      <c r="B69" s="24"/>
+      <c r="C69" s="24"/>
+      <c r="D69" s="24"/>
+      <c r="E69" s="24"/>
     </row>
     <row r="70" spans="1:5">
-      <c r="A70" s="25"/>
-      <c r="B70" s="25"/>
-      <c r="C70" s="25"/>
-      <c r="D70" s="25"/>
-      <c r="E70" s="25"/>
+      <c r="A70" s="24"/>
+      <c r="B70" s="24"/>
+      <c r="C70" s="24"/>
+      <c r="D70" s="24"/>
+      <c r="E70" s="24"/>
     </row>
     <row r="71" spans="1:5">
-      <c r="A71" s="25"/>
-      <c r="B71" s="25"/>
-      <c r="C71" s="25"/>
-      <c r="D71" s="25"/>
-      <c r="E71" s="25"/>
+      <c r="A71" s="24"/>
+      <c r="B71" s="24"/>
+      <c r="C71" s="24"/>
+      <c r="D71" s="24"/>
+      <c r="E71" s="24"/>
     </row>
     <row r="72" spans="1:5">
-      <c r="A72" s="25"/>
-      <c r="B72" s="25"/>
-      <c r="C72" s="25"/>
-      <c r="D72" s="25"/>
-      <c r="E72" s="25"/>
+      <c r="A72" s="24"/>
+      <c r="B72" s="24"/>
+      <c r="C72" s="24"/>
+      <c r="D72" s="24"/>
+      <c r="E72" s="24"/>
     </row>
     <row r="73" spans="1:5">
-      <c r="A73" s="25"/>
-      <c r="B73" s="25"/>
-      <c r="C73" s="25"/>
-      <c r="D73" s="25"/>
-      <c r="E73" s="25"/>
+      <c r="A73" s="24"/>
+      <c r="B73" s="24"/>
+      <c r="C73" s="24"/>
+      <c r="D73" s="24"/>
+      <c r="E73" s="24"/>
     </row>
     <row r="74" spans="1:5">
-      <c r="A74" s="25"/>
-      <c r="B74" s="25"/>
-      <c r="C74" s="25"/>
-      <c r="D74" s="25"/>
-      <c r="E74" s="25"/>
+      <c r="A74" s="24"/>
+      <c r="B74" s="24"/>
+      <c r="C74" s="24"/>
+      <c r="D74" s="24"/>
+      <c r="E74" s="24"/>
     </row>
     <row r="75" spans="1:5">
-      <c r="A75" s="25"/>
-      <c r="B75" s="25"/>
-      <c r="C75" s="25"/>
-      <c r="D75" s="25"/>
-      <c r="E75" s="25"/>
+      <c r="A75" s="24"/>
+      <c r="B75" s="24"/>
+      <c r="C75" s="24"/>
+      <c r="D75" s="24"/>
+      <c r="E75" s="24"/>
     </row>
     <row r="76" spans="1:5">
-      <c r="A76" s="25"/>
-      <c r="B76" s="25"/>
-      <c r="C76" s="25"/>
-      <c r="D76" s="25"/>
-      <c r="E76" s="25"/>
+      <c r="A76" s="24"/>
+      <c r="B76" s="24"/>
+      <c r="C76" s="24"/>
+      <c r="D76" s="24"/>
+      <c r="E76" s="24"/>
     </row>
     <row r="77" spans="1:5">
-      <c r="A77" s="25"/>
-      <c r="B77" s="25"/>
-      <c r="C77" s="25"/>
-      <c r="D77" s="25"/>
-      <c r="E77" s="25"/>
+      <c r="A77" s="24"/>
+      <c r="B77" s="24"/>
+      <c r="C77" s="24"/>
+      <c r="D77" s="24"/>
+      <c r="E77" s="24"/>
     </row>
     <row r="78" spans="1:5">
-      <c r="A78" s="25"/>
-      <c r="B78" s="25"/>
-      <c r="C78" s="25"/>
-      <c r="D78" s="25"/>
-      <c r="E78" s="25"/>
+      <c r="A78" s="24"/>
+      <c r="B78" s="24"/>
+      <c r="C78" s="24"/>
+      <c r="D78" s="24"/>
+      <c r="E78" s="24"/>
     </row>
     <row r="79" spans="1:5">
-      <c r="A79" s="25"/>
-      <c r="B79" s="25"/>
-      <c r="C79" s="25"/>
-      <c r="D79" s="25"/>
-      <c r="E79" s="25"/>
+      <c r="A79" s="24"/>
+      <c r="B79" s="24"/>
+      <c r="C79" s="24"/>
+      <c r="D79" s="24"/>
+      <c r="E79" s="24"/>
     </row>
     <row r="80" spans="1:5">
-      <c r="A80" s="25"/>
-      <c r="B80" s="25"/>
-      <c r="C80" s="25"/>
-      <c r="D80" s="25"/>
-      <c r="E80" s="25"/>
+      <c r="A80" s="24"/>
+      <c r="B80" s="24"/>
+      <c r="C80" s="24"/>
+      <c r="D80" s="24"/>
+      <c r="E80" s="24"/>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="25"/>
-      <c r="B81" s="25"/>
-      <c r="C81" s="25"/>
-      <c r="D81" s="25"/>
-      <c r="E81" s="25"/>
+      <c r="A81" s="24"/>
+      <c r="B81" s="24"/>
+      <c r="C81" s="24"/>
+      <c r="D81" s="24"/>
+      <c r="E81" s="24"/>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="25"/>
-      <c r="B82" s="25"/>
-      <c r="C82" s="25"/>
-      <c r="D82" s="25"/>
-      <c r="E82" s="25"/>
+      <c r="A82" s="24"/>
+      <c r="B82" s="24"/>
+      <c r="C82" s="24"/>
+      <c r="D82" s="24"/>
+      <c r="E82" s="24"/>
     </row>
     <row r="83" spans="1:5">
-      <c r="A83" s="25"/>
-      <c r="B83" s="25"/>
-      <c r="C83" s="25"/>
-      <c r="D83" s="25"/>
-      <c r="E83" s="25"/>
+      <c r="A83" s="24"/>
+      <c r="B83" s="24"/>
+      <c r="C83" s="24"/>
+      <c r="D83" s="24"/>
+      <c r="E83" s="24"/>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="25"/>
-      <c r="B84" s="25"/>
-      <c r="C84" s="25"/>
-      <c r="D84" s="25"/>
-      <c r="E84" s="25"/>
+      <c r="A84" s="24"/>
+      <c r="B84" s="24"/>
+      <c r="C84" s="24"/>
+      <c r="D84" s="24"/>
+      <c r="E84" s="24"/>
     </row>
     <row r="85" spans="1:5">
-      <c r="A85" s="25"/>
-      <c r="B85" s="25"/>
-      <c r="C85" s="25"/>
-      <c r="D85" s="25"/>
-      <c r="E85" s="25"/>
+      <c r="A85" s="24"/>
+      <c r="B85" s="24"/>
+      <c r="C85" s="24"/>
+      <c r="D85" s="24"/>
+      <c r="E85" s="24"/>
     </row>
     <row r="86" spans="1:5">
-      <c r="A86" s="25"/>
-      <c r="B86" s="25"/>
-      <c r="C86" s="25"/>
-      <c r="D86" s="25"/>
-      <c r="E86" s="25"/>
+      <c r="A86" s="24"/>
+      <c r="B86" s="24"/>
+      <c r="C86" s="24"/>
+      <c r="D86" s="24"/>
+      <c r="E86" s="24"/>
     </row>
     <row r="87" spans="1:5">
-      <c r="A87" s="25"/>
-      <c r="B87" s="25"/>
-      <c r="C87" s="25"/>
-      <c r="D87" s="25"/>
-      <c r="E87" s="25"/>
+      <c r="A87" s="24"/>
+      <c r="B87" s="24"/>
+      <c r="C87" s="24"/>
+      <c r="D87" s="24"/>
+      <c r="E87" s="24"/>
     </row>
     <row r="88" spans="1:5">
-      <c r="A88" s="25"/>
-      <c r="B88" s="25"/>
-      <c r="C88" s="25"/>
-      <c r="D88" s="25"/>
-      <c r="E88" s="25"/>
+      <c r="A88" s="24"/>
+      <c r="B88" s="24"/>
+      <c r="C88" s="24"/>
+      <c r="D88" s="24"/>
+      <c r="E88" s="24"/>
     </row>
     <row r="89" spans="1:5">
-      <c r="A89" s="25"/>
-      <c r="B89" s="25"/>
-      <c r="C89" s="25"/>
-      <c r="D89" s="25"/>
-      <c r="E89" s="25"/>
+      <c r="A89" s="24"/>
+      <c r="B89" s="24"/>
+      <c r="C89" s="24"/>
+      <c r="D89" s="24"/>
+      <c r="E89" s="24"/>
     </row>
     <row r="90" spans="1:5">
-      <c r="A90" s="25"/>
-      <c r="B90" s="25"/>
-      <c r="C90" s="25"/>
-      <c r="D90" s="25"/>
-      <c r="E90" s="25"/>
+      <c r="A90" s="24"/>
+      <c r="B90" s="24"/>
+      <c r="C90" s="24"/>
+      <c r="D90" s="24"/>
+      <c r="E90" s="24"/>
     </row>
     <row r="91" spans="1:5">
-      <c r="A91" s="25"/>
-      <c r="B91" s="25"/>
-      <c r="C91" s="25"/>
-      <c r="D91" s="25"/>
-      <c r="E91" s="25"/>
+      <c r="A91" s="24"/>
+      <c r="B91" s="24"/>
+      <c r="C91" s="24"/>
+      <c r="D91" s="24"/>
+      <c r="E91" s="24"/>
     </row>
     <row r="92" spans="1:5">
-      <c r="A92" s="25"/>
-      <c r="B92" s="25"/>
-      <c r="C92" s="25"/>
-      <c r="D92" s="25"/>
-      <c r="E92" s="25"/>
+      <c r="A92" s="24"/>
+      <c r="B92" s="24"/>
+      <c r="C92" s="24"/>
+      <c r="D92" s="24"/>
+      <c r="E92" s="24"/>
     </row>
     <row r="93" spans="1:5">
-      <c r="A93" s="25"/>
-      <c r="B93" s="25"/>
-      <c r="C93" s="25"/>
-      <c r="D93" s="25"/>
-      <c r="E93" s="25"/>
+      <c r="A93" s="24"/>
+      <c r="B93" s="24"/>
+      <c r="C93" s="24"/>
+      <c r="D93" s="24"/>
+      <c r="E93" s="24"/>
     </row>
     <row r="94" spans="1:5">
-      <c r="A94" s="25"/>
-      <c r="B94" s="25"/>
-      <c r="C94" s="25"/>
-      <c r="D94" s="25"/>
-      <c r="E94" s="25"/>
+      <c r="A94" s="24"/>
+      <c r="B94" s="24"/>
+      <c r="C94" s="24"/>
+      <c r="D94" s="24"/>
+      <c r="E94" s="24"/>
     </row>
     <row r="95" spans="1:5">
-      <c r="A95" s="25"/>
-      <c r="B95" s="25"/>
-      <c r="C95" s="25"/>
-      <c r="D95" s="25"/>
-      <c r="E95" s="25"/>
+      <c r="A95" s="24"/>
+      <c r="B95" s="24"/>
+      <c r="C95" s="24"/>
+      <c r="D95" s="24"/>
+      <c r="E95" s="24"/>
     </row>
     <row r="96" spans="1:5">
-      <c r="A96" s="25"/>
-      <c r="B96" s="25"/>
-      <c r="C96" s="25"/>
-      <c r="D96" s="25"/>
-      <c r="E96" s="25"/>
+      <c r="A96" s="24"/>
+      <c r="B96" s="24"/>
+      <c r="C96" s="24"/>
+      <c r="D96" s="24"/>
+      <c r="E96" s="24"/>
     </row>
     <row r="97" spans="1:5">
-      <c r="A97" s="25"/>
-      <c r="B97" s="25"/>
-      <c r="C97" s="25"/>
-      <c r="D97" s="25"/>
-      <c r="E97" s="25"/>
+      <c r="A97" s="24"/>
+      <c r="B97" s="24"/>
+      <c r="C97" s="24"/>
+      <c r="D97" s="24"/>
+      <c r="E97" s="24"/>
     </row>
     <row r="98" spans="1:5">
-      <c r="A98" s="25"/>
-      <c r="B98" s="25"/>
-      <c r="C98" s="25"/>
-      <c r="D98" s="25"/>
-      <c r="E98" s="25"/>
+      <c r="A98" s="24"/>
+      <c r="B98" s="24"/>
+      <c r="C98" s="24"/>
+      <c r="D98" s="24"/>
+      <c r="E98" s="24"/>
     </row>
     <row r="99" spans="1:5">
-      <c r="A99" s="25"/>
-      <c r="B99" s="25"/>
-      <c r="C99" s="25"/>
-      <c r="D99" s="25"/>
-      <c r="E99" s="25"/>
+      <c r="A99" s="24"/>
+      <c r="B99" s="24"/>
+      <c r="C99" s="24"/>
+      <c r="D99" s="24"/>
+      <c r="E99" s="24"/>
     </row>
     <row r="100" spans="1:5">
-      <c r="A100" s="25"/>
-      <c r="B100" s="25"/>
-      <c r="C100" s="25"/>
-      <c r="D100" s="25"/>
-      <c r="E100" s="25"/>
+      <c r="A100" s="24"/>
+      <c r="B100" s="24"/>
+      <c r="C100" s="24"/>
+      <c r="D100" s="24"/>
+      <c r="E100" s="24"/>
     </row>
     <row r="101" spans="1:5">
-      <c r="A101" s="25"/>
-      <c r="B101" s="25"/>
-      <c r="C101" s="25"/>
-      <c r="D101" s="25"/>
-      <c r="E101" s="25"/>
+      <c r="A101" s="24"/>
+      <c r="B101" s="24"/>
+      <c r="C101" s="24"/>
+      <c r="D101" s="24"/>
+      <c r="E101" s="24"/>
     </row>
     <row r="102" spans="1:5">
-      <c r="A102" s="25"/>
-      <c r="B102" s="25"/>
-      <c r="C102" s="25"/>
-      <c r="D102" s="25"/>
-      <c r="E102" s="25"/>
+      <c r="A102" s="24"/>
+      <c r="B102" s="24"/>
+      <c r="C102" s="24"/>
+      <c r="D102" s="24"/>
+      <c r="E102" s="24"/>
     </row>
     <row r="103" spans="1:5">
-      <c r="A103" s="25"/>
-      <c r="B103" s="25"/>
-      <c r="C103" s="25"/>
-      <c r="D103" s="25"/>
-      <c r="E103" s="25"/>
+      <c r="A103" s="24"/>
+      <c r="B103" s="24"/>
+      <c r="C103" s="24"/>
+      <c r="D103" s="24"/>
+      <c r="E103" s="24"/>
     </row>
     <row r="104" spans="1:5">
-      <c r="A104" s="25"/>
-      <c r="B104" s="25"/>
-      <c r="C104" s="25"/>
-      <c r="D104" s="25"/>
-      <c r="E104" s="25"/>
+      <c r="A104" s="24"/>
+      <c r="B104" s="24"/>
+      <c r="C104" s="24"/>
+      <c r="D104" s="24"/>
+      <c r="E104" s="24"/>
     </row>
     <row r="105" spans="1:5">
-      <c r="A105" s="25"/>
-      <c r="B105" s="25"/>
-      <c r="C105" s="25"/>
-      <c r="D105" s="25"/>
-      <c r="E105" s="25"/>
+      <c r="A105" s="24"/>
+      <c r="B105" s="24"/>
+      <c r="C105" s="24"/>
+      <c r="D105" s="24"/>
+      <c r="E105" s="24"/>
     </row>
     <row r="106" spans="1:5">
-      <c r="A106" s="25"/>
-      <c r="B106" s="25"/>
-      <c r="C106" s="25"/>
-      <c r="D106" s="25"/>
-      <c r="E106" s="25"/>
+      <c r="A106" s="24"/>
+      <c r="B106" s="24"/>
+      <c r="C106" s="24"/>
+      <c r="D106" s="24"/>
+      <c r="E106" s="24"/>
     </row>
     <row r="107" spans="1:5">
-      <c r="A107" s="25"/>
-      <c r="B107" s="25"/>
-      <c r="C107" s="25"/>
-      <c r="D107" s="25"/>
-      <c r="E107" s="25"/>
+      <c r="A107" s="24"/>
+      <c r="B107" s="24"/>
+      <c r="C107" s="24"/>
+      <c r="D107" s="24"/>
+      <c r="E107" s="24"/>
     </row>
     <row r="108" spans="1:5">
-      <c r="A108" s="25"/>
-      <c r="B108" s="25"/>
-      <c r="C108" s="25"/>
-      <c r="D108" s="25"/>
-      <c r="E108" s="25"/>
+      <c r="A108" s="24"/>
+      <c r="B108" s="24"/>
+      <c r="C108" s="24"/>
+      <c r="D108" s="24"/>
+      <c r="E108" s="24"/>
     </row>
     <row r="109" spans="1:5">
-      <c r="A109" s="25"/>
-      <c r="B109" s="25"/>
-      <c r="C109" s="25"/>
-      <c r="D109" s="25"/>
-      <c r="E109" s="25"/>
+      <c r="A109" s="24"/>
+      <c r="B109" s="24"/>
+      <c r="C109" s="24"/>
+      <c r="D109" s="24"/>
+      <c r="E109" s="24"/>
     </row>
     <row r="110" spans="1:5">
-      <c r="A110" s="25"/>
-      <c r="B110" s="25"/>
-      <c r="C110" s="25"/>
-      <c r="D110" s="25"/>
-      <c r="E110" s="25"/>
+      <c r="A110" s="24"/>
+      <c r="B110" s="24"/>
+      <c r="C110" s="24"/>
+      <c r="D110" s="24"/>
+      <c r="E110" s="24"/>
     </row>
     <row r="111" spans="1:5">
-      <c r="A111" s="25"/>
-      <c r="B111" s="25"/>
-      <c r="C111" s="25"/>
-      <c r="D111" s="25"/>
-      <c r="E111" s="25"/>
+      <c r="A111" s="24"/>
+      <c r="B111" s="24"/>
+      <c r="C111" s="24"/>
+      <c r="D111" s="24"/>
+      <c r="E111" s="24"/>
     </row>
     <row r="112" spans="1:5">
-      <c r="A112" s="25"/>
-      <c r="B112" s="25"/>
-      <c r="C112" s="25"/>
-      <c r="D112" s="25"/>
-      <c r="E112" s="25"/>
+      <c r="A112" s="24"/>
+      <c r="B112" s="24"/>
+      <c r="C112" s="24"/>
+      <c r="D112" s="24"/>
+      <c r="E112" s="24"/>
     </row>
     <row r="113" spans="1:5">
-      <c r="A113" s="25"/>
-      <c r="B113" s="25"/>
-      <c r="C113" s="25"/>
-      <c r="D113" s="25"/>
-      <c r="E113" s="25"/>
+      <c r="A113" s="24"/>
+      <c r="B113" s="24"/>
+      <c r="C113" s="24"/>
+      <c r="D113" s="24"/>
+      <c r="E113" s="24"/>
     </row>
     <row r="114" spans="1:5">
-      <c r="A114" s="25"/>
-      <c r="B114" s="25"/>
-      <c r="C114" s="25"/>
-      <c r="D114" s="25"/>
-      <c r="E114" s="25"/>
+      <c r="A114" s="24"/>
+      <c r="B114" s="24"/>
+      <c r="C114" s="24"/>
+      <c r="D114" s="24"/>
+      <c r="E114" s="24"/>
     </row>
     <row r="115" spans="1:5">
-      <c r="A115" s="25"/>
-      <c r="B115" s="25"/>
-      <c r="C115" s="25"/>
-      <c r="D115" s="25"/>
-      <c r="E115" s="25"/>
+      <c r="A115" s="24"/>
+      <c r="B115" s="24"/>
+      <c r="C115" s="24"/>
+      <c r="D115" s="24"/>
+      <c r="E115" s="24"/>
     </row>
     <row r="116" spans="1:5">
-      <c r="A116" s="25"/>
-      <c r="B116" s="25"/>
-      <c r="C116" s="25"/>
-      <c r="D116" s="25"/>
-      <c r="E116" s="25"/>
+      <c r="A116" s="24"/>
+      <c r="B116" s="24"/>
+      <c r="C116" s="24"/>
+      <c r="D116" s="24"/>
+      <c r="E116" s="24"/>
     </row>
     <row r="117" spans="1:5">
-      <c r="A117" s="25"/>
-      <c r="B117" s="25"/>
-      <c r="C117" s="25"/>
-      <c r="D117" s="25"/>
-      <c r="E117" s="25"/>
+      <c r="A117" s="24"/>
+      <c r="B117" s="24"/>
+      <c r="C117" s="24"/>
+      <c r="D117" s="24"/>
+      <c r="E117" s="24"/>
     </row>
     <row r="118" spans="1:5">
-      <c r="A118" s="25"/>
-      <c r="B118" s="25"/>
-      <c r="C118" s="25"/>
-      <c r="D118" s="25"/>
-      <c r="E118" s="25"/>
+      <c r="A118" s="24"/>
+      <c r="B118" s="24"/>
+      <c r="C118" s="24"/>
+      <c r="D118" s="24"/>
+      <c r="E118" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -9763,7 +9861,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="24.7777777777778" customWidth="1"/>
@@ -9772,312 +9870,347 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="47" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="2" ht="409.5" spans="1:3">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="31" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="3" ht="86.4" spans="1:3">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="29"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" ht="57.6" spans="1:3">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="29"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" ht="72" spans="1:3">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="29"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="29"/>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
+      <c r="A6" s="28"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" ht="144" spans="1:3">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="29"/>
+      <c r="C7" s="28"/>
     </row>
     <row r="8" ht="158.4" spans="1:3">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="29"/>
+      <c r="C8" s="28"/>
     </row>
     <row r="9" ht="345.6" spans="1:3">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="C9" s="29"/>
+      <c r="C9" s="28"/>
     </row>
     <row r="10" ht="403.2" spans="1:3">
-      <c r="A10" s="29"/>
-      <c r="B10" s="32" t="s">
+      <c r="A10" s="28"/>
+      <c r="B10" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="C10" s="29"/>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="29"/>
-      <c r="C11" s="29"/>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="29"/>
-      <c r="C12" s="29"/>
-    </row>
-    <row r="13" ht="409.5" spans="1:3">
-      <c r="A13" s="29"/>
-      <c r="B13" s="32" t="s">
+      <c r="C10" s="28"/>
+    </row>
+    <row r="11" ht="259.2" spans="1:3">
+      <c r="A11" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="29"/>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="29"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="29"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="29"/>
+      <c r="B11" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="28"/>
+    </row>
+    <row r="12" ht="43.2" spans="1:3">
+      <c r="A12" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" s="28"/>
+    </row>
+    <row r="13" ht="115.2" spans="1:3">
+      <c r="A13" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="51" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="28"/>
+    </row>
+    <row r="14" ht="187.2" spans="1:3">
+      <c r="A14" s="52" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" s="51" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" s="28"/>
+    </row>
+    <row r="15" ht="201.6" spans="1:3">
+      <c r="A15" s="53" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" s="54" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="28"/>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="29"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
+      <c r="A16" s="28"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="28"/>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="29"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="29"/>
+      <c r="A17" s="28"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="29"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="29"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="29"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="29"/>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="29"/>
-      <c r="B21" s="29"/>
-      <c r="C21" s="29"/>
+      <c r="A21" s="28"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="28"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="29"/>
-      <c r="B22" s="29"/>
-      <c r="C22" s="29"/>
+      <c r="A22" s="28"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="28"/>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="29"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
+      <c r="A23" s="28"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="28"/>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="29"/>
-      <c r="B24" s="29"/>
-      <c r="C24" s="29"/>
+      <c r="A24" s="28"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="28"/>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="29"/>
-      <c r="B25" s="29"/>
-      <c r="C25" s="29"/>
+      <c r="A25" s="28"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="28"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="29"/>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
+      <c r="A26" s="28"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="29"/>
-      <c r="B27" s="29"/>
-      <c r="C27" s="29"/>
+      <c r="A27" s="28"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="29"/>
-      <c r="B28" s="29"/>
-      <c r="C28" s="29"/>
+      <c r="A28" s="28"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="28"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="29"/>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
+      <c r="A29" s="28"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="29"/>
-      <c r="B30" s="29"/>
-      <c r="C30" s="29"/>
+      <c r="A30" s="28"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="29"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="29"/>
+      <c r="A31" s="28"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="28"/>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="29"/>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
+      <c r="A32" s="28"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="29"/>
-      <c r="B33" s="29"/>
-      <c r="C33" s="29"/>
+      <c r="A33" s="28"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="28"/>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="29"/>
-      <c r="B34" s="29"/>
-      <c r="C34" s="29"/>
+      <c r="A34" s="28"/>
+      <c r="B34" s="28"/>
+      <c r="C34" s="28"/>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="29"/>
-      <c r="B35" s="29"/>
-      <c r="C35" s="29"/>
+      <c r="A35" s="28"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="28"/>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="29"/>
-      <c r="B36" s="29"/>
-      <c r="C36" s="29"/>
+      <c r="A36" s="28"/>
+      <c r="B36" s="28"/>
+      <c r="C36" s="28"/>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="29"/>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
+      <c r="A37" s="28"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="29"/>
-      <c r="B38" s="29"/>
-      <c r="C38" s="29"/>
+      <c r="A38" s="28"/>
+      <c r="B38" s="28"/>
+      <c r="C38" s="28"/>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="29"/>
-      <c r="B39" s="29"/>
-      <c r="C39" s="29"/>
+      <c r="A39" s="28"/>
+      <c r="B39" s="28"/>
+      <c r="C39" s="28"/>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="29"/>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
+      <c r="A40" s="28"/>
+      <c r="B40" s="28"/>
+      <c r="C40" s="28"/>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="29"/>
-      <c r="B41" s="29"/>
-      <c r="C41" s="29"/>
+      <c r="A41" s="28"/>
+      <c r="B41" s="28"/>
+      <c r="C41" s="28"/>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="29"/>
-      <c r="B42" s="29"/>
-      <c r="C42" s="29"/>
+      <c r="A42" s="28"/>
+      <c r="B42" s="28"/>
+      <c r="C42" s="28"/>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="29"/>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
+      <c r="A43" s="28"/>
+      <c r="B43" s="28"/>
+      <c r="C43" s="28"/>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="29"/>
-      <c r="B44" s="29"/>
-      <c r="C44" s="29"/>
+      <c r="A44" s="28"/>
+      <c r="B44" s="28"/>
+      <c r="C44" s="28"/>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="29"/>
-      <c r="B45" s="29"/>
-      <c r="C45" s="29"/>
+      <c r="A45" s="28"/>
+      <c r="B45" s="28"/>
+      <c r="C45" s="28"/>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="29"/>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
+      <c r="A46" s="28"/>
+      <c r="B46" s="28"/>
+      <c r="C46" s="28"/>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="29"/>
-      <c r="B47" s="29"/>
-      <c r="C47" s="29"/>
+      <c r="A47" s="28"/>
+      <c r="B47" s="28"/>
+      <c r="C47" s="28"/>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="29"/>
-      <c r="B48" s="29"/>
-      <c r="C48" s="29"/>
+      <c r="A48" s="28"/>
+      <c r="B48" s="28"/>
+      <c r="C48" s="28"/>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="29"/>
-      <c r="B49" s="29"/>
-      <c r="C49" s="29"/>
+      <c r="A49" s="28"/>
+      <c r="B49" s="28"/>
+      <c r="C49" s="28"/>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="29"/>
-      <c r="B50" s="29"/>
-      <c r="C50" s="29"/>
+      <c r="A50" s="28"/>
+      <c r="B50" s="28"/>
+      <c r="C50" s="28"/>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="29"/>
-      <c r="B51" s="29"/>
-      <c r="C51" s="29"/>
+      <c r="A51" s="28"/>
+      <c r="B51" s="28"/>
+      <c r="C51" s="28"/>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="29"/>
-      <c r="B52" s="29"/>
-      <c r="C52" s="29"/>
+      <c r="A52" s="28"/>
+      <c r="B52" s="28"/>
+      <c r="C52" s="28"/>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="29"/>
-      <c r="B53" s="29"/>
-      <c r="C53" s="29"/>
+      <c r="A53" s="28"/>
+      <c r="B53" s="28"/>
+      <c r="C53" s="28"/>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="29"/>
-      <c r="B54" s="29"/>
-      <c r="C54" s="29"/>
+      <c r="A54" s="28"/>
+      <c r="B54" s="28"/>
+      <c r="C54" s="28"/>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="28"/>
+      <c r="B55" s="28"/>
+      <c r="C55" s="28"/>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="28"/>
+      <c r="B56" s="28"/>
+      <c r="C56" s="28"/>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="28"/>
+      <c r="B57" s="28"/>
+      <c r="C57" s="28"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10096,58 +10229,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="B1" s="29"/>
+      <c r="A1" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="28"/>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="46">
+      <c r="A2" s="42">
         <v>45962</v>
       </c>
-      <c r="B2" s="29"/>
+      <c r="B2" s="28"/>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="B3" s="47" t="s">
-        <v>82</v>
+      <c r="A3" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="29" t="s">
-        <v>83</v>
-      </c>
-      <c r="B4" s="47" t="s">
-        <v>84</v>
+      <c r="A4" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="29" t="s">
-        <v>85</v>
-      </c>
-      <c r="B5" s="47" t="s">
-        <v>86</v>
+      <c r="A5" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="48">
+      <c r="A6" s="44">
         <v>45969</v>
       </c>
-      <c r="B6" s="29"/>
-    </row>
-    <row r="7" s="45" customFormat="1" ht="57.6" spans="1:2">
-      <c r="A7" s="49" t="s">
-        <v>87</v>
-      </c>
-      <c r="B7" s="50" t="s">
-        <v>88</v>
+      <c r="B6" s="28"/>
+    </row>
+    <row r="7" s="41" customFormat="1" ht="57.6" spans="1:2">
+      <c r="A7" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" s="46" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="10" ht="187.2" spans="1:1">
       <c r="A10" s="11" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -10162,775 +10295,775 @@
   <dimension ref="A1:D87"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="38.4444444444444" style="29" customWidth="1"/>
-    <col min="2" max="2" width="88.4444444444444" style="29" customWidth="1"/>
-    <col min="3" max="3" width="45.2222222222222" style="29" customWidth="1"/>
-    <col min="4" max="4" width="9.55555555555556" style="29" customWidth="1"/>
-    <col min="5" max="16384" width="8.88888888888889" style="29"/>
+    <col min="1" max="1" width="38.4444444444444" style="28" customWidth="1"/>
+    <col min="2" max="2" width="88.4444444444444" style="28" customWidth="1"/>
+    <col min="3" max="3" width="45.2222222222222" style="28" customWidth="1"/>
+    <col min="4" max="4" width="9.55555555555556" style="28" customWidth="1"/>
+    <col min="5" max="16384" width="8.88888888888889" style="28"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="B1" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="C1" s="31" t="s">
+      <c r="A1" s="29" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" s="30" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="2" ht="201.6" spans="1:3">
-      <c r="A2" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="B2" s="32" t="s">
-        <v>93</v>
-      </c>
-      <c r="C2" s="32" t="s">
-        <v>94</v>
+      <c r="A2" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="3" ht="100.8" spans="1:3">
-      <c r="A3" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="B3" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="C3" s="32" t="s">
-        <v>97</v>
+      <c r="A3" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="4" ht="72" spans="1:2">
-      <c r="A4" s="33" t="s">
-        <v>98</v>
-      </c>
-      <c r="B4" s="27" t="s">
-        <v>99</v>
+      <c r="A4" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="5" ht="129.6" spans="1:3">
-      <c r="A5" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="B5" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="C5" s="32" t="s">
-        <v>102</v>
+      <c r="A5" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="6" ht="129.6" spans="1:4">
-      <c r="A6" s="32" t="s">
-        <v>103</v>
-      </c>
-      <c r="B6" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="C6" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="D6" s="32" t="s">
-        <v>106</v>
+      <c r="A6" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="7" ht="158.4" spans="1:3">
-      <c r="A7" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="B7" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>109</v>
+      <c r="A7" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="8" ht="86.4" spans="1:2">
-      <c r="A8" s="27" t="s">
-        <v>110</v>
-      </c>
-      <c r="B8" s="27" t="s">
-        <v>111</v>
+      <c r="A8" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="9" ht="129.6" spans="1:2">
-      <c r="A9" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="B9" s="27" t="s">
-        <v>113</v>
+      <c r="A9" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="10" ht="129.6" spans="1:2">
-      <c r="A10" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>115</v>
+      <c r="A10" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="11" ht="158.4" spans="1:2">
-      <c r="A11" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="B11" s="27" t="s">
-        <v>117</v>
+      <c r="A11" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="12" ht="115.2" spans="1:3">
-      <c r="A12" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>120</v>
+      <c r="A12" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="13" ht="158.4" spans="1:3">
-      <c r="A13" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="B13" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="C13" s="32" t="s">
-        <v>123</v>
+      <c r="A13" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="14" ht="158.4" spans="1:3">
-      <c r="A14" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="B14" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="C14" s="32"/>
+      <c r="A14" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="C14" s="31"/>
     </row>
     <row r="15" ht="43.2" spans="1:3">
-      <c r="A15" s="25" t="s">
-        <v>126</v>
-      </c>
-      <c r="B15" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="C15" s="32"/>
+      <c r="A15" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="C15" s="31"/>
     </row>
     <row r="16" ht="129.6" spans="1:3">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="C16" s="32" t="s">
-        <v>129</v>
+      <c r="B16" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="17" ht="172.8" spans="1:3">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="27" t="s">
-        <v>130</v>
-      </c>
-      <c r="C17" s="32" t="s">
-        <v>131</v>
+      <c r="B17" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="18" ht="409.5" spans="1:4">
-      <c r="A18" s="34" t="s">
+      <c r="A18" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="35" t="s">
-        <v>132</v>
-      </c>
-      <c r="C18" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="D18" s="32" t="s">
-        <v>134</v>
+      <c r="B18" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="C18" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="D18" s="31" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="19" ht="409.5" spans="1:4">
-      <c r="A19" s="25" t="s">
+      <c r="A19" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="C19" s="32" t="s">
-        <v>136</v>
-      </c>
-      <c r="D19" s="32" t="s">
-        <v>137</v>
+      <c r="B19" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="D19" s="31" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="20" ht="409.5" spans="1:4">
-      <c r="A20" s="25" t="s">
-        <v>138</v>
-      </c>
-      <c r="B20" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="C20" s="32" t="s">
-        <v>140</v>
-      </c>
-      <c r="D20" s="32" t="s">
-        <v>141</v>
+      <c r="A20" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="C20" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="D20" s="31" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="21" ht="174" customHeight="1" spans="1:2">
-      <c r="A21" s="25" t="s">
-        <v>142</v>
-      </c>
-      <c r="B21" s="27" t="s">
-        <v>143</v>
+      <c r="A21" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="22" ht="187.2" spans="1:2">
-      <c r="A22" s="25" t="s">
-        <v>144</v>
-      </c>
-      <c r="B22" s="27" t="s">
-        <v>145</v>
+      <c r="A22" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="23" ht="244.8" spans="1:2">
-      <c r="A23" s="25" t="s">
-        <v>146</v>
-      </c>
-      <c r="B23" s="27" t="s">
-        <v>147</v>
+      <c r="A23" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="24" ht="158.4" spans="1:2">
-      <c r="A24" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="B24" s="27" t="s">
-        <v>149</v>
+      <c r="A24" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="25" ht="100.8" spans="1:2">
-      <c r="A25" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="B25" s="27" t="s">
-        <v>151</v>
+      <c r="A25" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="26" ht="409" customHeight="1" spans="1:3">
-      <c r="A26" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="B26" s="27" t="s">
-        <v>153</v>
-      </c>
-      <c r="C26" s="32" t="s">
-        <v>154</v>
+      <c r="A26" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>162</v>
+      </c>
+      <c r="C26" s="31" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="27" ht="57.6" spans="1:2">
-      <c r="A27" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="B27" s="27" t="s">
-        <v>156</v>
+      <c r="A27" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="28" ht="409.5" spans="1:4">
-      <c r="A28" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="B28" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="C28" s="32" t="s">
-        <v>159</v>
-      </c>
-      <c r="D28" s="32" t="s">
-        <v>160</v>
+      <c r="A28" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>167</v>
+      </c>
+      <c r="C28" s="31" t="s">
+        <v>168</v>
+      </c>
+      <c r="D28" s="31" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="29" ht="244.8" spans="1:3">
-      <c r="A29" s="25" t="s">
-        <v>161</v>
-      </c>
-      <c r="B29" s="27" t="s">
-        <v>162</v>
-      </c>
-      <c r="C29" s="32" t="s">
-        <v>163</v>
+      <c r="A29" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>171</v>
+      </c>
+      <c r="C29" s="31" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="30" ht="244.8" spans="1:2">
-      <c r="A30" s="25" t="s">
-        <v>164</v>
-      </c>
-      <c r="B30" s="27" t="s">
-        <v>165</v>
+      <c r="A30" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="31" ht="187.2" spans="1:2">
-      <c r="A31" s="37" t="s">
-        <v>166</v>
-      </c>
-      <c r="B31" s="27" t="s">
-        <v>167</v>
+      <c r="A31" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="32" ht="345.6" spans="1:2">
-      <c r="A32" s="38"/>
-      <c r="B32" s="39" t="s">
-        <v>168</v>
+      <c r="A32" s="37"/>
+      <c r="B32" s="38" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="33" ht="259.2" spans="1:2">
-      <c r="A33" s="40" t="s">
-        <v>169</v>
-      </c>
-      <c r="B33" s="39" t="s">
-        <v>170</v>
+      <c r="A33" s="39" t="s">
+        <v>178</v>
+      </c>
+      <c r="B33" s="38" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="34" ht="100.8" spans="1:2">
-      <c r="A34" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="B34" s="27" t="s">
-        <v>172</v>
+      <c r="A34" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="35" ht="72" spans="1:2">
-      <c r="A35" s="25" t="s">
-        <v>173</v>
-      </c>
-      <c r="B35" s="27" t="s">
-        <v>174</v>
+      <c r="A35" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="36" ht="409" customHeight="1" spans="1:3">
-      <c r="A36" s="25" t="s">
-        <v>175</v>
-      </c>
-      <c r="B36" s="27" t="s">
-        <v>176</v>
-      </c>
-      <c r="C36" s="41" t="s">
-        <v>177</v>
+      <c r="A36" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="C36" s="40" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="37" ht="187.2" spans="1:3">
-      <c r="A37" s="25" t="s">
-        <v>178</v>
-      </c>
-      <c r="B37" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="C37" s="41"/>
+      <c r="A37" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="B37" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="C37" s="40"/>
     </row>
     <row r="38" ht="288" spans="1:3">
-      <c r="A38" s="25" t="s">
-        <v>180</v>
-      </c>
-      <c r="B38" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="C38" s="41"/>
+      <c r="A38" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="B38" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="C38" s="40"/>
     </row>
     <row r="39" ht="216" spans="1:2">
-      <c r="A39" s="25" t="s">
-        <v>182</v>
-      </c>
-      <c r="B39" s="27" t="s">
-        <v>183</v>
+      <c r="A39" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="B39" s="26" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="40" ht="100.8" spans="1:2">
-      <c r="A40" s="27" t="s">
+      <c r="A40" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="B40" s="26" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="24" t="s">
         <v>184</v>
       </c>
-      <c r="B40" s="27" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="25" t="s">
-        <v>175</v>
-      </c>
-      <c r="B41" s="25"/>
+      <c r="B41" s="24"/>
     </row>
     <row r="42" ht="144" spans="1:3">
-      <c r="A42" s="27" t="s">
-        <v>186</v>
-      </c>
-      <c r="B42" s="27" t="s">
-        <v>187</v>
-      </c>
-      <c r="C42" s="32" t="s">
-        <v>188</v>
+      <c r="A42" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="B42" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="C42" s="31" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="43" ht="57.6" spans="1:2">
-      <c r="A43" s="27" t="s">
-        <v>189</v>
-      </c>
-      <c r="B43" s="27" t="s">
-        <v>190</v>
+      <c r="A43" s="26" t="s">
+        <v>198</v>
+      </c>
+      <c r="B43" s="26" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="44" ht="273.6" spans="1:2">
-      <c r="A44" s="27" t="s">
-        <v>191</v>
-      </c>
-      <c r="B44" s="27" t="s">
-        <v>192</v>
+      <c r="A44" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="B44" s="26" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="45" ht="172.8" spans="1:3">
-      <c r="A45" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="B45" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="C45" s="32" t="s">
-        <v>195</v>
+      <c r="A45" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="C45" s="31" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="46" ht="43.2" spans="1:2">
-      <c r="A46" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="B46" s="27" t="s">
-        <v>197</v>
+      <c r="A46" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="47" ht="144" spans="1:2">
-      <c r="A47" s="25" t="s">
-        <v>198</v>
-      </c>
-      <c r="B47" s="27" t="s">
-        <v>199</v>
+      <c r="A47" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="B47" s="26" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="48" ht="72" spans="1:2">
-      <c r="A48" s="25" t="s">
-        <v>200</v>
-      </c>
-      <c r="B48" s="27" t="s">
-        <v>201</v>
+      <c r="A48" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="B48" s="26" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="49" ht="57.6" spans="1:2">
-      <c r="A49" s="25" t="s">
-        <v>202</v>
-      </c>
-      <c r="B49" s="27" t="s">
-        <v>203</v>
+      <c r="A49" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="50" ht="28.8" spans="1:2">
-      <c r="A50" s="25" t="s">
-        <v>204</v>
-      </c>
-      <c r="B50" s="27" t="s">
-        <v>205</v>
+      <c r="A50" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="51" ht="230.4" spans="1:2">
-      <c r="A51" s="25" t="s">
-        <v>206</v>
-      </c>
-      <c r="B51" s="27" t="s">
-        <v>207</v>
+      <c r="A51" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="B51" s="26" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="52" ht="158.4" spans="1:2">
-      <c r="A52" s="25" t="s">
-        <v>208</v>
-      </c>
-      <c r="B52" s="27" t="s">
-        <v>209</v>
+      <c r="A52" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="B52" s="26" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="53" ht="129.6" spans="1:2">
-      <c r="A53" s="25" t="s">
-        <v>210</v>
-      </c>
-      <c r="B53" s="27" t="s">
-        <v>211</v>
+      <c r="A53" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="54" ht="409.5" spans="1:2">
-      <c r="A54" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="B54" s="27" t="s">
-        <v>213</v>
+      <c r="A54" s="24" t="s">
+        <v>221</v>
+      </c>
+      <c r="B54" s="26" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="55" ht="201.6" spans="1:3">
-      <c r="A55" s="25" t="s">
-        <v>214</v>
-      </c>
-      <c r="B55" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="C55" s="32" t="s">
-        <v>216</v>
+      <c r="A55" s="24" t="s">
+        <v>223</v>
+      </c>
+      <c r="B55" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="C55" s="31" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="56" ht="409.5" spans="1:2">
-      <c r="A56" s="25"/>
-      <c r="B56" s="32" t="s">
-        <v>217</v>
+      <c r="A56" s="24"/>
+      <c r="B56" s="31" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="57" ht="409.5" spans="1:2">
-      <c r="A57" s="25"/>
-      <c r="B57" s="32" t="s">
-        <v>218</v>
+      <c r="A57" s="24"/>
+      <c r="B57" s="31" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="58" ht="115.2" spans="1:2">
-      <c r="A58" s="29" t="s">
-        <v>219</v>
-      </c>
-      <c r="B58" s="27" t="s">
-        <v>220</v>
+      <c r="A58" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="B58" s="26" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="59" ht="100.8" spans="1:2">
-      <c r="A59" s="25" t="s">
-        <v>221</v>
-      </c>
-      <c r="B59" s="27" t="s">
-        <v>222</v>
+      <c r="A59" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="B59" s="26" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="25" t="s">
-        <v>223</v>
-      </c>
-      <c r="B60" s="25" t="s">
-        <v>224</v>
+      <c r="A60" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="B60" s="24" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="61" ht="86.4" spans="1:2">
-      <c r="A61" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="B61" s="27" t="s">
-        <v>226</v>
+      <c r="A61" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="B61" s="26" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="62" ht="144" spans="1:2">
-      <c r="A62" s="25" t="s">
-        <v>227</v>
-      </c>
-      <c r="B62" s="27" t="s">
-        <v>228</v>
+      <c r="A62" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="B62" s="26" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="63" ht="43.2" spans="1:2">
-      <c r="A63" s="25" t="s">
-        <v>229</v>
-      </c>
-      <c r="B63" s="27" t="s">
-        <v>230</v>
+      <c r="A63" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="B63" s="26" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="64" ht="28.8" spans="1:2">
-      <c r="A64" s="25" t="s">
-        <v>231</v>
-      </c>
-      <c r="B64" s="27" t="s">
-        <v>232</v>
+      <c r="A64" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="B64" s="26" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="65" ht="86.4" spans="1:2">
-      <c r="A65" s="29" t="s">
-        <v>233</v>
-      </c>
-      <c r="B65" s="27" t="s">
-        <v>234</v>
+      <c r="A65" s="28" t="s">
+        <v>242</v>
+      </c>
+      <c r="B65" s="26" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="66" ht="86.4" spans="1:2">
-      <c r="A66" s="25" t="s">
-        <v>235</v>
-      </c>
-      <c r="B66" s="27" t="s">
-        <v>236</v>
+      <c r="A66" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="B66" s="26" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="67" ht="28.8" spans="1:2">
-      <c r="A67" s="29" t="s">
-        <v>237</v>
-      </c>
-      <c r="B67" s="32" t="s">
-        <v>238</v>
+      <c r="A67" s="28" t="s">
+        <v>246</v>
+      </c>
+      <c r="B67" s="31" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="68" ht="43.2" spans="1:2">
-      <c r="A68" s="25" t="s">
-        <v>239</v>
-      </c>
-      <c r="B68" s="27" t="s">
-        <v>240</v>
+      <c r="A68" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="B68" s="26" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="69" ht="28.8" spans="1:2">
-      <c r="A69" s="29" t="s">
-        <v>241</v>
-      </c>
-      <c r="B69" s="27" t="s">
-        <v>242</v>
+      <c r="A69" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="B69" s="26" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="70" ht="28.8" spans="1:2">
-      <c r="A70" s="25" t="s">
-        <v>243</v>
-      </c>
-      <c r="B70" s="27" t="s">
-        <v>244</v>
+      <c r="A70" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="B70" s="26" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="71" ht="100.8" spans="1:2">
-      <c r="A71" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="B71" s="27" t="s">
-        <v>246</v>
+      <c r="A71" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="B71" s="26" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="72" ht="158.4" spans="1:2">
-      <c r="A72" s="25" t="s">
-        <v>247</v>
-      </c>
-      <c r="B72" s="27" t="s">
-        <v>248</v>
+      <c r="A72" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="B72" s="26" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="73" ht="86.4" spans="1:2">
-      <c r="A73" s="25" t="s">
-        <v>249</v>
-      </c>
-      <c r="B73" s="27" t="s">
-        <v>250</v>
+      <c r="A73" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="B73" s="26" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="74" ht="409.5" spans="1:2">
-      <c r="A74" s="25" t="s">
-        <v>251</v>
-      </c>
-      <c r="B74" s="27" t="s">
-        <v>252</v>
+      <c r="A74" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="B74" s="26" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="75" ht="360" spans="1:3">
-      <c r="A75" s="25" t="s">
-        <v>253</v>
-      </c>
-      <c r="B75" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="C75" s="32" t="s">
-        <v>255</v>
+      <c r="A75" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="B75" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="C75" s="31" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="76" ht="172.8" spans="1:3">
-      <c r="A76" s="25" t="s">
-        <v>256</v>
-      </c>
-      <c r="B76" s="27" t="s">
-        <v>257</v>
-      </c>
-      <c r="C76" s="32" t="s">
-        <v>258</v>
+      <c r="A76" s="24" t="s">
+        <v>265</v>
+      </c>
+      <c r="B76" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="C76" s="31" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="77" ht="409.5" spans="1:3">
-      <c r="A77" s="25" t="s">
-        <v>259</v>
-      </c>
-      <c r="B77" s="27" t="s">
-        <v>260</v>
-      </c>
-      <c r="C77" s="32" t="s">
-        <v>261</v>
+      <c r="A77" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="B77" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="C77" s="31" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="78" ht="409.5" spans="1:2">
-      <c r="A78" s="25" t="s">
-        <v>262</v>
-      </c>
-      <c r="B78" s="27" t="s">
-        <v>263</v>
+      <c r="A78" s="24" t="s">
+        <v>271</v>
+      </c>
+      <c r="B78" s="26" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="79" ht="302.4" spans="1:2">
-      <c r="A79" s="25" t="s">
-        <v>264</v>
-      </c>
-      <c r="B79" s="27" t="s">
-        <v>265</v>
+      <c r="A79" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="B79" s="26" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="80" ht="187.2" spans="1:3">
-      <c r="A80" s="25" t="s">
-        <v>266</v>
-      </c>
-      <c r="B80" s="27" t="s">
-        <v>267</v>
-      </c>
-      <c r="C80" s="42" t="s">
-        <v>268</v>
+      <c r="A80" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="B80" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="C80" s="31" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="81" ht="158.4" spans="1:2">
-      <c r="A81" s="43" t="s">
-        <v>269</v>
-      </c>
-      <c r="B81" s="27" t="s">
-        <v>270</v>
+      <c r="A81" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B81" s="26" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="82" ht="115.2" spans="1:2">
-      <c r="A82" s="44" t="s">
-        <v>271</v>
-      </c>
-      <c r="B82" s="27" t="s">
-        <v>272</v>
+      <c r="A82" s="24" t="s">
+        <v>280</v>
+      </c>
+      <c r="B82" s="26" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="83" ht="86.4" spans="1:2">
-      <c r="A83" s="27" t="s">
-        <v>273</v>
-      </c>
-      <c r="B83" s="27" t="s">
-        <v>274</v>
+      <c r="A83" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="B83" s="26" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="25"/>
-      <c r="B84" s="25"/>
+      <c r="A84" s="24"/>
+      <c r="B84" s="24"/>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="25"/>
-      <c r="B85" s="25"/>
+      <c r="A85" s="24"/>
+      <c r="B85" s="24"/>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="25"/>
-      <c r="B86" s="25"/>
+      <c r="A86" s="24"/>
+      <c r="B86" s="24"/>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="25"/>
-      <c r="B87" s="25"/>
+      <c r="A87" s="24"/>
+      <c r="B87" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -10953,82 +11086,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="25" t="s">
-        <v>92</v>
+      <c r="A1" s="24" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="25" t="s">
-        <v>95</v>
+      <c r="A2" s="24" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="26" t="s">
-        <v>98</v>
+      <c r="A3" s="25" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="27" t="s">
-        <v>100</v>
+      <c r="A4" s="26" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="27" t="s">
-        <v>103</v>
+      <c r="A5" s="26" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="25" t="s">
-        <v>107</v>
+      <c r="A6" s="24" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="27" t="s">
-        <v>110</v>
+      <c r="A7" s="26" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="27" t="s">
-        <v>112</v>
+      <c r="A8" s="26" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="25" t="s">
-        <v>114</v>
+      <c r="A9" s="24" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="25" t="s">
-        <v>275</v>
+      <c r="A10" s="24" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="27" t="s">
-        <v>118</v>
+      <c r="A11" s="26" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="25" t="s">
-        <v>121</v>
+      <c r="A12" s="24" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="25" t="s">
-        <v>124</v>
+      <c r="A13" s="24" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="25" t="s">
-        <v>126</v>
+      <c r="A14" s="24" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="24" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="24" t="s">
         <v>36</v>
       </c>
     </row>
@@ -11037,7 +11170,7 @@
         <v>38</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -11047,76 +11180,76 @@
     </row>
     <row r="19" ht="72" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21" ht="100.8" spans="1:2">
       <c r="A21" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="28" t="s">
-        <v>281</v>
+      <c r="A22" s="27" t="s">
+        <v>290</v>
       </c>
       <c r="B22" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
     </row>
     <row r="23" ht="57.6" spans="1:2">
       <c r="A23" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
     </row>
     <row r="24" ht="72" spans="1:2">
       <c r="A24" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
     </row>
     <row r="25" ht="86.4" spans="1:2">
       <c r="A25" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
     </row>
     <row r="26" ht="43.2" spans="1:2">
       <c r="A26" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
     </row>
     <row r="27" ht="28.8" spans="1:2">
       <c r="A27" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
     </row>
     <row r="28" ht="43.2" spans="1:2">
       <c r="A28" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -11136,27 +11269,27 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="22" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8" ht="15" spans="1:1">
       <c r="A8" s="23" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
     </row>
     <row r="9" ht="120" customHeight="1" spans="1:1">
-      <c r="A9" s="24" t="s">
-        <v>299</v>
+      <c r="A9" s="11" t="s">
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -11180,302 +11313,302 @@
   <sheetData>
     <row r="1" spans="2:3">
       <c r="B1" s="16" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2" spans="2:3">
       <c r="B2" s="17" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3" spans="2:3">
       <c r="B3" s="17" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" s="17" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="B5" s="17" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="2:3">
       <c r="B6" s="17" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="B7" s="17" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8" ht="43.2" spans="2:3">
       <c r="B8" s="17" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" s="18" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10" spans="2:2">
       <c r="B10" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11" ht="23.4" spans="2:2">
       <c r="B11" s="19" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" s="20" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
     </row>
     <row r="15" spans="2:2">
       <c r="B15" s="20" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
     </row>
     <row r="16" spans="2:2">
       <c r="B16" s="20" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" s="20" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" s="20" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" s="20" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" s="20" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" s="20" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" s="20" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" s="20" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
     </row>
     <row r="26" ht="23.4" spans="2:2">
       <c r="B26" s="19" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" s="20" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
     </row>
     <row r="29" spans="2:2">
       <c r="B29" s="20" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" s="20" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
     </row>
     <row r="31" spans="2:2">
       <c r="B31" s="20" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" s="20" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" s="20" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" s="20" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" s="20" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" s="20" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" s="20" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="39" spans="2:2">
       <c r="B39" s="20" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
     </row>
     <row r="41" ht="23.4" spans="2:2">
       <c r="B41" s="19" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="43" spans="2:2">
       <c r="B43" s="20" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" s="20" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
     </row>
     <row r="45" spans="2:2">
       <c r="B45" s="20" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" s="20" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" s="21" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" s="21" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" s="21" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" s="21" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
     </row>
     <row r="54" ht="13" customHeight="1"/>
     <row r="55" ht="22" customHeight="1" spans="2:2">
       <c r="B55" s="19" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
     </row>
     <row r="57" spans="2:2">
       <c r="B57" s="20" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
     </row>
     <row r="58" spans="2:2">
@@ -11485,22 +11618,22 @@
     </row>
     <row r="59" spans="2:2">
       <c r="B59" s="20" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
     </row>
     <row r="60" spans="2:2">
       <c r="B60" s="20" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61" s="20" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -11517,7 +11650,7 @@
   <sheetData>
     <row r="1" spans="1:21">
       <c r="A1" s="12" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -11532,7 +11665,7 @@
       <c r="L1" s="12"/>
       <c r="M1" s="12"/>
       <c r="N1" s="14" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="O1" s="15"/>
       <c r="P1" s="15"/>
@@ -11774,7 +11907,7 @@
     </row>
     <row r="12" spans="1:21">
       <c r="A12" s="12" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
@@ -11960,7 +12093,7 @@
     </row>
     <row r="22" spans="1:21">
       <c r="A22" s="13" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="B22" s="13"/>
       <c r="C22" s="13"/>

--- a/JavaPrograms/Work Done.xlsx
+++ b/JavaPrograms/Work Done.xlsx
@@ -19,7 +19,7 @@
     <sheet name="Checklist" sheetId="10" r:id="rId10"/>
     <sheet name="Revision" sheetId="12" r:id="rId11"/>
     <sheet name="Sheet1" sheetId="13" r:id="rId12"/>
-    <sheet name="Sheet2" sheetId="14" r:id="rId13"/>
+    <sheet name="fot Interview" sheetId="14" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="483">
   <si>
     <r>
       <rPr>
@@ -5120,6 +5120,9 @@
   </si>
   <si>
     <t>Interview Questions</t>
+  </si>
+  <si>
+    <t>Introduction</t>
   </si>
   <si>
     <t>why are you looking for job change?</t>
@@ -8692,8 +8695,8 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="1"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="54.8888888888889" customWidth="1"/>
     <col min="2" max="2" width="99" customWidth="1"/>
@@ -8707,12 +8710,17 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" ht="100.8" spans="1:2">
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
         <v>480</v>
       </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="3" ht="100.8" spans="1:2">
+      <c r="A3" t="s">
         <v>481</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>482</v>
       </c>
     </row>
   </sheetData>

--- a/JavaPrograms/Work Done.xlsx
+++ b/JavaPrograms/Work Done.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000" firstSheet="2" activeTab="4"/>
+    <workbookView windowWidth="23040" windowHeight="9000" firstSheet="2" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="DSA plan" sheetId="4" r:id="rId1"/>
@@ -4583,15 +4583,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <i/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>

--- a/JavaPrograms/Work Done.xlsx
+++ b/JavaPrograms/Work Done.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000" firstSheet="2" activeTab="6"/>
+    <workbookView windowWidth="23040" windowHeight="8280" firstSheet="2" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="DSA plan" sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="380">
   <si>
     <r>
       <rPr>
@@ -3693,6 +3693,163 @@
   </si>
   <si>
     <t xml:space="preserve">A priority queue is a data structure that manages elements based on assigned priority, not just arrival order, always processing the highest (or lowest) priority item first, unlike a standard FIFO queue. Think of an ER: critical patients (high priority) are seen before minor cases (low priority). Common implementations use binary heaps (min-heap or max-heap) for efficiency, making it crucial for tasks like pathfinding (Dijkstra's), scheduling, and real-time systems. </t>
+  </si>
+  <si>
+    <t>Linkedlist Revision</t>
+  </si>
+  <si>
+    <t>1️⃣ What is a node?
+A node is a small box.
+Inside the box:
+one value (like 5)
+one arrow pointing to the next box
+Example:
+[5 | next] → [7 | next] → [9 | null]
+A linked list is just boxes connected by arrows.
+2️⃣ What does a pointer store?
+A pointer stores the address of a box, not the value.
+It’s like:
+not holding the house
+but holding the house address
+So when you do:
+curr = curr.next;
+You are saying:
+“Move to the next box.”
+3️⃣ Why do we use dummy nodes?
+A dummy node is a fake box added before the real list.
+dummy → 1 → 2 → 3
+Why?
+To avoid special cases
+Especially when deleting the first node
+Dummy guarantees:
+“Every real node has a previous node.”
+That makes code calm and uniform.
+4️⃣ Why do most bugs come from .next?
+Because:
+.next can be null
+accessing null.next crashes the program
+Most linked list bugs are:
+moving one step too far
+stopping one step too late
+forgetting that .next might not exist
+Linked lists punish off-by-one mistakes.
+5️⃣ What do prev, curr, next mean?
+In reverse list:
+curr → node we are currently standing on
+next → node after curr (saved before breaking link)
+prev → node behind us (already reversed part)
+You reverse arrows like:
+curr.next = prev
+If you don’t save next first → list breaks.
+6️⃣ Why does fast move 2 steps?
+Because we want speed difference.
+slow = 1 step
+fast = 2 steps
+This difference helps us:
+find the middle
+detect cycles
+Fast running twice as fast is the core trick.
+7️⃣ Why does slow end at the middle?
+Because:
+fast covers the list twice as fast
+when fast reaches the end
+slow has covered half
+It’s like two runners:
+when the faster one finishes
+the slower one is halfway
+8️⃣ Why even length returns the second middle?
+Example:
+1 → 2 → 3 → 4
+Slow moves after fast checks.
+So slow lands on:
+3
+The problem asks for the second middle — so this behavior is intentional.
+9️⃣ Why does order of assignments matter?
+In reverse list:
+❌ Wrong:
+curr.next = prev;
+curr = curr.next; // LOST the rest
+✅ Correct:
+next = curr.next;
+curr.next = prev;
+prev = curr;
+curr = next;
+If you break the arrow before saving next, you lose the list.
+🔁 CYCLES
+🔟 How do we know a cycle exists?
+If:
+slow moves 1 step
+fast moves 2 steps
+and they meet
+Then:
+Fast caught up → list must loop
+In a straight line, fast can never meet slow again.
+1️⃣1️⃣ Why resetting slow to head works?
+When slow &amp; fast meet:
+slow has traveled A + B
+fast has traveled A + B + cycle loops
+That extra looping distance lines up so that:
+Starting slow from head and fast from meeting point
+both reach cycle start together
+No math needed — just movement symmetry.
+1️⃣2️⃣ Why do they meet at cycle start?
+Because:
+both move one step at a time
+distances are balanced
+first common point becomes the cycle entry
+That’s why we return that node.
+🔁 REMOVE NTH FROM END
+1️⃣3️⃣ Why does fast move n steps first?
+So we create a fixed gap of n nodes.
+This gap guarantees:
+When fast reaches the end, slow is right before the node to delete.
+Distance = control.
+1️⃣4️⃣ Why is the loop fast.next != null?
+Because we want:
+slow to stop before the node to delete
+not ON the node
+Stopping when fast == null is one step too late.
+1️⃣5️⃣ Why must slow stop before delete?
+To delete a node, we must do:
+slow.next = slow.next.next;
+That requires slow to be the previous node.
+Linked lists can’t delete the current node without previous.
+🔁 MERGING
+1️⃣6️⃣ LC 21 — Why dummy?
+Same reason as before:
+clean start
+no special case for first node
+always have a prev
+Dummy makes merging calm.
+1️⃣7️⃣ Why attach remainder directly?
+Because:
+remaining list is already sorted
+no need to compare anymore
+attaching saves time
+Example:
+1 → 3 → 5
+         ↑
+       attach rest
+🔁 MERGE K LISTS
+1️⃣8️⃣ Why heap?
+Because:
+we need the smallest head among K lists
+heap gives smallest in log K
+Heap is a smart selector.
+1️⃣9️⃣ Why heap size ≤ K?
+Because:
+only the current head of each list is inside heap
+once popped, we push its .next
+Never more than K nodes inside.
+2️⃣0️⃣ Time complexity of Merge K Lists?
+Each node processed once → N
+Heap operation → log K
+Total:
+O(N log K)
+This is optimal.
+🧠 FINAL LOCK-IN SENTENCE
+Linked lists are about references, not values, and every trick is about controlling distance and stopping points.
+If all this made sense reading calmly, you’re good.</t>
   </si>
   <si>
     <t>Space Complexity</t>
@@ -6816,7 +6973,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>100</v>
@@ -6824,24 +6981,24 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B2" s="1"/>
     </row>
     <row r="3" ht="100.8" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4" ht="57.6" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -9226,9 +9383,13 @@
         <v>285</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
-      <c r="A85" s="16"/>
-      <c r="B85" s="16"/>
+    <row r="85" ht="409.5" spans="1:2">
+      <c r="A85" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="B85" s="18" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="16"/>
@@ -9305,7 +9466,7 @@
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="16" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -9343,7 +9504,7 @@
         <v>38</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -9353,76 +9514,76 @@
     </row>
     <row r="19" ht="72" spans="1:1">
       <c r="A19" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:1">
       <c r="A20" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" ht="100.8" spans="1:2">
       <c r="A21" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="19" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B22" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="23" ht="57.6" spans="1:2">
       <c r="A23" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="24" ht="72" spans="1:2">
       <c r="A24" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="25" ht="86.4" spans="1:2">
       <c r="A25" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="26" ht="43.2" spans="1:2">
       <c r="A26" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="27" ht="28.8" spans="1:2">
       <c r="A27" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="28" ht="43.2" spans="1:2">
       <c r="A28" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -9442,27 +9603,27 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="14" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="8" ht="15" spans="1:1">
       <c r="A8" s="15" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="9" ht="120" customHeight="1" spans="1:1">
       <c r="A9" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -9486,201 +9647,201 @@
   <sheetData>
     <row r="1" spans="2:3">
       <c r="B1" s="7" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2" spans="2:3">
       <c r="B2" s="8" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" spans="2:3">
       <c r="B3" s="8" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>316</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="B5" s="8" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6" spans="2:3">
       <c r="B6" s="8" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="B7" s="8" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="8" ht="43.2" spans="2:3">
       <c r="B8" s="8" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" s="10" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10" spans="2:2">
       <c r="B10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="11" ht="23.4" spans="2:2">
       <c r="B11" s="11" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" s="12" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="15" spans="2:2">
       <c r="B15" s="12" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="16" spans="2:2">
       <c r="B16" s="12" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" s="12" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" s="12" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" s="12" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" s="12" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" s="12" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" s="12" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" s="12" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="26" ht="23.4" spans="2:2">
       <c r="B26" s="11" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" s="12" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="29" spans="2:2">
       <c r="B29" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" s="12" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="31" spans="2:2">
       <c r="B31" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" s="12" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" s="12" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" s="12" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="36" spans="2:2">
@@ -9705,83 +9866,83 @@
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="41" ht="23.4" spans="2:2">
       <c r="B41" s="11" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="43" spans="2:2">
       <c r="B43" s="12" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" s="12" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="45" spans="2:2">
       <c r="B45" s="12" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" s="12" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" s="13" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" s="13" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" s="13" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" s="13" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="54" ht="13" customHeight="1"/>
     <row r="55" ht="22" customHeight="1" spans="2:2">
       <c r="B55" s="11" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="57" spans="2:2">
       <c r="B57" s="12" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="58" spans="2:2">
@@ -9796,17 +9957,17 @@
     </row>
     <row r="60" spans="2:2">
       <c r="B60" s="12" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61" s="12" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
@@ -9823,7 +9984,7 @@
   <sheetData>
     <row r="1" spans="1:21">
       <c r="A1" s="3" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -9838,7 +9999,7 @@
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
       <c r="N1" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
@@ -10080,7 +10241,7 @@
     </row>
     <row r="12" spans="1:21">
       <c r="A12" s="3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -10266,7 +10427,7 @@
     </row>
     <row r="22" spans="1:21">
       <c r="A22" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>

--- a/JavaPrograms/Work Done.xlsx
+++ b/JavaPrograms/Work Done.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8280" firstSheet="2" activeTab="4"/>
+    <workbookView windowWidth="23040" windowHeight="9000" firstSheet="2" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="DSA plan" sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="383">
   <si>
     <r>
       <rPr>
@@ -3852,6 +3852,47 @@
 If all this made sense reading calmly, you’re good.</t>
   </si>
   <si>
+    <t>Stack</t>
+  </si>
+  <si>
+    <t>Think of a stack of plates.
+You put a plate on top
+You remove the top plate
+You can’t remove the middle plate directly
+So stack =
+👉 Last In, First Out (LIFO)
+Why stacks exist in DSA problems:
+To remember something temporarily
+To undo / go back
+To wait until the right moment
+3️⃣ Stack — Normal explanation (pattern view)
+A stack helps when:
+Current decision depends on future elements
+You need to pause processing and resume later
+Order matters more than values
+Common signals:
+“nearest greater”
+“previous smaller”
+parentheses
+backtracking-like behavior
+If you see “wait until”, think stack.</t>
+  </si>
+  <si>
+    <t>Your car-door analogy (validated)
+Order of opening:
+Driver door
+Behind driver
+Opposite to behind driver
+Opposite to driver
+Now real-life constraint:
+You cannot close door #1 until doors #4, #3, #2 are closed.
+The last opened door must be closed first.
+That is exactly a stack.
+So yes:
+First close opposite to driver → then behind → then opposite → then driver
+That is LIFO in real life.</t>
+  </si>
+  <si>
     <t>Space Complexity</t>
   </si>
   <si>
@@ -4740,15 +4781,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <i/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -5355,7 +5396,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5454,6 +5495,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
@@ -6159,246 +6203,246 @@
   </cols>
   <sheetData>
     <row r="1" ht="90" customHeight="1" spans="1:6">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="58" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="59"/>
-      <c r="E1" s="60" t="s">
+      <c r="D1" s="60"/>
+      <c r="E1" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="60"/>
+      <c r="F1" s="61"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="62" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="16"/>
-      <c r="C2" s="62" t="s">
+      <c r="C2" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="63"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="16"/>
       <c r="B4" s="16"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="16"/>
       <c r="B5" s="16"/>
-      <c r="C5" s="64"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="16"/>
       <c r="B6" s="16"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="16"/>
       <c r="B7" s="16"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="60"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="16"/>
       <c r="B8" s="16"/>
-      <c r="C8" s="66"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="61" t="s">
+      <c r="A9" s="62" t="s">
         <v>5</v>
       </c>
       <c r="B9" s="18"/>
-      <c r="C9" s="68" t="s">
+      <c r="C9" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="69"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="18"/>
       <c r="B10" s="18"/>
-      <c r="C10" s="70"/>
-      <c r="D10" s="71"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
+      <c r="C10" s="71"/>
+      <c r="D10" s="72"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="18"/>
       <c r="B11" s="18"/>
-      <c r="C11" s="70"/>
-      <c r="D11" s="71"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="60"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="72"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="18"/>
       <c r="B12" s="18"/>
-      <c r="C12" s="70"/>
-      <c r="D12" s="71"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
+      <c r="C12" s="71"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="18"/>
       <c r="B13" s="18"/>
-      <c r="C13" s="70"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="61"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="18"/>
       <c r="B14" s="18"/>
-      <c r="C14" s="70"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="61"/>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:6">
       <c r="A15" s="18"/>
       <c r="B15" s="18"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="73"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
+      <c r="C15" s="73"/>
+      <c r="D15" s="74"/>
+      <c r="E15" s="61"/>
+      <c r="F15" s="61"/>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="18"/>
       <c r="B16" s="18"/>
-      <c r="C16" s="74" t="s">
+      <c r="C16" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="75"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
+      <c r="D16" s="76"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="61"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="18"/>
       <c r="B17" s="18"/>
-      <c r="C17" s="76"/>
-      <c r="D17" s="77"/>
-      <c r="E17" s="60"/>
-      <c r="F17" s="60"/>
+      <c r="C17" s="77"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="61"/>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="18"/>
       <c r="B18" s="18"/>
-      <c r="C18" s="76"/>
-      <c r="D18" s="77"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="60"/>
+      <c r="C18" s="77"/>
+      <c r="D18" s="78"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="61"/>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="61" t="s">
+      <c r="A19" s="62" t="s">
         <v>8</v>
       </c>
       <c r="B19" s="16"/>
-      <c r="C19" s="76"/>
-      <c r="D19" s="77"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
+      <c r="C19" s="77"/>
+      <c r="D19" s="78"/>
+      <c r="E19" s="61"/>
+      <c r="F19" s="61"/>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="16"/>
       <c r="B20" s="16"/>
-      <c r="C20" s="76"/>
-      <c r="D20" s="77"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
+      <c r="C20" s="77"/>
+      <c r="D20" s="78"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="61"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="16"/>
       <c r="B21" s="16"/>
-      <c r="C21" s="76"/>
-      <c r="D21" s="77"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="60"/>
+      <c r="C21" s="77"/>
+      <c r="D21" s="78"/>
+      <c r="E21" s="61"/>
+      <c r="F21" s="61"/>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="16"/>
       <c r="B22" s="16"/>
-      <c r="C22" s="76"/>
-      <c r="D22" s="77"/>
+      <c r="C22" s="77"/>
+      <c r="D22" s="78"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="16"/>
       <c r="B23" s="16"/>
-      <c r="C23" s="78"/>
-      <c r="D23" s="79"/>
+      <c r="C23" s="79"/>
+      <c r="D23" s="80"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="16"/>
       <c r="B24" s="16"/>
-      <c r="C24" s="80" t="s">
+      <c r="C24" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="81"/>
+      <c r="D24" s="82"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="16"/>
       <c r="B25" s="16"/>
-      <c r="C25" s="82"/>
-      <c r="D25" s="83"/>
+      <c r="C25" s="83"/>
+      <c r="D25" s="84"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="16"/>
       <c r="B26" s="16"/>
-      <c r="C26" s="82"/>
-      <c r="D26" s="83"/>
+      <c r="C26" s="83"/>
+      <c r="D26" s="84"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="16"/>
       <c r="B27" s="16"/>
-      <c r="C27" s="82"/>
-      <c r="D27" s="83"/>
+      <c r="C27" s="83"/>
+      <c r="D27" s="84"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="16"/>
       <c r="B28" s="16"/>
-      <c r="C28" s="84"/>
-      <c r="D28" s="85"/>
+      <c r="C28" s="85"/>
+      <c r="D28" s="86"/>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="16"/>
@@ -6413,7 +6457,7 @@
       <c r="D30" s="20"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="61" t="s">
+      <c r="A31" s="62" t="s">
         <v>10</v>
       </c>
       <c r="B31" s="18"/>
@@ -6469,7 +6513,7 @@
       <c r="D39" s="20"/>
     </row>
     <row r="40" ht="18" customHeight="1" spans="1:4">
-      <c r="A40" s="61" t="s">
+      <c r="A40" s="62" t="s">
         <v>11</v>
       </c>
       <c r="B40" s="18"/>
@@ -6531,7 +6575,7 @@
       <c r="D49" s="20"/>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="61" t="s">
+      <c r="A50" s="62" t="s">
         <v>12</v>
       </c>
       <c r="B50" s="18"/>
@@ -6587,7 +6631,7 @@
       <c r="D58" s="20"/>
     </row>
     <row r="59" spans="1:4">
-      <c r="A59" s="61" t="s">
+      <c r="A59" s="62" t="s">
         <v>13</v>
       </c>
       <c r="B59" s="16"/>
@@ -6643,7 +6687,7 @@
       <c r="D67" s="20"/>
     </row>
     <row r="68" spans="1:4">
-      <c r="A68" s="61" t="s">
+      <c r="A68" s="62" t="s">
         <v>14</v>
       </c>
       <c r="B68" s="16"/>
@@ -6705,7 +6749,7 @@
       <c r="D77" s="20"/>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="61" t="s">
+      <c r="A78" s="62" t="s">
         <v>15</v>
       </c>
       <c r="B78" s="16"/>
@@ -6767,7 +6811,7 @@
       <c r="D87" s="20"/>
     </row>
     <row r="88" spans="1:4">
-      <c r="A88" s="61" t="s">
+      <c r="A88" s="62" t="s">
         <v>16</v>
       </c>
       <c r="B88" s="16"/>
@@ -6823,7 +6867,7 @@
       <c r="D96" s="20"/>
     </row>
     <row r="97" spans="1:4">
-      <c r="A97" s="61" t="s">
+      <c r="A97" s="62" t="s">
         <v>17</v>
       </c>
       <c r="B97" s="18"/>
@@ -6879,7 +6923,7 @@
       <c r="D105" s="20"/>
     </row>
     <row r="106" spans="1:4">
-      <c r="A106" s="61" t="s">
+      <c r="A106" s="62" t="s">
         <v>18</v>
       </c>
       <c r="B106" s="16"/>
@@ -6973,7 +7017,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>100</v>
@@ -6981,24 +7025,24 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B2" s="1"/>
     </row>
     <row r="3" ht="100.8" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="4" ht="57.6" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -7033,7 +7077,7 @@
       <c r="D1" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="E1" s="45" t="s">
         <v>23</v>
       </c>
     </row>
@@ -7041,31 +7085,31 @@
       <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="45">
+      <c r="B2" s="46">
         <v>45976</v>
       </c>
-      <c r="C2" s="46">
+      <c r="C2" s="47">
         <v>45983</v>
       </c>
       <c r="D2" s="16">
         <v>4</v>
       </c>
-      <c r="E2" s="47"/>
+      <c r="E2" s="48"/>
     </row>
     <row r="3" ht="115.2" spans="1:5">
       <c r="A3" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="45">
+      <c r="B3" s="46">
         <v>45976</v>
       </c>
-      <c r="C3" s="46">
+      <c r="C3" s="47">
         <v>45983</v>
       </c>
       <c r="D3" s="16">
         <v>4</v>
       </c>
-      <c r="E3" s="48" t="s">
+      <c r="E3" s="49" t="s">
         <v>26</v>
       </c>
     </row>
@@ -7073,16 +7117,16 @@
       <c r="A4" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="45">
+      <c r="B4" s="46">
         <v>45976</v>
       </c>
-      <c r="C4" s="46">
+      <c r="C4" s="47">
         <v>45983</v>
       </c>
       <c r="D4" s="16">
         <v>3</v>
       </c>
-      <c r="E4" s="49" t="s">
+      <c r="E4" s="50" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7090,125 +7134,125 @@
       <c r="A5" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="45">
+      <c r="B5" s="46">
         <v>45976</v>
       </c>
-      <c r="C5" s="46">
+      <c r="C5" s="47">
         <v>45983</v>
       </c>
       <c r="D5" s="16">
         <v>2</v>
       </c>
-      <c r="E5" s="50"/>
+      <c r="E5" s="51"/>
     </row>
     <row r="6" ht="115.2" spans="1:5">
       <c r="A6" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="45">
+      <c r="B6" s="46">
         <v>45976</v>
       </c>
-      <c r="C6" s="46">
+      <c r="C6" s="47">
         <v>45983</v>
       </c>
       <c r="D6" s="16">
         <v>2</v>
       </c>
-      <c r="E6" s="50"/>
+      <c r="E6" s="51"/>
     </row>
     <row r="7" ht="129.6" spans="1:5">
       <c r="A7" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="45">
+      <c r="B7" s="46">
         <v>45976</v>
       </c>
-      <c r="C7" s="46">
+      <c r="C7" s="47">
         <v>45983</v>
       </c>
       <c r="D7" s="16">
         <v>2</v>
       </c>
-      <c r="E7" s="50"/>
-    </row>
-    <row r="8" s="43" customFormat="1" ht="144" spans="1:5">
-      <c r="A8" s="51" t="s">
+      <c r="E7" s="51"/>
+    </row>
+    <row r="8" s="44" customFormat="1" ht="144" spans="1:5">
+      <c r="A8" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="46">
+      <c r="B8" s="47">
         <v>45976</v>
       </c>
-      <c r="C8" s="46">
+      <c r="C8" s="47">
         <v>45983</v>
       </c>
-      <c r="D8" s="52">
+      <c r="D8" s="53">
         <v>2</v>
       </c>
-      <c r="E8" s="53"/>
-    </row>
-    <row r="9" s="43" customFormat="1" ht="158.4" spans="1:5">
-      <c r="A9" s="51" t="s">
+      <c r="E8" s="54"/>
+    </row>
+    <row r="9" s="44" customFormat="1" ht="158.4" spans="1:5">
+      <c r="A9" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="46">
+      <c r="B9" s="47">
         <v>45976</v>
       </c>
-      <c r="C9" s="46">
+      <c r="C9" s="47">
         <v>45983</v>
       </c>
-      <c r="D9" s="52">
+      <c r="D9" s="53">
         <v>1</v>
       </c>
-      <c r="E9" s="54"/>
-    </row>
-    <row r="10" s="43" customFormat="1" spans="1:5">
-      <c r="A10" s="52" t="s">
+      <c r="E9" s="55"/>
+    </row>
+    <row r="10" s="44" customFormat="1" spans="1:5">
+      <c r="A10" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="46">
+      <c r="B10" s="47">
         <v>45976</v>
       </c>
-      <c r="C10" s="46">
+      <c r="C10" s="47">
         <v>45983</v>
       </c>
-      <c r="D10" s="52">
+      <c r="D10" s="53">
         <v>1</v>
       </c>
-      <c r="E10" s="55" t="s">
+      <c r="E10" s="56" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" s="43" customFormat="1" spans="1:5">
-      <c r="A11" s="52" t="s">
+    <row r="11" s="44" customFormat="1" spans="1:5">
+      <c r="A11" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="46">
+      <c r="B11" s="47">
         <v>45976</v>
       </c>
-      <c r="C11" s="46">
+      <c r="C11" s="47">
         <v>45983</v>
       </c>
-      <c r="D11" s="52">
+      <c r="D11" s="53">
         <v>1</v>
       </c>
-      <c r="E11" s="55" t="s">
+      <c r="E11" s="56" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" s="43" customFormat="1" spans="1:5">
-      <c r="A12" s="52" t="s">
+    <row r="12" s="44" customFormat="1" spans="1:5">
+      <c r="A12" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="46">
+      <c r="B12" s="47">
         <v>45976</v>
       </c>
-      <c r="C12" s="46">
+      <c r="C12" s="47">
         <v>45983</v>
       </c>
-      <c r="D12" s="52">
+      <c r="D12" s="53">
         <v>1</v>
       </c>
-      <c r="E12" s="55" t="s">
+      <c r="E12" s="56" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7216,16 +7260,16 @@
       <c r="A13" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="46">
+      <c r="B13" s="47">
         <v>45977</v>
       </c>
-      <c r="C13" s="46">
+      <c r="C13" s="47">
         <v>45982</v>
       </c>
       <c r="D13" s="16">
         <v>1</v>
       </c>
-      <c r="E13" s="55" t="s">
+      <c r="E13" s="56" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7233,16 +7277,16 @@
       <c r="A14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="46">
+      <c r="B14" s="47">
         <v>45980</v>
       </c>
-      <c r="C14" s="46">
+      <c r="C14" s="47">
         <v>45982</v>
       </c>
       <c r="D14" s="16">
         <v>1</v>
       </c>
-      <c r="E14" s="55" t="s">
+      <c r="E14" s="56" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7250,16 +7294,16 @@
       <c r="A15" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="46">
+      <c r="B15" s="47">
         <v>45980</v>
       </c>
-      <c r="C15" s="46">
+      <c r="C15" s="47">
         <v>45982</v>
       </c>
       <c r="D15" s="16">
         <v>1</v>
       </c>
-      <c r="E15" s="55" t="s">
+      <c r="E15" s="56" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7267,16 +7311,16 @@
       <c r="A16" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="46">
+      <c r="B16" s="47">
         <v>45980</v>
       </c>
-      <c r="C16" s="46">
+      <c r="C16" s="47">
         <v>45982</v>
       </c>
       <c r="D16" s="16">
         <v>1</v>
       </c>
-      <c r="E16" s="55" t="s">
+      <c r="E16" s="56" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7284,16 +7328,16 @@
       <c r="A17" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="46">
+      <c r="B17" s="47">
         <v>45980</v>
       </c>
-      <c r="C17" s="46">
+      <c r="C17" s="47">
         <v>45982</v>
       </c>
       <c r="D17" s="16">
         <v>1</v>
       </c>
-      <c r="E17" s="55" t="s">
+      <c r="E17" s="56" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7301,16 +7345,16 @@
       <c r="A18" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="46">
+      <c r="B18" s="47">
         <v>45981</v>
       </c>
-      <c r="C18" s="46">
+      <c r="C18" s="47">
         <v>45983</v>
       </c>
       <c r="D18" s="16">
         <v>1</v>
       </c>
-      <c r="E18" s="55" t="s">
+      <c r="E18" s="56" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7318,16 +7362,16 @@
       <c r="A19" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="46">
+      <c r="B19" s="47">
         <v>45982</v>
       </c>
-      <c r="C19" s="46">
+      <c r="C19" s="47">
         <v>45984</v>
       </c>
       <c r="D19" s="16">
         <v>1</v>
       </c>
-      <c r="E19" s="55" t="s">
+      <c r="E19" s="56" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7335,16 +7379,16 @@
       <c r="A20" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="46">
+      <c r="B20" s="47">
         <v>45983</v>
       </c>
-      <c r="C20" s="46">
+      <c r="C20" s="47">
         <v>45985</v>
       </c>
       <c r="D20" s="16">
         <v>1</v>
       </c>
-      <c r="E20" s="55" t="s">
+      <c r="E20" s="56" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7352,16 +7396,16 @@
       <c r="A21" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="46">
+      <c r="B21" s="47">
         <v>45986</v>
       </c>
-      <c r="C21" s="46">
+      <c r="C21" s="47">
         <v>45987</v>
       </c>
       <c r="D21" s="16">
         <v>1</v>
       </c>
-      <c r="E21" s="55" t="s">
+      <c r="E21" s="56" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7369,16 +7413,16 @@
       <c r="A22" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="46">
+      <c r="B22" s="47">
         <v>45986</v>
       </c>
-      <c r="C22" s="46">
+      <c r="C22" s="47">
         <v>45987</v>
       </c>
       <c r="D22" s="16">
         <v>1</v>
       </c>
-      <c r="E22" s="55" t="s">
+      <c r="E22" s="56" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7386,16 +7430,16 @@
       <c r="A23" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="46">
+      <c r="B23" s="47">
         <v>45986</v>
       </c>
-      <c r="C23" s="46">
+      <c r="C23" s="47">
         <v>45987</v>
       </c>
       <c r="D23" s="16">
         <v>1</v>
       </c>
-      <c r="E23" s="55" t="s">
+      <c r="E23" s="56" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7403,16 +7447,16 @@
       <c r="A24" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="46">
+      <c r="B24" s="47">
         <v>45986</v>
       </c>
-      <c r="C24" s="46">
+      <c r="C24" s="47">
         <v>45987</v>
       </c>
       <c r="D24" s="16">
         <v>1</v>
       </c>
-      <c r="E24" s="55" t="s">
+      <c r="E24" s="56" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7420,16 +7464,16 @@
       <c r="A25" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="46">
+      <c r="B25" s="47">
         <v>45986</v>
       </c>
-      <c r="C25" s="46">
+      <c r="C25" s="47">
         <v>45987</v>
       </c>
       <c r="D25" s="16">
         <v>1</v>
       </c>
-      <c r="E25" s="55" t="s">
+      <c r="E25" s="56" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7437,16 +7481,16 @@
       <c r="A26" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="46">
+      <c r="B26" s="47">
         <v>45986</v>
       </c>
-      <c r="C26" s="46">
+      <c r="C26" s="47">
         <v>45987</v>
       </c>
       <c r="D26" s="16">
         <v>1</v>
       </c>
-      <c r="E26" s="55" t="s">
+      <c r="E26" s="56" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7454,16 +7498,16 @@
       <c r="A27" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="46">
+      <c r="B27" s="47">
         <v>45986</v>
       </c>
-      <c r="C27" s="46">
+      <c r="C27" s="47">
         <v>45987</v>
       </c>
       <c r="D27" s="16">
         <v>1</v>
       </c>
-      <c r="E27" s="55" t="s">
+      <c r="E27" s="56" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7471,16 +7515,16 @@
       <c r="A28" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="46">
+      <c r="B28" s="47">
         <v>45986</v>
       </c>
-      <c r="C28" s="46">
+      <c r="C28" s="47">
         <v>45987</v>
       </c>
       <c r="D28" s="16">
         <v>1</v>
       </c>
-      <c r="E28" s="55" t="s">
+      <c r="E28" s="56" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7488,16 +7532,16 @@
       <c r="A29" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="46">
+      <c r="B29" s="47">
         <v>45986</v>
       </c>
-      <c r="C29" s="46">
+      <c r="C29" s="47">
         <v>45987</v>
       </c>
       <c r="D29" s="16">
         <v>1</v>
       </c>
-      <c r="E29" s="55" t="s">
+      <c r="E29" s="56" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7505,16 +7549,16 @@
       <c r="A30" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="46">
+      <c r="B30" s="47">
         <v>45986</v>
       </c>
-      <c r="C30" s="46">
+      <c r="C30" s="47">
         <v>45987</v>
       </c>
       <c r="D30" s="16">
         <v>1</v>
       </c>
-      <c r="E30" s="55" t="s">
+      <c r="E30" s="56" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7522,16 +7566,16 @@
       <c r="A31" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="46">
+      <c r="B31" s="47">
         <v>45992</v>
       </c>
-      <c r="C31" s="46">
+      <c r="C31" s="47">
         <v>45993</v>
       </c>
       <c r="D31" s="16">
         <v>1</v>
       </c>
-      <c r="E31" s="55" t="s">
+      <c r="E31" s="56" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7539,16 +7583,16 @@
       <c r="A32" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="46">
+      <c r="B32" s="47">
         <v>45992</v>
       </c>
-      <c r="C32" s="46">
+      <c r="C32" s="47">
         <v>45993</v>
       </c>
       <c r="D32" s="16">
         <v>1</v>
       </c>
-      <c r="E32" s="55" t="s">
+      <c r="E32" s="56" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7556,16 +7600,16 @@
       <c r="A33" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="46">
+      <c r="B33" s="47">
         <v>45992</v>
       </c>
-      <c r="C33" s="46">
+      <c r="C33" s="47">
         <v>45993</v>
       </c>
       <c r="D33" s="16">
         <v>1</v>
       </c>
-      <c r="E33" s="55" t="s">
+      <c r="E33" s="56" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7573,16 +7617,16 @@
       <c r="A34" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="46">
+      <c r="B34" s="47">
         <v>45993</v>
       </c>
-      <c r="C34" s="46">
+      <c r="C34" s="47">
         <v>45993</v>
       </c>
       <c r="D34" s="16">
         <v>1</v>
       </c>
-      <c r="E34" s="55" t="s">
+      <c r="E34" s="56" t="s">
         <v>35</v>
       </c>
     </row>
@@ -8196,21 +8240,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="40" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="2" ht="409.5" spans="1:3">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="42" t="s">
         <v>64</v>
       </c>
       <c r="C2" s="23" t="s">
@@ -8323,7 +8367,7 @@
       <c r="A15" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="42" t="s">
+      <c r="B15" s="43" t="s">
         <v>88</v>
       </c>
       <c r="C15" s="20"/>
@@ -8561,7 +8605,7 @@
       <c r="B1" s="20"/>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="34">
+      <c r="A2" s="35">
         <v>45962</v>
       </c>
       <c r="B2" s="20"/>
@@ -8570,7 +8614,7 @@
       <c r="A3" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="36" t="s">
         <v>91</v>
       </c>
     </row>
@@ -8578,7 +8622,7 @@
       <c r="A4" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="36" t="s">
         <v>93</v>
       </c>
     </row>
@@ -8586,21 +8630,21 @@
       <c r="A5" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="36" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="36">
+      <c r="A6" s="37">
         <v>45969</v>
       </c>
       <c r="B6" s="20"/>
     </row>
-    <row r="7" s="33" customFormat="1" ht="57.6" spans="1:2">
-      <c r="A7" s="37" t="s">
+    <row r="7" s="34" customFormat="1" ht="57.6" spans="1:2">
+      <c r="A7" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="39" t="s">
         <v>97</v>
       </c>
     </row>
@@ -9391,9 +9435,16 @@
         <v>287</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
-      <c r="A86" s="16"/>
-      <c r="B86" s="16"/>
+    <row r="86" ht="302.4" spans="1:3">
+      <c r="A86" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="B86" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="C86" s="33" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="16"/>
@@ -9466,7 +9517,7 @@
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="16" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -9504,7 +9555,7 @@
         <v>38</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -9514,76 +9565,76 @@
     </row>
     <row r="19" ht="72" spans="1:1">
       <c r="A19" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:1">
       <c r="A20" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="21" ht="100.8" spans="1:2">
       <c r="A21" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="19" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B22" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="23" ht="57.6" spans="1:2">
       <c r="A23" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="24" ht="72" spans="1:2">
       <c r="A24" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="25" ht="86.4" spans="1:2">
       <c r="A25" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="26" ht="43.2" spans="1:2">
       <c r="A26" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="27" ht="28.8" spans="1:2">
       <c r="A27" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="28" ht="43.2" spans="1:2">
       <c r="A28" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -9603,27 +9654,27 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="14" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="8" ht="15" spans="1:1">
       <c r="A8" s="15" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9" ht="120" customHeight="1" spans="1:1">
       <c r="A9" s="9" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -9647,201 +9698,201 @@
   <sheetData>
     <row r="1" spans="2:3">
       <c r="B1" s="7" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2" spans="2:3">
       <c r="B2" s="8" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="2:3">
       <c r="B3" s="8" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" s="8" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="B5" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>319</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="6" spans="2:3">
       <c r="B6" s="8" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="B7" s="8" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="8" ht="43.2" spans="2:3">
       <c r="B8" s="8" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" s="10" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10" spans="2:2">
       <c r="B10" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="11" ht="23.4" spans="2:2">
       <c r="B11" s="11" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" s="12" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="15" spans="2:2">
       <c r="B15" s="12" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="16" spans="2:2">
       <c r="B16" s="12" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" s="12" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" s="12" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" s="12" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" s="12" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" s="12" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" s="12" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" s="12" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="26" ht="23.4" spans="2:2">
       <c r="B26" s="11" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" s="12" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="29" spans="2:2">
       <c r="B29" s="12" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" s="12" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="31" spans="2:2">
       <c r="B31" s="12" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" s="12" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" s="12" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" s="12" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="36" spans="2:2">
@@ -9866,83 +9917,83 @@
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="41" ht="23.4" spans="2:2">
       <c r="B41" s="11" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="43" spans="2:2">
       <c r="B43" s="12" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" s="12" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="45" spans="2:2">
       <c r="B45" s="12" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" s="12" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" s="13" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" s="13" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" s="13" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" s="13" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="54" ht="13" customHeight="1"/>
     <row r="55" ht="22" customHeight="1" spans="2:2">
       <c r="B55" s="11" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="57" spans="2:2">
       <c r="B57" s="12" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="58" spans="2:2">
@@ -9957,17 +10008,17 @@
     </row>
     <row r="60" spans="2:2">
       <c r="B60" s="12" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61" s="12" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -9984,7 +10035,7 @@
   <sheetData>
     <row r="1" spans="1:21">
       <c r="A1" s="3" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -9999,7 +10050,7 @@
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
       <c r="N1" s="5" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
@@ -10241,7 +10292,7 @@
     </row>
     <row r="12" spans="1:21">
       <c r="A12" s="3" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -10427,7 +10478,7 @@
     </row>
     <row r="22" spans="1:21">
       <c r="A22" s="4" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>

--- a/JavaPrograms/Work Done.xlsx
+++ b/JavaPrograms/Work Done.xlsx
@@ -3888,9 +3888,11 @@
 You cannot close door #1 until doors #4, #3, #2 are closed.
 The last opened door must be closed first.
 That is exactly a stack.
-So yes:
-First close opposite to driver → then behind → then opposite → then driver
-That is LIFO in real life.</t>
+So yes: First close opposite to driver → then behind → then opposite → then driver
+That is LIFO in real life.
+How to explain it more simply (even cleaner)
+Here’s the simplest version you can say without thinking:
+“Whenever things must be closed in the reverse order of opening, we use a stack.”</t>
   </si>
   <si>
     <t>Space Complexity</t>

--- a/JavaPrograms/Work Done.xlsx
+++ b/JavaPrograms/Work Done.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="385">
   <si>
     <r>
       <rPr>
@@ -3707,6 +3707,7 @@
 [5 | next] → [7 | next] → [9 | null]
 A linked list is just boxes connected by arrows.
 2️⃣ What does a pointer store?
+222
 A pointer stores the address of a box, not the value.
 It’s like:
 not holding the house
@@ -3893,6 +3894,80 @@
 How to explain it more simply (even cleaner)
 Here’s the simplest version you can say without thinking:
 “Whenever things must be closed in the reverse order of opening, we use a stack.”</t>
+  </si>
+  <si>
+    <t>Monotonic Stack</t>
+  </si>
+  <si>
+    <t>Imagine you’re standing in a line of people.
+You want to know:
+“For each person, who is the next taller person in front?”
+You could check everyone one by one (slow).
+Instead, you do this:
+Keep a stack of people who still haven’t found a taller person.
+When a taller person arrives, they become the answer for many behind them.
+That’s monotonic stack.
+2️⃣ What “monotonic” means (simple)
+Monotonic = always in one order
+Two types:
+✅ Monotonic Increasing Stack
+Stack values go like:
+1 3 5 8
+(never decreases)
+✅ Monotonic Decreasing Stack
+Stack values go like:
+8 6 4 2
+(never increases)
+3️⃣ Why do we even need this?
+Because it solves problems like:
+Next Greater Element
+Next Smaller Element
+Previous Greater/Smaller
+Daily Temperatures
+Stock Span
+Largest Rectangle in Histogram
+These problems share one demand:
+“Find the next thing to the right (or left) that breaks a condition.”
+4️⃣ The one rule you must memorize
+Pop until the stack becomes valid again.
+That’s it.
+Monotonic stack is basically:
+✅ keep stack ordered
+✅ when new element breaks order → popImagine you’re standing in a line of people.
+You want to know:
+“For each person, who is the next taller person in front?”
+You could check everyone one by one (slow).
+Instead, you do this:
+Keep a stack of people who still haven’t found a taller person.
+When a taller person arrives, they become the answer for many behind them.
+That’s monotonic stack.
+2️⃣ What “monotonic” means (simple)
+Monotonic = always in one order
+Two types
+✅ Monotonic Increasing Stack
+Stack values go like:
+1 3 5 8
+(never decreases)
+✅ Monotonic Decreasing Stack
+Stack values go like:
+8 6 4 2
+(never increases)
+3️⃣ Why do we even need this?
+Because it solves problems like:
+Next Greater Element
+Next Smaller Element
+Previous Greater/Smaller
+Daily Temperatures
+Stock Span
+Largest Rectangle in Histogram
+These problems share one demand:
+“Find the next thing to the right (or left) that breaks a condition.”
+4️⃣ The one rule you must memorize
+Pop until the stack becomes valid again.
+That’s it.
+Monotonic stack is basically:
+✅ keep stack ordered
+✅ when new element breaks order → pop</t>
   </si>
   <si>
     <t>Space Complexity</t>
@@ -4783,15 +4858,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <i/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -5398,7 +5473,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5497,9 +5572,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
@@ -6205,246 +6277,246 @@
   </cols>
   <sheetData>
     <row r="1" ht="90" customHeight="1" spans="1:6">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="59" t="s">
+      <c r="B1" s="57"/>
+      <c r="C1" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="60"/>
-      <c r="E1" s="61" t="s">
+      <c r="D1" s="59"/>
+      <c r="E1" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="61"/>
+      <c r="F1" s="60"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="61" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="16"/>
-      <c r="C2" s="63" t="s">
+      <c r="C2" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="64"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="16"/>
       <c r="B4" s="16"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="61"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="16"/>
       <c r="B5" s="16"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="60"/>
+      <c r="F5" s="60"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="16"/>
       <c r="B6" s="16"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="16"/>
       <c r="B7" s="16"/>
-      <c r="C7" s="65"/>
-      <c r="D7" s="66"/>
-      <c r="E7" s="61"/>
-      <c r="F7" s="61"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="16"/>
       <c r="B8" s="16"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="68"/>
-      <c r="E8" s="61"/>
-      <c r="F8" s="61"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="62" t="s">
+      <c r="A9" s="61" t="s">
         <v>5</v>
       </c>
       <c r="B9" s="18"/>
-      <c r="C9" s="69" t="s">
+      <c r="C9" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="70"/>
-      <c r="E9" s="61"/>
-      <c r="F9" s="61"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="18"/>
       <c r="B10" s="18"/>
-      <c r="C10" s="71"/>
-      <c r="D10" s="72"/>
-      <c r="E10" s="61"/>
-      <c r="F10" s="61"/>
+      <c r="C10" s="70"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="18"/>
       <c r="B11" s="18"/>
-      <c r="C11" s="71"/>
-      <c r="D11" s="72"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
+      <c r="C11" s="70"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="18"/>
       <c r="B12" s="18"/>
-      <c r="C12" s="71"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="61"/>
+      <c r="C12" s="70"/>
+      <c r="D12" s="71"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="18"/>
       <c r="B13" s="18"/>
-      <c r="C13" s="71"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="61"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="18"/>
       <c r="B14" s="18"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="61"/>
+      <c r="C14" s="70"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:6">
       <c r="A15" s="18"/>
       <c r="B15" s="18"/>
-      <c r="C15" s="73"/>
-      <c r="D15" s="74"/>
-      <c r="E15" s="61"/>
-      <c r="F15" s="61"/>
+      <c r="C15" s="72"/>
+      <c r="D15" s="73"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="18"/>
       <c r="B16" s="18"/>
-      <c r="C16" s="75" t="s">
+      <c r="C16" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="76"/>
-      <c r="E16" s="61"/>
-      <c r="F16" s="61"/>
+      <c r="D16" s="75"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="60"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="18"/>
       <c r="B17" s="18"/>
-      <c r="C17" s="77"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="61"/>
-      <c r="F17" s="61"/>
+      <c r="C17" s="76"/>
+      <c r="D17" s="77"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="60"/>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="18"/>
       <c r="B18" s="18"/>
-      <c r="C18" s="77"/>
-      <c r="D18" s="78"/>
-      <c r="E18" s="61"/>
-      <c r="F18" s="61"/>
+      <c r="C18" s="76"/>
+      <c r="D18" s="77"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="62" t="s">
+      <c r="A19" s="61" t="s">
         <v>8</v>
       </c>
       <c r="B19" s="16"/>
-      <c r="C19" s="77"/>
-      <c r="D19" s="78"/>
-      <c r="E19" s="61"/>
-      <c r="F19" s="61"/>
+      <c r="C19" s="76"/>
+      <c r="D19" s="77"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60"/>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="16"/>
       <c r="B20" s="16"/>
-      <c r="C20" s="77"/>
-      <c r="D20" s="78"/>
-      <c r="E20" s="61"/>
-      <c r="F20" s="61"/>
+      <c r="C20" s="76"/>
+      <c r="D20" s="77"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="16"/>
       <c r="B21" s="16"/>
-      <c r="C21" s="77"/>
-      <c r="D21" s="78"/>
-      <c r="E21" s="61"/>
-      <c r="F21" s="61"/>
+      <c r="C21" s="76"/>
+      <c r="D21" s="77"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="60"/>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="16"/>
       <c r="B22" s="16"/>
-      <c r="C22" s="77"/>
-      <c r="D22" s="78"/>
+      <c r="C22" s="76"/>
+      <c r="D22" s="77"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="16"/>
       <c r="B23" s="16"/>
-      <c r="C23" s="79"/>
-      <c r="D23" s="80"/>
+      <c r="C23" s="78"/>
+      <c r="D23" s="79"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="16"/>
       <c r="B24" s="16"/>
-      <c r="C24" s="81" t="s">
+      <c r="C24" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="82"/>
+      <c r="D24" s="81"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="16"/>
       <c r="B25" s="16"/>
-      <c r="C25" s="83"/>
-      <c r="D25" s="84"/>
+      <c r="C25" s="82"/>
+      <c r="D25" s="83"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="16"/>
       <c r="B26" s="16"/>
-      <c r="C26" s="83"/>
-      <c r="D26" s="84"/>
+      <c r="C26" s="82"/>
+      <c r="D26" s="83"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="16"/>
       <c r="B27" s="16"/>
-      <c r="C27" s="83"/>
-      <c r="D27" s="84"/>
+      <c r="C27" s="82"/>
+      <c r="D27" s="83"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="16"/>
       <c r="B28" s="16"/>
-      <c r="C28" s="85"/>
-      <c r="D28" s="86"/>
+      <c r="C28" s="84"/>
+      <c r="D28" s="85"/>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="16"/>
@@ -6459,7 +6531,7 @@
       <c r="D30" s="20"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="62" t="s">
+      <c r="A31" s="61" t="s">
         <v>10</v>
       </c>
       <c r="B31" s="18"/>
@@ -6515,7 +6587,7 @@
       <c r="D39" s="20"/>
     </row>
     <row r="40" ht="18" customHeight="1" spans="1:4">
-      <c r="A40" s="62" t="s">
+      <c r="A40" s="61" t="s">
         <v>11</v>
       </c>
       <c r="B40" s="18"/>
@@ -6577,7 +6649,7 @@
       <c r="D49" s="20"/>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="62" t="s">
+      <c r="A50" s="61" t="s">
         <v>12</v>
       </c>
       <c r="B50" s="18"/>
@@ -6633,7 +6705,7 @@
       <c r="D58" s="20"/>
     </row>
     <row r="59" spans="1:4">
-      <c r="A59" s="62" t="s">
+      <c r="A59" s="61" t="s">
         <v>13</v>
       </c>
       <c r="B59" s="16"/>
@@ -6689,7 +6761,7 @@
       <c r="D67" s="20"/>
     </row>
     <row r="68" spans="1:4">
-      <c r="A68" s="62" t="s">
+      <c r="A68" s="61" t="s">
         <v>14</v>
       </c>
       <c r="B68" s="16"/>
@@ -6751,7 +6823,7 @@
       <c r="D77" s="20"/>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="62" t="s">
+      <c r="A78" s="61" t="s">
         <v>15</v>
       </c>
       <c r="B78" s="16"/>
@@ -6813,7 +6885,7 @@
       <c r="D87" s="20"/>
     </row>
     <row r="88" spans="1:4">
-      <c r="A88" s="62" t="s">
+      <c r="A88" s="61" t="s">
         <v>16</v>
       </c>
       <c r="B88" s="16"/>
@@ -6869,7 +6941,7 @@
       <c r="D96" s="20"/>
     </row>
     <row r="97" spans="1:4">
-      <c r="A97" s="62" t="s">
+      <c r="A97" s="61" t="s">
         <v>17</v>
       </c>
       <c r="B97" s="18"/>
@@ -6925,7 +6997,7 @@
       <c r="D105" s="20"/>
     </row>
     <row r="106" spans="1:4">
-      <c r="A106" s="62" t="s">
+      <c r="A106" s="61" t="s">
         <v>18</v>
       </c>
       <c r="B106" s="16"/>
@@ -7019,7 +7091,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>100</v>
@@ -7027,24 +7099,24 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B2" s="1"/>
     </row>
     <row r="3" ht="100.8" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="4" ht="57.6" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -7079,7 +7151,7 @@
       <c r="D1" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="45" t="s">
+      <c r="E1" s="44" t="s">
         <v>23</v>
       </c>
     </row>
@@ -7087,31 +7159,31 @@
       <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="46">
+      <c r="B2" s="45">
         <v>45976</v>
       </c>
-      <c r="C2" s="47">
+      <c r="C2" s="46">
         <v>45983</v>
       </c>
       <c r="D2" s="16">
         <v>4</v>
       </c>
-      <c r="E2" s="48"/>
+      <c r="E2" s="47"/>
     </row>
     <row r="3" ht="115.2" spans="1:5">
       <c r="A3" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="46">
+      <c r="B3" s="45">
         <v>45976</v>
       </c>
-      <c r="C3" s="47">
+      <c r="C3" s="46">
         <v>45983</v>
       </c>
       <c r="D3" s="16">
         <v>4</v>
       </c>
-      <c r="E3" s="49" t="s">
+      <c r="E3" s="48" t="s">
         <v>26</v>
       </c>
     </row>
@@ -7119,16 +7191,16 @@
       <c r="A4" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="46">
+      <c r="B4" s="45">
         <v>45976</v>
       </c>
-      <c r="C4" s="47">
+      <c r="C4" s="46">
         <v>45983</v>
       </c>
       <c r="D4" s="16">
         <v>3</v>
       </c>
-      <c r="E4" s="50" t="s">
+      <c r="E4" s="49" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7136,125 +7208,125 @@
       <c r="A5" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="46">
+      <c r="B5" s="45">
         <v>45976</v>
       </c>
-      <c r="C5" s="47">
+      <c r="C5" s="46">
         <v>45983</v>
       </c>
       <c r="D5" s="16">
         <v>2</v>
       </c>
-      <c r="E5" s="51"/>
+      <c r="E5" s="50"/>
     </row>
     <row r="6" ht="115.2" spans="1:5">
       <c r="A6" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="46">
+      <c r="B6" s="45">
         <v>45976</v>
       </c>
-      <c r="C6" s="47">
+      <c r="C6" s="46">
         <v>45983</v>
       </c>
       <c r="D6" s="16">
         <v>2</v>
       </c>
-      <c r="E6" s="51"/>
+      <c r="E6" s="50"/>
     </row>
     <row r="7" ht="129.6" spans="1:5">
       <c r="A7" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="46">
+      <c r="B7" s="45">
         <v>45976</v>
       </c>
-      <c r="C7" s="47">
+      <c r="C7" s="46">
         <v>45983</v>
       </c>
       <c r="D7" s="16">
         <v>2</v>
       </c>
-      <c r="E7" s="51"/>
-    </row>
-    <row r="8" s="44" customFormat="1" ht="144" spans="1:5">
-      <c r="A8" s="52" t="s">
+      <c r="E7" s="50"/>
+    </row>
+    <row r="8" s="43" customFormat="1" ht="144" spans="1:5">
+      <c r="A8" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="47">
+      <c r="B8" s="46">
         <v>45976</v>
       </c>
-      <c r="C8" s="47">
+      <c r="C8" s="46">
         <v>45983</v>
       </c>
-      <c r="D8" s="53">
+      <c r="D8" s="52">
         <v>2</v>
       </c>
-      <c r="E8" s="54"/>
-    </row>
-    <row r="9" s="44" customFormat="1" ht="158.4" spans="1:5">
-      <c r="A9" s="52" t="s">
+      <c r="E8" s="53"/>
+    </row>
+    <row r="9" s="43" customFormat="1" ht="158.4" spans="1:5">
+      <c r="A9" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="47">
+      <c r="B9" s="46">
         <v>45976</v>
       </c>
-      <c r="C9" s="47">
+      <c r="C9" s="46">
         <v>45983</v>
       </c>
-      <c r="D9" s="53">
+      <c r="D9" s="52">
         <v>1</v>
       </c>
-      <c r="E9" s="55"/>
-    </row>
-    <row r="10" s="44" customFormat="1" spans="1:5">
-      <c r="A10" s="53" t="s">
+      <c r="E9" s="54"/>
+    </row>
+    <row r="10" s="43" customFormat="1" spans="1:5">
+      <c r="A10" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="47">
+      <c r="B10" s="46">
         <v>45976</v>
       </c>
-      <c r="C10" s="47">
+      <c r="C10" s="46">
         <v>45983</v>
       </c>
-      <c r="D10" s="53">
+      <c r="D10" s="52">
         <v>1</v>
       </c>
-      <c r="E10" s="56" t="s">
+      <c r="E10" s="55" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" s="44" customFormat="1" spans="1:5">
-      <c r="A11" s="53" t="s">
+    <row r="11" s="43" customFormat="1" spans="1:5">
+      <c r="A11" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="47">
+      <c r="B11" s="46">
         <v>45976</v>
       </c>
-      <c r="C11" s="47">
+      <c r="C11" s="46">
         <v>45983</v>
       </c>
-      <c r="D11" s="53">
+      <c r="D11" s="52">
         <v>1</v>
       </c>
-      <c r="E11" s="56" t="s">
+      <c r="E11" s="55" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" s="44" customFormat="1" spans="1:5">
-      <c r="A12" s="53" t="s">
+    <row r="12" s="43" customFormat="1" spans="1:5">
+      <c r="A12" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="47">
+      <c r="B12" s="46">
         <v>45976</v>
       </c>
-      <c r="C12" s="47">
+      <c r="C12" s="46">
         <v>45983</v>
       </c>
-      <c r="D12" s="53">
+      <c r="D12" s="52">
         <v>1</v>
       </c>
-      <c r="E12" s="56" t="s">
+      <c r="E12" s="55" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7262,16 +7334,16 @@
       <c r="A13" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="47">
+      <c r="B13" s="46">
         <v>45977</v>
       </c>
-      <c r="C13" s="47">
+      <c r="C13" s="46">
         <v>45982</v>
       </c>
       <c r="D13" s="16">
         <v>1</v>
       </c>
-      <c r="E13" s="56" t="s">
+      <c r="E13" s="55" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7279,16 +7351,16 @@
       <c r="A14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="47">
+      <c r="B14" s="46">
         <v>45980</v>
       </c>
-      <c r="C14" s="47">
+      <c r="C14" s="46">
         <v>45982</v>
       </c>
       <c r="D14" s="16">
         <v>1</v>
       </c>
-      <c r="E14" s="56" t="s">
+      <c r="E14" s="55" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7296,16 +7368,16 @@
       <c r="A15" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="47">
+      <c r="B15" s="46">
         <v>45980</v>
       </c>
-      <c r="C15" s="47">
+      <c r="C15" s="46">
         <v>45982</v>
       </c>
       <c r="D15" s="16">
         <v>1</v>
       </c>
-      <c r="E15" s="56" t="s">
+      <c r="E15" s="55" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7313,16 +7385,16 @@
       <c r="A16" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="47">
+      <c r="B16" s="46">
         <v>45980</v>
       </c>
-      <c r="C16" s="47">
+      <c r="C16" s="46">
         <v>45982</v>
       </c>
       <c r="D16" s="16">
         <v>1</v>
       </c>
-      <c r="E16" s="56" t="s">
+      <c r="E16" s="55" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7330,16 +7402,16 @@
       <c r="A17" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="47">
+      <c r="B17" s="46">
         <v>45980</v>
       </c>
-      <c r="C17" s="47">
+      <c r="C17" s="46">
         <v>45982</v>
       </c>
       <c r="D17" s="16">
         <v>1</v>
       </c>
-      <c r="E17" s="56" t="s">
+      <c r="E17" s="55" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7347,16 +7419,16 @@
       <c r="A18" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="47">
+      <c r="B18" s="46">
         <v>45981</v>
       </c>
-      <c r="C18" s="47">
+      <c r="C18" s="46">
         <v>45983</v>
       </c>
       <c r="D18" s="16">
         <v>1</v>
       </c>
-      <c r="E18" s="56" t="s">
+      <c r="E18" s="55" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7364,16 +7436,16 @@
       <c r="A19" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="47">
+      <c r="B19" s="46">
         <v>45982</v>
       </c>
-      <c r="C19" s="47">
+      <c r="C19" s="46">
         <v>45984</v>
       </c>
       <c r="D19" s="16">
         <v>1</v>
       </c>
-      <c r="E19" s="56" t="s">
+      <c r="E19" s="55" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7381,16 +7453,16 @@
       <c r="A20" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="47">
+      <c r="B20" s="46">
         <v>45983</v>
       </c>
-      <c r="C20" s="47">
+      <c r="C20" s="46">
         <v>45985</v>
       </c>
       <c r="D20" s="16">
         <v>1</v>
       </c>
-      <c r="E20" s="56" t="s">
+      <c r="E20" s="55" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7398,16 +7470,16 @@
       <c r="A21" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="47">
+      <c r="B21" s="46">
         <v>45986</v>
       </c>
-      <c r="C21" s="47">
+      <c r="C21" s="46">
         <v>45987</v>
       </c>
       <c r="D21" s="16">
         <v>1</v>
       </c>
-      <c r="E21" s="56" t="s">
+      <c r="E21" s="55" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7415,16 +7487,16 @@
       <c r="A22" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="47">
+      <c r="B22" s="46">
         <v>45986</v>
       </c>
-      <c r="C22" s="47">
+      <c r="C22" s="46">
         <v>45987</v>
       </c>
       <c r="D22" s="16">
         <v>1</v>
       </c>
-      <c r="E22" s="56" t="s">
+      <c r="E22" s="55" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7432,16 +7504,16 @@
       <c r="A23" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="47">
+      <c r="B23" s="46">
         <v>45986</v>
       </c>
-      <c r="C23" s="47">
+      <c r="C23" s="46">
         <v>45987</v>
       </c>
       <c r="D23" s="16">
         <v>1</v>
       </c>
-      <c r="E23" s="56" t="s">
+      <c r="E23" s="55" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7449,16 +7521,16 @@
       <c r="A24" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="47">
+      <c r="B24" s="46">
         <v>45986</v>
       </c>
-      <c r="C24" s="47">
+      <c r="C24" s="46">
         <v>45987</v>
       </c>
       <c r="D24" s="16">
         <v>1</v>
       </c>
-      <c r="E24" s="56" t="s">
+      <c r="E24" s="55" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7466,16 +7538,16 @@
       <c r="A25" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="47">
+      <c r="B25" s="46">
         <v>45986</v>
       </c>
-      <c r="C25" s="47">
+      <c r="C25" s="46">
         <v>45987</v>
       </c>
       <c r="D25" s="16">
         <v>1</v>
       </c>
-      <c r="E25" s="56" t="s">
+      <c r="E25" s="55" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7483,16 +7555,16 @@
       <c r="A26" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="47">
+      <c r="B26" s="46">
         <v>45986</v>
       </c>
-      <c r="C26" s="47">
+      <c r="C26" s="46">
         <v>45987</v>
       </c>
       <c r="D26" s="16">
         <v>1</v>
       </c>
-      <c r="E26" s="56" t="s">
+      <c r="E26" s="55" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7500,16 +7572,16 @@
       <c r="A27" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="47">
+      <c r="B27" s="46">
         <v>45986</v>
       </c>
-      <c r="C27" s="47">
+      <c r="C27" s="46">
         <v>45987</v>
       </c>
       <c r="D27" s="16">
         <v>1</v>
       </c>
-      <c r="E27" s="56" t="s">
+      <c r="E27" s="55" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7517,16 +7589,16 @@
       <c r="A28" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="47">
+      <c r="B28" s="46">
         <v>45986</v>
       </c>
-      <c r="C28" s="47">
+      <c r="C28" s="46">
         <v>45987</v>
       </c>
       <c r="D28" s="16">
         <v>1</v>
       </c>
-      <c r="E28" s="56" t="s">
+      <c r="E28" s="55" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7534,16 +7606,16 @@
       <c r="A29" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="47">
+      <c r="B29" s="46">
         <v>45986</v>
       </c>
-      <c r="C29" s="47">
+      <c r="C29" s="46">
         <v>45987</v>
       </c>
       <c r="D29" s="16">
         <v>1</v>
       </c>
-      <c r="E29" s="56" t="s">
+      <c r="E29" s="55" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7551,16 +7623,16 @@
       <c r="A30" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="47">
+      <c r="B30" s="46">
         <v>45986</v>
       </c>
-      <c r="C30" s="47">
+      <c r="C30" s="46">
         <v>45987</v>
       </c>
       <c r="D30" s="16">
         <v>1</v>
       </c>
-      <c r="E30" s="56" t="s">
+      <c r="E30" s="55" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7568,16 +7640,16 @@
       <c r="A31" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="47">
+      <c r="B31" s="46">
         <v>45992</v>
       </c>
-      <c r="C31" s="47">
+      <c r="C31" s="46">
         <v>45993</v>
       </c>
       <c r="D31" s="16">
         <v>1</v>
       </c>
-      <c r="E31" s="56" t="s">
+      <c r="E31" s="55" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7585,16 +7657,16 @@
       <c r="A32" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="47">
+      <c r="B32" s="46">
         <v>45992</v>
       </c>
-      <c r="C32" s="47">
+      <c r="C32" s="46">
         <v>45993</v>
       </c>
       <c r="D32" s="16">
         <v>1</v>
       </c>
-      <c r="E32" s="56" t="s">
+      <c r="E32" s="55" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7602,16 +7674,16 @@
       <c r="A33" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="47">
+      <c r="B33" s="46">
         <v>45992</v>
       </c>
-      <c r="C33" s="47">
+      <c r="C33" s="46">
         <v>45993</v>
       </c>
       <c r="D33" s="16">
         <v>1</v>
       </c>
-      <c r="E33" s="56" t="s">
+      <c r="E33" s="55" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7619,16 +7691,16 @@
       <c r="A34" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="47">
+      <c r="B34" s="46">
         <v>45993</v>
       </c>
-      <c r="C34" s="47">
+      <c r="C34" s="46">
         <v>45993</v>
       </c>
       <c r="D34" s="16">
         <v>1</v>
       </c>
-      <c r="E34" s="56" t="s">
+      <c r="E34" s="55" t="s">
         <v>35</v>
       </c>
     </row>
@@ -8242,21 +8314,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="39" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="2" ht="409.5" spans="1:3">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="40" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="41" t="s">
         <v>64</v>
       </c>
       <c r="C2" s="23" t="s">
@@ -8369,7 +8441,7 @@
       <c r="A15" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="43" t="s">
+      <c r="B15" s="42" t="s">
         <v>88</v>
       </c>
       <c r="C15" s="20"/>
@@ -8607,7 +8679,7 @@
       <c r="B1" s="20"/>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="35">
+      <c r="A2" s="34">
         <v>45962</v>
       </c>
       <c r="B2" s="20"/>
@@ -8616,7 +8688,7 @@
       <c r="A3" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="35" t="s">
         <v>91</v>
       </c>
     </row>
@@ -8624,7 +8696,7 @@
       <c r="A4" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="35" t="s">
         <v>93</v>
       </c>
     </row>
@@ -8632,21 +8704,21 @@
       <c r="A5" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="35" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="37">
+      <c r="A6" s="36">
         <v>45969</v>
       </c>
       <c r="B6" s="20"/>
     </row>
-    <row r="7" s="34" customFormat="1" ht="57.6" spans="1:2">
-      <c r="A7" s="38" t="s">
+    <row r="7" s="33" customFormat="1" ht="57.6" spans="1:2">
+      <c r="A7" s="37" t="s">
         <v>96</v>
       </c>
-      <c r="B7" s="39" t="s">
+      <c r="B7" s="38" t="s">
         <v>97</v>
       </c>
     </row>
@@ -9444,13 +9516,17 @@
       <c r="B86" s="18" t="s">
         <v>289</v>
       </c>
-      <c r="C86" s="33" t="s">
+      <c r="C86" s="23" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
-      <c r="A87" s="16"/>
-      <c r="B87" s="16"/>
+    <row r="87" ht="409.5" spans="1:2">
+      <c r="A87" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="B87" s="18" t="s">
+        <v>292</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -9519,7 +9595,7 @@
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="16" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -9557,7 +9633,7 @@
         <v>38</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -9567,76 +9643,76 @@
     </row>
     <row r="19" ht="72" spans="1:1">
       <c r="A19" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:1">
       <c r="A20" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="21" ht="100.8" spans="1:2">
       <c r="A21" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="19" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B22" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="23" ht="57.6" spans="1:2">
       <c r="A23" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="24" ht="72" spans="1:2">
       <c r="A24" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="25" ht="86.4" spans="1:2">
       <c r="A25" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="26" ht="43.2" spans="1:2">
       <c r="A26" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="27" ht="28.8" spans="1:2">
       <c r="A27" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="28" ht="43.2" spans="1:2">
       <c r="A28" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -9656,27 +9732,27 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="14" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="8" ht="15" spans="1:1">
       <c r="A8" s="15" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="9" ht="120" customHeight="1" spans="1:1">
       <c r="A9" s="9" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -9700,201 +9776,201 @@
   <sheetData>
     <row r="1" spans="2:3">
       <c r="B1" s="7" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="2" spans="2:3">
       <c r="B2" s="8" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="2:3">
       <c r="B3" s="8" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>321</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="B5" s="8" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" spans="2:3">
       <c r="B6" s="8" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="B7" s="8" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="8" ht="43.2" spans="2:3">
       <c r="B8" s="8" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" s="10" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10" spans="2:2">
       <c r="B10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" ht="23.4" spans="2:2">
       <c r="B11" s="11" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" s="12" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="15" spans="2:2">
       <c r="B15" s="12" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="16" spans="2:2">
       <c r="B16" s="12" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" s="12" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" s="12" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" s="12" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" s="12" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" s="12" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" s="12" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="26" ht="23.4" spans="2:2">
       <c r="B26" s="11" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" s="12" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="29" spans="2:2">
       <c r="B29" s="12" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" s="12" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="31" spans="2:2">
       <c r="B31" s="12" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" s="12" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" s="12" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" s="12" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="36" spans="2:2">
@@ -9919,83 +9995,83 @@
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="41" ht="23.4" spans="2:2">
       <c r="B41" s="11" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="43" spans="2:2">
       <c r="B43" s="12" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" s="12" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="45" spans="2:2">
       <c r="B45" s="12" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" s="12" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" s="13" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" s="13" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" s="13" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" s="13" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="54" ht="13" customHeight="1"/>
     <row r="55" ht="22" customHeight="1" spans="2:2">
       <c r="B55" s="11" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="57" spans="2:2">
       <c r="B57" s="12" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="58" spans="2:2">
@@ -10010,17 +10086,17 @@
     </row>
     <row r="60" spans="2:2">
       <c r="B60" s="12" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61" s="12" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -10037,7 +10113,7 @@
   <sheetData>
     <row r="1" spans="1:21">
       <c r="A1" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -10052,7 +10128,7 @@
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
       <c r="N1" s="5" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
@@ -10294,7 +10370,7 @@
     </row>
     <row r="12" spans="1:21">
       <c r="A12" s="3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -10480,7 +10556,7 @@
     </row>
     <row r="22" spans="1:21">
       <c r="A22" s="4" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>

--- a/JavaPrograms/Work Done.xlsx
+++ b/JavaPrograms/Work Done.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000" firstSheet="2" activeTab="4"/>
+    <workbookView windowWidth="23040" windowHeight="8280" firstSheet="2" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="DSA plan" sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="387">
   <si>
     <r>
       <rPr>
@@ -3968,6 +3968,24 @@
 Monotonic stack is basically:
 ✅ keep stack ordered
 ✅ when new element breaks order → pop</t>
+  </si>
+  <si>
+    <t>HASHING &amp; SETS</t>
+  </si>
+  <si>
+    <t>This phase is about one superpower:
+O(1) lookup to detect patterns fast
+Hashing solves:
+counting
+uniqueness
+grouping
+existence checking
+ ELI5
+A HashMap is like a notebook:
+you write: “I have seen this before”
+or: “I have seen it 5 times”
+or: “this item belongs to this group”
+Instead of searching full list again and again, you just look in notebook.</t>
   </si>
   <si>
     <t>Space Complexity</t>
@@ -5473,7 +5491,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5572,6 +5590,12 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
@@ -6277,246 +6301,246 @@
   </cols>
   <sheetData>
     <row r="1" ht="90" customHeight="1" spans="1:6">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="58" t="s">
+      <c r="B1" s="59"/>
+      <c r="C1" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="59"/>
-      <c r="E1" s="60" t="s">
+      <c r="D1" s="61"/>
+      <c r="E1" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="60"/>
+      <c r="F1" s="62"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="63" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="16"/>
-      <c r="C2" s="62" t="s">
+      <c r="C2" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="63"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="16"/>
       <c r="B4" s="16"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="16"/>
       <c r="B5" s="16"/>
-      <c r="C5" s="64"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="16"/>
       <c r="B6" s="16"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="16"/>
       <c r="B7" s="16"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="60"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="16"/>
       <c r="B8" s="16"/>
-      <c r="C8" s="66"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="62"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="61" t="s">
+      <c r="A9" s="63" t="s">
         <v>5</v>
       </c>
       <c r="B9" s="18"/>
-      <c r="C9" s="68" t="s">
+      <c r="C9" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="69"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="62"/>
+      <c r="F9" s="62"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="18"/>
       <c r="B10" s="18"/>
-      <c r="C10" s="70"/>
-      <c r="D10" s="71"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
+      <c r="C10" s="72"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="62"/>
+      <c r="F10" s="62"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="18"/>
       <c r="B11" s="18"/>
-      <c r="C11" s="70"/>
-      <c r="D11" s="71"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="60"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="18"/>
       <c r="B12" s="18"/>
-      <c r="C12" s="70"/>
-      <c r="D12" s="71"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="62"/>
+      <c r="F12" s="62"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="18"/>
       <c r="B13" s="18"/>
-      <c r="C13" s="70"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="73"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="62"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="18"/>
       <c r="B14" s="18"/>
-      <c r="C14" s="70"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:6">
       <c r="A15" s="18"/>
       <c r="B15" s="18"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="73"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
+      <c r="C15" s="74"/>
+      <c r="D15" s="75"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="18"/>
       <c r="B16" s="18"/>
-      <c r="C16" s="74" t="s">
+      <c r="C16" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="75"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
+      <c r="D16" s="77"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="62"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="18"/>
       <c r="B17" s="18"/>
-      <c r="C17" s="76"/>
-      <c r="D17" s="77"/>
-      <c r="E17" s="60"/>
-      <c r="F17" s="60"/>
+      <c r="C17" s="78"/>
+      <c r="D17" s="79"/>
+      <c r="E17" s="62"/>
+      <c r="F17" s="62"/>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="18"/>
       <c r="B18" s="18"/>
-      <c r="C18" s="76"/>
-      <c r="D18" s="77"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="60"/>
+      <c r="C18" s="78"/>
+      <c r="D18" s="79"/>
+      <c r="E18" s="62"/>
+      <c r="F18" s="62"/>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="61" t="s">
+      <c r="A19" s="63" t="s">
         <v>8</v>
       </c>
       <c r="B19" s="16"/>
-      <c r="C19" s="76"/>
-      <c r="D19" s="77"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
+      <c r="C19" s="78"/>
+      <c r="D19" s="79"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="62"/>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="16"/>
       <c r="B20" s="16"/>
-      <c r="C20" s="76"/>
-      <c r="D20" s="77"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
+      <c r="C20" s="78"/>
+      <c r="D20" s="79"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="62"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="16"/>
       <c r="B21" s="16"/>
-      <c r="C21" s="76"/>
-      <c r="D21" s="77"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="60"/>
+      <c r="C21" s="78"/>
+      <c r="D21" s="79"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="62"/>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="16"/>
       <c r="B22" s="16"/>
-      <c r="C22" s="76"/>
-      <c r="D22" s="77"/>
+      <c r="C22" s="78"/>
+      <c r="D22" s="79"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="16"/>
       <c r="B23" s="16"/>
-      <c r="C23" s="78"/>
-      <c r="D23" s="79"/>
+      <c r="C23" s="80"/>
+      <c r="D23" s="81"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="16"/>
       <c r="B24" s="16"/>
-      <c r="C24" s="80" t="s">
+      <c r="C24" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="81"/>
+      <c r="D24" s="83"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="16"/>
       <c r="B25" s="16"/>
-      <c r="C25" s="82"/>
-      <c r="D25" s="83"/>
+      <c r="C25" s="84"/>
+      <c r="D25" s="85"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="16"/>
       <c r="B26" s="16"/>
-      <c r="C26" s="82"/>
-      <c r="D26" s="83"/>
+      <c r="C26" s="84"/>
+      <c r="D26" s="85"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="16"/>
       <c r="B27" s="16"/>
-      <c r="C27" s="82"/>
-      <c r="D27" s="83"/>
+      <c r="C27" s="84"/>
+      <c r="D27" s="85"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="16"/>
       <c r="B28" s="16"/>
-      <c r="C28" s="84"/>
-      <c r="D28" s="85"/>
+      <c r="C28" s="86"/>
+      <c r="D28" s="87"/>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="16"/>
@@ -6531,7 +6555,7 @@
       <c r="D30" s="20"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="61" t="s">
+      <c r="A31" s="63" t="s">
         <v>10</v>
       </c>
       <c r="B31" s="18"/>
@@ -6587,7 +6611,7 @@
       <c r="D39" s="20"/>
     </row>
     <row r="40" ht="18" customHeight="1" spans="1:4">
-      <c r="A40" s="61" t="s">
+      <c r="A40" s="63" t="s">
         <v>11</v>
       </c>
       <c r="B40" s="18"/>
@@ -6649,7 +6673,7 @@
       <c r="D49" s="20"/>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="61" t="s">
+      <c r="A50" s="63" t="s">
         <v>12</v>
       </c>
       <c r="B50" s="18"/>
@@ -6705,7 +6729,7 @@
       <c r="D58" s="20"/>
     </row>
     <row r="59" spans="1:4">
-      <c r="A59" s="61" t="s">
+      <c r="A59" s="63" t="s">
         <v>13</v>
       </c>
       <c r="B59" s="16"/>
@@ -6761,7 +6785,7 @@
       <c r="D67" s="20"/>
     </row>
     <row r="68" spans="1:4">
-      <c r="A68" s="61" t="s">
+      <c r="A68" s="63" t="s">
         <v>14</v>
       </c>
       <c r="B68" s="16"/>
@@ -6823,7 +6847,7 @@
       <c r="D77" s="20"/>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="61" t="s">
+      <c r="A78" s="63" t="s">
         <v>15</v>
       </c>
       <c r="B78" s="16"/>
@@ -6885,7 +6909,7 @@
       <c r="D87" s="20"/>
     </row>
     <row r="88" spans="1:4">
-      <c r="A88" s="61" t="s">
+      <c r="A88" s="63" t="s">
         <v>16</v>
       </c>
       <c r="B88" s="16"/>
@@ -6941,7 +6965,7 @@
       <c r="D96" s="20"/>
     </row>
     <row r="97" spans="1:4">
-      <c r="A97" s="61" t="s">
+      <c r="A97" s="63" t="s">
         <v>17</v>
       </c>
       <c r="B97" s="18"/>
@@ -6997,7 +7021,7 @@
       <c r="D105" s="20"/>
     </row>
     <row r="106" spans="1:4">
-      <c r="A106" s="61" t="s">
+      <c r="A106" s="63" t="s">
         <v>18</v>
       </c>
       <c r="B106" s="16"/>
@@ -7091,7 +7115,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>100</v>
@@ -7099,24 +7123,24 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B2" s="1"/>
     </row>
     <row r="3" ht="100.8" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="4" ht="57.6" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -7151,7 +7175,7 @@
       <c r="D1" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="E1" s="46" t="s">
         <v>23</v>
       </c>
     </row>
@@ -7159,31 +7183,31 @@
       <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="45">
+      <c r="B2" s="47">
         <v>45976</v>
       </c>
-      <c r="C2" s="46">
+      <c r="C2" s="48">
         <v>45983</v>
       </c>
       <c r="D2" s="16">
         <v>4</v>
       </c>
-      <c r="E2" s="47"/>
+      <c r="E2" s="49"/>
     </row>
     <row r="3" ht="115.2" spans="1:5">
       <c r="A3" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="45">
+      <c r="B3" s="47">
         <v>45976</v>
       </c>
-      <c r="C3" s="46">
+      <c r="C3" s="48">
         <v>45983</v>
       </c>
       <c r="D3" s="16">
         <v>4</v>
       </c>
-      <c r="E3" s="48" t="s">
+      <c r="E3" s="50" t="s">
         <v>26</v>
       </c>
     </row>
@@ -7191,16 +7215,16 @@
       <c r="A4" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="45">
+      <c r="B4" s="47">
         <v>45976</v>
       </c>
-      <c r="C4" s="46">
+      <c r="C4" s="48">
         <v>45983</v>
       </c>
       <c r="D4" s="16">
         <v>3</v>
       </c>
-      <c r="E4" s="49" t="s">
+      <c r="E4" s="51" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7208,125 +7232,125 @@
       <c r="A5" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="45">
+      <c r="B5" s="47">
         <v>45976</v>
       </c>
-      <c r="C5" s="46">
+      <c r="C5" s="48">
         <v>45983</v>
       </c>
       <c r="D5" s="16">
         <v>2</v>
       </c>
-      <c r="E5" s="50"/>
+      <c r="E5" s="52"/>
     </row>
     <row r="6" ht="115.2" spans="1:5">
       <c r="A6" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="45">
+      <c r="B6" s="47">
         <v>45976</v>
       </c>
-      <c r="C6" s="46">
+      <c r="C6" s="48">
         <v>45983</v>
       </c>
       <c r="D6" s="16">
         <v>2</v>
       </c>
-      <c r="E6" s="50"/>
+      <c r="E6" s="52"/>
     </row>
     <row r="7" ht="129.6" spans="1:5">
       <c r="A7" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="45">
+      <c r="B7" s="47">
         <v>45976</v>
       </c>
-      <c r="C7" s="46">
+      <c r="C7" s="48">
         <v>45983</v>
       </c>
       <c r="D7" s="16">
         <v>2</v>
       </c>
-      <c r="E7" s="50"/>
-    </row>
-    <row r="8" s="43" customFormat="1" ht="144" spans="1:5">
-      <c r="A8" s="51" t="s">
+      <c r="E7" s="52"/>
+    </row>
+    <row r="8" s="45" customFormat="1" ht="144" spans="1:5">
+      <c r="A8" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="46">
+      <c r="B8" s="48">
         <v>45976</v>
       </c>
-      <c r="C8" s="46">
+      <c r="C8" s="48">
         <v>45983</v>
       </c>
-      <c r="D8" s="52">
+      <c r="D8" s="54">
         <v>2</v>
       </c>
-      <c r="E8" s="53"/>
-    </row>
-    <row r="9" s="43" customFormat="1" ht="158.4" spans="1:5">
-      <c r="A9" s="51" t="s">
+      <c r="E8" s="55"/>
+    </row>
+    <row r="9" s="45" customFormat="1" ht="158.4" spans="1:5">
+      <c r="A9" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="46">
+      <c r="B9" s="48">
         <v>45976</v>
       </c>
-      <c r="C9" s="46">
+      <c r="C9" s="48">
         <v>45983</v>
       </c>
-      <c r="D9" s="52">
+      <c r="D9" s="54">
         <v>1</v>
       </c>
-      <c r="E9" s="54"/>
-    </row>
-    <row r="10" s="43" customFormat="1" spans="1:5">
-      <c r="A10" s="52" t="s">
+      <c r="E9" s="56"/>
+    </row>
+    <row r="10" s="45" customFormat="1" spans="1:5">
+      <c r="A10" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="46">
+      <c r="B10" s="48">
         <v>45976</v>
       </c>
-      <c r="C10" s="46">
+      <c r="C10" s="48">
         <v>45983</v>
       </c>
-      <c r="D10" s="52">
+      <c r="D10" s="54">
         <v>1</v>
       </c>
-      <c r="E10" s="55" t="s">
+      <c r="E10" s="57" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" s="43" customFormat="1" spans="1:5">
-      <c r="A11" s="52" t="s">
+    <row r="11" s="45" customFormat="1" spans="1:5">
+      <c r="A11" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="46">
+      <c r="B11" s="48">
         <v>45976</v>
       </c>
-      <c r="C11" s="46">
+      <c r="C11" s="48">
         <v>45983</v>
       </c>
-      <c r="D11" s="52">
+      <c r="D11" s="54">
         <v>1</v>
       </c>
-      <c r="E11" s="55" t="s">
+      <c r="E11" s="57" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" s="43" customFormat="1" spans="1:5">
-      <c r="A12" s="52" t="s">
+    <row r="12" s="45" customFormat="1" spans="1:5">
+      <c r="A12" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="46">
+      <c r="B12" s="48">
         <v>45976</v>
       </c>
-      <c r="C12" s="46">
+      <c r="C12" s="48">
         <v>45983</v>
       </c>
-      <c r="D12" s="52">
+      <c r="D12" s="54">
         <v>1</v>
       </c>
-      <c r="E12" s="55" t="s">
+      <c r="E12" s="57" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7334,16 +7358,16 @@
       <c r="A13" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="46">
+      <c r="B13" s="48">
         <v>45977</v>
       </c>
-      <c r="C13" s="46">
+      <c r="C13" s="48">
         <v>45982</v>
       </c>
       <c r="D13" s="16">
         <v>1</v>
       </c>
-      <c r="E13" s="55" t="s">
+      <c r="E13" s="57" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7351,16 +7375,16 @@
       <c r="A14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="46">
+      <c r="B14" s="48">
         <v>45980</v>
       </c>
-      <c r="C14" s="46">
+      <c r="C14" s="48">
         <v>45982</v>
       </c>
       <c r="D14" s="16">
         <v>1</v>
       </c>
-      <c r="E14" s="55" t="s">
+      <c r="E14" s="57" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7368,16 +7392,16 @@
       <c r="A15" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="46">
+      <c r="B15" s="48">
         <v>45980</v>
       </c>
-      <c r="C15" s="46">
+      <c r="C15" s="48">
         <v>45982</v>
       </c>
       <c r="D15" s="16">
         <v>1</v>
       </c>
-      <c r="E15" s="55" t="s">
+      <c r="E15" s="57" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7385,16 +7409,16 @@
       <c r="A16" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="46">
+      <c r="B16" s="48">
         <v>45980</v>
       </c>
-      <c r="C16" s="46">
+      <c r="C16" s="48">
         <v>45982</v>
       </c>
       <c r="D16" s="16">
         <v>1</v>
       </c>
-      <c r="E16" s="55" t="s">
+      <c r="E16" s="57" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7402,16 +7426,16 @@
       <c r="A17" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="46">
+      <c r="B17" s="48">
         <v>45980</v>
       </c>
-      <c r="C17" s="46">
+      <c r="C17" s="48">
         <v>45982</v>
       </c>
       <c r="D17" s="16">
         <v>1</v>
       </c>
-      <c r="E17" s="55" t="s">
+      <c r="E17" s="57" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7419,16 +7443,16 @@
       <c r="A18" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="46">
+      <c r="B18" s="48">
         <v>45981</v>
       </c>
-      <c r="C18" s="46">
+      <c r="C18" s="48">
         <v>45983</v>
       </c>
       <c r="D18" s="16">
         <v>1</v>
       </c>
-      <c r="E18" s="55" t="s">
+      <c r="E18" s="57" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7436,16 +7460,16 @@
       <c r="A19" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="46">
+      <c r="B19" s="48">
         <v>45982</v>
       </c>
-      <c r="C19" s="46">
+      <c r="C19" s="48">
         <v>45984</v>
       </c>
       <c r="D19" s="16">
         <v>1</v>
       </c>
-      <c r="E19" s="55" t="s">
+      <c r="E19" s="57" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7453,16 +7477,16 @@
       <c r="A20" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="46">
+      <c r="B20" s="48">
         <v>45983</v>
       </c>
-      <c r="C20" s="46">
+      <c r="C20" s="48">
         <v>45985</v>
       </c>
       <c r="D20" s="16">
         <v>1</v>
       </c>
-      <c r="E20" s="55" t="s">
+      <c r="E20" s="57" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7470,16 +7494,16 @@
       <c r="A21" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="46">
+      <c r="B21" s="48">
         <v>45986</v>
       </c>
-      <c r="C21" s="46">
+      <c r="C21" s="48">
         <v>45987</v>
       </c>
       <c r="D21" s="16">
         <v>1</v>
       </c>
-      <c r="E21" s="55" t="s">
+      <c r="E21" s="57" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7487,16 +7511,16 @@
       <c r="A22" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="46">
+      <c r="B22" s="48">
         <v>45986</v>
       </c>
-      <c r="C22" s="46">
+      <c r="C22" s="48">
         <v>45987</v>
       </c>
       <c r="D22" s="16">
         <v>1</v>
       </c>
-      <c r="E22" s="55" t="s">
+      <c r="E22" s="57" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7504,16 +7528,16 @@
       <c r="A23" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="46">
+      <c r="B23" s="48">
         <v>45986</v>
       </c>
-      <c r="C23" s="46">
+      <c r="C23" s="48">
         <v>45987</v>
       </c>
       <c r="D23" s="16">
         <v>1</v>
       </c>
-      <c r="E23" s="55" t="s">
+      <c r="E23" s="57" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7521,16 +7545,16 @@
       <c r="A24" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="46">
+      <c r="B24" s="48">
         <v>45986</v>
       </c>
-      <c r="C24" s="46">
+      <c r="C24" s="48">
         <v>45987</v>
       </c>
       <c r="D24" s="16">
         <v>1</v>
       </c>
-      <c r="E24" s="55" t="s">
+      <c r="E24" s="57" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7538,16 +7562,16 @@
       <c r="A25" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="46">
+      <c r="B25" s="48">
         <v>45986</v>
       </c>
-      <c r="C25" s="46">
+      <c r="C25" s="48">
         <v>45987</v>
       </c>
       <c r="D25" s="16">
         <v>1</v>
       </c>
-      <c r="E25" s="55" t="s">
+      <c r="E25" s="57" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7555,16 +7579,16 @@
       <c r="A26" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="46">
+      <c r="B26" s="48">
         <v>45986</v>
       </c>
-      <c r="C26" s="46">
+      <c r="C26" s="48">
         <v>45987</v>
       </c>
       <c r="D26" s="16">
         <v>1</v>
       </c>
-      <c r="E26" s="55" t="s">
+      <c r="E26" s="57" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7572,16 +7596,16 @@
       <c r="A27" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="46">
+      <c r="B27" s="48">
         <v>45986</v>
       </c>
-      <c r="C27" s="46">
+      <c r="C27" s="48">
         <v>45987</v>
       </c>
       <c r="D27" s="16">
         <v>1</v>
       </c>
-      <c r="E27" s="55" t="s">
+      <c r="E27" s="57" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7589,16 +7613,16 @@
       <c r="A28" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="46">
+      <c r="B28" s="48">
         <v>45986</v>
       </c>
-      <c r="C28" s="46">
+      <c r="C28" s="48">
         <v>45987</v>
       </c>
       <c r="D28" s="16">
         <v>1</v>
       </c>
-      <c r="E28" s="55" t="s">
+      <c r="E28" s="57" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7606,16 +7630,16 @@
       <c r="A29" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="46">
+      <c r="B29" s="48">
         <v>45986</v>
       </c>
-      <c r="C29" s="46">
+      <c r="C29" s="48">
         <v>45987</v>
       </c>
       <c r="D29" s="16">
         <v>1</v>
       </c>
-      <c r="E29" s="55" t="s">
+      <c r="E29" s="57" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7623,16 +7647,16 @@
       <c r="A30" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="46">
+      <c r="B30" s="48">
         <v>45986</v>
       </c>
-      <c r="C30" s="46">
+      <c r="C30" s="48">
         <v>45987</v>
       </c>
       <c r="D30" s="16">
         <v>1</v>
       </c>
-      <c r="E30" s="55" t="s">
+      <c r="E30" s="57" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7640,16 +7664,16 @@
       <c r="A31" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="46">
+      <c r="B31" s="48">
         <v>45992</v>
       </c>
-      <c r="C31" s="46">
+      <c r="C31" s="48">
         <v>45993</v>
       </c>
       <c r="D31" s="16">
         <v>1</v>
       </c>
-      <c r="E31" s="55" t="s">
+      <c r="E31" s="57" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7657,16 +7681,16 @@
       <c r="A32" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="46">
+      <c r="B32" s="48">
         <v>45992</v>
       </c>
-      <c r="C32" s="46">
+      <c r="C32" s="48">
         <v>45993</v>
       </c>
       <c r="D32" s="16">
         <v>1</v>
       </c>
-      <c r="E32" s="55" t="s">
+      <c r="E32" s="57" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7674,16 +7698,16 @@
       <c r="A33" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="46">
+      <c r="B33" s="48">
         <v>45992</v>
       </c>
-      <c r="C33" s="46">
+      <c r="C33" s="48">
         <v>45993</v>
       </c>
       <c r="D33" s="16">
         <v>1</v>
       </c>
-      <c r="E33" s="55" t="s">
+      <c r="E33" s="57" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7691,16 +7715,16 @@
       <c r="A34" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="46">
+      <c r="B34" s="48">
         <v>45993</v>
       </c>
-      <c r="C34" s="46">
+      <c r="C34" s="48">
         <v>45993</v>
       </c>
       <c r="D34" s="16">
         <v>1</v>
       </c>
-      <c r="E34" s="55" t="s">
+      <c r="E34" s="57" t="s">
         <v>35</v>
       </c>
     </row>
@@ -8314,21 +8338,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="41" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="2" ht="409.5" spans="1:3">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="43" t="s">
         <v>64</v>
       </c>
       <c r="C2" s="23" t="s">
@@ -8441,7 +8465,7 @@
       <c r="A15" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="42" t="s">
+      <c r="B15" s="44" t="s">
         <v>88</v>
       </c>
       <c r="C15" s="20"/>
@@ -8679,7 +8703,7 @@
       <c r="B1" s="20"/>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="34">
+      <c r="A2" s="36">
         <v>45962</v>
       </c>
       <c r="B2" s="20"/>
@@ -8688,7 +8712,7 @@
       <c r="A3" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="37" t="s">
         <v>91</v>
       </c>
     </row>
@@ -8696,7 +8720,7 @@
       <c r="A4" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="37" t="s">
         <v>93</v>
       </c>
     </row>
@@ -8704,21 +8728,21 @@
       <c r="A5" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="37" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="36">
+      <c r="A6" s="38">
         <v>45969</v>
       </c>
       <c r="B6" s="20"/>
     </row>
-    <row r="7" s="33" customFormat="1" ht="57.6" spans="1:2">
-      <c r="A7" s="37" t="s">
+    <row r="7" s="35" customFormat="1" ht="57.6" spans="1:2">
+      <c r="A7" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="40" t="s">
         <v>97</v>
       </c>
     </row>
@@ -8736,7 +8760,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="38.4444444444444" style="20" customWidth="1"/>
@@ -9526,6 +9550,14 @@
       </c>
       <c r="B87" s="18" t="s">
         <v>292</v>
+      </c>
+    </row>
+    <row r="88" ht="216" spans="1:2">
+      <c r="A88" s="33" t="s">
+        <v>293</v>
+      </c>
+      <c r="B88" s="34" t="s">
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -9595,7 +9627,7 @@
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="16" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -9633,7 +9665,7 @@
         <v>38</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -9643,76 +9675,76 @@
     </row>
     <row r="19" ht="72" spans="1:1">
       <c r="A19" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:1">
       <c r="A20" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="21" ht="100.8" spans="1:2">
       <c r="A21" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="19" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B22" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="23" ht="57.6" spans="1:2">
       <c r="A23" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="24" ht="72" spans="1:2">
       <c r="A24" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="25" ht="86.4" spans="1:2">
       <c r="A25" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="26" ht="43.2" spans="1:2">
       <c r="A26" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="27" ht="28.8" spans="1:2">
       <c r="A27" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="28" ht="43.2" spans="1:2">
       <c r="A28" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -9732,27 +9764,27 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="14" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="8" ht="15" spans="1:1">
       <c r="A8" s="15" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9" ht="120" customHeight="1" spans="1:1">
       <c r="A9" s="9" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -9776,201 +9808,201 @@
   <sheetData>
     <row r="1" spans="2:3">
       <c r="B1" s="7" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2" spans="2:3">
       <c r="B2" s="8" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" spans="2:3">
       <c r="B3" s="8" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>323</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="B5" s="8" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" spans="2:3">
       <c r="B6" s="8" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="B7" s="8" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8" ht="43.2" spans="2:3">
       <c r="B8" s="8" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" s="10" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10" spans="2:2">
       <c r="B10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="11" ht="23.4" spans="2:2">
       <c r="B11" s="11" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" s="12" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="15" spans="2:2">
       <c r="B15" s="12" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="16" spans="2:2">
       <c r="B16" s="12" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" s="12" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" s="12" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" s="12" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" s="12" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" s="12" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="26" ht="23.4" spans="2:2">
       <c r="B26" s="11" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" s="12" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="29" spans="2:2">
       <c r="B29" s="12" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" s="12" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="31" spans="2:2">
       <c r="B31" s="12" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" s="12" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" s="12" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" s="12" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="36" spans="2:2">
@@ -9995,83 +10027,83 @@
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="41" ht="23.4" spans="2:2">
       <c r="B41" s="11" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="43" spans="2:2">
       <c r="B43" s="12" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" s="12" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="45" spans="2:2">
       <c r="B45" s="12" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" s="12" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" s="13" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" s="13" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" s="13" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" s="13" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="54" ht="13" customHeight="1"/>
     <row r="55" ht="22" customHeight="1" spans="2:2">
       <c r="B55" s="11" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="57" spans="2:2">
       <c r="B57" s="12" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="58" spans="2:2">
@@ -10086,17 +10118,17 @@
     </row>
     <row r="60" spans="2:2">
       <c r="B60" s="12" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61" s="12" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -10113,7 +10145,7 @@
   <sheetData>
     <row r="1" spans="1:21">
       <c r="A1" s="3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -10128,7 +10160,7 @@
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
       <c r="N1" s="5" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
@@ -10370,7 +10402,7 @@
     </row>
     <row r="12" spans="1:21">
       <c r="A12" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -10556,7 +10588,7 @@
     </row>
     <row r="22" spans="1:21">
       <c r="A22" s="4" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>

--- a/JavaPrograms/Work Done.xlsx
+++ b/JavaPrograms/Work Done.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8280" firstSheet="2" activeTab="4"/>
+    <workbookView windowWidth="23040" windowHeight="9000" firstSheet="2" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="DSA plan" sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="389">
   <si>
     <r>
       <rPr>
@@ -3988,6 +3988,12 @@
 Instead of searching full list again and again, you just look in notebook.</t>
   </si>
   <si>
+    <t>HashSet</t>
+  </si>
+  <si>
+    <t>A HashSet is a data structure that stores unique elements (no duplicates) in an unordered way, using a hash table for fast average O(1) addition, removal, and checking, making it ideal for quickly finding if an item exists or removing duplicates from a collection</t>
+  </si>
+  <si>
     <t>Space Complexity</t>
   </si>
   <si>
@@ -4876,15 +4882,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <i/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -5594,7 +5600,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -7115,7 +7121,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>100</v>
@@ -7123,24 +7129,24 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B2" s="1"/>
     </row>
     <row r="3" ht="100.8" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="4" ht="57.6" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -8760,7 +8766,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="38.4444444444444" style="20" customWidth="1"/>
@@ -9553,11 +9559,19 @@
       </c>
     </row>
     <row r="88" ht="216" spans="1:2">
-      <c r="A88" s="33" t="s">
+      <c r="A88" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="B88" s="34" t="s">
+      <c r="B88" s="23" t="s">
         <v>294</v>
+      </c>
+    </row>
+    <row r="89" ht="43.2" spans="1:2">
+      <c r="A89" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="B89" s="34" t="s">
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -9627,7 +9641,7 @@
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="16" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -9665,7 +9679,7 @@
         <v>38</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -9675,76 +9689,76 @@
     </row>
     <row r="19" ht="72" spans="1:1">
       <c r="A19" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:1">
       <c r="A20" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="21" ht="100.8" spans="1:2">
       <c r="A21" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="19" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B22" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="23" ht="57.6" spans="1:2">
       <c r="A23" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="24" ht="72" spans="1:2">
       <c r="A24" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="25" ht="86.4" spans="1:2">
       <c r="A25" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="26" ht="43.2" spans="1:2">
       <c r="A26" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="27" ht="28.8" spans="1:2">
       <c r="A27" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="28" ht="43.2" spans="1:2">
       <c r="A28" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -9764,27 +9778,27 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="14" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="8" ht="15" spans="1:1">
       <c r="A8" s="15" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9" ht="120" customHeight="1" spans="1:1">
       <c r="A9" s="9" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -9808,201 +9822,201 @@
   <sheetData>
     <row r="1" spans="2:3">
       <c r="B1" s="7" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="2:3">
       <c r="B2" s="8" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3" spans="2:3">
       <c r="B3" s="8" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>325</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="B5" s="8" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="6" spans="2:3">
       <c r="B6" s="8" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="B7" s="8" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="8" ht="43.2" spans="2:3">
       <c r="B8" s="8" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10" spans="2:2">
       <c r="B10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="11" ht="23.4" spans="2:2">
       <c r="B11" s="11" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" s="12" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="15" spans="2:2">
       <c r="B15" s="12" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="16" spans="2:2">
       <c r="B16" s="12" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" s="12" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" s="12" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" s="12" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" s="12" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" s="12" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" s="12" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="26" ht="23.4" spans="2:2">
       <c r="B26" s="11" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" s="12" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="29" spans="2:2">
       <c r="B29" s="12" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" s="12" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="31" spans="2:2">
       <c r="B31" s="12" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" s="12" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" s="12" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" s="12" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="36" spans="2:2">
@@ -10027,83 +10041,83 @@
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="41" ht="23.4" spans="2:2">
       <c r="B41" s="11" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="43" spans="2:2">
       <c r="B43" s="12" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" s="12" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="45" spans="2:2">
       <c r="B45" s="12" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" s="12" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" s="13" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" s="13" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" s="13" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" s="13" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="54" ht="13" customHeight="1"/>
     <row r="55" ht="22" customHeight="1" spans="2:2">
       <c r="B55" s="11" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="57" spans="2:2">
       <c r="B57" s="12" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="58" spans="2:2">
@@ -10118,17 +10132,17 @@
     </row>
     <row r="60" spans="2:2">
       <c r="B60" s="12" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61" s="12" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -10145,7 +10159,7 @@
   <sheetData>
     <row r="1" spans="1:21">
       <c r="A1" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -10160,7 +10174,7 @@
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
       <c r="N1" s="5" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
@@ -10402,7 +10416,7 @@
     </row>
     <row r="12" spans="1:21">
       <c r="A12" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -10588,7 +10602,7 @@
     </row>
     <row r="22" spans="1:21">
       <c r="A22" s="4" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>

--- a/JavaPrograms/Work Done.xlsx
+++ b/JavaPrograms/Work Done.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="393">
   <si>
     <r>
       <rPr>
@@ -3992,6 +3992,46 @@
   </si>
   <si>
     <t>A HashSet is a data structure that stores unique elements (no duplicates) in an unordered way, using a hash table for fast average O(1) addition, removal, and checking, making it ideal for quickly finding if an item exists or removing duplicates from a collection</t>
+  </si>
+  <si>
+    <t>Graphs</t>
+  </si>
+  <si>
+    <t>A graph is just:
+nodes (things)
+edges (connections)
+Like:
+people connected by friendship
+cities connected by roads
+web pages connected by links
+So graph questions are basically asking:
+“Starting somewhere, can you reach / count / explore connected stuff?”
+That’s it.</t>
+  </si>
+  <si>
+    <t>Graph traversal patterns</t>
+  </si>
+  <si>
+    <t>DFS (Depth First Search)
+ELI5:
+“Go deep first, keep walking until you can’t, then come back.”
+Works like:
+recursion
+stack
+Used for:
+exploring components
+island problems
+cycle detection
+path existence
+BFS (Breadth First Search)
+ELI5:
+“Explore level by level.”
+Works like:
+queue
+Used for:
+shortest path in unweighted graph
+minimum steps
+multi-source spread problems</t>
   </si>
   <si>
     <t>Space Complexity</t>
@@ -5497,7 +5537,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5601,6 +5641,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -6307,246 +6350,246 @@
   </cols>
   <sheetData>
     <row r="1" ht="90" customHeight="1" spans="1:6">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="60" t="s">
+      <c r="B1" s="60"/>
+      <c r="C1" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="61"/>
-      <c r="E1" s="62" t="s">
+      <c r="D1" s="62"/>
+      <c r="E1" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="62"/>
+      <c r="F1" s="63"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="64" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="16"/>
-      <c r="C2" s="64" t="s">
+      <c r="C2" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="65"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="16"/>
       <c r="B4" s="16"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="16"/>
       <c r="B5" s="16"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="63"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="16"/>
       <c r="B6" s="16"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="16"/>
       <c r="B7" s="16"/>
-      <c r="C7" s="66"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="62"/>
-      <c r="F7" s="62"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="63"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="16"/>
       <c r="B8" s="16"/>
-      <c r="C8" s="68"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="62"/>
-      <c r="F8" s="62"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="63"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="63" t="s">
+      <c r="A9" s="64" t="s">
         <v>5</v>
       </c>
       <c r="B9" s="18"/>
-      <c r="C9" s="70" t="s">
+      <c r="C9" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="71"/>
-      <c r="E9" s="62"/>
-      <c r="F9" s="62"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="18"/>
       <c r="B10" s="18"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="73"/>
-      <c r="E10" s="62"/>
-      <c r="F10" s="62"/>
+      <c r="C10" s="73"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="63"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="18"/>
       <c r="B11" s="18"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="73"/>
-      <c r="E11" s="62"/>
-      <c r="F11" s="62"/>
+      <c r="C11" s="73"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="63"/>
+      <c r="F11" s="63"/>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="18"/>
       <c r="B12" s="18"/>
-      <c r="C12" s="72"/>
-      <c r="D12" s="73"/>
-      <c r="E12" s="62"/>
-      <c r="F12" s="62"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="63"/>
+      <c r="F12" s="63"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="18"/>
       <c r="B13" s="18"/>
-      <c r="C13" s="72"/>
-      <c r="D13" s="73"/>
-      <c r="E13" s="62"/>
-      <c r="F13" s="62"/>
+      <c r="C13" s="73"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="63"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="18"/>
       <c r="B14" s="18"/>
-      <c r="C14" s="72"/>
-      <c r="D14" s="73"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="63"/>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:6">
       <c r="A15" s="18"/>
       <c r="B15" s="18"/>
-      <c r="C15" s="74"/>
-      <c r="D15" s="75"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="62"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="76"/>
+      <c r="E15" s="63"/>
+      <c r="F15" s="63"/>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="18"/>
       <c r="B16" s="18"/>
-      <c r="C16" s="76" t="s">
+      <c r="C16" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="77"/>
-      <c r="E16" s="62"/>
-      <c r="F16" s="62"/>
+      <c r="D16" s="78"/>
+      <c r="E16" s="63"/>
+      <c r="F16" s="63"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="18"/>
       <c r="B17" s="18"/>
-      <c r="C17" s="78"/>
-      <c r="D17" s="79"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="62"/>
+      <c r="C17" s="79"/>
+      <c r="D17" s="80"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="63"/>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="18"/>
       <c r="B18" s="18"/>
-      <c r="C18" s="78"/>
-      <c r="D18" s="79"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="62"/>
+      <c r="C18" s="79"/>
+      <c r="D18" s="80"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="63"/>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="63" t="s">
+      <c r="A19" s="64" t="s">
         <v>8</v>
       </c>
       <c r="B19" s="16"/>
-      <c r="C19" s="78"/>
-      <c r="D19" s="79"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="62"/>
+      <c r="C19" s="79"/>
+      <c r="D19" s="80"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="63"/>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="16"/>
       <c r="B20" s="16"/>
-      <c r="C20" s="78"/>
-      <c r="D20" s="79"/>
-      <c r="E20" s="62"/>
-      <c r="F20" s="62"/>
+      <c r="C20" s="79"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="63"/>
+      <c r="F20" s="63"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="16"/>
       <c r="B21" s="16"/>
-      <c r="C21" s="78"/>
-      <c r="D21" s="79"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="62"/>
+      <c r="C21" s="79"/>
+      <c r="D21" s="80"/>
+      <c r="E21" s="63"/>
+      <c r="F21" s="63"/>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="16"/>
       <c r="B22" s="16"/>
-      <c r="C22" s="78"/>
-      <c r="D22" s="79"/>
+      <c r="C22" s="79"/>
+      <c r="D22" s="80"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="16"/>
       <c r="B23" s="16"/>
-      <c r="C23" s="80"/>
-      <c r="D23" s="81"/>
+      <c r="C23" s="81"/>
+      <c r="D23" s="82"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="16"/>
       <c r="B24" s="16"/>
-      <c r="C24" s="82" t="s">
+      <c r="C24" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="83"/>
+      <c r="D24" s="84"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="16"/>
       <c r="B25" s="16"/>
-      <c r="C25" s="84"/>
-      <c r="D25" s="85"/>
+      <c r="C25" s="85"/>
+      <c r="D25" s="86"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9"/>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="16"/>
       <c r="B26" s="16"/>
-      <c r="C26" s="84"/>
-      <c r="D26" s="85"/>
+      <c r="C26" s="85"/>
+      <c r="D26" s="86"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="16"/>
       <c r="B27" s="16"/>
-      <c r="C27" s="84"/>
-      <c r="D27" s="85"/>
+      <c r="C27" s="85"/>
+      <c r="D27" s="86"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="16"/>
       <c r="B28" s="16"/>
-      <c r="C28" s="86"/>
-      <c r="D28" s="87"/>
+      <c r="C28" s="87"/>
+      <c r="D28" s="88"/>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="16"/>
@@ -6561,7 +6604,7 @@
       <c r="D30" s="20"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="63" t="s">
+      <c r="A31" s="64" t="s">
         <v>10</v>
       </c>
       <c r="B31" s="18"/>
@@ -6617,7 +6660,7 @@
       <c r="D39" s="20"/>
     </row>
     <row r="40" ht="18" customHeight="1" spans="1:4">
-      <c r="A40" s="63" t="s">
+      <c r="A40" s="64" t="s">
         <v>11</v>
       </c>
       <c r="B40" s="18"/>
@@ -6679,7 +6722,7 @@
       <c r="D49" s="20"/>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="63" t="s">
+      <c r="A50" s="64" t="s">
         <v>12</v>
       </c>
       <c r="B50" s="18"/>
@@ -6735,7 +6778,7 @@
       <c r="D58" s="20"/>
     </row>
     <row r="59" spans="1:4">
-      <c r="A59" s="63" t="s">
+      <c r="A59" s="64" t="s">
         <v>13</v>
       </c>
       <c r="B59" s="16"/>
@@ -6791,7 +6834,7 @@
       <c r="D67" s="20"/>
     </row>
     <row r="68" spans="1:4">
-      <c r="A68" s="63" t="s">
+      <c r="A68" s="64" t="s">
         <v>14</v>
       </c>
       <c r="B68" s="16"/>
@@ -6853,7 +6896,7 @@
       <c r="D77" s="20"/>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="63" t="s">
+      <c r="A78" s="64" t="s">
         <v>15</v>
       </c>
       <c r="B78" s="16"/>
@@ -6915,7 +6958,7 @@
       <c r="D87" s="20"/>
     </row>
     <row r="88" spans="1:4">
-      <c r="A88" s="63" t="s">
+      <c r="A88" s="64" t="s">
         <v>16</v>
       </c>
       <c r="B88" s="16"/>
@@ -6971,7 +7014,7 @@
       <c r="D96" s="20"/>
     </row>
     <row r="97" spans="1:4">
-      <c r="A97" s="63" t="s">
+      <c r="A97" s="64" t="s">
         <v>17</v>
       </c>
       <c r="B97" s="18"/>
@@ -7027,7 +7070,7 @@
       <c r="D105" s="20"/>
     </row>
     <row r="106" spans="1:4">
-      <c r="A106" s="63" t="s">
+      <c r="A106" s="64" t="s">
         <v>18</v>
       </c>
       <c r="B106" s="16"/>
@@ -7121,7 +7164,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>100</v>
@@ -7129,24 +7172,24 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B2" s="1"/>
     </row>
     <row r="3" ht="100.8" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="4" ht="57.6" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -7181,7 +7224,7 @@
       <c r="D1" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="46" t="s">
+      <c r="E1" s="47" t="s">
         <v>23</v>
       </c>
     </row>
@@ -7189,31 +7232,31 @@
       <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="47">
+      <c r="B2" s="48">
         <v>45976</v>
       </c>
-      <c r="C2" s="48">
+      <c r="C2" s="49">
         <v>45983</v>
       </c>
       <c r="D2" s="16">
         <v>4</v>
       </c>
-      <c r="E2" s="49"/>
+      <c r="E2" s="50"/>
     </row>
     <row r="3" ht="115.2" spans="1:5">
       <c r="A3" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="47">
+      <c r="B3" s="48">
         <v>45976</v>
       </c>
-      <c r="C3" s="48">
+      <c r="C3" s="49">
         <v>45983</v>
       </c>
       <c r="D3" s="16">
         <v>4</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="E3" s="51" t="s">
         <v>26</v>
       </c>
     </row>
@@ -7221,16 +7264,16 @@
       <c r="A4" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="47">
+      <c r="B4" s="48">
         <v>45976</v>
       </c>
-      <c r="C4" s="48">
+      <c r="C4" s="49">
         <v>45983</v>
       </c>
       <c r="D4" s="16">
         <v>3</v>
       </c>
-      <c r="E4" s="51" t="s">
+      <c r="E4" s="52" t="s">
         <v>28</v>
       </c>
     </row>
@@ -7238,125 +7281,125 @@
       <c r="A5" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="47">
+      <c r="B5" s="48">
         <v>45976</v>
       </c>
-      <c r="C5" s="48">
+      <c r="C5" s="49">
         <v>45983</v>
       </c>
       <c r="D5" s="16">
         <v>2</v>
       </c>
-      <c r="E5" s="52"/>
+      <c r="E5" s="53"/>
     </row>
     <row r="6" ht="115.2" spans="1:5">
       <c r="A6" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="47">
+      <c r="B6" s="48">
         <v>45976</v>
       </c>
-      <c r="C6" s="48">
+      <c r="C6" s="49">
         <v>45983</v>
       </c>
       <c r="D6" s="16">
         <v>2</v>
       </c>
-      <c r="E6" s="52"/>
+      <c r="E6" s="53"/>
     </row>
     <row r="7" ht="129.6" spans="1:5">
       <c r="A7" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="47">
+      <c r="B7" s="48">
         <v>45976</v>
       </c>
-      <c r="C7" s="48">
+      <c r="C7" s="49">
         <v>45983</v>
       </c>
       <c r="D7" s="16">
         <v>2</v>
       </c>
-      <c r="E7" s="52"/>
-    </row>
-    <row r="8" s="45" customFormat="1" ht="144" spans="1:5">
-      <c r="A8" s="53" t="s">
+      <c r="E7" s="53"/>
+    </row>
+    <row r="8" s="46" customFormat="1" ht="144" spans="1:5">
+      <c r="A8" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="48">
+      <c r="B8" s="49">
         <v>45976</v>
       </c>
-      <c r="C8" s="48">
+      <c r="C8" s="49">
         <v>45983</v>
       </c>
-      <c r="D8" s="54">
+      <c r="D8" s="55">
         <v>2</v>
       </c>
-      <c r="E8" s="55"/>
-    </row>
-    <row r="9" s="45" customFormat="1" ht="158.4" spans="1:5">
-      <c r="A9" s="53" t="s">
+      <c r="E8" s="56"/>
+    </row>
+    <row r="9" s="46" customFormat="1" ht="158.4" spans="1:5">
+      <c r="A9" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="48">
+      <c r="B9" s="49">
         <v>45976</v>
       </c>
-      <c r="C9" s="48">
+      <c r="C9" s="49">
         <v>45983</v>
       </c>
-      <c r="D9" s="54">
+      <c r="D9" s="55">
         <v>1</v>
       </c>
-      <c r="E9" s="56"/>
-    </row>
-    <row r="10" s="45" customFormat="1" spans="1:5">
-      <c r="A10" s="54" t="s">
+      <c r="E9" s="57"/>
+    </row>
+    <row r="10" s="46" customFormat="1" spans="1:5">
+      <c r="A10" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="48">
+      <c r="B10" s="49">
         <v>45976</v>
       </c>
-      <c r="C10" s="48">
+      <c r="C10" s="49">
         <v>45983</v>
       </c>
-      <c r="D10" s="54">
+      <c r="D10" s="55">
         <v>1</v>
       </c>
-      <c r="E10" s="57" t="s">
+      <c r="E10" s="58" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" s="45" customFormat="1" spans="1:5">
-      <c r="A11" s="54" t="s">
+    <row r="11" s="46" customFormat="1" spans="1:5">
+      <c r="A11" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="48">
+      <c r="B11" s="49">
         <v>45976</v>
       </c>
-      <c r="C11" s="48">
+      <c r="C11" s="49">
         <v>45983</v>
       </c>
-      <c r="D11" s="54">
+      <c r="D11" s="55">
         <v>1</v>
       </c>
-      <c r="E11" s="57" t="s">
+      <c r="E11" s="58" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" s="45" customFormat="1" spans="1:5">
-      <c r="A12" s="54" t="s">
+    <row r="12" s="46" customFormat="1" spans="1:5">
+      <c r="A12" s="55" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="48">
+      <c r="B12" s="49">
         <v>45976</v>
       </c>
-      <c r="C12" s="48">
+      <c r="C12" s="49">
         <v>45983</v>
       </c>
-      <c r="D12" s="54">
+      <c r="D12" s="55">
         <v>1</v>
       </c>
-      <c r="E12" s="57" t="s">
+      <c r="E12" s="58" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7364,16 +7407,16 @@
       <c r="A13" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="48">
+      <c r="B13" s="49">
         <v>45977</v>
       </c>
-      <c r="C13" s="48">
+      <c r="C13" s="49">
         <v>45982</v>
       </c>
       <c r="D13" s="16">
         <v>1</v>
       </c>
-      <c r="E13" s="57" t="s">
+      <c r="E13" s="58" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7381,16 +7424,16 @@
       <c r="A14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="48">
+      <c r="B14" s="49">
         <v>45980</v>
       </c>
-      <c r="C14" s="48">
+      <c r="C14" s="49">
         <v>45982</v>
       </c>
       <c r="D14" s="16">
         <v>1</v>
       </c>
-      <c r="E14" s="57" t="s">
+      <c r="E14" s="58" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7398,16 +7441,16 @@
       <c r="A15" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="48">
+      <c r="B15" s="49">
         <v>45980</v>
       </c>
-      <c r="C15" s="48">
+      <c r="C15" s="49">
         <v>45982</v>
       </c>
       <c r="D15" s="16">
         <v>1</v>
       </c>
-      <c r="E15" s="57" t="s">
+      <c r="E15" s="58" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7415,16 +7458,16 @@
       <c r="A16" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="48">
+      <c r="B16" s="49">
         <v>45980</v>
       </c>
-      <c r="C16" s="48">
+      <c r="C16" s="49">
         <v>45982</v>
       </c>
       <c r="D16" s="16">
         <v>1</v>
       </c>
-      <c r="E16" s="57" t="s">
+      <c r="E16" s="58" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7432,16 +7475,16 @@
       <c r="A17" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="48">
+      <c r="B17" s="49">
         <v>45980</v>
       </c>
-      <c r="C17" s="48">
+      <c r="C17" s="49">
         <v>45982</v>
       </c>
       <c r="D17" s="16">
         <v>1</v>
       </c>
-      <c r="E17" s="57" t="s">
+      <c r="E17" s="58" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7449,16 +7492,16 @@
       <c r="A18" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="48">
+      <c r="B18" s="49">
         <v>45981</v>
       </c>
-      <c r="C18" s="48">
+      <c r="C18" s="49">
         <v>45983</v>
       </c>
       <c r="D18" s="16">
         <v>1</v>
       </c>
-      <c r="E18" s="57" t="s">
+      <c r="E18" s="58" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7466,16 +7509,16 @@
       <c r="A19" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="48">
+      <c r="B19" s="49">
         <v>45982</v>
       </c>
-      <c r="C19" s="48">
+      <c r="C19" s="49">
         <v>45984</v>
       </c>
       <c r="D19" s="16">
         <v>1</v>
       </c>
-      <c r="E19" s="57" t="s">
+      <c r="E19" s="58" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7483,16 +7526,16 @@
       <c r="A20" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="48">
+      <c r="B20" s="49">
         <v>45983</v>
       </c>
-      <c r="C20" s="48">
+      <c r="C20" s="49">
         <v>45985</v>
       </c>
       <c r="D20" s="16">
         <v>1</v>
       </c>
-      <c r="E20" s="57" t="s">
+      <c r="E20" s="58" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7500,16 +7543,16 @@
       <c r="A21" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="48">
+      <c r="B21" s="49">
         <v>45986</v>
       </c>
-      <c r="C21" s="48">
+      <c r="C21" s="49">
         <v>45987</v>
       </c>
       <c r="D21" s="16">
         <v>1</v>
       </c>
-      <c r="E21" s="57" t="s">
+      <c r="E21" s="58" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7517,16 +7560,16 @@
       <c r="A22" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="48">
+      <c r="B22" s="49">
         <v>45986</v>
       </c>
-      <c r="C22" s="48">
+      <c r="C22" s="49">
         <v>45987</v>
       </c>
       <c r="D22" s="16">
         <v>1</v>
       </c>
-      <c r="E22" s="57" t="s">
+      <c r="E22" s="58" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7534,16 +7577,16 @@
       <c r="A23" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="48">
+      <c r="B23" s="49">
         <v>45986</v>
       </c>
-      <c r="C23" s="48">
+      <c r="C23" s="49">
         <v>45987</v>
       </c>
       <c r="D23" s="16">
         <v>1</v>
       </c>
-      <c r="E23" s="57" t="s">
+      <c r="E23" s="58" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7551,16 +7594,16 @@
       <c r="A24" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="48">
+      <c r="B24" s="49">
         <v>45986</v>
       </c>
-      <c r="C24" s="48">
+      <c r="C24" s="49">
         <v>45987</v>
       </c>
       <c r="D24" s="16">
         <v>1</v>
       </c>
-      <c r="E24" s="57" t="s">
+      <c r="E24" s="58" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7568,16 +7611,16 @@
       <c r="A25" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="48">
+      <c r="B25" s="49">
         <v>45986</v>
       </c>
-      <c r="C25" s="48">
+      <c r="C25" s="49">
         <v>45987</v>
       </c>
       <c r="D25" s="16">
         <v>1</v>
       </c>
-      <c r="E25" s="57" t="s">
+      <c r="E25" s="58" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7585,16 +7628,16 @@
       <c r="A26" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="48">
+      <c r="B26" s="49">
         <v>45986</v>
       </c>
-      <c r="C26" s="48">
+      <c r="C26" s="49">
         <v>45987</v>
       </c>
       <c r="D26" s="16">
         <v>1</v>
       </c>
-      <c r="E26" s="57" t="s">
+      <c r="E26" s="58" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7602,16 +7645,16 @@
       <c r="A27" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="48">
+      <c r="B27" s="49">
         <v>45986</v>
       </c>
-      <c r="C27" s="48">
+      <c r="C27" s="49">
         <v>45987</v>
       </c>
       <c r="D27" s="16">
         <v>1</v>
       </c>
-      <c r="E27" s="57" t="s">
+      <c r="E27" s="58" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7619,16 +7662,16 @@
       <c r="A28" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="48">
+      <c r="B28" s="49">
         <v>45986</v>
       </c>
-      <c r="C28" s="48">
+      <c r="C28" s="49">
         <v>45987</v>
       </c>
       <c r="D28" s="16">
         <v>1</v>
       </c>
-      <c r="E28" s="57" t="s">
+      <c r="E28" s="58" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7636,16 +7679,16 @@
       <c r="A29" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="48">
+      <c r="B29" s="49">
         <v>45986</v>
       </c>
-      <c r="C29" s="48">
+      <c r="C29" s="49">
         <v>45987</v>
       </c>
       <c r="D29" s="16">
         <v>1</v>
       </c>
-      <c r="E29" s="57" t="s">
+      <c r="E29" s="58" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7653,16 +7696,16 @@
       <c r="A30" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="48">
+      <c r="B30" s="49">
         <v>45986</v>
       </c>
-      <c r="C30" s="48">
+      <c r="C30" s="49">
         <v>45987</v>
       </c>
       <c r="D30" s="16">
         <v>1</v>
       </c>
-      <c r="E30" s="57" t="s">
+      <c r="E30" s="58" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7670,16 +7713,16 @@
       <c r="A31" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="48">
+      <c r="B31" s="49">
         <v>45992</v>
       </c>
-      <c r="C31" s="48">
+      <c r="C31" s="49">
         <v>45993</v>
       </c>
       <c r="D31" s="16">
         <v>1</v>
       </c>
-      <c r="E31" s="57" t="s">
+      <c r="E31" s="58" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7687,16 +7730,16 @@
       <c r="A32" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="48">
+      <c r="B32" s="49">
         <v>45992</v>
       </c>
-      <c r="C32" s="48">
+      <c r="C32" s="49">
         <v>45993</v>
       </c>
       <c r="D32" s="16">
         <v>1</v>
       </c>
-      <c r="E32" s="57" t="s">
+      <c r="E32" s="58" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7704,16 +7747,16 @@
       <c r="A33" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="48">
+      <c r="B33" s="49">
         <v>45992</v>
       </c>
-      <c r="C33" s="48">
+      <c r="C33" s="49">
         <v>45993</v>
       </c>
       <c r="D33" s="16">
         <v>1</v>
       </c>
-      <c r="E33" s="57" t="s">
+      <c r="E33" s="58" t="s">
         <v>35</v>
       </c>
     </row>
@@ -7721,16 +7764,16 @@
       <c r="A34" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="48">
+      <c r="B34" s="49">
         <v>45993</v>
       </c>
-      <c r="C34" s="48">
+      <c r="C34" s="49">
         <v>45993</v>
       </c>
       <c r="D34" s="16">
         <v>1</v>
       </c>
-      <c r="E34" s="57" t="s">
+      <c r="E34" s="58" t="s">
         <v>35</v>
       </c>
     </row>
@@ -8344,21 +8387,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="42" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="2" ht="409.5" spans="1:3">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="44" t="s">
         <v>64</v>
       </c>
       <c r="C2" s="23" t="s">
@@ -8471,7 +8514,7 @@
       <c r="A15" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="44" t="s">
+      <c r="B15" s="45" t="s">
         <v>88</v>
       </c>
       <c r="C15" s="20"/>
@@ -8709,7 +8752,7 @@
       <c r="B1" s="20"/>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="36">
+      <c r="A2" s="37">
         <v>45962</v>
       </c>
       <c r="B2" s="20"/>
@@ -8718,7 +8761,7 @@
       <c r="A3" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="38" t="s">
         <v>91</v>
       </c>
     </row>
@@ -8726,7 +8769,7 @@
       <c r="A4" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="38" t="s">
         <v>93</v>
       </c>
     </row>
@@ -8734,21 +8777,21 @@
       <c r="A5" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="38" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="38">
+      <c r="A6" s="39">
         <v>45969</v>
       </c>
       <c r="B6" s="20"/>
     </row>
-    <row r="7" s="35" customFormat="1" ht="57.6" spans="1:2">
-      <c r="A7" s="39" t="s">
+    <row r="7" s="36" customFormat="1" ht="57.6" spans="1:2">
+      <c r="A7" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="41" t="s">
         <v>97</v>
       </c>
     </row>
@@ -8766,7 +8809,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="38.4444444444444" style="20" customWidth="1"/>
@@ -9572,6 +9615,22 @@
       </c>
       <c r="B89" s="34" t="s">
         <v>296</v>
+      </c>
+    </row>
+    <row r="90" ht="144" spans="1:2">
+      <c r="A90" s="33" t="s">
+        <v>297</v>
+      </c>
+      <c r="B90" s="35" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="91" ht="302.4" spans="1:2">
+      <c r="A91" s="33" t="s">
+        <v>299</v>
+      </c>
+      <c r="B91" s="35" t="s">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -9641,7 +9700,7 @@
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="16" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -9679,7 +9738,7 @@
         <v>38</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -9689,76 +9748,76 @@
     </row>
     <row r="19" ht="72" spans="1:1">
       <c r="A19" s="2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:1">
       <c r="A20" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="21" ht="100.8" spans="1:2">
       <c r="A21" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="19" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B22" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="23" ht="57.6" spans="1:2">
       <c r="A23" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="24" ht="72" spans="1:2">
       <c r="A24" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="25" ht="86.4" spans="1:2">
       <c r="A25" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="26" ht="43.2" spans="1:2">
       <c r="A26" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="27" ht="28.8" spans="1:2">
       <c r="A27" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="28" ht="43.2" spans="1:2">
       <c r="A28" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -9778,27 +9837,27 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="14" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8" ht="15" spans="1:1">
       <c r="A8" s="15" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9" ht="120" customHeight="1" spans="1:1">
       <c r="A9" s="9" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -9822,201 +9881,201 @@
   <sheetData>
     <row r="1" spans="2:3">
       <c r="B1" s="7" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2" spans="2:3">
       <c r="B2" s="8" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3" spans="2:3">
       <c r="B3" s="8" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" s="8" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="B5" s="8" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" spans="2:3">
       <c r="B6" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>329</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="B7" s="8" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="8" ht="43.2" spans="2:3">
       <c r="B8" s="8" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" s="10" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10" spans="2:2">
       <c r="B10" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="11" ht="23.4" spans="2:2">
       <c r="B11" s="11" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" s="12" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="15" spans="2:2">
       <c r="B15" s="12" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="16" spans="2:2">
       <c r="B16" s="12" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" s="12" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" s="12" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" s="12" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" s="12" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" s="12" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" s="12" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" s="12" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="26" ht="23.4" spans="2:2">
       <c r="B26" s="11" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" s="12" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="29" spans="2:2">
       <c r="B29" s="12" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" s="12" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="31" spans="2:2">
       <c r="B31" s="12" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" s="12" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" s="12" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" s="12" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="36" spans="2:2">
@@ -10041,83 +10100,83 @@
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="41" ht="23.4" spans="2:2">
       <c r="B41" s="11" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="43" spans="2:2">
       <c r="B43" s="12" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" s="12" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="45" spans="2:2">
       <c r="B45" s="12" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" s="12" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" s="13" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" s="13" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" s="13" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" s="13" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="54" ht="13" customHeight="1"/>
     <row r="55" ht="22" customHeight="1" spans="2:2">
       <c r="B55" s="11" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="57" spans="2:2">
       <c r="B57" s="12" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="58" spans="2:2">
@@ -10132,17 +10191,17 @@
     </row>
     <row r="60" spans="2:2">
       <c r="B60" s="12" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61" s="12" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -10159,7 +10218,7 @@
   <sheetData>
     <row r="1" spans="1:21">
       <c r="A1" s="3" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -10174,7 +10233,7 @@
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
       <c r="N1" s="5" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
@@ -10416,7 +10475,7 @@
     </row>
     <row r="12" spans="1:21">
       <c r="A12" s="3" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -10602,7 +10661,7 @@
     </row>
     <row r="22" spans="1:21">
       <c r="A22" s="4" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>

--- a/JavaPrograms/Work Done.xlsx
+++ b/JavaPrograms/Work Done.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8280" firstSheet="3" activeTab="10"/>
+    <workbookView windowWidth="23040" windowHeight="9000" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="DSA plan" sheetId="4" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="416">
   <si>
     <r>
       <rPr>
@@ -957,6 +957,9 @@
       <t>: The backend connects to Google's Gemini 2.5 via a secure API gateway."
 That is how a Senior Engineer speaks. You have earned the right to say that now.</t>
     </r>
+  </si>
+  <si>
+    <t>666666666666666++</t>
   </si>
   <si>
     <t>Recall</t>
@@ -4995,15 +4998,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <i/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -7234,32 +7237,32 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B2" s="3"/>
     </row>
     <row r="3" ht="100.8" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4" ht="57.6" spans="1:2">
       <c r="A4" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -7280,102 +7283,102 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C5" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B6" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C6" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C7" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C8" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D8" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -8731,7 +8734,9 @@
       <c r="C20" s="22"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="22"/>
+      <c r="A21" s="22" t="s">
+        <v>89</v>
+      </c>
       <c r="B21" s="22"/>
       <c r="C21" s="22"/>
     </row>
@@ -8933,7 +8938,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B1" s="22"/>
     </row>
@@ -8945,26 +8950,26 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B3" s="37" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B4" s="37" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="22" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -8975,15 +8980,15 @@
     </row>
     <row r="7" s="35" customFormat="1" ht="57.6" spans="1:2">
       <c r="A7" s="39" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" ht="187.2" spans="1:1">
       <c r="A10" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -9007,10 +9012,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="23" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C1" s="24" t="s">
         <v>62</v>
@@ -9018,139 +9023,139 @@
     </row>
     <row r="2" ht="201.6" spans="1:3">
       <c r="A2" s="22" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" ht="100.8" spans="1:3">
       <c r="A3" s="22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" ht="72" spans="1:2">
       <c r="A4" s="26" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" ht="129.6" spans="1:3">
       <c r="A5" s="25" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" ht="129.6" spans="1:4">
       <c r="A6" s="25" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" ht="158.4" spans="1:3">
       <c r="A7" s="18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" ht="86.4" spans="1:2">
       <c r="A8" s="20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" ht="129.6" spans="1:2">
       <c r="A9" s="20" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" ht="129.6" spans="1:2">
       <c r="A10" s="18" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" ht="158.4" spans="1:2">
       <c r="A11" s="18" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" ht="115.2" spans="1:3">
       <c r="A12" s="20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" ht="158.4" spans="1:3">
       <c r="A13" s="18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" ht="158.4" spans="1:3">
       <c r="A14" s="18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C14" s="25"/>
     </row>
     <row r="15" ht="43.2" spans="1:3">
       <c r="A15" s="18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C15" s="25"/>
     </row>
@@ -9159,10 +9164,10 @@
         <v>34</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" ht="172.8" spans="1:3">
@@ -9170,10 +9175,10 @@
         <v>36</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="18" ht="409.5" spans="1:4">
@@ -9181,13 +9186,13 @@
         <v>37</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" ht="409.5" spans="1:4">
@@ -9195,628 +9200,628 @@
         <v>38</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D19" s="25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" ht="409.5" spans="1:4">
       <c r="A20" s="18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" ht="174" customHeight="1" spans="1:2">
       <c r="A21" s="18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" ht="187.2" spans="1:2">
       <c r="A22" s="18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" ht="244.8" spans="1:2">
       <c r="A23" s="18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" ht="158.4" spans="1:2">
       <c r="A24" s="18" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" ht="100.8" spans="1:2">
       <c r="A25" s="18" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" ht="409" customHeight="1" spans="1:3">
       <c r="A26" s="18" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" ht="57.6" spans="1:2">
       <c r="A27" s="18" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28" ht="409.5" spans="1:4">
       <c r="A28" s="18" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C28" s="25" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="29" ht="244.8" spans="1:3">
       <c r="A29" s="18" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30" ht="244.8" spans="1:2">
       <c r="A30" s="18" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" ht="187.2" spans="1:2">
       <c r="A31" s="30" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="32" ht="345.6" spans="1:2">
       <c r="A32" s="31"/>
       <c r="B32" s="32" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="33" ht="259.2" spans="1:2">
       <c r="A33" s="33" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B33" s="32" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="34" ht="100.8" spans="1:2">
       <c r="A34" s="18" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="35" ht="72" spans="1:2">
       <c r="A35" s="18" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="36" ht="409" customHeight="1" spans="1:3">
       <c r="A36" s="18" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C36" s="34" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="37" ht="187.2" spans="1:3">
       <c r="A37" s="18" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C37" s="34"/>
     </row>
     <row r="38" ht="288" spans="1:3">
       <c r="A38" s="18" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C38" s="34"/>
     </row>
     <row r="39" ht="216" spans="1:2">
       <c r="A39" s="18" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="40" ht="100.8" spans="1:2">
       <c r="A40" s="20" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="18" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B41" s="18"/>
     </row>
     <row r="42" ht="144" spans="1:3">
       <c r="A42" s="20" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C42" s="25" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="43" ht="57.6" spans="1:2">
       <c r="A43" s="20" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="44" ht="273.6" spans="1:2">
       <c r="A44" s="20" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="45" ht="172.8" spans="1:3">
       <c r="A45" s="18" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C45" s="25" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="46" ht="43.2" spans="1:2">
       <c r="A46" s="18" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="47" ht="144" spans="1:2">
       <c r="A47" s="18" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="48" ht="72" spans="1:2">
       <c r="A48" s="18" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="49" ht="57.6" spans="1:2">
       <c r="A49" s="18" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="50" ht="28.8" spans="1:2">
       <c r="A50" s="18" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="51" ht="230.4" spans="1:2">
       <c r="A51" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="52" ht="158.4" spans="1:2">
       <c r="A52" s="18" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="53" ht="129.6" spans="1:2">
       <c r="A53" s="18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="54" ht="409.5" spans="1:2">
       <c r="A54" s="18" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="55" ht="201.6" spans="1:3">
       <c r="A55" s="18" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B55" s="20" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C55" s="25" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="56" ht="409.5" spans="1:2">
       <c r="A56" s="18"/>
       <c r="B56" s="25" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="57" ht="409.5" spans="1:2">
       <c r="A57" s="18"/>
       <c r="B57" s="25" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="58" ht="115.2" spans="1:2">
       <c r="A58" s="22" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B58" s="20" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="59" ht="100.8" spans="1:2">
       <c r="A59" s="18" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B59" s="20" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="18" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B60" s="18" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="61" ht="86.4" spans="1:2">
       <c r="A61" s="18" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B61" s="20" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="62" ht="144" spans="1:2">
       <c r="A62" s="18" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B62" s="20" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="63" ht="43.2" spans="1:2">
       <c r="A63" s="18" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B63" s="20" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="64" ht="28.8" spans="1:2">
       <c r="A64" s="18" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B64" s="20" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="65" ht="86.4" spans="1:2">
       <c r="A65" s="22" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B65" s="20" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="66" ht="86.4" spans="1:2">
       <c r="A66" s="18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B66" s="20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="67" ht="28.8" spans="1:2">
       <c r="A67" s="22" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B67" s="25" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="68" ht="43.2" spans="1:2">
       <c r="A68" s="18" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B68" s="20" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="69" ht="28.8" spans="1:2">
       <c r="A69" s="22" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B69" s="20" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="70" ht="28.8" spans="1:2">
       <c r="A70" s="18" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B70" s="20" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="71" ht="100.8" spans="1:2">
       <c r="A71" s="20" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B71" s="20" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="72" ht="158.4" spans="1:2">
       <c r="A72" s="18" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B72" s="20" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="73" ht="86.4" spans="1:2">
       <c r="A73" s="18" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B73" s="20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="74" ht="409.5" spans="1:2">
       <c r="A74" s="18" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B74" s="20" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="75" ht="360" spans="1:3">
       <c r="A75" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B75" s="20" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C75" s="25" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="76" ht="172.8" spans="1:3">
       <c r="A76" s="18" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B76" s="20" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C76" s="25" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="77" ht="409.5" spans="1:3">
       <c r="A77" s="18" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B77" s="20" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C77" s="25" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="78" ht="409.5" spans="1:2">
       <c r="A78" s="18" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B78" s="20" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="79" ht="302.4" spans="1:2">
       <c r="A79" s="18" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B79" s="20" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="80" ht="187.2" spans="1:3">
       <c r="A80" s="18" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B80" s="20" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C80" s="25" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="81" ht="158.4" spans="1:2">
       <c r="A81" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B81" s="20" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="82" ht="115.2" spans="1:2">
       <c r="A82" s="18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B82" s="20" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="83" ht="86.4" spans="1:2">
       <c r="A83" s="20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B83" s="20" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="84" ht="72" spans="1:2">
       <c r="A84" s="18" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B84" s="20" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="85" ht="409.5" spans="1:2">
       <c r="A85" s="18" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B85" s="20" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="86" ht="302.4" spans="1:3">
       <c r="A86" s="18" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B86" s="20" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C86" s="25" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="87" ht="409.5" spans="1:2">
       <c r="A87" s="18" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B87" s="20" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="88" ht="216" spans="1:2">
       <c r="A88" s="18" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B88" s="25" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="89" ht="43.2" spans="1:2">
       <c r="A89" s="18" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="90" ht="144" spans="1:2">
       <c r="A90" s="18" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B90" s="25" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="91" ht="302.4" spans="1:2">
       <c r="A91" s="18" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B91" s="25" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -9841,72 +9846,72 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="19" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="20" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="20" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="18" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="18" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="20" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:1">
@@ -9924,7 +9929,7 @@
         <v>38</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -9934,76 +9939,76 @@
     </row>
     <row r="19" ht="72" spans="1:1">
       <c r="A19" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:1">
       <c r="A20" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="21" ht="100.8" spans="1:2">
       <c r="A21" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="21" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B22" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="23" ht="57.6" spans="1:2">
       <c r="A23" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="24" ht="72" spans="1:2">
       <c r="A24" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="25" ht="86.4" spans="1:2">
       <c r="A25" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="26" ht="43.2" spans="1:2">
       <c r="A26" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="27" ht="28.8" spans="1:2">
       <c r="A27" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="28" ht="43.2" spans="1:2">
       <c r="A28" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -10023,27 +10028,27 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="16" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="8" ht="15" spans="1:1">
       <c r="A8" s="17" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9" ht="120" customHeight="1" spans="1:1">
       <c r="A9" s="11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -10067,302 +10072,302 @@
   <sheetData>
     <row r="1" spans="2:3">
       <c r="B1" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2" spans="2:3">
       <c r="B2" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="3" spans="2:3">
       <c r="B3" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>330</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="B5" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6" spans="2:3">
       <c r="B6" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="B7" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8" ht="43.2" spans="2:3">
       <c r="B8" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" s="12" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10" spans="2:2">
       <c r="B10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="11" ht="23.4" spans="2:2">
       <c r="B11" s="13" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" s="14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="15" spans="2:2">
       <c r="B15" s="14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="16" spans="2:2">
       <c r="B16" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" s="14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" s="14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" s="14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" s="14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" s="14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" s="14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="26" ht="23.4" spans="2:2">
       <c r="B26" s="13" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="29" spans="2:2">
       <c r="B29" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" s="14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="31" spans="2:2">
       <c r="B31" s="14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" s="14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" s="14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" s="14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="39" spans="2:2">
       <c r="B39" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="41" ht="23.4" spans="2:2">
       <c r="B41" s="13" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="43" spans="2:2">
       <c r="B43" s="14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" s="14" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="45" spans="2:2">
       <c r="B45" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" s="14" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" s="15" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" s="15" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" s="15" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" s="15" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="54" ht="13" customHeight="1"/>
     <row r="55" ht="22" customHeight="1" spans="2:2">
       <c r="B55" s="13" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="57" spans="2:2">
       <c r="B57" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="58" spans="2:2">
@@ -10372,22 +10377,22 @@
     </row>
     <row r="59" spans="2:2">
       <c r="B59" s="14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="60" spans="2:2">
       <c r="B60" s="14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61" s="14" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -10404,7 +10409,7 @@
   <sheetData>
     <row r="1" spans="1:21">
       <c r="A1" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -10419,7 +10424,7 @@
       <c r="L1" s="5"/>
       <c r="M1" s="5"/>
       <c r="N1" s="7" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O1" s="8"/>
       <c r="P1" s="8"/>
@@ -10661,7 +10666,7 @@
     </row>
     <row r="12" spans="1:21">
       <c r="A12" s="5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -10847,7 +10852,7 @@
     </row>
     <row r="22" spans="1:21">
       <c r="A22" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>

--- a/JavaPrograms/Work Done.xlsx
+++ b/JavaPrograms/Work Done.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="415">
   <si>
     <r>
       <rPr>
@@ -957,9 +957,6 @@
       <t>: The backend connects to Google's Gemini 2.5 via a secure API gateway."
 That is how a Senior Engineer speaks. You have earned the right to say that now.</t>
     </r>
-  </si>
-  <si>
-    <t>666666666666666++</t>
   </si>
   <si>
     <t>Recall</t>
@@ -4998,15 +4995,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <i/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -7237,32 +7234,32 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B2" s="3"/>
     </row>
     <row r="3" ht="100.8" spans="1:2">
       <c r="A3" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>390</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="4" ht="57.6" spans="1:2">
       <c r="A4" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>392</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -7283,102 +7280,102 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>396</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>397</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" t="s">
         <v>399</v>
-      </c>
-      <c r="C2" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C3" t="s">
         <v>401</v>
-      </c>
-      <c r="C3" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C4" t="s">
         <v>403</v>
-      </c>
-      <c r="C4" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C5" t="s">
         <v>405</v>
-      </c>
-      <c r="C5" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B6" t="s">
+        <v>406</v>
+      </c>
+      <c r="C6" t="s">
         <v>407</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>408</v>
-      </c>
-      <c r="D6" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C7" t="s">
         <v>410</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>411</v>
-      </c>
-      <c r="D7" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C8" t="s">
         <v>413</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>414</v>
-      </c>
-      <c r="D8" t="s">
-        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -8734,9 +8731,7 @@
       <c r="C20" s="22"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="22" t="s">
-        <v>89</v>
-      </c>
+      <c r="A21" s="22"/>
       <c r="B21" s="22"/>
       <c r="C21" s="22"/>
     </row>
@@ -8938,7 +8933,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B1" s="22"/>
     </row>
@@ -8950,26 +8945,26 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="37" t="s">
         <v>91</v>
-      </c>
-      <c r="B3" s="37" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="37" t="s">
         <v>93</v>
-      </c>
-      <c r="B4" s="37" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="37" t="s">
         <v>95</v>
-      </c>
-      <c r="B5" s="37" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -8980,15 +8975,15 @@
     </row>
     <row r="7" s="35" customFormat="1" ht="57.6" spans="1:2">
       <c r="A7" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" s="40" t="s">
         <v>97</v>
-      </c>
-      <c r="B7" s="40" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="10" ht="187.2" spans="1:1">
       <c r="A10" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -9012,10 +9007,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="23" t="s">
         <v>100</v>
-      </c>
-      <c r="B1" s="23" t="s">
-        <v>101</v>
       </c>
       <c r="C1" s="24" t="s">
         <v>62</v>
@@ -9023,139 +9018,139 @@
     </row>
     <row r="2" ht="201.6" spans="1:3">
       <c r="A2" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="C2" s="25" t="s">
         <v>103</v>
-      </c>
-      <c r="C2" s="25" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="3" ht="100.8" spans="1:3">
       <c r="A3" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="C3" s="25" t="s">
         <v>106</v>
-      </c>
-      <c r="C3" s="25" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="4" ht="72" spans="1:2">
       <c r="A4" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="B4" s="20" t="s">
         <v>108</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="5" ht="129.6" spans="1:3">
       <c r="A5" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="C5" s="25" t="s">
         <v>111</v>
-      </c>
-      <c r="C5" s="25" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="6" ht="129.6" spans="1:4">
       <c r="A6" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="B6" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="C6" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="D6" s="25" t="s">
         <v>115</v>
-      </c>
-      <c r="D6" s="25" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="7" ht="158.4" spans="1:3">
       <c r="A7" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="C7" s="25" t="s">
         <v>118</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="8" ht="86.4" spans="1:2">
       <c r="A8" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="B8" s="20" t="s">
         <v>120</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="9" ht="129.6" spans="1:2">
       <c r="A9" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="B9" s="20" t="s">
         <v>122</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="10" ht="129.6" spans="1:2">
       <c r="A10" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" s="20" t="s">
         <v>124</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="11" ht="158.4" spans="1:2">
       <c r="A11" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="B11" s="20" t="s">
         <v>126</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="12" ht="115.2" spans="1:3">
       <c r="A12" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="C12" s="25" t="s">
         <v>129</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="13" ht="158.4" spans="1:3">
       <c r="A13" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="B13" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="C13" s="25" t="s">
         <v>132</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="14" ht="158.4" spans="1:3">
       <c r="A14" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14" s="20" t="s">
         <v>134</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>135</v>
       </c>
       <c r="C14" s="25"/>
     </row>
     <row r="15" ht="43.2" spans="1:3">
       <c r="A15" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="B15" s="20" t="s">
         <v>136</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>137</v>
       </c>
       <c r="C15" s="25"/>
     </row>
@@ -9164,10 +9159,10 @@
         <v>34</v>
       </c>
       <c r="B16" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="C16" s="25" t="s">
         <v>138</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="17" ht="172.8" spans="1:3">
@@ -9175,10 +9170,10 @@
         <v>36</v>
       </c>
       <c r="B17" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="C17" s="25" t="s">
         <v>140</v>
-      </c>
-      <c r="C17" s="25" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="18" ht="409.5" spans="1:4">
@@ -9186,13 +9181,13 @@
         <v>37</v>
       </c>
       <c r="B18" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="C18" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="D18" s="25" t="s">
         <v>143</v>
-      </c>
-      <c r="D18" s="25" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="19" ht="409.5" spans="1:4">
@@ -9200,628 +9195,628 @@
         <v>38</v>
       </c>
       <c r="B19" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="C19" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="C19" s="25" t="s">
+      <c r="D19" s="25" t="s">
         <v>146</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="20" ht="409.5" spans="1:4">
       <c r="A20" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="B20" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="C20" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="C20" s="25" t="s">
+      <c r="D20" s="25" t="s">
         <v>150</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="21" ht="174" customHeight="1" spans="1:2">
       <c r="A21" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="B21" s="20" t="s">
         <v>152</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="22" ht="187.2" spans="1:2">
       <c r="A22" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="B22" s="20" t="s">
         <v>154</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="23" ht="244.8" spans="1:2">
       <c r="A23" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="B23" s="20" t="s">
         <v>156</v>
-      </c>
-      <c r="B23" s="20" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="24" ht="158.4" spans="1:2">
       <c r="A24" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="B24" s="20" t="s">
         <v>158</v>
-      </c>
-      <c r="B24" s="20" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="25" ht="100.8" spans="1:2">
       <c r="A25" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="B25" s="20" t="s">
         <v>160</v>
-      </c>
-      <c r="B25" s="20" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="26" ht="409" customHeight="1" spans="1:3">
       <c r="A26" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="B26" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="B26" s="20" t="s">
+      <c r="C26" s="25" t="s">
         <v>163</v>
-      </c>
-      <c r="C26" s="25" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="27" ht="57.6" spans="1:2">
       <c r="A27" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="B27" s="20" t="s">
         <v>165</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="28" ht="409.5" spans="1:4">
       <c r="A28" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="B28" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="B28" s="20" t="s">
+      <c r="C28" s="25" t="s">
         <v>168</v>
       </c>
-      <c r="C28" s="25" t="s">
+      <c r="D28" s="25" t="s">
         <v>169</v>
-      </c>
-      <c r="D28" s="25" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="29" ht="244.8" spans="1:3">
       <c r="A29" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="B29" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="B29" s="20" t="s">
+      <c r="C29" s="25" t="s">
         <v>172</v>
-      </c>
-      <c r="C29" s="25" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="30" ht="244.8" spans="1:2">
       <c r="A30" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="B30" s="20" t="s">
         <v>174</v>
-      </c>
-      <c r="B30" s="20" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="31" ht="187.2" spans="1:2">
       <c r="A31" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="B31" s="20" t="s">
         <v>176</v>
-      </c>
-      <c r="B31" s="20" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="32" ht="345.6" spans="1:2">
       <c r="A32" s="31"/>
       <c r="B32" s="32" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" ht="259.2" spans="1:2">
       <c r="A33" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B33" s="32" t="s">
         <v>179</v>
-      </c>
-      <c r="B33" s="32" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="34" ht="100.8" spans="1:2">
       <c r="A34" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="B34" s="20" t="s">
         <v>181</v>
-      </c>
-      <c r="B34" s="20" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="35" ht="72" spans="1:2">
       <c r="A35" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="B35" s="20" t="s">
         <v>183</v>
-      </c>
-      <c r="B35" s="20" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="36" ht="409" customHeight="1" spans="1:3">
       <c r="A36" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="B36" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="B36" s="20" t="s">
+      <c r="C36" s="34" t="s">
         <v>186</v>
-      </c>
-      <c r="C36" s="34" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="37" ht="187.2" spans="1:3">
       <c r="A37" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="B37" s="20" t="s">
         <v>188</v>
-      </c>
-      <c r="B37" s="20" t="s">
-        <v>189</v>
       </c>
       <c r="C37" s="34"/>
     </row>
     <row r="38" ht="288" spans="1:3">
       <c r="A38" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="B38" s="20" t="s">
         <v>190</v>
-      </c>
-      <c r="B38" s="20" t="s">
-        <v>191</v>
       </c>
       <c r="C38" s="34"/>
     </row>
     <row r="39" ht="216" spans="1:2">
       <c r="A39" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="B39" s="20" t="s">
         <v>192</v>
-      </c>
-      <c r="B39" s="20" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="40" ht="100.8" spans="1:2">
       <c r="A40" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="B40" s="20" t="s">
         <v>194</v>
-      </c>
-      <c r="B40" s="20" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="18" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B41" s="18"/>
     </row>
     <row r="42" ht="144" spans="1:3">
       <c r="A42" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="B42" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="B42" s="20" t="s">
+      <c r="C42" s="25" t="s">
         <v>197</v>
-      </c>
-      <c r="C42" s="25" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="43" ht="57.6" spans="1:2">
       <c r="A43" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="B43" s="20" t="s">
         <v>199</v>
-      </c>
-      <c r="B43" s="20" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="44" ht="273.6" spans="1:2">
       <c r="A44" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="B44" s="20" t="s">
         <v>201</v>
-      </c>
-      <c r="B44" s="20" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="45" ht="172.8" spans="1:3">
       <c r="A45" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="B45" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="B45" s="20" t="s">
+      <c r="C45" s="25" t="s">
         <v>204</v>
-      </c>
-      <c r="C45" s="25" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="46" ht="43.2" spans="1:2">
       <c r="A46" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="B46" s="20" t="s">
         <v>206</v>
-      </c>
-      <c r="B46" s="20" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="47" ht="144" spans="1:2">
       <c r="A47" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="B47" s="20" t="s">
         <v>208</v>
-      </c>
-      <c r="B47" s="20" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="48" ht="72" spans="1:2">
       <c r="A48" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="B48" s="20" t="s">
         <v>210</v>
-      </c>
-      <c r="B48" s="20" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="49" ht="57.6" spans="1:2">
       <c r="A49" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="B49" s="20" t="s">
         <v>212</v>
-      </c>
-      <c r="B49" s="20" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="50" ht="28.8" spans="1:2">
       <c r="A50" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="B50" s="20" t="s">
         <v>214</v>
-      </c>
-      <c r="B50" s="20" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="51" ht="230.4" spans="1:2">
       <c r="A51" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="B51" s="20" t="s">
         <v>216</v>
-      </c>
-      <c r="B51" s="20" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="52" ht="158.4" spans="1:2">
       <c r="A52" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="B52" s="20" t="s">
         <v>218</v>
-      </c>
-      <c r="B52" s="20" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="53" ht="129.6" spans="1:2">
       <c r="A53" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="B53" s="20" t="s">
         <v>220</v>
-      </c>
-      <c r="B53" s="20" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="54" ht="409.5" spans="1:2">
       <c r="A54" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="B54" s="20" t="s">
         <v>222</v>
-      </c>
-      <c r="B54" s="20" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="55" ht="201.6" spans="1:3">
       <c r="A55" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="B55" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="B55" s="20" t="s">
+      <c r="C55" s="25" t="s">
         <v>225</v>
-      </c>
-      <c r="C55" s="25" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="56" ht="409.5" spans="1:2">
       <c r="A56" s="18"/>
       <c r="B56" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="57" ht="409.5" spans="1:2">
       <c r="A57" s="18"/>
       <c r="B57" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="58" ht="115.2" spans="1:2">
       <c r="A58" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="B58" s="20" t="s">
         <v>229</v>
-      </c>
-      <c r="B58" s="20" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="59" ht="100.8" spans="1:2">
       <c r="A59" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="B59" s="20" t="s">
         <v>231</v>
-      </c>
-      <c r="B59" s="20" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="B60" s="18" t="s">
         <v>233</v>
-      </c>
-      <c r="B60" s="18" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="61" ht="86.4" spans="1:2">
       <c r="A61" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="B61" s="20" t="s">
         <v>235</v>
-      </c>
-      <c r="B61" s="20" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="62" ht="144" spans="1:2">
       <c r="A62" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="B62" s="20" t="s">
         <v>237</v>
-      </c>
-      <c r="B62" s="20" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="63" ht="43.2" spans="1:2">
       <c r="A63" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="B63" s="20" t="s">
         <v>239</v>
-      </c>
-      <c r="B63" s="20" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="64" ht="28.8" spans="1:2">
       <c r="A64" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="B64" s="20" t="s">
         <v>241</v>
-      </c>
-      <c r="B64" s="20" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="65" ht="86.4" spans="1:2">
       <c r="A65" s="22" t="s">
+        <v>242</v>
+      </c>
+      <c r="B65" s="20" t="s">
         <v>243</v>
-      </c>
-      <c r="B65" s="20" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="66" ht="86.4" spans="1:2">
       <c r="A66" s="18" t="s">
+        <v>244</v>
+      </c>
+      <c r="B66" s="20" t="s">
         <v>245</v>
-      </c>
-      <c r="B66" s="20" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="67" ht="28.8" spans="1:2">
       <c r="A67" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="B67" s="25" t="s">
         <v>247</v>
-      </c>
-      <c r="B67" s="25" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="68" ht="43.2" spans="1:2">
       <c r="A68" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="B68" s="20" t="s">
         <v>249</v>
-      </c>
-      <c r="B68" s="20" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="69" ht="28.8" spans="1:2">
       <c r="A69" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="B69" s="20" t="s">
         <v>251</v>
-      </c>
-      <c r="B69" s="20" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="70" ht="28.8" spans="1:2">
       <c r="A70" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="B70" s="20" t="s">
         <v>253</v>
-      </c>
-      <c r="B70" s="20" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="71" ht="100.8" spans="1:2">
       <c r="A71" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="B71" s="20" t="s">
         <v>255</v>
-      </c>
-      <c r="B71" s="20" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="72" ht="158.4" spans="1:2">
       <c r="A72" s="18" t="s">
+        <v>256</v>
+      </c>
+      <c r="B72" s="20" t="s">
         <v>257</v>
-      </c>
-      <c r="B72" s="20" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="73" ht="86.4" spans="1:2">
       <c r="A73" s="18" t="s">
+        <v>258</v>
+      </c>
+      <c r="B73" s="20" t="s">
         <v>259</v>
-      </c>
-      <c r="B73" s="20" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="74" ht="409.5" spans="1:2">
       <c r="A74" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="B74" s="20" t="s">
         <v>261</v>
-      </c>
-      <c r="B74" s="20" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="75" ht="360" spans="1:3">
       <c r="A75" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="B75" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="B75" s="20" t="s">
+      <c r="C75" s="25" t="s">
         <v>264</v>
-      </c>
-      <c r="C75" s="25" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="76" ht="172.8" spans="1:3">
       <c r="A76" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="B76" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="B76" s="20" t="s">
+      <c r="C76" s="25" t="s">
         <v>267</v>
-      </c>
-      <c r="C76" s="25" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="77" ht="409.5" spans="1:3">
       <c r="A77" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="B77" s="20" t="s">
         <v>269</v>
       </c>
-      <c r="B77" s="20" t="s">
+      <c r="C77" s="25" t="s">
         <v>270</v>
-      </c>
-      <c r="C77" s="25" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="78" ht="409.5" spans="1:2">
       <c r="A78" s="18" t="s">
+        <v>271</v>
+      </c>
+      <c r="B78" s="20" t="s">
         <v>272</v>
-      </c>
-      <c r="B78" s="20" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="79" ht="302.4" spans="1:2">
       <c r="A79" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="B79" s="20" t="s">
         <v>274</v>
-      </c>
-      <c r="B79" s="20" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="80" ht="187.2" spans="1:3">
       <c r="A80" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="B80" s="20" t="s">
         <v>276</v>
       </c>
-      <c r="B80" s="20" t="s">
+      <c r="C80" s="25" t="s">
         <v>277</v>
-      </c>
-      <c r="C80" s="25" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="81" ht="158.4" spans="1:2">
       <c r="A81" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B81" s="20" t="s">
         <v>279</v>
-      </c>
-      <c r="B81" s="20" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="82" ht="115.2" spans="1:2">
       <c r="A82" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="B82" s="20" t="s">
         <v>281</v>
-      </c>
-      <c r="B82" s="20" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="83" ht="86.4" spans="1:2">
       <c r="A83" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="B83" s="20" t="s">
         <v>283</v>
-      </c>
-      <c r="B83" s="20" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="84" ht="72" spans="1:2">
       <c r="A84" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="B84" s="20" t="s">
         <v>285</v>
-      </c>
-      <c r="B84" s="20" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="85" ht="409.5" spans="1:2">
       <c r="A85" s="18" t="s">
+        <v>286</v>
+      </c>
+      <c r="B85" s="20" t="s">
         <v>287</v>
-      </c>
-      <c r="B85" s="20" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="86" ht="302.4" spans="1:3">
       <c r="A86" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="B86" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="B86" s="20" t="s">
+      <c r="C86" s="25" t="s">
         <v>290</v>
-      </c>
-      <c r="C86" s="25" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="87" ht="409.5" spans="1:2">
       <c r="A87" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="B87" s="20" t="s">
         <v>292</v>
-      </c>
-      <c r="B87" s="20" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="88" ht="216" spans="1:2">
       <c r="A88" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="B88" s="25" t="s">
         <v>294</v>
-      </c>
-      <c r="B88" s="25" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="89" ht="43.2" spans="1:2">
       <c r="A89" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="B89" s="11" t="s">
         <v>296</v>
-      </c>
-      <c r="B89" s="11" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="90" ht="144" spans="1:2">
       <c r="A90" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="B90" s="25" t="s">
         <v>298</v>
-      </c>
-      <c r="B90" s="25" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="91" ht="302.4" spans="1:2">
       <c r="A91" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="B91" s="25" t="s">
         <v>300</v>
-      </c>
-      <c r="B91" s="25" t="s">
-        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -9846,72 +9841,72 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="20" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="18" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="18" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="18" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:1">
@@ -9929,7 +9924,7 @@
         <v>38</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -9939,76 +9934,76 @@
     </row>
     <row r="19" ht="72" spans="1:1">
       <c r="A19" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:1">
       <c r="A20" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="21" ht="100.8" spans="1:2">
       <c r="A21" t="s">
+        <v>305</v>
+      </c>
+      <c r="B21" s="11" t="s">
         <v>306</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="B22" t="s">
         <v>308</v>
-      </c>
-      <c r="B22" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="23" ht="57.6" spans="1:2">
       <c r="A23" t="s">
+        <v>309</v>
+      </c>
+      <c r="B23" s="11" t="s">
         <v>310</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="24" ht="72" spans="1:2">
       <c r="A24" t="s">
+        <v>311</v>
+      </c>
+      <c r="B24" s="11" t="s">
         <v>312</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="25" ht="86.4" spans="1:2">
       <c r="A25" t="s">
+        <v>313</v>
+      </c>
+      <c r="B25" s="11" t="s">
         <v>314</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="26" ht="43.2" spans="1:2">
       <c r="A26" t="s">
+        <v>315</v>
+      </c>
+      <c r="B26" s="11" t="s">
         <v>316</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="27" ht="28.8" spans="1:2">
       <c r="A27" t="s">
+        <v>317</v>
+      </c>
+      <c r="B27" s="11" t="s">
         <v>318</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="28" ht="43.2" spans="1:2">
       <c r="A28" t="s">
+        <v>319</v>
+      </c>
+      <c r="B28" s="11" t="s">
         <v>320</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -10028,27 +10023,27 @@
   <sheetData>
     <row r="2" spans="1:1">
       <c r="A2" s="16" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8" ht="15" spans="1:1">
       <c r="A8" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9" ht="120" customHeight="1" spans="1:1">
       <c r="A9" s="11" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -10072,302 +10067,302 @@
   <sheetData>
     <row r="1" spans="2:3">
       <c r="B1" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>327</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="2" spans="2:3">
       <c r="B2" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>329</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="3" spans="2:3">
       <c r="B3" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="B5" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" spans="2:3">
       <c r="B6" s="10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="B7" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="8" ht="43.2" spans="2:3">
       <c r="B8" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="C8" s="11" t="s">
         <v>336</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" s="12" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10" spans="2:2">
       <c r="B10" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="11" ht="23.4" spans="2:2">
       <c r="B11" s="13" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" s="14" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="15" spans="2:2">
       <c r="B15" s="14" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="16" spans="2:2">
       <c r="B16" s="14" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" s="14" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" s="14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" s="14" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" s="14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" s="14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" s="14" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" s="14" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="26" ht="23.4" spans="2:2">
       <c r="B26" s="13" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" s="14" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="29" spans="2:2">
       <c r="B29" s="14" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" s="14" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="31" spans="2:2">
       <c r="B31" s="14" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" s="14" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" s="14" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" s="14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" s="14" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" s="14" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="39" spans="2:2">
       <c r="B39" s="14" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="41" ht="23.4" spans="2:2">
       <c r="B41" s="13" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="43" spans="2:2">
       <c r="B43" s="14" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" s="14" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="45" spans="2:2">
       <c r="B45" s="14" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" s="14" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" s="15" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" s="15" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" s="15" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" s="15" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="54" ht="13" customHeight="1"/>
     <row r="55" ht="22" customHeight="1" spans="2:2">
       <c r="B55" s="13" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="57" spans="2:2">
       <c r="B57" s="14" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="58" spans="2:2">
@@ -10377,22 +10372,22 @@
     </row>
     <row r="59" spans="2:2">
       <c r="B59" s="14" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="60" spans="2:2">
       <c r="B60" s="14" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61" s="14" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -10409,7 +10404,7 @@
   <sheetData>
     <row r="1" spans="1:21">
       <c r="A1" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -10424,7 +10419,7 @@
       <c r="L1" s="5"/>
       <c r="M1" s="5"/>
       <c r="N1" s="7" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="O1" s="8"/>
       <c r="P1" s="8"/>
@@ -10666,7 +10661,7 @@
     </row>
     <row r="12" spans="1:21">
       <c r="A12" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -10852,7 +10847,7 @@
     </row>
     <row r="22" spans="1:21">
       <c r="A22" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
